--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS USA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS USA History" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,8 +31,20 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +55,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
         <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+        <bgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
   </fills>
@@ -57,8 +76,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -425,7 +454,188 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV1"/>
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>AEGIS USA PORTFOLIO · as of today</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Realized P&amp;L (closed)</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>0 closed</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Best position</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> +0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Unrealized P&amp;L (open)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>0 open</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Worst position</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> +0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>COMBINED PORTFOLIO</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>0 positions</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Win rate</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>0.0% (0W / 0L / 0 flat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Cap</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Entry Date</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Entry</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>P&amp;L %</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Days</t>
+        </is>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>Alerts</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>Exit Reason</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AW1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -454,248 +664,253 @@
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="6" customWidth="1" min="25" max="25"/>
     <col width="13" customWidth="1" min="26" max="26"/>
-    <col width="18" customWidth="1" min="48" max="48"/>
+    <col width="18" customWidth="1" min="49" max="49"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Position ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>Run_Type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>Exit Reason</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>Exit P&amp;L %</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>Prior Rank</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="7" t="inlineStr">
         <is>
           <t>Rank Δ</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="7" t="inlineStr">
         <is>
           <t>Health</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="7" t="inlineStr">
         <is>
           <t>Risk Meter</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="7" t="inlineStr">
         <is>
           <t>Adj Conf</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="7" t="inlineStr">
         <is>
           <t>Ctx Drag</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" s="7" t="inlineStr">
         <is>
           <t>Ctx Reason</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="7" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="7" t="inlineStr">
         <is>
           <t>Alerts</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="7" t="inlineStr">
         <is>
           <t>Confidence %</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="7" t="inlineStr">
         <is>
           <t>Conf Type</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" s="7" t="inlineStr">
         <is>
           <t>Model Score</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" s="7" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" s="7" t="inlineStr">
         <is>
           <t>Trading Days</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" s="7" t="inlineStr">
         <is>
           <t>Horizon (d)</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" s="7" t="inlineStr">
         <is>
           <t>Days Left</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" s="7" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" s="7" t="inlineStr">
         <is>
           <t>Current Price</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" s="7" t="inlineStr">
         <is>
           <t>Entry Price</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" s="7" t="inlineStr">
         <is>
           <t>Buy Zone Low</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" s="7" t="inlineStr">
         <is>
           <t>Buy Zone High</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" s="7" t="inlineStr">
         <is>
           <t>Stop Loss</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" s="7" t="inlineStr">
         <is>
           <t>Risk %</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" s="7" t="inlineStr">
         <is>
           <t>Target 1</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" s="7" t="inlineStr">
         <is>
           <t>T1 %</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" s="7" t="inlineStr">
         <is>
           <t>Target 2</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" s="7" t="inlineStr">
         <is>
           <t>T2 %</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" s="7" t="inlineStr">
         <is>
           <t>Prev Close</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" s="7" t="inlineStr">
         <is>
           <t>Today Move %</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" s="7" t="inlineStr">
         <is>
           <t>Current Perf %</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" s="7" t="inlineStr">
         <is>
           <t>Max Gain %</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" s="7" t="inlineStr">
         <is>
           <t>Max DD %</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" s="7" t="inlineStr">
         <is>
           <t>Top Drivers</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" s="7" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" s="7" t="inlineStr">
         <is>
           <t>Portfolio Weight %</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" s="7" t="inlineStr">
         <is>
           <t>Expected Alpha %</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" s="7" t="inlineStr">
         <is>
           <t>Last Updated (UTC)</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" s="7" t="inlineStr">
         <is>
           <t>Cap Size</t>
+        </is>
+      </c>
+      <c r="AW1" s="7" t="inlineStr">
+        <is>
+          <t>Opp Age</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="+0.00%;-0.00%;0.00%"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -76,14 +78,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -454,21 +458,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -484,12 +491,10 @@
           <t>Realized P&amp;L (closed)</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>0 closed</t>
         </is>
@@ -499,7 +504,7 @@
           <t>Best position</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"> +0.00%</t>
         </is>
@@ -511,12 +516,10 @@
           <t>Unrealized P&amp;L (open)</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>0 open</t>
         </is>
@@ -526,24 +529,22 @@
           <t>Worst position</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"> +0.00%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>COMBINED PORTFOLIO</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>+0.00%</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>0 positions</t>
         </is>
@@ -553,69 +554,84 @@
           <t>Win rate</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>0.0% (0W / 0L / 0 flat)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Runner</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>Cap</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>Entry</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>Exit Price</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
         <is>
           <t>Days</t>
         </is>
       </c>
-      <c r="K7" s="6" t="inlineStr">
+      <c r="N7" s="8" t="inlineStr">
         <is>
           <t>Alerts</t>
         </is>
       </c>
-      <c r="L7" s="6" t="inlineStr">
+      <c r="O7" s="8" t="inlineStr">
         <is>
           <t>Exit Reason</t>
         </is>
@@ -668,247 +684,247 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>Position ID</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C1" s="7" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="D1" s="7" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>Run_Type</t>
         </is>
       </c>
-      <c r="E1" s="7" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="F1" s="7" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="G1" s="7" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H1" s="7" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Exit Reason</t>
         </is>
       </c>
-      <c r="I1" s="7" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Exit P&amp;L %</t>
         </is>
       </c>
-      <c r="J1" s="7" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="K1" s="7" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>Prior Rank</t>
         </is>
       </c>
-      <c r="L1" s="7" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>Rank Δ</t>
         </is>
       </c>
-      <c r="M1" s="7" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>Health</t>
         </is>
       </c>
-      <c r="N1" s="7" t="inlineStr">
+      <c r="N1" s="9" t="inlineStr">
         <is>
           <t>Risk Meter</t>
         </is>
       </c>
-      <c r="O1" s="7" t="inlineStr">
+      <c r="O1" s="9" t="inlineStr">
         <is>
           <t>Adj Conf</t>
         </is>
       </c>
-      <c r="P1" s="7" t="inlineStr">
+      <c r="P1" s="9" t="inlineStr">
         <is>
           <t>Ctx Drag</t>
         </is>
       </c>
-      <c r="Q1" s="7" t="inlineStr">
+      <c r="Q1" s="9" t="inlineStr">
         <is>
           <t>Ctx Reason</t>
         </is>
       </c>
-      <c r="R1" s="7" t="inlineStr">
+      <c r="R1" s="9" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="S1" s="7" t="inlineStr">
+      <c r="S1" s="9" t="inlineStr">
         <is>
           <t>Alerts</t>
         </is>
       </c>
-      <c r="T1" s="7" t="inlineStr">
+      <c r="T1" s="9" t="inlineStr">
         <is>
           <t>Confidence %</t>
         </is>
       </c>
-      <c r="U1" s="7" t="inlineStr">
+      <c r="U1" s="9" t="inlineStr">
         <is>
           <t>Conf Type</t>
         </is>
       </c>
-      <c r="V1" s="7" t="inlineStr">
+      <c r="V1" s="9" t="inlineStr">
         <is>
           <t>Model Score</t>
         </is>
       </c>
-      <c r="W1" s="7" t="inlineStr">
+      <c r="W1" s="9" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="X1" s="7" t="inlineStr">
+      <c r="X1" s="9" t="inlineStr">
         <is>
           <t>Trading Days</t>
         </is>
       </c>
-      <c r="Y1" s="7" t="inlineStr">
+      <c r="Y1" s="9" t="inlineStr">
         <is>
           <t>Horizon (d)</t>
         </is>
       </c>
-      <c r="Z1" s="7" t="inlineStr">
+      <c r="Z1" s="9" t="inlineStr">
         <is>
           <t>Days Left</t>
         </is>
       </c>
-      <c r="AA1" s="7" t="inlineStr">
+      <c r="AA1" s="9" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="AB1" s="7" t="inlineStr">
+      <c r="AB1" s="9" t="inlineStr">
         <is>
           <t>Current Price</t>
         </is>
       </c>
-      <c r="AC1" s="7" t="inlineStr">
+      <c r="AC1" s="9" t="inlineStr">
         <is>
           <t>Entry Price</t>
         </is>
       </c>
-      <c r="AD1" s="7" t="inlineStr">
+      <c r="AD1" s="9" t="inlineStr">
         <is>
           <t>Buy Zone Low</t>
         </is>
       </c>
-      <c r="AE1" s="7" t="inlineStr">
+      <c r="AE1" s="9" t="inlineStr">
         <is>
           <t>Buy Zone High</t>
         </is>
       </c>
-      <c r="AF1" s="7" t="inlineStr">
+      <c r="AF1" s="9" t="inlineStr">
         <is>
           <t>Stop Loss</t>
         </is>
       </c>
-      <c r="AG1" s="7" t="inlineStr">
+      <c r="AG1" s="9" t="inlineStr">
         <is>
           <t>Risk %</t>
         </is>
       </c>
-      <c r="AH1" s="7" t="inlineStr">
+      <c r="AH1" s="9" t="inlineStr">
         <is>
           <t>Target 1</t>
         </is>
       </c>
-      <c r="AI1" s="7" t="inlineStr">
+      <c r="AI1" s="9" t="inlineStr">
         <is>
           <t>T1 %</t>
         </is>
       </c>
-      <c r="AJ1" s="7" t="inlineStr">
+      <c r="AJ1" s="9" t="inlineStr">
         <is>
           <t>Target 2</t>
         </is>
       </c>
-      <c r="AK1" s="7" t="inlineStr">
+      <c r="AK1" s="9" t="inlineStr">
         <is>
           <t>T2 %</t>
         </is>
       </c>
-      <c r="AL1" s="7" t="inlineStr">
+      <c r="AL1" s="9" t="inlineStr">
         <is>
           <t>Prev Close</t>
         </is>
       </c>
-      <c r="AM1" s="7" t="inlineStr">
+      <c r="AM1" s="9" t="inlineStr">
         <is>
           <t>Today Move %</t>
         </is>
       </c>
-      <c r="AN1" s="7" t="inlineStr">
+      <c r="AN1" s="9" t="inlineStr">
         <is>
           <t>Current Perf %</t>
         </is>
       </c>
-      <c r="AO1" s="7" t="inlineStr">
+      <c r="AO1" s="9" t="inlineStr">
         <is>
           <t>Max Gain %</t>
         </is>
       </c>
-      <c r="AP1" s="7" t="inlineStr">
+      <c r="AP1" s="9" t="inlineStr">
         <is>
           <t>Max DD %</t>
         </is>
       </c>
-      <c r="AQ1" s="7" t="inlineStr">
+      <c r="AQ1" s="9" t="inlineStr">
         <is>
           <t>Top Drivers</t>
         </is>
       </c>
-      <c r="AR1" s="7" t="inlineStr">
+      <c r="AR1" s="9" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="AS1" s="7" t="inlineStr">
+      <c r="AS1" s="9" t="inlineStr">
         <is>
           <t>Portfolio Weight %</t>
         </is>
       </c>
-      <c r="AT1" s="7" t="inlineStr">
+      <c r="AT1" s="9" t="inlineStr">
         <is>
           <t>Expected Alpha %</t>
         </is>
       </c>
-      <c r="AU1" s="7" t="inlineStr">
+      <c r="AU1" s="9" t="inlineStr">
         <is>
           <t>Last Updated (UTC)</t>
         </is>
       </c>
-      <c r="AV1" s="7" t="inlineStr">
+      <c r="AV1" s="9" t="inlineStr">
         <is>
           <t>Cap Size</t>
         </is>
       </c>
-      <c r="AW1" s="7" t="inlineStr">
+      <c r="AW1" s="9" t="inlineStr">
         <is>
           <t>Opp Age</t>
         </is>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -471,11 +471,14 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="8" customWidth="1" min="13" max="13"/>
-    <col width="40" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -598,40 +601,55 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
+          <t>Exit Date</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
           <t>Entry</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="J7" s="8" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>Exit Price</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>Stop Loss</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>Target 1</t>
+        </is>
+      </c>
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t>Target 2</t>
+        </is>
+      </c>
+      <c r="O7" s="8" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="L7" s="8" t="inlineStr">
-        <is>
-          <t>Confidence</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
+      <c r="P7" s="8" t="inlineStr">
         <is>
           <t>Days</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr">
+      <c r="Q7" s="8" t="inlineStr">
         <is>
           <t>Alerts</t>
         </is>
       </c>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="R7" s="8" t="inlineStr">
         <is>
           <t>Exit Reason</t>
         </is>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -476,9 +476,11 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="8" customWidth="1" min="16" max="16"/>
-    <col width="40" customWidth="1" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="40" customWidth="1" min="19" max="19"/>
+    <col width="30" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -641,15 +643,25 @@
       </c>
       <c r="P7" s="8" t="inlineStr">
         <is>
+          <t>Investability</t>
+        </is>
+      </c>
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
+          <t>Inv Verdict</t>
+        </is>
+      </c>
+      <c r="R7" s="8" t="inlineStr">
+        <is>
           <t>Days</t>
         </is>
       </c>
-      <c r="Q7" s="8" t="inlineStr">
+      <c r="S7" s="8" t="inlineStr">
         <is>
           <t>Alerts</t>
         </is>
       </c>
-      <c r="R7" s="8" t="inlineStr">
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>Exit Reason</t>
         </is>
@@ -669,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW1"/>
+  <dimension ref="A1:AY1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -698,7 +710,7 @@
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="6" customWidth="1" min="25" max="25"/>
     <col width="13" customWidth="1" min="26" max="26"/>
-    <col width="18" customWidth="1" min="49" max="49"/>
+    <col width="18" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -945,6 +957,16 @@
       <c r="AW1" s="9" t="inlineStr">
         <is>
           <t>Opp Age</t>
+        </is>
+      </c>
+      <c r="AX1" s="9" t="inlineStr">
+        <is>
+          <t>Investability</t>
+        </is>
+      </c>
+      <c r="AY1" s="9" t="inlineStr">
+        <is>
+          <t>Inv Verdict</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T7"/>
+  <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -466,21 +466,23 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="8" customWidth="1" min="18" max="18"/>
-    <col width="40" customWidth="1" min="19" max="19"/>
-    <col width="30" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="40" customWidth="1" min="20" max="20"/>
+    <col width="40" customWidth="1" min="21" max="21"/>
+    <col width="30" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -588,80 +590,90 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
+          <t>Entry Date</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Exit Date</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Days</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>🎯 Priority</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>Entry Date</t>
-        </is>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>Exit Date</t>
-        </is>
-      </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>Inv Quality</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>Investability</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>Final Action</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
         <is>
           <t>Entry</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="N7" s="8" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="O7" s="8" t="inlineStr">
         <is>
           <t>Exit Price</t>
         </is>
       </c>
-      <c r="L7" s="8" t="inlineStr">
+      <c r="P7" s="8" t="inlineStr">
+        <is>
+          <t>P&amp;L %</t>
+        </is>
+      </c>
+      <c r="Q7" s="8" t="inlineStr">
         <is>
           <t>Stop Loss</t>
         </is>
       </c>
-      <c r="M7" s="8" t="inlineStr">
+      <c r="R7" s="8" t="inlineStr">
         <is>
           <t>Target 1</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr">
+      <c r="S7" s="8" t="inlineStr">
         <is>
           <t>Target 2</t>
         </is>
       </c>
-      <c r="O7" s="8" t="inlineStr">
-        <is>
-          <t>P&amp;L %</t>
-        </is>
-      </c>
-      <c r="P7" s="8" t="inlineStr">
-        <is>
-          <t>Investability</t>
-        </is>
-      </c>
-      <c r="Q7" s="8" t="inlineStr">
-        <is>
-          <t>Inv Verdict</t>
-        </is>
-      </c>
-      <c r="R7" s="8" t="inlineStr">
-        <is>
-          <t>Days</t>
-        </is>
-      </c>
-      <c r="S7" s="8" t="inlineStr">
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>Action Note</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
         <is>
           <t>Alerts</t>
         </is>
       </c>
-      <c r="T7" s="8" t="inlineStr">
+      <c r="V7" s="8" t="inlineStr">
         <is>
           <t>Exit Reason</t>
         </is>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -458,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V7"/>
+  <dimension ref="A1:X7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -468,21 +468,23 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="30" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
     <col width="12" customWidth="1" min="19" max="19"/>
-    <col width="40" customWidth="1" min="20" max="20"/>
-    <col width="40" customWidth="1" min="21" max="21"/>
-    <col width="30" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="40" customWidth="1" min="22" max="22"/>
+    <col width="40" customWidth="1" min="23" max="23"/>
+    <col width="30" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -605,75 +607,85 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>🎯 Priority</t>
+          <t>🎯 Urgency</t>
         </is>
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="M7" s="8" t="inlineStr">
         <is>
           <t>Inv Quality</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="N7" s="8" t="inlineStr">
         <is>
           <t>Investability</t>
         </is>
       </c>
-      <c r="L7" s="8" t="inlineStr">
-        <is>
-          <t>Final Action</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
+      <c r="O7" s="8" t="inlineStr">
         <is>
           <t>Entry</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr">
+      <c r="P7" s="8" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="Q7" s="8" t="inlineStr">
         <is>
           <t>Exit Price</t>
         </is>
       </c>
-      <c r="P7" s="8" t="inlineStr">
+      <c r="R7" s="8" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="Q7" s="8" t="inlineStr">
+      <c r="S7" s="8" t="inlineStr">
         <is>
           <t>Stop Loss</t>
         </is>
       </c>
-      <c r="R7" s="8" t="inlineStr">
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>Target 1</t>
         </is>
       </c>
-      <c r="S7" s="8" t="inlineStr">
+      <c r="U7" s="8" t="inlineStr">
         <is>
           <t>Target 2</t>
         </is>
       </c>
-      <c r="T7" s="8" t="inlineStr">
+      <c r="V7" s="8" t="inlineStr">
         <is>
           <t>Action Note</t>
         </is>
       </c>
-      <c r="U7" s="8" t="inlineStr">
+      <c r="W7" s="8" t="inlineStr">
         <is>
           <t>Alerts</t>
         </is>
       </c>
-      <c r="V7" s="8" t="inlineStr">
+      <c r="X7" s="8" t="inlineStr">
         <is>
           <t>Exit Reason</t>
         </is>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -458,33 +458,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X7"/>
+  <dimension ref="A1:Y7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="40" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
     <col width="40" customWidth="1" min="23" max="23"/>
-    <col width="30" customWidth="1" min="24" max="24"/>
+    <col width="40" customWidth="1" min="24" max="24"/>
+    <col width="30" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -577,115 +578,120 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
+          <t>🎯 DECISION</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
           <t>Runner</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>Cap</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>Exit Date</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
         <is>
           <t>Days</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>🎯 Urgency</t>
-        </is>
-      </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
+          <t>Urgency</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
           <t>Reason</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="L7" s="8" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
       </c>
-      <c r="L7" s="8" t="inlineStr">
+      <c r="M7" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="M7" s="8" t="inlineStr">
+      <c r="N7" s="8" t="inlineStr">
         <is>
           <t>Inv Quality</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr">
+      <c r="O7" s="8" t="inlineStr">
         <is>
           <t>Investability</t>
         </is>
       </c>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="P7" s="8" t="inlineStr">
         <is>
           <t>Entry</t>
         </is>
       </c>
-      <c r="P7" s="8" t="inlineStr">
+      <c r="Q7" s="8" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="Q7" s="8" t="inlineStr">
+      <c r="R7" s="8" t="inlineStr">
         <is>
           <t>Exit Price</t>
         </is>
       </c>
-      <c r="R7" s="8" t="inlineStr">
+      <c r="S7" s="8" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="S7" s="8" t="inlineStr">
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>Stop Loss</t>
         </is>
       </c>
-      <c r="T7" s="8" t="inlineStr">
+      <c r="U7" s="8" t="inlineStr">
         <is>
           <t>Target 1</t>
         </is>
       </c>
-      <c r="U7" s="8" t="inlineStr">
+      <c r="V7" s="8" t="inlineStr">
         <is>
           <t>Target 2</t>
         </is>
       </c>
-      <c r="V7" s="8" t="inlineStr">
+      <c r="W7" s="8" t="inlineStr">
         <is>
           <t>Action Note</t>
         </is>
       </c>
-      <c r="W7" s="8" t="inlineStr">
+      <c r="X7" s="8" t="inlineStr">
         <is>
           <t>Alerts</t>
         </is>
       </c>
-      <c r="X7" s="8" t="inlineStr">
+      <c r="Y7" s="8" t="inlineStr">
         <is>
           <t>Exit Reason</t>
         </is>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -711,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY1"/>
+  <dimension ref="A1:BD1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -740,7 +740,7 @@
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="6" customWidth="1" min="25" max="25"/>
     <col width="13" customWidth="1" min="26" max="26"/>
-    <col width="18" customWidth="1" min="51" max="51"/>
+    <col width="18" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -997,6 +997,31 @@
       <c r="AY1" s="9" t="inlineStr">
         <is>
           <t>Inv Verdict</t>
+        </is>
+      </c>
+      <c r="AZ1" s="9" t="inlineStr">
+        <is>
+          <t>🎯 DECISION</t>
+        </is>
+      </c>
+      <c r="BA1" s="9" t="inlineStr">
+        <is>
+          <t>Urgency</t>
+        </is>
+      </c>
+      <c r="BB1" s="9" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="BC1" s="9" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="BD1" s="9" t="inlineStr">
+        <is>
+          <t>Review</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -1,3 +1,173 @@
+
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portfolio" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AEGIS USA History" sheetId="2" state="visible" r:id="rId2"/>
+  </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+</workbook>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="+0.00%;-0.00%;0.00%"/>
+  </numFmts>
+  <fonts count="5">
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
+  </fonts>
+  <fills count="4">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+        <bgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
+</file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
@@ -280,4 +450,636 @@
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AB7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="40" customWidth="1" min="26" max="26"/>
+    <col width="40" customWidth="1" min="27" max="27"/>
+    <col width="30" customWidth="1" min="28" max="28"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>AEGIS USA PORTFOLIO · as of today</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Realized P&amp;L (closed)</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>0 closed</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Best position</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> +0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Unrealized P&amp;L (open)</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>0 open</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Worst position</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> +0.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>COMBINED PORTFOLIO</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>0 positions</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Win rate</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>0.0% (0W / 0L / 0 flat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>🎯 DECISION</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Price Trigger</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Next Review</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Execution Window</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Runner</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>Cap</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
+        <is>
+          <t>Entry Date</t>
+        </is>
+      </c>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>Exit Date</t>
+        </is>
+      </c>
+      <c r="K7" s="8" t="inlineStr">
+        <is>
+          <t>Days</t>
+        </is>
+      </c>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>Urgency</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="O7" s="8" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="P7" s="8" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
+          <t>Inv Quality</t>
+        </is>
+      </c>
+      <c r="R7" s="8" t="inlineStr">
+        <is>
+          <t>Investability</t>
+        </is>
+      </c>
+      <c r="S7" s="8" t="inlineStr">
+        <is>
+          <t>Entry</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>Exit Price</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t>P&amp;L %</t>
+        </is>
+      </c>
+      <c r="W7" s="8" t="inlineStr">
+        <is>
+          <t>Stop Loss</t>
+        </is>
+      </c>
+      <c r="X7" s="8" t="inlineStr">
+        <is>
+          <t>Target 1</t>
+        </is>
+      </c>
+      <c r="Y7" s="8" t="inlineStr">
+        <is>
+          <t>Target 2</t>
+        </is>
+      </c>
+      <c r="Z7" s="8" t="inlineStr">
+        <is>
+          <t>Action Note</t>
+        </is>
+      </c>
+      <c r="AA7" s="8" t="inlineStr">
+        <is>
+          <t>Alerts</t>
+        </is>
+      </c>
+      <c r="AB7" s="8" t="inlineStr">
+        <is>
+          <t>Exit Reason</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:BG1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="6" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="50" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="20" max="20"/>
+    <col width="44" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="6" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="14" customWidth="1" min="29" max="29"/>
+    <col width="14" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="13" customWidth="1" min="32" max="32"/>
+    <col width="13" customWidth="1" min="33" max="33"/>
+    <col width="11" customWidth="1" min="34" max="34"/>
+    <col width="9" customWidth="1" min="35" max="35"/>
+    <col width="11" customWidth="1" min="36" max="36"/>
+    <col width="8" customWidth="1" min="37" max="37"/>
+    <col width="11" customWidth="1" min="38" max="38"/>
+    <col width="8" customWidth="1" min="39" max="39"/>
+    <col width="11" customWidth="1" min="40" max="40"/>
+    <col width="13" customWidth="1" min="41" max="41"/>
+    <col width="15" customWidth="1" min="42" max="42"/>
+    <col width="12" customWidth="1" min="43" max="43"/>
+    <col width="11" customWidth="1" min="44" max="44"/>
+    <col width="32" customWidth="1" min="45" max="45"/>
+    <col width="20" customWidth="1" min="46" max="46"/>
+    <col width="18" customWidth="1" min="47" max="47"/>
+    <col width="18" customWidth="1" min="59" max="59"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Position ID</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Run_Type</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>Exit Reason</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>Exit P&amp;L %</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>Prior Rank</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>Rank Δ</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
+        <is>
+          <t>Health</t>
+        </is>
+      </c>
+      <c r="N1" s="9" t="inlineStr">
+        <is>
+          <t>Risk Meter</t>
+        </is>
+      </c>
+      <c r="O1" s="9" t="inlineStr">
+        <is>
+          <t>Adj Conf</t>
+        </is>
+      </c>
+      <c r="P1" s="9" t="inlineStr">
+        <is>
+          <t>Ctx Drag</t>
+        </is>
+      </c>
+      <c r="Q1" s="9" t="inlineStr">
+        <is>
+          <t>Ctx Reason</t>
+        </is>
+      </c>
+      <c r="R1" s="9" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="S1" s="9" t="inlineStr">
+        <is>
+          <t>Alerts</t>
+        </is>
+      </c>
+      <c r="T1" s="9" t="inlineStr">
+        <is>
+          <t>Confidence %</t>
+        </is>
+      </c>
+      <c r="U1" s="9" t="inlineStr">
+        <is>
+          <t>Conf Type</t>
+        </is>
+      </c>
+      <c r="V1" s="9" t="inlineStr">
+        <is>
+          <t>Model Score</t>
+        </is>
+      </c>
+      <c r="W1" s="9" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="X1" s="9" t="inlineStr">
+        <is>
+          <t>Trading Days</t>
+        </is>
+      </c>
+      <c r="Y1" s="9" t="inlineStr">
+        <is>
+          <t>Horizon (d)</t>
+        </is>
+      </c>
+      <c r="Z1" s="9" t="inlineStr">
+        <is>
+          <t>Days Left</t>
+        </is>
+      </c>
+      <c r="AA1" s="9" t="inlineStr">
+        <is>
+          <t>Recommended</t>
+        </is>
+      </c>
+      <c r="AB1" s="9" t="inlineStr">
+        <is>
+          <t>Current Price</t>
+        </is>
+      </c>
+      <c r="AC1" s="9" t="inlineStr">
+        <is>
+          <t>Entry Price</t>
+        </is>
+      </c>
+      <c r="AD1" s="9" t="inlineStr">
+        <is>
+          <t>Buy Zone Low</t>
+        </is>
+      </c>
+      <c r="AE1" s="9" t="inlineStr">
+        <is>
+          <t>Buy Zone High</t>
+        </is>
+      </c>
+      <c r="AF1" s="9" t="inlineStr">
+        <is>
+          <t>Stop Loss</t>
+        </is>
+      </c>
+      <c r="AG1" s="9" t="inlineStr">
+        <is>
+          <t>Risk %</t>
+        </is>
+      </c>
+      <c r="AH1" s="9" t="inlineStr">
+        <is>
+          <t>Target 1</t>
+        </is>
+      </c>
+      <c r="AI1" s="9" t="inlineStr">
+        <is>
+          <t>T1 %</t>
+        </is>
+      </c>
+      <c r="AJ1" s="9" t="inlineStr">
+        <is>
+          <t>Target 2</t>
+        </is>
+      </c>
+      <c r="AK1" s="9" t="inlineStr">
+        <is>
+          <t>T2 %</t>
+        </is>
+      </c>
+      <c r="AL1" s="9" t="inlineStr">
+        <is>
+          <t>Prev Close</t>
+        </is>
+      </c>
+      <c r="AM1" s="9" t="inlineStr">
+        <is>
+          <t>Today Move %</t>
+        </is>
+      </c>
+      <c r="AN1" s="9" t="inlineStr">
+        <is>
+          <t>Current Perf %</t>
+        </is>
+      </c>
+      <c r="AO1" s="9" t="inlineStr">
+        <is>
+          <t>Max Gain %</t>
+        </is>
+      </c>
+      <c r="AP1" s="9" t="inlineStr">
+        <is>
+          <t>Max DD %</t>
+        </is>
+      </c>
+      <c r="AQ1" s="9" t="inlineStr">
+        <is>
+          <t>Top Drivers</t>
+        </is>
+      </c>
+      <c r="AR1" s="9" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="AS1" s="9" t="inlineStr">
+        <is>
+          <t>Portfolio Weight %</t>
+        </is>
+      </c>
+      <c r="AT1" s="9" t="inlineStr">
+        <is>
+          <t>Expected Alpha %</t>
+        </is>
+      </c>
+      <c r="AU1" s="9" t="inlineStr">
+        <is>
+          <t>Last Updated (UTC)</t>
+        </is>
+      </c>
+      <c r="AV1" s="9" t="inlineStr">
+        <is>
+          <t>Cap Size</t>
+        </is>
+      </c>
+      <c r="AW1" s="9" t="inlineStr">
+        <is>
+          <t>Opp Age</t>
+        </is>
+      </c>
+      <c r="AX1" s="9" t="inlineStr">
+        <is>
+          <t>Investability</t>
+        </is>
+      </c>
+      <c r="AY1" s="9" t="inlineStr">
+        <is>
+          <t>Inv Verdict</t>
+        </is>
+      </c>
+      <c r="AZ1" s="9" t="inlineStr">
+        <is>
+          <t>🎯 DECISION</t>
+        </is>
+      </c>
+      <c r="BA1" s="9" t="inlineStr">
+        <is>
+          <t>Urgency</t>
+        </is>
+      </c>
+      <c r="BB1" s="9" t="inlineStr">
+        <is>
+          <t>Reason</t>
+        </is>
+      </c>
+      <c r="BC1" s="9" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="BD1" s="9" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="BE1" s="9" t="inlineStr">
+        <is>
+          <t>Price Trigger</t>
+        </is>
+      </c>
+      <c r="BF1" s="9" t="inlineStr">
+        <is>
+          <t>Next Review</t>
+        </is>
+      </c>
+      <c r="BG1" s="9" t="inlineStr">
+        <is>
+          <t>Execution Window</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -17,8 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="+0.00%;-0.00%;0.00%"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -46,7 +47,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -61,8 +62,50 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
+        <bgColor rgb="00F8CBAD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFE699"/>
         <bgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCC66"/>
+        <bgColor rgb="00FFCC66"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6DCE4"/>
+        <bgColor rgb="00D6DCE4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7E6E6"/>
+        <bgColor rgb="00E7E6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D08E"/>
+        <bgColor rgb="00A9D08E"/>
       </patternFill>
     </fill>
   </fills>
@@ -78,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -86,13 +129,76 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -458,43 +564,45 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB7"/>
+  <dimension ref="A1:AD32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
     <col width="14" customWidth="1" min="17" max="17"/>
     <col width="12" customWidth="1" min="18" max="18"/>
-    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
     <col width="12" customWidth="1" min="20" max="20"/>
     <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="40" customWidth="1" min="26" max="26"/>
-    <col width="40" customWidth="1" min="27" max="27"/>
-    <col width="30" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="12" customWidth="1" min="27" max="27"/>
+    <col width="40" customWidth="1" min="28" max="28"/>
+    <col width="40" customWidth="1" min="29" max="29"/>
+    <col width="30" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS USA PORTFOLIO · as of today</t>
+          <t>AEGIS USA PORTFOLIO · as of 2026-08-10</t>
         </is>
       </c>
     </row>
@@ -505,11 +613,11 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>0</v>
+        <v>-0.7878000000000002</v>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>0 closed</t>
+          <t>13 closed</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -519,7 +627,7 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> +0.00%</t>
+          <t>AAPL +7.31%</t>
         </is>
       </c>
     </row>
@@ -534,7 +642,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>0 open</t>
+          <t>12 open</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -544,7 +652,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> +0.00%</t>
+          <t>MSFT -19.21%</t>
         </is>
       </c>
     </row>
@@ -555,11 +663,11 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0</v>
+        <v>-0.7878000000000002</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>0 positions</t>
+          <t>25 positions</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -569,7 +677,7 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>0.0% (0W / 0L / 0 flat)</t>
+          <t>8.0% (2W / 11L / 12 flat)</t>
         </is>
       </c>
     </row>
@@ -586,134 +694,2970 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
+          <t>Lifecycle</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
           <t>Price Trigger</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr">
         <is>
           <t>Next Review</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="F7" s="8" t="inlineStr">
         <is>
           <t>Execution Window</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>Runner</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>R1/R2 Consensus</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="J7" s="8" t="inlineStr">
         <is>
           <t>Cap</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="L7" s="8" t="inlineStr">
         <is>
           <t>Exit Date</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="M7" s="8" t="inlineStr">
         <is>
           <t>Days</t>
         </is>
       </c>
-      <c r="L7" s="8" t="inlineStr">
+      <c r="N7" s="8" t="inlineStr">
         <is>
           <t>Urgency</t>
         </is>
       </c>
-      <c r="M7" s="8" t="inlineStr">
+      <c r="O7" s="8" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr">
+      <c r="P7" s="8" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="Q7" s="8" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
       </c>
-      <c r="P7" s="8" t="inlineStr">
+      <c r="R7" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="Q7" s="8" t="inlineStr">
+      <c r="S7" s="8" t="inlineStr">
         <is>
           <t>Inv Quality</t>
         </is>
       </c>
-      <c r="R7" s="8" t="inlineStr">
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>Investability</t>
         </is>
       </c>
-      <c r="S7" s="8" t="inlineStr">
+      <c r="U7" s="8" t="inlineStr">
         <is>
           <t>Entry</t>
         </is>
       </c>
-      <c r="T7" s="8" t="inlineStr">
+      <c r="V7" s="8" t="inlineStr">
         <is>
           <t>Current</t>
         </is>
       </c>
-      <c r="U7" s="8" t="inlineStr">
+      <c r="W7" s="8" t="inlineStr">
         <is>
           <t>Exit Price</t>
         </is>
       </c>
-      <c r="V7" s="8" t="inlineStr">
+      <c r="X7" s="8" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="W7" s="8" t="inlineStr">
+      <c r="Y7" s="8" t="inlineStr">
         <is>
           <t>Stop Loss</t>
         </is>
       </c>
-      <c r="X7" s="8" t="inlineStr">
+      <c r="Z7" s="8" t="inlineStr">
         <is>
           <t>Target 1</t>
         </is>
       </c>
-      <c r="Y7" s="8" t="inlineStr">
+      <c r="AA7" s="8" t="inlineStr">
         <is>
           <t>Target 2</t>
         </is>
       </c>
-      <c r="Z7" s="8" t="inlineStr">
+      <c r="AB7" s="8" t="inlineStr">
         <is>
           <t>Action Note</t>
         </is>
       </c>
-      <c r="AA7" s="8" t="inlineStr">
+      <c r="AC7" s="8" t="inlineStr">
         <is>
           <t>Alerts</t>
         </is>
       </c>
-      <c r="AB7" s="8" t="inlineStr">
+      <c r="AD7" s="8" t="inlineStr">
         <is>
           <t>Exit Reason</t>
         </is>
       </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>🟠 REVIEW</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>🟢 ACTIVE</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Review @ 333.74</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>🟠 No execution · investigate + decide</t>
+        </is>
+      </c>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <t>✅ AGREE</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="M8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="9" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="inlineStr">
+        <is>
+          <t>Premature Exit?</t>
+        </is>
+      </c>
+      <c r="P8" s="9" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="Q8" s="9" t="inlineStr">
+        <is>
+          <t>5 DAYS</t>
+        </is>
+      </c>
+      <c r="R8" s="9" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="S8" s="9" t="inlineStr">
+        <is>
+          <t>🏆 QUALITY</t>
+        </is>
+      </c>
+      <c r="T8" s="12" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="U8" s="13" t="n">
+        <v>311</v>
+      </c>
+      <c r="V8" s="13" t="n">
+        <v>333.74</v>
+      </c>
+      <c r="W8" s="13" t="n">
+        <v>333.74</v>
+      </c>
+      <c r="X8" s="14" t="n">
+        <v>0.0731</v>
+      </c>
+      <c r="Y8" s="13" t="n"/>
+      <c r="Z8" s="13" t="n"/>
+      <c r="AA8" s="13" t="n"/>
+      <c r="AB8" s="9" t="inlineStr">
+        <is>
+          <t>Sell/rotate today · closed position</t>
+        </is>
+      </c>
+      <c r="AC8" s="9" t="inlineStr"/>
+      <c r="AD8" s="9" t="inlineStr">
+        <is>
+          <t>→ TRV · +14.9pp alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>🔒 CLOSED</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr"/>
+      <c r="E9" s="9" t="inlineStr"/>
+      <c r="F9" s="9" t="inlineStr"/>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <t>✅ AGREE</t>
+        </is>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="M9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="9" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="O9" s="9" t="inlineStr">
+        <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="P9" s="9" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="Q9" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R9" s="9" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="S9" s="9" t="inlineStr"/>
+      <c r="T9" s="15" t="n"/>
+      <c r="U9" s="13" t="n">
+        <v>1060.380004882812</v>
+      </c>
+      <c r="V9" s="13" t="n">
+        <v>1065.22</v>
+      </c>
+      <c r="W9" s="13" t="n">
+        <v>1065.22</v>
+      </c>
+      <c r="X9" s="14" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="Y9" s="13" t="n"/>
+      <c r="Z9" s="13" t="n"/>
+      <c r="AA9" s="13" t="n"/>
+      <c r="AB9" s="9" t="inlineStr">
+        <is>
+          <t>Sell/rotate today · closed position</t>
+        </is>
+      </c>
+      <c r="AC9" s="9" t="inlineStr"/>
+      <c r="AD9" s="9" t="inlineStr">
+        <is>
+          <t>→ TRV · +14.8pp alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>MCD</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>🔒 CLOSED</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr"/>
+      <c r="E10" s="9" t="inlineStr"/>
+      <c r="F10" s="9" t="inlineStr"/>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
+        <is>
+          <t>🔹 R2 ONLY</t>
+        </is>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="M10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="9" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="O10" s="9" t="inlineStr">
+        <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="P10" s="9" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="Q10" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R10" s="9" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="S10" s="9" t="inlineStr"/>
+      <c r="T10" s="15" t="n"/>
+      <c r="U10" s="13" t="n">
+        <v>274</v>
+      </c>
+      <c r="V10" s="13" t="n">
+        <v>267.71</v>
+      </c>
+      <c r="W10" s="13" t="n">
+        <v>267.71</v>
+      </c>
+      <c r="X10" s="14" t="n">
+        <v>-0.023</v>
+      </c>
+      <c r="Y10" s="13" t="n"/>
+      <c r="Z10" s="13" t="n"/>
+      <c r="AA10" s="13" t="n"/>
+      <c r="AB10" s="9" t="inlineStr">
+        <is>
+          <t>Sell/rotate today · closed position</t>
+        </is>
+      </c>
+      <c r="AC10" s="9" t="inlineStr"/>
+      <c r="AD10" s="9" t="inlineStr">
+        <is>
+          <t>→ TRV · +45.9pp alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>🔒 CLOSED</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr"/>
+      <c r="E11" s="9" t="inlineStr"/>
+      <c r="F11" s="9" t="inlineStr"/>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
+        <is>
+          <t>🔹 R2 ONLY</t>
+        </is>
+      </c>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="M11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="9" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="O11" s="9" t="inlineStr">
+        <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="P11" s="9" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="Q11" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R11" s="9" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="S11" s="9" t="inlineStr"/>
+      <c r="T11" s="15" t="n"/>
+      <c r="U11" s="13" t="n">
+        <v>101.7600021362305</v>
+      </c>
+      <c r="V11" s="13" t="n">
+        <v>97.67</v>
+      </c>
+      <c r="W11" s="13" t="n">
+        <v>97.67</v>
+      </c>
+      <c r="X11" s="14" t="n">
+        <v>-0.04019999999999999</v>
+      </c>
+      <c r="Y11" s="13" t="n"/>
+      <c r="Z11" s="13" t="n"/>
+      <c r="AA11" s="13" t="n"/>
+      <c r="AB11" s="9" t="inlineStr">
+        <is>
+          <t>Sell/rotate today · closed position</t>
+        </is>
+      </c>
+      <c r="AC11" s="9" t="inlineStr"/>
+      <c r="AD11" s="9" t="inlineStr">
+        <is>
+          <t>→ TRV · +45.6pp alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>🔒 CLOSED</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr"/>
+      <c r="E12" s="9" t="inlineStr"/>
+      <c r="F12" s="9" t="inlineStr"/>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>🔹 R2 ONLY</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="M12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="9" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="O12" s="9" t="inlineStr">
+        <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="P12" s="9" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="Q12" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R12" s="9" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="S12" s="9" t="inlineStr"/>
+      <c r="T12" s="15" t="n"/>
+      <c r="U12" s="13" t="n">
+        <v>353.1400146484375</v>
+      </c>
+      <c r="V12" s="13" t="n">
+        <v>338.87</v>
+      </c>
+      <c r="W12" s="13" t="n">
+        <v>338.87</v>
+      </c>
+      <c r="X12" s="14" t="n">
+        <v>-0.0404</v>
+      </c>
+      <c r="Y12" s="13" t="n"/>
+      <c r="Z12" s="13" t="n"/>
+      <c r="AA12" s="13" t="n"/>
+      <c r="AB12" s="9" t="inlineStr">
+        <is>
+          <t>Sell/rotate today · closed position</t>
+        </is>
+      </c>
+      <c r="AC12" s="9" t="inlineStr"/>
+      <c r="AD12" s="9" t="inlineStr">
+        <is>
+          <t>→ TRV · +43.9pp alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>🔒 CLOSED</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr"/>
+      <c r="E13" s="9" t="inlineStr"/>
+      <c r="F13" s="9" t="inlineStr"/>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
+        <is>
+          <t>✅ AGREE</t>
+        </is>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L13" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="M13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="9" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="O13" s="9" t="inlineStr">
+        <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="P13" s="9" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="Q13" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R13" s="9" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="S13" s="9" t="inlineStr"/>
+      <c r="T13" s="15" t="n"/>
+      <c r="U13" s="13" t="n">
+        <v>359.239990234375</v>
+      </c>
+      <c r="V13" s="13" t="n">
+        <v>341.1</v>
+      </c>
+      <c r="W13" s="13" t="n">
+        <v>341.1</v>
+      </c>
+      <c r="X13" s="14" t="n">
+        <v>-0.0505</v>
+      </c>
+      <c r="Y13" s="13" t="n"/>
+      <c r="Z13" s="13" t="n"/>
+      <c r="AA13" s="13" t="n"/>
+      <c r="AB13" s="9" t="inlineStr">
+        <is>
+          <t>Sell/rotate today · closed position</t>
+        </is>
+      </c>
+      <c r="AC13" s="9" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-5.0% ≤ -5.0% · exit</t>
+        </is>
+      </c>
+      <c r="AD13" s="9" t="inlineStr">
+        <is>
+          <t>→ TRV · +13.0pp alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>🔒 CLOSED</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr"/>
+      <c r="E14" s="9" t="inlineStr"/>
+      <c r="F14" s="9" t="inlineStr"/>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
+        <is>
+          <t>🔹 R2 ONLY</t>
+        </is>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="M14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="9" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="O14" s="9" t="inlineStr">
+        <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="P14" s="9" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="Q14" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R14" s="9" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="S14" s="9" t="inlineStr"/>
+      <c r="T14" s="15" t="n"/>
+      <c r="U14" s="13" t="n">
+        <v>101.0599975585938</v>
+      </c>
+      <c r="V14" s="13" t="n">
+        <v>95.04000000000001</v>
+      </c>
+      <c r="W14" s="13" t="n">
+        <v>95.04000000000001</v>
+      </c>
+      <c r="X14" s="14" t="n">
+        <v>-0.0596</v>
+      </c>
+      <c r="Y14" s="13" t="n"/>
+      <c r="Z14" s="13" t="n"/>
+      <c r="AA14" s="13" t="n"/>
+      <c r="AB14" s="9" t="inlineStr">
+        <is>
+          <t>Sell/rotate today · closed position</t>
+        </is>
+      </c>
+      <c r="AC14" s="9" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-6.0% ≤ -5.0% · exit</t>
+        </is>
+      </c>
+      <c r="AD14" s="9" t="inlineStr">
+        <is>
+          <t>→ TRV · +37.2pp alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>🔒 CLOSED</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr"/>
+      <c r="E15" s="9" t="inlineStr"/>
+      <c r="F15" s="9" t="inlineStr"/>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
+        <is>
+          <t>✅ AGREE</t>
+        </is>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="M15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="9" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="O15" s="9" t="inlineStr">
+        <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="P15" s="9" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="Q15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R15" s="9" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="S15" s="9" t="inlineStr"/>
+      <c r="T15" s="15" t="n"/>
+      <c r="U15" s="13" t="n">
+        <v>86.83000183105469</v>
+      </c>
+      <c r="V15" s="13" t="n">
+        <v>81.56</v>
+      </c>
+      <c r="W15" s="13" t="n">
+        <v>81.56</v>
+      </c>
+      <c r="X15" s="14" t="n">
+        <v>-0.0607</v>
+      </c>
+      <c r="Y15" s="13" t="n"/>
+      <c r="Z15" s="13" t="n"/>
+      <c r="AA15" s="13" t="n"/>
+      <c r="AB15" s="9" t="inlineStr">
+        <is>
+          <t>Sell/rotate today · closed position</t>
+        </is>
+      </c>
+      <c r="AC15" s="9" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-6.1% ≤ -5.0% · exit</t>
+        </is>
+      </c>
+      <c r="AD15" s="9" t="inlineStr">
+        <is>
+          <t>→ TRV · +15.5pp alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>🔒 CLOSED</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr"/>
+      <c r="E16" s="9" t="inlineStr"/>
+      <c r="F16" s="9" t="inlineStr"/>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
+        <is>
+          <t>✅ AGREE</t>
+        </is>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="M16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="9" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="O16" s="9" t="inlineStr">
+        <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="P16" s="9" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="Q16" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R16" s="9" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="S16" s="9" t="inlineStr"/>
+      <c r="T16" s="15" t="n"/>
+      <c r="U16" s="13" t="n">
+        <v>219.2200012207031</v>
+      </c>
+      <c r="V16" s="13" t="n">
+        <v>202.81</v>
+      </c>
+      <c r="W16" s="13" t="n">
+        <v>202.81</v>
+      </c>
+      <c r="X16" s="14" t="n">
+        <v>-0.07490000000000001</v>
+      </c>
+      <c r="Y16" s="13" t="n"/>
+      <c r="Z16" s="13" t="n"/>
+      <c r="AA16" s="13" t="n"/>
+      <c r="AB16" s="9" t="inlineStr">
+        <is>
+          <t>Sell/rotate today · closed position</t>
+        </is>
+      </c>
+      <c r="AC16" s="9" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-7.5% ≤ -5.0% · exit</t>
+        </is>
+      </c>
+      <c r="AD16" s="9" t="inlineStr">
+        <is>
+          <t>→ TRV · +12.2pp alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>🔒 CLOSED</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr"/>
+      <c r="E17" s="9" t="inlineStr"/>
+      <c r="F17" s="9" t="inlineStr"/>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
+        <is>
+          <t>✅ AGREE</t>
+        </is>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="M17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="9" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="O17" s="9" t="inlineStr">
+        <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="P17" s="9" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="Q17" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R17" s="9" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="S17" s="9" t="inlineStr"/>
+      <c r="T17" s="15" t="n"/>
+      <c r="U17" s="13" t="n">
+        <v>248.1199951171875</v>
+      </c>
+      <c r="V17" s="13" t="n">
+        <v>225.02</v>
+      </c>
+      <c r="W17" s="13" t="n">
+        <v>225.02</v>
+      </c>
+      <c r="X17" s="14" t="n">
+        <v>-0.0931</v>
+      </c>
+      <c r="Y17" s="13" t="n"/>
+      <c r="Z17" s="13" t="n"/>
+      <c r="AA17" s="13" t="n"/>
+      <c r="AB17" s="9" t="inlineStr">
+        <is>
+          <t>Sell/rotate today · closed position</t>
+        </is>
+      </c>
+      <c r="AC17" s="9" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-9.3% ≤ -8.0% · EXIT URGENT</t>
+        </is>
+      </c>
+      <c r="AD17" s="9" t="inlineStr">
+        <is>
+          <t>→ TRV · +14.4pp alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>🔒 CLOSED</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr"/>
+      <c r="E18" s="9" t="inlineStr"/>
+      <c r="F18" s="9" t="inlineStr"/>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>🔹 R2 ONLY</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="M18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="9" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="O18" s="9" t="inlineStr">
+        <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="P18" s="9" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="Q18" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R18" s="9" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="S18" s="9" t="inlineStr"/>
+      <c r="T18" s="15" t="n"/>
+      <c r="U18" s="13" t="n">
+        <v>240.1900024414062</v>
+      </c>
+      <c r="V18" s="13" t="n">
+        <v>214.03</v>
+      </c>
+      <c r="W18" s="13" t="n">
+        <v>214.03</v>
+      </c>
+      <c r="X18" s="14" t="n">
+        <v>-0.1089</v>
+      </c>
+      <c r="Y18" s="13" t="n"/>
+      <c r="Z18" s="13" t="n"/>
+      <c r="AA18" s="13" t="n"/>
+      <c r="AB18" s="9" t="inlineStr">
+        <is>
+          <t>Sell/rotate today · closed position</t>
+        </is>
+      </c>
+      <c r="AC18" s="9" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-10.9% ≤ -8.0% · EXIT URGENT</t>
+        </is>
+      </c>
+      <c r="AD18" s="9" t="inlineStr">
+        <is>
+          <t>→ TRV · +37.8pp alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>MMM</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>🔒 CLOSED</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr"/>
+      <c r="E19" s="9" t="inlineStr"/>
+      <c r="F19" s="9" t="inlineStr"/>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
+        <is>
+          <t>✅ AGREE</t>
+        </is>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L19" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="M19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="9" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="O19" s="9" t="inlineStr">
+        <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="P19" s="9" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="Q19" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R19" s="9" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="S19" s="9" t="inlineStr"/>
+      <c r="T19" s="15" t="n"/>
+      <c r="U19" s="13" t="n">
+        <v>182.0800018310547</v>
+      </c>
+      <c r="V19" s="13" t="n">
+        <v>159.84</v>
+      </c>
+      <c r="W19" s="13" t="n">
+        <v>159.84</v>
+      </c>
+      <c r="X19" s="14" t="n">
+        <v>-0.1221</v>
+      </c>
+      <c r="Y19" s="13" t="n"/>
+      <c r="Z19" s="13" t="n"/>
+      <c r="AA19" s="13" t="n"/>
+      <c r="AB19" s="9" t="inlineStr">
+        <is>
+          <t>Sell/rotate today · closed position</t>
+        </is>
+      </c>
+      <c r="AC19" s="9" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-12.2% ≤ -8.0% · EXIT URGENT</t>
+        </is>
+      </c>
+      <c r="AD19" s="9" t="inlineStr">
+        <is>
+          <t>→ TRV · +16.4pp alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>🔒 CLOSED</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr"/>
+      <c r="E20" s="9" t="inlineStr"/>
+      <c r="F20" s="9" t="inlineStr"/>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
+        <is>
+          <t>✅ AGREE</t>
+        </is>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="M20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="9" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="O20" s="9" t="inlineStr">
+        <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="P20" s="9" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="Q20" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R20" s="9" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="S20" s="9" t="inlineStr"/>
+      <c r="T20" s="15" t="n"/>
+      <c r="U20" s="13" t="n">
+        <v>487.4599914550781</v>
+      </c>
+      <c r="V20" s="13" t="n">
+        <v>393.82</v>
+      </c>
+      <c r="W20" s="13" t="n">
+        <v>393.82</v>
+      </c>
+      <c r="X20" s="14" t="n">
+        <v>-0.1921</v>
+      </c>
+      <c r="Y20" s="13" t="n"/>
+      <c r="Z20" s="13" t="n"/>
+      <c r="AA20" s="13" t="n"/>
+      <c r="AB20" s="9" t="inlineStr">
+        <is>
+          <t>Sell/rotate today · closed position</t>
+        </is>
+      </c>
+      <c r="AC20" s="9" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-19.2% ≤ -8.0% · EXIT URGENT</t>
+        </is>
+      </c>
+      <c r="AD20" s="9" t="inlineStr">
+        <is>
+          <t>→ TRV · +15.2pp alpha</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>TRV</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="C21" s="16" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 346.84</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+      <c r="G21" s="16" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="H21" s="16" t="inlineStr">
+        <is>
+          <t>✅ AGREE</t>
+        </is>
+      </c>
+      <c r="I21" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K21" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L21" s="16" t="n"/>
+      <c r="M21" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="16" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="O21" s="16" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="P21" s="16" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="Q21" s="16" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="R21" s="16" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="S21" s="16" t="inlineStr"/>
+      <c r="T21" s="19" t="n"/>
+      <c r="U21" s="20" t="n">
+        <v>382.4500122070312</v>
+      </c>
+      <c r="V21" s="20" t="n">
+        <v>382.45</v>
+      </c>
+      <c r="W21" s="20" t="n"/>
+      <c r="X21" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="20" t="n">
+        <v>346.84</v>
+      </c>
+      <c r="Z21" s="20" t="n">
+        <v>413.26</v>
+      </c>
+      <c r="AA21" s="20" t="n">
+        <v>457.54</v>
+      </c>
+      <c r="AB21" s="16" t="inlineStr">
+        <is>
+          <t>Enter or add · in buy zone</t>
+        </is>
+      </c>
+      <c r="AC21" s="16" t="inlineStr"/>
+      <c r="AD21" s="16" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 350.11</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>✅ AGREE</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K22" s="22" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L22" s="22" t="n"/>
+      <c r="M22" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="22" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="O22" s="22" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="P22" s="22" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="Q22" s="22" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="R22" s="22" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="S22" s="22" t="inlineStr"/>
+      <c r="T22" s="25" t="n"/>
+      <c r="U22" s="26" t="n">
+        <v>368.5400085449219</v>
+      </c>
+      <c r="V22" s="26" t="n">
+        <v>368.54</v>
+      </c>
+      <c r="W22" s="26" t="n"/>
+      <c r="X22" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="26" t="n">
+        <v>350.11</v>
+      </c>
+      <c r="Z22" s="26" t="n">
+        <v>398.02</v>
+      </c>
+      <c r="AA22" s="26" t="n">
+        <v>423.82</v>
+      </c>
+      <c r="AB22" s="22" t="inlineStr">
+        <is>
+          <t>Hold · no action needed today</t>
+        </is>
+      </c>
+      <c r="AC22" s="22" t="inlineStr"/>
+      <c r="AD22" s="22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 340.63</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+      <c r="G23" s="16" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H23" s="16" t="inlineStr">
+        <is>
+          <t>✅ AGREE</t>
+        </is>
+      </c>
+      <c r="I23" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K23" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L23" s="16" t="n"/>
+      <c r="M23" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="16" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="O23" s="16" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="P23" s="16" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="Q23" s="16" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="R23" s="16" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="S23" s="16" t="inlineStr"/>
+      <c r="T23" s="19" t="n"/>
+      <c r="U23" s="20" t="n">
+        <v>368.5400085449219</v>
+      </c>
+      <c r="V23" s="20" t="n">
+        <v>368.54</v>
+      </c>
+      <c r="W23" s="20" t="n"/>
+      <c r="X23" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="20" t="n">
+        <v>340.632</v>
+      </c>
+      <c r="Z23" s="20" t="n">
+        <v>387.2448000000001</v>
+      </c>
+      <c r="AA23" s="20" t="n">
+        <v>414.3519360000001</v>
+      </c>
+      <c r="AB23" s="16" t="inlineStr">
+        <is>
+          <t>Enter or add · in buy zone</t>
+        </is>
+      </c>
+      <c r="AC23" s="16" t="inlineStr"/>
+      <c r="AD23" s="16" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>TRV</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 350.53</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+      <c r="G24" s="16" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H24" s="16" t="inlineStr">
+        <is>
+          <t>✅ AGREE</t>
+        </is>
+      </c>
+      <c r="I24" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K24" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L24" s="16" t="n"/>
+      <c r="M24" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="16" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="O24" s="16" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="P24" s="16" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="Q24" s="16" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="R24" s="16" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="S24" s="16" t="inlineStr"/>
+      <c r="T24" s="19" t="n"/>
+      <c r="U24" s="20" t="n">
+        <v>382.4500122070312</v>
+      </c>
+      <c r="V24" s="20" t="n">
+        <v>382.45</v>
+      </c>
+      <c r="W24" s="20" t="n"/>
+      <c r="X24" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="20" t="n">
+        <v>350.531</v>
+      </c>
+      <c r="Z24" s="20" t="n">
+        <v>413.26</v>
+      </c>
+      <c r="AA24" s="20" t="n">
+        <v>442.1882</v>
+      </c>
+      <c r="AB24" s="16" t="inlineStr">
+        <is>
+          <t>Enter or add · in buy zone</t>
+        </is>
+      </c>
+      <c r="AC24" s="16" t="inlineStr"/>
+      <c r="AD24" s="16" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 192.67</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+      <c r="G25" s="16" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H25" s="16" t="inlineStr">
+        <is>
+          <t>✅ AGREE</t>
+        </is>
+      </c>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K25" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L25" s="16" t="n"/>
+      <c r="M25" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="16" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="O25" s="16" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="P25" s="16" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="Q25" s="16" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="R25" s="16" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="S25" s="16" t="inlineStr"/>
+      <c r="T25" s="19" t="n"/>
+      <c r="U25" s="20" t="n">
+        <v>219.2200012207031</v>
+      </c>
+      <c r="V25" s="20" t="n">
+        <v>219.22</v>
+      </c>
+      <c r="W25" s="20" t="n"/>
+      <c r="X25" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="20" t="n">
+        <v>192.6695</v>
+      </c>
+      <c r="Z25" s="20" t="n">
+        <v>219.0348</v>
+      </c>
+      <c r="AA25" s="20" t="n">
+        <v>234.367236</v>
+      </c>
+      <c r="AB25" s="16" t="inlineStr">
+        <is>
+          <t>Enter or add · in buy zone</t>
+        </is>
+      </c>
+      <c r="AC25" s="16" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-7.5% ≤ -5.0% · exit</t>
+        </is>
+      </c>
+      <c r="AD25" s="16" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 374.13</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+      <c r="G26" s="16" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H26" s="16" t="inlineStr">
+        <is>
+          <t>✅ AGREE</t>
+        </is>
+      </c>
+      <c r="I26" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K26" s="16" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L26" s="16" t="n"/>
+      <c r="M26" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="16" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="O26" s="16" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="P26" s="16" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="Q26" s="16" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="R26" s="16" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="S26" s="16" t="inlineStr"/>
+      <c r="T26" s="19" t="n"/>
+      <c r="U26" s="20" t="n">
+        <v>487.4599914550781</v>
+      </c>
+      <c r="V26" s="20" t="n">
+        <v>487.46</v>
+      </c>
+      <c r="W26" s="20" t="n"/>
+      <c r="X26" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="20" t="n">
+        <v>374.129</v>
+      </c>
+      <c r="Z26" s="20" t="n">
+        <v>425.3256</v>
+      </c>
+      <c r="AA26" s="20" t="n">
+        <v>455.098392</v>
+      </c>
+      <c r="AB26" s="16" t="inlineStr">
+        <is>
+          <t>Enter or add · in buy zone</t>
+        </is>
+      </c>
+      <c r="AC26" s="16" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-19.2% ≤ -8.0% · EXIT URGENT</t>
+        </is>
+      </c>
+      <c r="AD26" s="16" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 77.48</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>✅ AGREE</t>
+        </is>
+      </c>
+      <c r="I27" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J27" s="22" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K27" s="22" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L27" s="22" t="n"/>
+      <c r="M27" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="22" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="O27" s="22" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="P27" s="22" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="Q27" s="22" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="R27" s="22" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="S27" s="22" t="inlineStr"/>
+      <c r="T27" s="25" t="n"/>
+      <c r="U27" s="26" t="n">
+        <v>86.83000183105469</v>
+      </c>
+      <c r="V27" s="26" t="n">
+        <v>86.83</v>
+      </c>
+      <c r="W27" s="26" t="n"/>
+      <c r="X27" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="26" t="n">
+        <v>77.482</v>
+      </c>
+      <c r="Z27" s="26" t="n">
+        <v>88.0848</v>
+      </c>
+      <c r="AA27" s="26" t="n">
+        <v>94.250736</v>
+      </c>
+      <c r="AB27" s="22" t="inlineStr">
+        <is>
+          <t>Hold · no action needed today</t>
+        </is>
+      </c>
+      <c r="AC27" s="22" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-6.1% ≤ -5.0% · exit</t>
+        </is>
+      </c>
+      <c r="AD27" s="22" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 213.77</t>
+        </is>
+      </c>
+      <c r="E28" s="22" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>✅ AGREE</t>
+        </is>
+      </c>
+      <c r="I28" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J28" s="22" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K28" s="22" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L28" s="22" t="n"/>
+      <c r="M28" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="22" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="O28" s="22" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="P28" s="22" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="Q28" s="22" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="R28" s="22" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="S28" s="22" t="inlineStr"/>
+      <c r="T28" s="25" t="n"/>
+      <c r="U28" s="26" t="n">
+        <v>248.1199951171875</v>
+      </c>
+      <c r="V28" s="26" t="n">
+        <v>248.12</v>
+      </c>
+      <c r="W28" s="26" t="n"/>
+      <c r="X28" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="26" t="n">
+        <v>213.769</v>
+      </c>
+      <c r="Z28" s="26" t="n">
+        <v>243.0216</v>
+      </c>
+      <c r="AA28" s="26" t="n">
+        <v>260.0331120000001</v>
+      </c>
+      <c r="AB28" s="22" t="inlineStr">
+        <is>
+          <t>Hold · no action needed today</t>
+        </is>
+      </c>
+      <c r="AC28" s="22" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-9.3% ≤ -8.0% · EXIT URGENT</t>
+        </is>
+      </c>
+      <c r="AD28" s="22" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B29" s="23" t="inlineStr">
+        <is>
+          <t>🟢 HOLD</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="D29" s="22" t="inlineStr">
+        <is>
+          <t>Watching @ 360.44</t>
+        </is>
+      </c>
+      <c r="E29" s="22" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>⚪ No immediate execution</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H29" s="22" t="inlineStr">
+        <is>
+          <t>✅ AGREE</t>
+        </is>
+      </c>
+      <c r="I29" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J29" s="22" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K29" s="22" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L29" s="22" t="n"/>
+      <c r="M29" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="22" t="inlineStr">
+        <is>
+          <t>🟢 LOW</t>
+        </is>
+      </c>
+      <c r="O29" s="22" t="inlineStr">
+        <is>
+          <t>Compounder</t>
+        </is>
+      </c>
+      <c r="P29" s="22" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="Q29" s="22" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="R29" s="22" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="S29" s="22" t="inlineStr">
+        <is>
+          <t>🏆 QUALITY</t>
+        </is>
+      </c>
+      <c r="T29" s="28" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="U29" s="26" t="n">
+        <v>311</v>
+      </c>
+      <c r="V29" s="26" t="n">
+        <v>311</v>
+      </c>
+      <c r="W29" s="26" t="n"/>
+      <c r="X29" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="26" t="n">
+        <v>317.053</v>
+      </c>
+      <c r="Z29" s="26" t="n">
+        <v>360.4392</v>
+      </c>
+      <c r="AA29" s="26" t="n">
+        <v>385.669944</v>
+      </c>
+      <c r="AB29" s="22" t="inlineStr">
+        <is>
+          <t>Hold · no action needed today</t>
+        </is>
+      </c>
+      <c r="AC29" s="22" t="inlineStr"/>
+      <c r="AD29" s="22" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="B30" s="23" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="D30" s="22" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 324.05</t>
+        </is>
+      </c>
+      <c r="E30" s="22" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+      <c r="G30" s="22" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H30" s="22" t="inlineStr">
+        <is>
+          <t>✅ AGREE</t>
+        </is>
+      </c>
+      <c r="I30" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J30" s="22" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K30" s="22" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L30" s="22" t="n"/>
+      <c r="M30" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="22" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="O30" s="22" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="P30" s="22" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="Q30" s="22" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="R30" s="22" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="S30" s="22" t="inlineStr"/>
+      <c r="T30" s="25" t="n"/>
+      <c r="U30" s="26" t="n">
+        <v>359.239990234375</v>
+      </c>
+      <c r="V30" s="26" t="n">
+        <v>359.24</v>
+      </c>
+      <c r="W30" s="26" t="n"/>
+      <c r="X30" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="26" t="n">
+        <v>324.045</v>
+      </c>
+      <c r="Z30" s="26" t="n">
+        <v>368.388</v>
+      </c>
+      <c r="AA30" s="26" t="n">
+        <v>394.1751600000001</v>
+      </c>
+      <c r="AB30" s="22" t="inlineStr">
+        <is>
+          <t>Hold · no action needed today</t>
+        </is>
+      </c>
+      <c r="AC30" s="22" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-5.0% ≤ -5.0% · exit</t>
+        </is>
+      </c>
+      <c r="AD30" s="22" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="B31" s="23" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="D31" s="22" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 1011.96</t>
+        </is>
+      </c>
+      <c r="E31" s="22" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+      <c r="G31" s="22" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H31" s="22" t="inlineStr">
+        <is>
+          <t>✅ AGREE</t>
+        </is>
+      </c>
+      <c r="I31" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J31" s="22" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K31" s="22" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L31" s="22" t="n"/>
+      <c r="M31" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="22" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="O31" s="22" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="P31" s="22" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="Q31" s="22" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="R31" s="22" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="S31" s="22" t="inlineStr"/>
+      <c r="T31" s="25" t="n"/>
+      <c r="U31" s="26" t="n">
+        <v>1060.380004882812</v>
+      </c>
+      <c r="V31" s="26" t="n">
+        <v>1060.38</v>
+      </c>
+      <c r="W31" s="26" t="n"/>
+      <c r="X31" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="26" t="n">
+        <v>1011.959</v>
+      </c>
+      <c r="Z31" s="26" t="n">
+        <v>1150.4376</v>
+      </c>
+      <c r="AA31" s="26" t="n">
+        <v>1230.968232</v>
+      </c>
+      <c r="AB31" s="22" t="inlineStr">
+        <is>
+          <t>Hold · no action needed today</t>
+        </is>
+      </c>
+      <c r="AC31" s="22" t="inlineStr"/>
+      <c r="AD31" s="22" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>MMM</t>
+        </is>
+      </c>
+      <c r="B32" s="23" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="C32" s="22" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="D32" s="22" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 151.85</t>
+        </is>
+      </c>
+      <c r="E32" s="22" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+      <c r="G32" s="22" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H32" s="22" t="inlineStr">
+        <is>
+          <t>✅ AGREE</t>
+        </is>
+      </c>
+      <c r="I32" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J32" s="22" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K32" s="22" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L32" s="22" t="n"/>
+      <c r="M32" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="22" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="O32" s="22" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="P32" s="22" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="Q32" s="22" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="R32" s="22" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="S32" s="22" t="inlineStr"/>
+      <c r="T32" s="25" t="n"/>
+      <c r="U32" s="26" t="n">
+        <v>182.0800018310547</v>
+      </c>
+      <c r="V32" s="26" t="n">
+        <v>182.08</v>
+      </c>
+      <c r="W32" s="26" t="n"/>
+      <c r="X32" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="26" t="n">
+        <v>151.848</v>
+      </c>
+      <c r="Z32" s="26" t="n">
+        <v>172.6272</v>
+      </c>
+      <c r="AA32" s="26" t="n">
+        <v>184.711104</v>
+      </c>
+      <c r="AB32" s="22" t="inlineStr">
+        <is>
+          <t>Hold · no action needed today</t>
+        </is>
+      </c>
+      <c r="AC32" s="22" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-12.2% ≤ -8.0% · EXIT URGENT</t>
+        </is>
+      </c>
+      <c r="AD32" s="22" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -729,7 +3673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG1"/>
+  <dimension ref="A1:BG26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -783,299 +3727,5548 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="inlineStr">
+      <c r="A1" s="29" t="inlineStr">
         <is>
           <t>Position ID</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="29" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="29" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="29" t="inlineStr">
         <is>
           <t>Run_Type</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="29" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="29" t="inlineStr">
         <is>
           <t>Company</t>
         </is>
       </c>
-      <c r="G1" s="9" t="inlineStr">
+      <c r="G1" s="29" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="H1" s="29" t="inlineStr">
         <is>
           <t>Exit Reason</t>
         </is>
       </c>
-      <c r="I1" s="9" t="inlineStr">
+      <c r="I1" s="29" t="inlineStr">
         <is>
           <t>Exit P&amp;L %</t>
         </is>
       </c>
-      <c r="J1" s="9" t="inlineStr">
+      <c r="J1" s="29" t="inlineStr">
         <is>
           <t>Rank</t>
         </is>
       </c>
-      <c r="K1" s="9" t="inlineStr">
+      <c r="K1" s="29" t="inlineStr">
         <is>
           <t>Prior Rank</t>
         </is>
       </c>
-      <c r="L1" s="9" t="inlineStr">
+      <c r="L1" s="29" t="inlineStr">
         <is>
           <t>Rank Δ</t>
         </is>
       </c>
-      <c r="M1" s="9" t="inlineStr">
+      <c r="M1" s="29" t="inlineStr">
         <is>
           <t>Health</t>
         </is>
       </c>
-      <c r="N1" s="9" t="inlineStr">
+      <c r="N1" s="29" t="inlineStr">
         <is>
           <t>Risk Meter</t>
         </is>
       </c>
-      <c r="O1" s="9" t="inlineStr">
+      <c r="O1" s="29" t="inlineStr">
         <is>
           <t>Adj Conf</t>
         </is>
       </c>
-      <c r="P1" s="9" t="inlineStr">
+      <c r="P1" s="29" t="inlineStr">
         <is>
           <t>Ctx Drag</t>
         </is>
       </c>
-      <c r="Q1" s="9" t="inlineStr">
+      <c r="Q1" s="29" t="inlineStr">
         <is>
           <t>Ctx Reason</t>
         </is>
       </c>
-      <c r="R1" s="9" t="inlineStr">
+      <c r="R1" s="29" t="inlineStr">
         <is>
           <t>Story</t>
         </is>
       </c>
-      <c r="S1" s="9" t="inlineStr">
+      <c r="S1" s="29" t="inlineStr">
         <is>
           <t>Alerts</t>
         </is>
       </c>
-      <c r="T1" s="9" t="inlineStr">
+      <c r="T1" s="29" t="inlineStr">
         <is>
           <t>Confidence %</t>
         </is>
       </c>
-      <c r="U1" s="9" t="inlineStr">
+      <c r="U1" s="29" t="inlineStr">
         <is>
           <t>Conf Type</t>
         </is>
       </c>
-      <c r="V1" s="9" t="inlineStr">
+      <c r="V1" s="29" t="inlineStr">
         <is>
           <t>Model Score</t>
         </is>
       </c>
-      <c r="W1" s="9" t="inlineStr">
+      <c r="W1" s="29" t="inlineStr">
         <is>
           <t>Day</t>
         </is>
       </c>
-      <c r="X1" s="9" t="inlineStr">
+      <c r="X1" s="29" t="inlineStr">
         <is>
           <t>Trading Days</t>
         </is>
       </c>
-      <c r="Y1" s="9" t="inlineStr">
+      <c r="Y1" s="29" t="inlineStr">
         <is>
           <t>Horizon (d)</t>
         </is>
       </c>
-      <c r="Z1" s="9" t="inlineStr">
+      <c r="Z1" s="29" t="inlineStr">
         <is>
           <t>Days Left</t>
         </is>
       </c>
-      <c r="AA1" s="9" t="inlineStr">
+      <c r="AA1" s="29" t="inlineStr">
         <is>
           <t>Recommended</t>
         </is>
       </c>
-      <c r="AB1" s="9" t="inlineStr">
+      <c r="AB1" s="29" t="inlineStr">
         <is>
           <t>Current Price</t>
         </is>
       </c>
-      <c r="AC1" s="9" t="inlineStr">
+      <c r="AC1" s="29" t="inlineStr">
         <is>
           <t>Entry Price</t>
         </is>
       </c>
-      <c r="AD1" s="9" t="inlineStr">
+      <c r="AD1" s="29" t="inlineStr">
         <is>
           <t>Buy Zone Low</t>
         </is>
       </c>
-      <c r="AE1" s="9" t="inlineStr">
+      <c r="AE1" s="29" t="inlineStr">
         <is>
           <t>Buy Zone High</t>
         </is>
       </c>
-      <c r="AF1" s="9" t="inlineStr">
+      <c r="AF1" s="29" t="inlineStr">
         <is>
           <t>Stop Loss</t>
         </is>
       </c>
-      <c r="AG1" s="9" t="inlineStr">
+      <c r="AG1" s="29" t="inlineStr">
         <is>
           <t>Risk %</t>
         </is>
       </c>
-      <c r="AH1" s="9" t="inlineStr">
+      <c r="AH1" s="29" t="inlineStr">
         <is>
           <t>Target 1</t>
         </is>
       </c>
-      <c r="AI1" s="9" t="inlineStr">
+      <c r="AI1" s="29" t="inlineStr">
         <is>
           <t>T1 %</t>
         </is>
       </c>
-      <c r="AJ1" s="9" t="inlineStr">
+      <c r="AJ1" s="29" t="inlineStr">
         <is>
           <t>Target 2</t>
         </is>
       </c>
-      <c r="AK1" s="9" t="inlineStr">
+      <c r="AK1" s="29" t="inlineStr">
         <is>
           <t>T2 %</t>
         </is>
       </c>
-      <c r="AL1" s="9" t="inlineStr">
+      <c r="AL1" s="29" t="inlineStr">
         <is>
           <t>Prev Close</t>
         </is>
       </c>
-      <c r="AM1" s="9" t="inlineStr">
+      <c r="AM1" s="29" t="inlineStr">
         <is>
           <t>Today Move %</t>
         </is>
       </c>
-      <c r="AN1" s="9" t="inlineStr">
+      <c r="AN1" s="29" t="inlineStr">
         <is>
           <t>Current Perf %</t>
         </is>
       </c>
-      <c r="AO1" s="9" t="inlineStr">
+      <c r="AO1" s="29" t="inlineStr">
         <is>
           <t>Max Gain %</t>
         </is>
       </c>
-      <c r="AP1" s="9" t="inlineStr">
+      <c r="AP1" s="29" t="inlineStr">
         <is>
           <t>Max DD %</t>
         </is>
       </c>
-      <c r="AQ1" s="9" t="inlineStr">
+      <c r="AQ1" s="29" t="inlineStr">
         <is>
           <t>Top Drivers</t>
         </is>
       </c>
-      <c r="AR1" s="9" t="inlineStr">
+      <c r="AR1" s="29" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="AS1" s="9" t="inlineStr">
+      <c r="AS1" s="29" t="inlineStr">
         <is>
           <t>Portfolio Weight %</t>
         </is>
       </c>
-      <c r="AT1" s="9" t="inlineStr">
+      <c r="AT1" s="29" t="inlineStr">
         <is>
           <t>Expected Alpha %</t>
         </is>
       </c>
-      <c r="AU1" s="9" t="inlineStr">
+      <c r="AU1" s="29" t="inlineStr">
         <is>
           <t>Last Updated (UTC)</t>
         </is>
       </c>
-      <c r="AV1" s="9" t="inlineStr">
+      <c r="AV1" s="29" t="inlineStr">
         <is>
           <t>Cap Size</t>
         </is>
       </c>
-      <c r="AW1" s="9" t="inlineStr">
+      <c r="AW1" s="29" t="inlineStr">
         <is>
           <t>Opp Age</t>
         </is>
       </c>
-      <c r="AX1" s="9" t="inlineStr">
+      <c r="AX1" s="29" t="inlineStr">
         <is>
           <t>Investability</t>
         </is>
       </c>
-      <c r="AY1" s="9" t="inlineStr">
+      <c r="AY1" s="29" t="inlineStr">
         <is>
           <t>Inv Verdict</t>
         </is>
       </c>
-      <c r="AZ1" s="9" t="inlineStr">
+      <c r="AZ1" s="29" t="inlineStr">
         <is>
           <t>🎯 DECISION</t>
         </is>
       </c>
-      <c r="BA1" s="9" t="inlineStr">
+      <c r="BA1" s="29" t="inlineStr">
         <is>
           <t>Urgency</t>
         </is>
       </c>
-      <c r="BB1" s="9" t="inlineStr">
+      <c r="BB1" s="29" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
       </c>
-      <c r="BC1" s="9" t="inlineStr">
+      <c r="BC1" s="29" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="BD1" s="9" t="inlineStr">
+      <c r="BD1" s="29" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
       </c>
-      <c r="BE1" s="9" t="inlineStr">
+      <c r="BE1" s="29" t="inlineStr">
         <is>
           <t>Price Trigger</t>
         </is>
       </c>
-      <c r="BF1" s="9" t="inlineStr">
+      <c r="BF1" s="29" t="inlineStr">
         <is>
           <t>Next Review</t>
         </is>
       </c>
-      <c r="BG1" s="9" t="inlineStr">
+      <c r="BG1" s="29" t="inlineStr">
         <is>
           <t>Execution Window</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="30" t="inlineStr">
+        <is>
+          <t>TRV_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B2" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C2" s="30" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D2" s="30" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E2" s="30" t="inlineStr">
+        <is>
+          <t>TRV</t>
+        </is>
+      </c>
+      <c r="F2" s="30" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="G2" s="30" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H2" s="30" t="n"/>
+      <c r="I2" s="30" t="n"/>
+      <c r="J2" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="30" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="N2" s="30" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O2" s="30" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="P2" s="30" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q2" s="30" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R2" s="30" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 1→1 · Conf 57% · band HOLD · 14d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S2" s="30" t="n"/>
+      <c r="T2" s="30" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="U2" s="30" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V2" s="30" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="W2" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="X2" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="30" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z2" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA2" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB2" s="30" t="n">
+        <v>382.45</v>
+      </c>
+      <c r="AC2" s="30" t="n">
+        <v>382.4500122070312</v>
+      </c>
+      <c r="AD2" s="30" t="n">
+        <v>365.29</v>
+      </c>
+      <c r="AE2" s="30" t="n">
+        <v>372.67</v>
+      </c>
+      <c r="AF2" s="30" t="n">
+        <v>346.84</v>
+      </c>
+      <c r="AG2" s="30" t="n">
+        <v>-9.31</v>
+      </c>
+      <c r="AH2" s="30" t="n">
+        <v>413.26</v>
+      </c>
+      <c r="AI2" s="30" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="AJ2" s="30" t="n">
+        <v>457.54</v>
+      </c>
+      <c r="AK2" s="30" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="AL2" s="30" t="n">
+        <v>377.15</v>
+      </c>
+      <c r="AM2" s="30" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN2" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" s="30" t="n"/>
+      <c r="AP2" s="30" t="n"/>
+      <c r="AQ2" s="30" t="inlineStr">
+        <is>
+          <t>Momentum · Value · Trend</t>
+        </is>
+      </c>
+      <c r="AR2" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS2" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT2" s="30" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="AU2" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-10 05:42</t>
+        </is>
+      </c>
+      <c r="AV2" s="30" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW2" s="30" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX2" s="30" t="n"/>
+      <c r="AY2" s="30" t="inlineStr"/>
+      <c r="AZ2" s="30" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA2" s="30" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB2" s="30" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC2" s="30" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD2" s="30" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE2" s="30" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 346.84</t>
+        </is>
+      </c>
+      <c r="BF2" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="BG2" s="30" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="31" t="inlineStr">
+        <is>
+          <t>V_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B3" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C3" s="31" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D3" s="31" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E3" s="31" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F3" s="31" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="G3" s="31" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H3" s="31" t="n"/>
+      <c r="I3" s="31" t="n"/>
+      <c r="J3" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="31" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="N3" s="31" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O3" s="31" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="P3" s="31" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q3" s="31" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R3" s="31" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-3.7%) · Rank → 2→2 · Conf 54% · band STRONG · 14d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S3" s="31" t="n"/>
+      <c r="T3" s="31" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="U3" s="31" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V3" s="31" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="W3" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="X3" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="31" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z3" s="31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA3" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB3" s="31" t="n">
+        <v>368.54</v>
+      </c>
+      <c r="AC3" s="31" t="n">
+        <v>368.5400085449219</v>
+      </c>
+      <c r="AD3" s="31" t="n">
+        <v>364.85</v>
+      </c>
+      <c r="AE3" s="31" t="n">
+        <v>372.23</v>
+      </c>
+      <c r="AF3" s="31" t="n">
+        <v>350.11</v>
+      </c>
+      <c r="AG3" s="31" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH3" s="31" t="n">
+        <v>398.02</v>
+      </c>
+      <c r="AI3" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ3" s="31" t="n">
+        <v>423.82</v>
+      </c>
+      <c r="AK3" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL3" s="31" t="n">
+        <v>369.59</v>
+      </c>
+      <c r="AM3" s="31" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="AN3" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="31" t="n"/>
+      <c r="AP3" s="31" t="n"/>
+      <c r="AQ3" s="31" t="inlineStr">
+        <is>
+          <t>Momentum · Trend · Quality</t>
+        </is>
+      </c>
+      <c r="AR3" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS3" s="31" t="n"/>
+      <c r="AT3" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU3" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-10 05:42</t>
+        </is>
+      </c>
+      <c r="AV3" s="31" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW3" s="31" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX3" s="31" t="n"/>
+      <c r="AY3" s="31" t="inlineStr"/>
+      <c r="AZ3" s="31" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA3" s="31" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB3" s="31" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC3" s="31" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD3" s="31" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE3" s="31" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 350.11</t>
+        </is>
+      </c>
+      <c r="BF3" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="BG3" s="31" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="32" t="inlineStr">
+        <is>
+          <t>NVDA_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B4" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C4" s="32" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D4" s="32" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E4" s="32" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="F4" s="32" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="G4" s="32" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H4" s="32" t="inlineStr">
+        <is>
+          <t>→ TRV · +12.2pp alpha</t>
+        </is>
+      </c>
+      <c r="I4" s="32" t="n">
+        <v>-7.49</v>
+      </c>
+      <c r="J4" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="32" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="N4" s="32" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O4" s="32" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="P4" s="32" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q4" s="32" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 21 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R4" s="32" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 3→3 · Conf 47% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="S4" s="32" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-7.5% ≤ -5.0% · exit</t>
+        </is>
+      </c>
+      <c r="T4" s="32" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="U4" s="32" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V4" s="32" t="n">
+        <v>17.1</v>
+      </c>
+      <c r="W4" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="X4" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z4" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA4" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB4" s="32" t="n">
+        <v>202.81</v>
+      </c>
+      <c r="AC4" s="32" t="n">
+        <v>219.2200012207031</v>
+      </c>
+      <c r="AD4" s="32" t="n">
+        <v>217.03</v>
+      </c>
+      <c r="AE4" s="32" t="n">
+        <v>221.41</v>
+      </c>
+      <c r="AF4" s="32" t="n">
+        <v>208.26</v>
+      </c>
+      <c r="AG4" s="32" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH4" s="32" t="n">
+        <v>236.76</v>
+      </c>
+      <c r="AI4" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ4" s="32" t="n">
+        <v>252.1</v>
+      </c>
+      <c r="AK4" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL4" s="32" t="n">
+        <v>211.94</v>
+      </c>
+      <c r="AM4" s="32" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AN4" s="32" t="n">
+        <v>-7.49</v>
+      </c>
+      <c r="AO4" s="32" t="n"/>
+      <c r="AP4" s="32" t="n"/>
+      <c r="AQ4" s="32" t="inlineStr">
+        <is>
+          <t>Quality · Growth · Mean Reversion</t>
+        </is>
+      </c>
+      <c r="AR4" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS4" s="32" t="n"/>
+      <c r="AT4" s="32" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="AU4" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10 05:42</t>
+        </is>
+      </c>
+      <c r="AV4" s="32" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW4" s="32" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX4" s="32" t="n"/>
+      <c r="AY4" s="32" t="inlineStr"/>
+      <c r="AZ4" s="32" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="BA4" s="32" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="BB4" s="32" t="inlineStr">
+        <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="BC4" s="32" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="BD4" s="32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BE4" s="32" t="inlineStr"/>
+      <c r="BF4" s="32" t="inlineStr"/>
+      <c r="BG4" s="32" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="32" t="inlineStr">
+        <is>
+          <t>JPM_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B5" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C5" s="32" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E5" s="32" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="F5" s="32" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase</t>
+        </is>
+      </c>
+      <c r="G5" s="32" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H5" s="32" t="inlineStr">
+        <is>
+          <t>→ TRV · +13.0pp alpha</t>
+        </is>
+      </c>
+      <c r="I5" s="32" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="J5" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="K5" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="L5" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="32" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="N5" s="32" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O5" s="32" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="P5" s="32" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q5" s="32" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 18 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R5" s="32" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 4→4 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="S5" s="32" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-5.0% ≤ -5.0% · exit</t>
+        </is>
+      </c>
+      <c r="T5" s="32" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="U5" s="32" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V5" s="32" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="W5" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z5" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA5" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB5" s="32" t="n">
+        <v>341.1</v>
+      </c>
+      <c r="AC5" s="32" t="n">
+        <v>359.239990234375</v>
+      </c>
+      <c r="AD5" s="32" t="n">
+        <v>355.65</v>
+      </c>
+      <c r="AE5" s="32" t="n">
+        <v>362.83</v>
+      </c>
+      <c r="AF5" s="32" t="n">
+        <v>341.28</v>
+      </c>
+      <c r="AG5" s="32" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH5" s="32" t="n">
+        <v>387.98</v>
+      </c>
+      <c r="AI5" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ5" s="32" t="n">
+        <v>413.13</v>
+      </c>
+      <c r="AK5" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL5" s="32" t="n">
+        <v>357.52</v>
+      </c>
+      <c r="AM5" s="32" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AN5" s="32" t="n">
+        <v>-5.05</v>
+      </c>
+      <c r="AO5" s="32" t="n"/>
+      <c r="AP5" s="32" t="n"/>
+      <c r="AQ5" s="32" t="inlineStr">
+        <is>
+          <t>Momentum · Value · Mean Reversion</t>
+        </is>
+      </c>
+      <c r="AR5" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS5" s="32" t="n"/>
+      <c r="AT5" s="32" t="n">
+        <v>12.97</v>
+      </c>
+      <c r="AU5" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10 05:42</t>
+        </is>
+      </c>
+      <c r="AV5" s="32" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW5" s="32" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX5" s="32" t="n"/>
+      <c r="AY5" s="32" t="inlineStr"/>
+      <c r="AZ5" s="32" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="BA5" s="32" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="BB5" s="32" t="inlineStr">
+        <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="BC5" s="32" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="BD5" s="32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BE5" s="32" t="inlineStr"/>
+      <c r="BF5" s="32" t="inlineStr"/>
+      <c r="BG5" s="32" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="32" t="inlineStr">
+        <is>
+          <t>HON_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B6" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C6" s="32" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D6" s="32" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E6" s="32" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="F6" s="32" t="inlineStr">
+        <is>
+          <t>Honeywell</t>
+        </is>
+      </c>
+      <c r="G6" s="32" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H6" s="32" t="inlineStr">
+        <is>
+          <t>→ TRV · +14.4pp alpha</t>
+        </is>
+      </c>
+      <c r="I6" s="32" t="n">
+        <v>-9.31</v>
+      </c>
+      <c r="J6" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="K6" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="L6" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="32" t="n">
+        <v>76</v>
+      </c>
+      <c r="N6" s="32" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O6" s="32" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="P6" s="32" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q6" s="32" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 48 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R6" s="32" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 5→5 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="S6" s="32" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-9.3% ≤ -8.0% · EXIT URGENT</t>
+        </is>
+      </c>
+      <c r="T6" s="32" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="U6" s="32" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V6" s="32" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="W6" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="X6" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z6" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA6" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB6" s="32" t="n">
+        <v>225.02</v>
+      </c>
+      <c r="AC6" s="32" t="n">
+        <v>248.1199951171875</v>
+      </c>
+      <c r="AD6" s="32" t="n">
+        <v>245.64</v>
+      </c>
+      <c r="AE6" s="32" t="n">
+        <v>250.6</v>
+      </c>
+      <c r="AF6" s="32" t="n">
+        <v>235.71</v>
+      </c>
+      <c r="AG6" s="32" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH6" s="32" t="n">
+        <v>267.97</v>
+      </c>
+      <c r="AI6" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ6" s="32" t="n">
+        <v>285.34</v>
+      </c>
+      <c r="AK6" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL6" s="32" t="n">
+        <v>248.79</v>
+      </c>
+      <c r="AM6" s="32" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="AN6" s="32" t="n">
+        <v>-9.31</v>
+      </c>
+      <c r="AO6" s="32" t="n"/>
+      <c r="AP6" s="32" t="n"/>
+      <c r="AQ6" s="32" t="inlineStr">
+        <is>
+          <t>Mean Reversion · Growth · Value</t>
+        </is>
+      </c>
+      <c r="AR6" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS6" s="32" t="n"/>
+      <c r="AT6" s="32" t="n">
+        <v>14.45</v>
+      </c>
+      <c r="AU6" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10 05:42</t>
+        </is>
+      </c>
+      <c r="AV6" s="32" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW6" s="32" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX6" s="32" t="n"/>
+      <c r="AY6" s="32" t="inlineStr"/>
+      <c r="AZ6" s="32" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="BA6" s="32" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="BB6" s="32" t="inlineStr">
+        <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="BC6" s="32" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="BD6" s="32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BE6" s="32" t="inlineStr"/>
+      <c r="BF6" s="32" t="inlineStr"/>
+      <c r="BG6" s="32" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="32" t="inlineStr">
+        <is>
+          <t>GS_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B7" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C7" s="32" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D7" s="32" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E7" s="32" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="F7" s="32" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="G7" s="32" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H7" s="32" t="inlineStr">
+        <is>
+          <t>→ TRV · +14.8pp alpha</t>
+        </is>
+      </c>
+      <c r="I7" s="32" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J7" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="K7" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="L7" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="32" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="N7" s="32" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O7" s="32" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="P7" s="32" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q7" s="32" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 9 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R7" s="32" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 6→6 · Conf 51% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="S7" s="32" t="n"/>
+      <c r="T7" s="32" t="n">
+        <v>51</v>
+      </c>
+      <c r="U7" s="32" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V7" s="32" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="W7" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="X7" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z7" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA7" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB7" s="32" t="n">
+        <v>1065.22</v>
+      </c>
+      <c r="AC7" s="32" t="n">
+        <v>1060.380004882812</v>
+      </c>
+      <c r="AD7" s="32" t="n">
+        <v>1049.78</v>
+      </c>
+      <c r="AE7" s="32" t="n">
+        <v>1070.98</v>
+      </c>
+      <c r="AF7" s="32" t="n">
+        <v>1007.36</v>
+      </c>
+      <c r="AG7" s="32" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH7" s="32" t="n">
+        <v>1145.21</v>
+      </c>
+      <c r="AI7" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ7" s="32" t="n">
+        <v>1219.44</v>
+      </c>
+      <c r="AK7" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL7" s="32" t="n">
+        <v>1052.98</v>
+      </c>
+      <c r="AM7" s="32" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AN7" s="32" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AO7" s="32" t="n"/>
+      <c r="AP7" s="32" t="n"/>
+      <c r="AQ7" s="32" t="inlineStr">
+        <is>
+          <t>Value · News · Event Driven</t>
+        </is>
+      </c>
+      <c r="AR7" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS7" s="32" t="n"/>
+      <c r="AT7" s="32" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="AU7" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10 05:42</t>
+        </is>
+      </c>
+      <c r="AV7" s="32" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW7" s="32" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX7" s="32" t="n"/>
+      <c r="AY7" s="32" t="inlineStr"/>
+      <c r="AZ7" s="32" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="BA7" s="32" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="BB7" s="32" t="inlineStr">
+        <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="BC7" s="32" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="BD7" s="32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BE7" s="32" t="inlineStr"/>
+      <c r="BF7" s="32" t="inlineStr"/>
+      <c r="BG7" s="32" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>AAPL_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B8" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C8" s="32" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D8" s="32" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E8" s="32" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="F8" s="32" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="G8" s="32" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H8" s="32" t="inlineStr">
+        <is>
+          <t>→ TRV · +14.9pp alpha</t>
+        </is>
+      </c>
+      <c r="I8" s="32" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="J8" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="K8" s="32" t="n">
+        <v>7</v>
+      </c>
+      <c r="L8" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="32" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="N8" s="32" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O8" s="32" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="P8" s="32" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q8" s="32" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R8" s="32" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 7→7 · Conf 50% · band STRONG · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="S8" s="32" t="n"/>
+      <c r="T8" s="32" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="U8" s="32" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V8" s="32" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="W8" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="X8" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z8" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA8" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB8" s="32" t="n">
+        <v>333.74</v>
+      </c>
+      <c r="AC8" s="32" t="n">
+        <v>311</v>
+      </c>
+      <c r="AD8" s="32" t="n">
+        <v>307.89</v>
+      </c>
+      <c r="AE8" s="32" t="n">
+        <v>314.11</v>
+      </c>
+      <c r="AF8" s="32" t="n">
+        <v>295.45</v>
+      </c>
+      <c r="AG8" s="32" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH8" s="32" t="n">
+        <v>335.88</v>
+      </c>
+      <c r="AI8" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ8" s="32" t="n">
+        <v>357.65</v>
+      </c>
+      <c r="AK8" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL8" s="32" t="n">
+        <v>309.38</v>
+      </c>
+      <c r="AM8" s="32" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AN8" s="32" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="AO8" s="32" t="n"/>
+      <c r="AP8" s="32" t="n"/>
+      <c r="AQ8" s="32" t="inlineStr">
+        <is>
+          <t>Value · Trend · Momentum</t>
+        </is>
+      </c>
+      <c r="AR8" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS8" s="32" t="n"/>
+      <c r="AT8" s="32" t="n">
+        <v>14.87</v>
+      </c>
+      <c r="AU8" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10 05:42</t>
+        </is>
+      </c>
+      <c r="AV8" s="32" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW8" s="32" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX8" s="32" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="AY8" s="32" t="inlineStr">
+        <is>
+          <t>🏆 QUALITY</t>
+        </is>
+      </c>
+      <c r="AZ8" s="32" t="inlineStr">
+        <is>
+          <t>🟠 REVIEW</t>
+        </is>
+      </c>
+      <c r="BA8" s="32" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB8" s="32" t="inlineStr">
+        <is>
+          <t>Premature Exit?</t>
+        </is>
+      </c>
+      <c r="BC8" s="32" t="inlineStr">
+        <is>
+          <t>REVIEW</t>
+        </is>
+      </c>
+      <c r="BD8" s="32" t="inlineStr">
+        <is>
+          <t>5 DAYS</t>
+        </is>
+      </c>
+      <c r="BE8" s="32" t="inlineStr">
+        <is>
+          <t>Review @ 333.74</t>
+        </is>
+      </c>
+      <c r="BF8" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="BG8" s="32" t="inlineStr">
+        <is>
+          <t>🟠 No execution · investigate + decide</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="32" t="inlineStr">
+        <is>
+          <t>MSFT_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B9" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C9" s="32" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D9" s="32" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E9" s="32" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="F9" s="32" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="G9" s="32" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H9" s="32" t="inlineStr">
+        <is>
+          <t>→ TRV · +15.2pp alpha</t>
+        </is>
+      </c>
+      <c r="I9" s="32" t="n">
+        <v>-19.21</v>
+      </c>
+      <c r="J9" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="K9" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="L9" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="32" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="N9" s="32" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O9" s="32" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="P9" s="32" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q9" s="32" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R9" s="32" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 8→8 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="S9" s="32" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-19.2% ≤ -8.0% · EXIT URGENT</t>
+        </is>
+      </c>
+      <c r="T9" s="32" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="U9" s="32" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V9" s="32" t="n">
+        <v>14</v>
+      </c>
+      <c r="W9" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="X9" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="32" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z9" s="32" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA9" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB9" s="32" t="n">
+        <v>393.82</v>
+      </c>
+      <c r="AC9" s="32" t="n">
+        <v>487.4599914550781</v>
+      </c>
+      <c r="AD9" s="32" t="n">
+        <v>482.59</v>
+      </c>
+      <c r="AE9" s="32" t="n">
+        <v>492.33</v>
+      </c>
+      <c r="AF9" s="32" t="n">
+        <v>463.09</v>
+      </c>
+      <c r="AG9" s="32" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH9" s="32" t="n">
+        <v>526.46</v>
+      </c>
+      <c r="AI9" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ9" s="32" t="n">
+        <v>560.58</v>
+      </c>
+      <c r="AK9" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL9" s="32" t="n">
+        <v>492.81</v>
+      </c>
+      <c r="AM9" s="32" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="AN9" s="32" t="n">
+        <v>-19.21</v>
+      </c>
+      <c r="AO9" s="32" t="n"/>
+      <c r="AP9" s="32" t="n"/>
+      <c r="AQ9" s="32" t="inlineStr">
+        <is>
+          <t>Quality · Mean Reversion · Trend</t>
+        </is>
+      </c>
+      <c r="AR9" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS9" s="32" t="n"/>
+      <c r="AT9" s="32" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="AU9" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10 05:42</t>
+        </is>
+      </c>
+      <c r="AV9" s="32" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW9" s="32" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX9" s="32" t="n"/>
+      <c r="AY9" s="32" t="inlineStr"/>
+      <c r="AZ9" s="32" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="BA9" s="32" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="BB9" s="32" t="inlineStr">
+        <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="BC9" s="32" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="BD9" s="32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BE9" s="32" t="inlineStr"/>
+      <c r="BF9" s="32" t="inlineStr"/>
+      <c r="BG9" s="32" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>KO_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B10" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C10" s="32" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D10" s="32" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E10" s="32" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="F10" s="32" t="inlineStr">
+        <is>
+          <t>Coca-Cola</t>
+        </is>
+      </c>
+      <c r="G10" s="32" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H10" s="32" t="inlineStr">
+        <is>
+          <t>→ TRV · +15.5pp alpha</t>
+        </is>
+      </c>
+      <c r="I10" s="32" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="J10" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="K10" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="L10" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="32" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="N10" s="32" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O10" s="32" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="P10" s="32" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q10" s="32" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 11 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R10" s="32" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 9→9 · Conf 50% · band STRONG · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="S10" s="32" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-6.1% ≤ -5.0% · exit</t>
+        </is>
+      </c>
+      <c r="T10" s="32" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="U10" s="32" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V10" s="32" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="W10" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="X10" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z10" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA10" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB10" s="32" t="n">
+        <v>81.56</v>
+      </c>
+      <c r="AC10" s="32" t="n">
+        <v>86.83000183105469</v>
+      </c>
+      <c r="AD10" s="32" t="n">
+        <v>85.95999999999999</v>
+      </c>
+      <c r="AE10" s="32" t="n">
+        <v>87.7</v>
+      </c>
+      <c r="AF10" s="32" t="n">
+        <v>82.48999999999999</v>
+      </c>
+      <c r="AG10" s="32" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH10" s="32" t="n">
+        <v>93.78</v>
+      </c>
+      <c r="AI10" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ10" s="32" t="n">
+        <v>99.84999999999999</v>
+      </c>
+      <c r="AK10" s="32" t="n">
+        <v>14.99</v>
+      </c>
+      <c r="AL10" s="32" t="n">
+        <v>86.56</v>
+      </c>
+      <c r="AM10" s="32" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AN10" s="32" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="AO10" s="32" t="n"/>
+      <c r="AP10" s="32" t="n"/>
+      <c r="AQ10" s="32" t="inlineStr">
+        <is>
+          <t>Momentum · News · Quality</t>
+        </is>
+      </c>
+      <c r="AR10" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS10" s="32" t="n"/>
+      <c r="AT10" s="32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AU10" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10 05:42</t>
+        </is>
+      </c>
+      <c r="AV10" s="32" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW10" s="32" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX10" s="32" t="n"/>
+      <c r="AY10" s="32" t="inlineStr"/>
+      <c r="AZ10" s="32" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="BA10" s="32" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="BB10" s="32" t="inlineStr">
+        <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="BC10" s="32" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="BD10" s="32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BE10" s="32" t="inlineStr"/>
+      <c r="BF10" s="32" t="inlineStr"/>
+      <c r="BG10" s="32" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="32" t="inlineStr">
+        <is>
+          <t>MMM_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B11" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C11" s="32" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D11" s="32" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E11" s="32" t="inlineStr">
+        <is>
+          <t>MMM</t>
+        </is>
+      </c>
+      <c r="F11" s="32" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="G11" s="32" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H11" s="32" t="inlineStr">
+        <is>
+          <t>→ TRV · +16.4pp alpha</t>
+        </is>
+      </c>
+      <c r="I11" s="32" t="n">
+        <v>-12.21</v>
+      </c>
+      <c r="J11" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="K11" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="32" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="N11" s="32" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O11" s="32" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="P11" s="32" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q11" s="32" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 15 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R11" s="32" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 10→10 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="S11" s="32" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-12.2% ≤ -8.0% · EXIT URGENT</t>
+        </is>
+      </c>
+      <c r="T11" s="32" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="U11" s="32" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V11" s="32" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="W11" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="X11" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="32" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z11" s="32" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA11" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB11" s="32" t="n">
+        <v>159.84</v>
+      </c>
+      <c r="AC11" s="32" t="n">
+        <v>182.0800018310547</v>
+      </c>
+      <c r="AD11" s="32" t="n">
+        <v>180.26</v>
+      </c>
+      <c r="AE11" s="32" t="n">
+        <v>183.9</v>
+      </c>
+      <c r="AF11" s="32" t="n">
+        <v>172.98</v>
+      </c>
+      <c r="AG11" s="32" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH11" s="32" t="n">
+        <v>196.65</v>
+      </c>
+      <c r="AI11" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ11" s="32" t="n">
+        <v>209.39</v>
+      </c>
+      <c r="AK11" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL11" s="32" t="n">
+        <v>181.45</v>
+      </c>
+      <c r="AM11" s="32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AN11" s="32" t="n">
+        <v>-12.21</v>
+      </c>
+      <c r="AO11" s="32" t="n"/>
+      <c r="AP11" s="32" t="n"/>
+      <c r="AQ11" s="32" t="inlineStr">
+        <is>
+          <t>Momentum · News · Value</t>
+        </is>
+      </c>
+      <c r="AR11" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS11" s="32" t="n"/>
+      <c r="AT11" s="32" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="AU11" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10 05:42</t>
+        </is>
+      </c>
+      <c r="AV11" s="32" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW11" s="32" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX11" s="32" t="n"/>
+      <c r="AY11" s="32" t="inlineStr"/>
+      <c r="AZ11" s="32" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="BA11" s="32" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="BB11" s="32" t="inlineStr">
+        <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="BC11" s="32" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="BD11" s="32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BE11" s="32" t="inlineStr"/>
+      <c r="BF11" s="32" t="inlineStr"/>
+      <c r="BG11" s="32" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="32" t="inlineStr">
+        <is>
+          <t>INTC_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B12" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C12" s="32" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D12" s="32" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E12" s="32" t="inlineStr">
+        <is>
+          <t>INTC</t>
+        </is>
+      </c>
+      <c r="F12" s="32" t="inlineStr">
+        <is>
+          <t>Intel</t>
+        </is>
+      </c>
+      <c r="G12" s="32" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H12" s="32" t="inlineStr">
+        <is>
+          <t>→ TRV · +37.2pp alpha</t>
+        </is>
+      </c>
+      <c r="I12" s="32" t="n">
+        <v>-5.96</v>
+      </c>
+      <c r="J12" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="K12" s="32" t="n">
+        <v>11</v>
+      </c>
+      <c r="L12" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="32" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="N12" s="32" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="O12" s="32" t="n">
+        <v>28</v>
+      </c>
+      <c r="P12" s="32" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q12" s="32" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 26 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R12" s="32" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 11→11 · Conf 29% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="S12" s="32" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-6.0% ≤ -5.0% · exit</t>
+        </is>
+      </c>
+      <c r="T12" s="32" t="n">
+        <v>28.7</v>
+      </c>
+      <c r="U12" s="32" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V12" s="32" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="W12" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="X12" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z12" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA12" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB12" s="32" t="n">
+        <v>95.04000000000001</v>
+      </c>
+      <c r="AC12" s="32" t="n">
+        <v>101.0599975585938</v>
+      </c>
+      <c r="AD12" s="32" t="n">
+        <v>100.05</v>
+      </c>
+      <c r="AE12" s="32" t="n">
+        <v>102.07</v>
+      </c>
+      <c r="AF12" s="32" t="n">
+        <v>96.01000000000001</v>
+      </c>
+      <c r="AG12" s="32" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH12" s="32" t="n">
+        <v>109.14</v>
+      </c>
+      <c r="AI12" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ12" s="32" t="n">
+        <v>116.22</v>
+      </c>
+      <c r="AK12" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL12" s="32" t="n">
+        <v>100.86</v>
+      </c>
+      <c r="AM12" s="32" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AN12" s="32" t="n">
+        <v>-5.96</v>
+      </c>
+      <c r="AO12" s="32" t="n"/>
+      <c r="AP12" s="32" t="n"/>
+      <c r="AQ12" s="32" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
+        </is>
+      </c>
+      <c r="AR12" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS12" s="32" t="n"/>
+      <c r="AT12" s="32" t="n">
+        <v>37.17</v>
+      </c>
+      <c r="AU12" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10 05:42</t>
+        </is>
+      </c>
+      <c r="AV12" s="32" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW12" s="32" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX12" s="32" t="n"/>
+      <c r="AY12" s="32" t="inlineStr"/>
+      <c r="AZ12" s="32" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="BA12" s="32" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="BB12" s="32" t="inlineStr">
+        <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="BC12" s="32" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="BD12" s="32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BE12" s="32" t="inlineStr"/>
+      <c r="BF12" s="32" t="inlineStr"/>
+      <c r="BG12" s="32" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="32" t="inlineStr">
+        <is>
+          <t>BA_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B13" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C13" s="32" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D13" s="32" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E13" s="32" t="inlineStr">
+        <is>
+          <t>BA</t>
+        </is>
+      </c>
+      <c r="F13" s="32" t="inlineStr">
+        <is>
+          <t>Boeing</t>
+        </is>
+      </c>
+      <c r="G13" s="32" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H13" s="32" t="inlineStr">
+        <is>
+          <t>→ TRV · +37.8pp alpha</t>
+        </is>
+      </c>
+      <c r="I13" s="32" t="n">
+        <v>-10.89</v>
+      </c>
+      <c r="J13" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="K13" s="32" t="n">
+        <v>12</v>
+      </c>
+      <c r="L13" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="32" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="N13" s="32" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="O13" s="32" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="P13" s="32" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q13" s="32" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R13" s="32" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 12→12 · Conf 31% · band EXIT · 58d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="S13" s="32" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-10.9% ≤ -8.0% · EXIT URGENT</t>
+        </is>
+      </c>
+      <c r="T13" s="32" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="U13" s="32" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V13" s="32" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="W13" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="X13" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="32" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z13" s="32" t="n">
+        <v>58</v>
+      </c>
+      <c r="AA13" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB13" s="32" t="n">
+        <v>214.03</v>
+      </c>
+      <c r="AC13" s="32" t="n">
+        <v>240.1900024414062</v>
+      </c>
+      <c r="AD13" s="32" t="n">
+        <v>237.79</v>
+      </c>
+      <c r="AE13" s="32" t="n">
+        <v>242.59</v>
+      </c>
+      <c r="AF13" s="32" t="n">
+        <v>228.18</v>
+      </c>
+      <c r="AG13" s="32" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH13" s="32" t="n">
+        <v>259.41</v>
+      </c>
+      <c r="AI13" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ13" s="32" t="n">
+        <v>276.22</v>
+      </c>
+      <c r="AK13" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL13" s="32" t="n">
+        <v>237.16</v>
+      </c>
+      <c r="AM13" s="32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN13" s="32" t="n">
+        <v>-10.89</v>
+      </c>
+      <c r="AO13" s="32" t="n"/>
+      <c r="AP13" s="32" t="n"/>
+      <c r="AQ13" s="32" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Close · Distance From 52W High Pct · Distance From 52W Low Pct</t>
+        </is>
+      </c>
+      <c r="AR13" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS13" s="32" t="n"/>
+      <c r="AT13" s="32" t="n">
+        <v>37.79</v>
+      </c>
+      <c r="AU13" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10 05:42</t>
+        </is>
+      </c>
+      <c r="AV13" s="32" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW13" s="32" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX13" s="32" t="n"/>
+      <c r="AY13" s="32" t="inlineStr"/>
+      <c r="AZ13" s="32" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="BA13" s="32" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="BB13" s="32" t="inlineStr">
+        <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="BC13" s="32" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="BD13" s="32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BE13" s="32" t="inlineStr"/>
+      <c r="BF13" s="32" t="inlineStr"/>
+      <c r="BG13" s="32" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="32" t="inlineStr">
+        <is>
+          <t>HD_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B14" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C14" s="32" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D14" s="32" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E14" s="32" t="inlineStr">
+        <is>
+          <t>HD</t>
+        </is>
+      </c>
+      <c r="F14" s="32" t="inlineStr">
+        <is>
+          <t>Home Depot</t>
+        </is>
+      </c>
+      <c r="G14" s="32" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H14" s="32" t="inlineStr">
+        <is>
+          <t>→ TRV · +43.9pp alpha</t>
+        </is>
+      </c>
+      <c r="I14" s="32" t="n">
+        <v>-4.04</v>
+      </c>
+      <c r="J14" s="32" t="n">
+        <v>13</v>
+      </c>
+      <c r="K14" s="32" t="n">
+        <v>13</v>
+      </c>
+      <c r="L14" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="32" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="N14" s="32" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="O14" s="32" t="n">
+        <v>34</v>
+      </c>
+      <c r="P14" s="32" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q14" s="32" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 13 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R14" s="32" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 13→13 · Conf 35% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="S14" s="32" t="n"/>
+      <c r="T14" s="32" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="U14" s="32" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V14" s="32" t="n">
+        <v>-14.6</v>
+      </c>
+      <c r="W14" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="X14" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z14" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA14" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB14" s="32" t="n">
+        <v>338.87</v>
+      </c>
+      <c r="AC14" s="32" t="n">
+        <v>353.1400146484375</v>
+      </c>
+      <c r="AD14" s="32" t="n">
+        <v>349.61</v>
+      </c>
+      <c r="AE14" s="32" t="n">
+        <v>356.67</v>
+      </c>
+      <c r="AF14" s="32" t="n">
+        <v>335.48</v>
+      </c>
+      <c r="AG14" s="32" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH14" s="32" t="n">
+        <v>381.39</v>
+      </c>
+      <c r="AI14" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ14" s="32" t="n">
+        <v>406.11</v>
+      </c>
+      <c r="AK14" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL14" s="32" t="n">
+        <v>348.24</v>
+      </c>
+      <c r="AM14" s="32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN14" s="32" t="n">
+        <v>-4.04</v>
+      </c>
+      <c r="AO14" s="32" t="n"/>
+      <c r="AP14" s="32" t="n"/>
+      <c r="AQ14" s="32" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
+        </is>
+      </c>
+      <c r="AR14" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS14" s="32" t="n"/>
+      <c r="AT14" s="32" t="n">
+        <v>43.85</v>
+      </c>
+      <c r="AU14" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10 05:42</t>
+        </is>
+      </c>
+      <c r="AV14" s="32" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW14" s="32" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX14" s="32" t="n"/>
+      <c r="AY14" s="32" t="inlineStr"/>
+      <c r="AZ14" s="32" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="BA14" s="32" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="BB14" s="32" t="inlineStr">
+        <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="BC14" s="32" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="BD14" s="32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BE14" s="32" t="inlineStr"/>
+      <c r="BF14" s="32" t="inlineStr"/>
+      <c r="BG14" s="32" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="32" t="inlineStr">
+        <is>
+          <t>DIS_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B15" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C15" s="32" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D15" s="32" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E15" s="32" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="F15" s="32" t="inlineStr">
+        <is>
+          <t>Walt Disney</t>
+        </is>
+      </c>
+      <c r="G15" s="32" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H15" s="32" t="inlineStr">
+        <is>
+          <t>→ TRV · +45.6pp alpha</t>
+        </is>
+      </c>
+      <c r="I15" s="32" t="n">
+        <v>-4.02</v>
+      </c>
+      <c r="J15" s="32" t="n">
+        <v>14</v>
+      </c>
+      <c r="K15" s="32" t="n">
+        <v>14</v>
+      </c>
+      <c r="L15" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="32" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="N15" s="32" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="O15" s="32" t="n">
+        <v>34</v>
+      </c>
+      <c r="P15" s="32" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q15" s="32" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 19 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R15" s="32" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 14→14 · Conf 35% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="S15" s="32" t="n"/>
+      <c r="T15" s="32" t="n">
+        <v>34.7</v>
+      </c>
+      <c r="U15" s="32" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V15" s="32" t="n">
+        <v>-16.4</v>
+      </c>
+      <c r="W15" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="X15" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z15" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA15" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB15" s="32" t="n">
+        <v>97.67</v>
+      </c>
+      <c r="AC15" s="32" t="n">
+        <v>101.7600021362305</v>
+      </c>
+      <c r="AD15" s="32" t="n">
+        <v>100.74</v>
+      </c>
+      <c r="AE15" s="32" t="n">
+        <v>102.78</v>
+      </c>
+      <c r="AF15" s="32" t="n">
+        <v>96.67</v>
+      </c>
+      <c r="AG15" s="32" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH15" s="32" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="AI15" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ15" s="32" t="n">
+        <v>117.02</v>
+      </c>
+      <c r="AK15" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL15" s="32" t="n">
+        <v>98.18000000000001</v>
+      </c>
+      <c r="AM15" s="32" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AN15" s="32" t="n">
+        <v>-4.02</v>
+      </c>
+      <c r="AO15" s="32" t="n"/>
+      <c r="AP15" s="32" t="n"/>
+      <c r="AQ15" s="32" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
+        </is>
+      </c>
+      <c r="AR15" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS15" s="32" t="n"/>
+      <c r="AT15" s="32" t="n">
+        <v>45.62</v>
+      </c>
+      <c r="AU15" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10 05:42</t>
+        </is>
+      </c>
+      <c r="AV15" s="32" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW15" s="32" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX15" s="32" t="n"/>
+      <c r="AY15" s="32" t="inlineStr"/>
+      <c r="AZ15" s="32" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="BA15" s="32" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="BB15" s="32" t="inlineStr">
+        <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="BC15" s="32" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="BD15" s="32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BE15" s="32" t="inlineStr"/>
+      <c r="BF15" s="32" t="inlineStr"/>
+      <c r="BG15" s="32" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="32" t="inlineStr">
+        <is>
+          <t>MCD_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B16" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C16" s="32" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D16" s="32" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E16" s="32" t="inlineStr">
+        <is>
+          <t>MCD</t>
+        </is>
+      </c>
+      <c r="F16" s="32" t="inlineStr">
+        <is>
+          <t>McDonald's</t>
+        </is>
+      </c>
+      <c r="G16" s="32" t="inlineStr">
+        <is>
+          <t>EXIT</t>
+        </is>
+      </c>
+      <c r="H16" s="32" t="inlineStr">
+        <is>
+          <t>→ TRV · +45.9pp alpha</t>
+        </is>
+      </c>
+      <c r="I16" s="32" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="J16" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="K16" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="L16" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="32" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="N16" s="32" t="inlineStr">
+        <is>
+          <t>🔴</t>
+        </is>
+      </c>
+      <c r="O16" s="32" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="P16" s="32" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q16" s="32" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 6 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R16" s="32" t="inlineStr">
+        <is>
+          <t>🔴 AVOID · Rank → 15→15 · Conf 28% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+        </is>
+      </c>
+      <c r="S16" s="32" t="n"/>
+      <c r="T16" s="32" t="n">
+        <v>28.3</v>
+      </c>
+      <c r="U16" s="32" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V16" s="32" t="n">
+        <v>-16.7</v>
+      </c>
+      <c r="W16" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="X16" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="32" t="n">
+        <v>9</v>
+      </c>
+      <c r="Z16" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA16" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB16" s="32" t="n">
+        <v>267.71</v>
+      </c>
+      <c r="AC16" s="32" t="n">
+        <v>274</v>
+      </c>
+      <c r="AD16" s="32" t="n">
+        <v>271.26</v>
+      </c>
+      <c r="AE16" s="32" t="n">
+        <v>276.74</v>
+      </c>
+      <c r="AF16" s="32" t="n">
+        <v>260.3</v>
+      </c>
+      <c r="AG16" s="32" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH16" s="32" t="n">
+        <v>295.92</v>
+      </c>
+      <c r="AI16" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ16" s="32" t="n">
+        <v>315.1</v>
+      </c>
+      <c r="AK16" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL16" s="32" t="n">
+        <v>268.34</v>
+      </c>
+      <c r="AM16" s="32" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AN16" s="32" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="AO16" s="32" t="n"/>
+      <c r="AP16" s="32" t="n"/>
+      <c r="AQ16" s="32" t="inlineStr">
+        <is>
+          <t>Adx 14 · Atr 14 Pct · Ca Days Since Last Dividend · Ca Last Dividend Amount · Close</t>
+        </is>
+      </c>
+      <c r="AR16" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS16" s="32" t="n"/>
+      <c r="AT16" s="32" t="n">
+        <v>45.94</v>
+      </c>
+      <c r="AU16" s="32" t="inlineStr">
+        <is>
+          <t>2026-08-10 05:42</t>
+        </is>
+      </c>
+      <c r="AV16" s="32" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW16" s="32" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX16" s="32" t="n"/>
+      <c r="AY16" s="32" t="inlineStr"/>
+      <c r="AZ16" s="32" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="BA16" s="32" t="inlineStr">
+        <is>
+          <t>⚪ CLOSED</t>
+        </is>
+      </c>
+      <c r="BB16" s="32" t="inlineStr">
+        <is>
+          <t>Clean Exit</t>
+        </is>
+      </c>
+      <c r="BC16" s="32" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="BD16" s="32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="BE16" s="32" t="inlineStr"/>
+      <c r="BF16" s="32" t="inlineStr"/>
+      <c r="BG16" s="32" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="30" t="inlineStr">
+        <is>
+          <t>V_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B17" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C17" s="30" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D17" s="30" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E17" s="30" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F17" s="30" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="G17" s="30" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H17" s="30" t="n"/>
+      <c r="I17" s="30" t="n"/>
+      <c r="J17" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="30" t="n"/>
+      <c r="L17" s="30" t="n"/>
+      <c r="M17" s="30" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="N17" s="30" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O17" s="30" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="P17" s="30" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q17" s="30" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R17" s="30" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #1 · Conf 54% · momentum → · band STRONG · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S17" s="30" t="n"/>
+      <c r="T17" s="30" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="U17" s="30" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V17" s="30" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="W17" s="30" t="n"/>
+      <c r="X17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="30" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z17" s="30" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA17" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB17" s="30" t="n">
+        <v>368.54</v>
+      </c>
+      <c r="AC17" s="30" t="n">
+        <v>368.5400085449219</v>
+      </c>
+      <c r="AD17" s="30" t="n">
+        <v>351.39</v>
+      </c>
+      <c r="AE17" s="30" t="n">
+        <v>365.73</v>
+      </c>
+      <c r="AF17" s="30" t="n">
+        <v>340.632</v>
+      </c>
+      <c r="AG17" s="30" t="n">
+        <v>-7.57</v>
+      </c>
+      <c r="AH17" s="30" t="n">
+        <v>387.2448000000001</v>
+      </c>
+      <c r="AI17" s="30" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="AJ17" s="30" t="n">
+        <v>414.3519360000001</v>
+      </c>
+      <c r="AK17" s="30" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="AL17" s="30" t="n">
+        <v>369.59</v>
+      </c>
+      <c r="AM17" s="30" t="n">
+        <v>-0.28</v>
+      </c>
+      <c r="AN17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" s="30" t="n"/>
+      <c r="AP17" s="30" t="n"/>
+      <c r="AQ17" s="30" t="n"/>
+      <c r="AR17" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS17" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT17" s="30" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="AU17" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-10 05:42</t>
+        </is>
+      </c>
+      <c r="AV17" s="30" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW17" s="30" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX17" s="30" t="n"/>
+      <c r="AY17" s="30" t="inlineStr"/>
+      <c r="AZ17" s="30" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA17" s="30" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB17" s="30" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC17" s="30" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD17" s="30" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE17" s="30" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 340.63</t>
+        </is>
+      </c>
+      <c r="BF17" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="BG17" s="30" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="30" t="inlineStr">
+        <is>
+          <t>TRV_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C18" s="30" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D18" s="30" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E18" s="30" t="inlineStr">
+        <is>
+          <t>TRV</t>
+        </is>
+      </c>
+      <c r="F18" s="30" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="G18" s="30" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H18" s="30" t="n"/>
+      <c r="I18" s="30" t="n"/>
+      <c r="J18" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" s="30" t="n"/>
+      <c r="L18" s="30" t="n"/>
+      <c r="M18" s="30" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="N18" s="30" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O18" s="30" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="P18" s="30" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q18" s="30" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R18" s="30" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 57% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S18" s="30" t="n"/>
+      <c r="T18" s="30" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="U18" s="30" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V18" s="30" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="W18" s="30" t="n"/>
+      <c r="X18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="30" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z18" s="30" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA18" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB18" s="30" t="n">
+        <v>382.45</v>
+      </c>
+      <c r="AC18" s="30" t="n">
+        <v>382.4500122070312</v>
+      </c>
+      <c r="AD18" s="30" t="n">
+        <v>365.29</v>
+      </c>
+      <c r="AE18" s="30" t="n">
+        <v>372.67</v>
+      </c>
+      <c r="AF18" s="30" t="n">
+        <v>350.531</v>
+      </c>
+      <c r="AG18" s="30" t="n">
+        <v>-8.35</v>
+      </c>
+      <c r="AH18" s="30" t="n">
+        <v>413.26</v>
+      </c>
+      <c r="AI18" s="30" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="AJ18" s="30" t="n">
+        <v>442.1882</v>
+      </c>
+      <c r="AK18" s="30" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="AL18" s="30" t="n">
+        <v>377.15</v>
+      </c>
+      <c r="AM18" s="30" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" s="30" t="n"/>
+      <c r="AP18" s="30" t="n"/>
+      <c r="AQ18" s="30" t="n"/>
+      <c r="AR18" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS18" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT18" s="30" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="AU18" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-10 05:42</t>
+        </is>
+      </c>
+      <c r="AV18" s="30" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW18" s="30" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX18" s="30" t="n"/>
+      <c r="AY18" s="30" t="inlineStr"/>
+      <c r="AZ18" s="30" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA18" s="30" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB18" s="30" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC18" s="30" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD18" s="30" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE18" s="30" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 350.53</t>
+        </is>
+      </c>
+      <c r="BF18" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="BG18" s="30" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="30" t="inlineStr">
+        <is>
+          <t>NVDA_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C19" s="30" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D19" s="30" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E19" s="30" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="F19" s="30" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="G19" s="30" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H19" s="30" t="n"/>
+      <c r="I19" s="30" t="n"/>
+      <c r="J19" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" s="30" t="n"/>
+      <c r="L19" s="30" t="n"/>
+      <c r="M19" s="30" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="N19" s="30" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O19" s="30" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="P19" s="30" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q19" s="30" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 21 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R19" s="30" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #3 · Conf 47% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S19" s="30" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-7.5% ≤ -5.0% · exit</t>
+        </is>
+      </c>
+      <c r="T19" s="30" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="U19" s="30" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V19" s="30" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="W19" s="30" t="n"/>
+      <c r="X19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="30" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z19" s="30" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA19" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB19" s="30" t="n">
+        <v>219.22</v>
+      </c>
+      <c r="AC19" s="30" t="n">
+        <v>219.2200012207031</v>
+      </c>
+      <c r="AD19" s="30" t="n">
+        <v>198.75</v>
+      </c>
+      <c r="AE19" s="30" t="n">
+        <v>206.87</v>
+      </c>
+      <c r="AF19" s="30" t="n">
+        <v>192.6695</v>
+      </c>
+      <c r="AG19" s="30" t="n">
+        <v>-12.11</v>
+      </c>
+      <c r="AH19" s="30" t="n">
+        <v>219.0348</v>
+      </c>
+      <c r="AI19" s="30" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AJ19" s="30" t="n">
+        <v>234.367236</v>
+      </c>
+      <c r="AK19" s="30" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="AL19" s="30" t="n">
+        <v>211.94</v>
+      </c>
+      <c r="AM19" s="30" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="AN19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" s="30" t="n"/>
+      <c r="AP19" s="30" t="n"/>
+      <c r="AQ19" s="30" t="n"/>
+      <c r="AR19" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS19" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT19" s="30" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AU19" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-10 05:42</t>
+        </is>
+      </c>
+      <c r="AV19" s="30" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW19" s="30" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX19" s="30" t="n"/>
+      <c r="AY19" s="30" t="inlineStr"/>
+      <c r="AZ19" s="30" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA19" s="30" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB19" s="30" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC19" s="30" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD19" s="30" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE19" s="30" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 192.67</t>
+        </is>
+      </c>
+      <c r="BF19" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="BG19" s="30" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>MSFT_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C20" s="30" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D20" s="30" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E20" s="30" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="F20" s="30" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="G20" s="30" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H20" s="30" t="n"/>
+      <c r="I20" s="30" t="n"/>
+      <c r="J20" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" s="30" t="n"/>
+      <c r="L20" s="30" t="n"/>
+      <c r="M20" s="30" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="N20" s="30" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O20" s="30" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="P20" s="30" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q20" s="30" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R20" s="30" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #4 · Conf 54% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S20" s="30" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-19.2% ≤ -8.0% · EXIT URGENT</t>
+        </is>
+      </c>
+      <c r="T20" s="30" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="U20" s="30" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V20" s="30" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="W20" s="30" t="n"/>
+      <c r="X20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="30" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z20" s="30" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA20" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB20" s="30" t="n">
+        <v>487.46</v>
+      </c>
+      <c r="AC20" s="30" t="n">
+        <v>487.4599914550781</v>
+      </c>
+      <c r="AD20" s="30" t="n">
+        <v>385.94</v>
+      </c>
+      <c r="AE20" s="30" t="n">
+        <v>401.7</v>
+      </c>
+      <c r="AF20" s="30" t="n">
+        <v>374.129</v>
+      </c>
+      <c r="AG20" s="30" t="n">
+        <v>-23.25</v>
+      </c>
+      <c r="AH20" s="30" t="n">
+        <v>425.3256</v>
+      </c>
+      <c r="AI20" s="30" t="n">
+        <v>-12.75</v>
+      </c>
+      <c r="AJ20" s="30" t="n">
+        <v>455.098392</v>
+      </c>
+      <c r="AK20" s="30" t="n">
+        <v>-6.64</v>
+      </c>
+      <c r="AL20" s="30" t="n">
+        <v>492.81</v>
+      </c>
+      <c r="AM20" s="30" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="AN20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="30" t="n"/>
+      <c r="AP20" s="30" t="n"/>
+      <c r="AQ20" s="30" t="n"/>
+      <c r="AR20" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS20" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT20" s="30" t="n">
+        <v>-12.75</v>
+      </c>
+      <c r="AU20" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-10 05:42</t>
+        </is>
+      </c>
+      <c r="AV20" s="30" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW20" s="30" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX20" s="30" t="n"/>
+      <c r="AY20" s="30" t="inlineStr"/>
+      <c r="AZ20" s="30" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA20" s="30" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB20" s="30" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC20" s="30" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD20" s="30" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE20" s="30" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 374.13</t>
+        </is>
+      </c>
+      <c r="BF20" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="BG20" s="30" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="31" t="inlineStr">
+        <is>
+          <t>KO_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B21" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="F21" s="31" t="inlineStr">
+        <is>
+          <t>Coca-Cola</t>
+        </is>
+      </c>
+      <c r="G21" s="31" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H21" s="31" t="n"/>
+      <c r="I21" s="31" t="n"/>
+      <c r="J21" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="K21" s="31" t="n"/>
+      <c r="L21" s="31" t="n"/>
+      <c r="M21" s="31" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="N21" s="31" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O21" s="31" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="P21" s="31" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q21" s="31" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 11 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R21" s="31" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #5 · Conf 50% · momentum → · band STRONG · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S21" s="31" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-6.1% ≤ -5.0% · exit</t>
+        </is>
+      </c>
+      <c r="T21" s="31" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="U21" s="31" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V21" s="31" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="W21" s="31" t="n"/>
+      <c r="X21" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="31" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z21" s="31" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA21" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB21" s="31" t="n">
+        <v>86.83</v>
+      </c>
+      <c r="AC21" s="31" t="n">
+        <v>86.83000183105469</v>
+      </c>
+      <c r="AD21" s="31" t="n">
+        <v>79.93000000000001</v>
+      </c>
+      <c r="AE21" s="31" t="n">
+        <v>83.19</v>
+      </c>
+      <c r="AF21" s="31" t="n">
+        <v>77.482</v>
+      </c>
+      <c r="AG21" s="31" t="n">
+        <v>-10.77</v>
+      </c>
+      <c r="AH21" s="31" t="n">
+        <v>88.0848</v>
+      </c>
+      <c r="AI21" s="31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AJ21" s="31" t="n">
+        <v>94.250736</v>
+      </c>
+      <c r="AK21" s="31" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="AL21" s="31" t="n">
+        <v>86.56</v>
+      </c>
+      <c r="AM21" s="31" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AN21" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" s="31" t="n"/>
+      <c r="AP21" s="31" t="n"/>
+      <c r="AQ21" s="31" t="n"/>
+      <c r="AR21" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS21" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT21" s="31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AU21" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-10 05:42</t>
+        </is>
+      </c>
+      <c r="AV21" s="31" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW21" s="31" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX21" s="31" t="n"/>
+      <c r="AY21" s="31" t="inlineStr"/>
+      <c r="AZ21" s="31" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA21" s="31" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB21" s="31" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC21" s="31" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD21" s="31" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE21" s="31" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 77.48</t>
+        </is>
+      </c>
+      <c r="BF21" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="BG21" s="31" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>HON_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B22" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D22" s="31" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E22" s="31" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="F22" s="31" t="inlineStr">
+        <is>
+          <t>Honeywell</t>
+        </is>
+      </c>
+      <c r="G22" s="31" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H22" s="31" t="n"/>
+      <c r="I22" s="31" t="n"/>
+      <c r="J22" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="K22" s="31" t="n"/>
+      <c r="L22" s="31" t="n"/>
+      <c r="M22" s="31" t="n">
+        <v>76</v>
+      </c>
+      <c r="N22" s="31" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O22" s="31" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="P22" s="31" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q22" s="31" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 48 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R22" s="31" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #6 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S22" s="31" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-9.3% ≤ -8.0% · EXIT URGENT</t>
+        </is>
+      </c>
+      <c r="T22" s="31" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="U22" s="31" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V22" s="31" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="W22" s="31" t="n"/>
+      <c r="X22" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="31" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z22" s="31" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA22" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB22" s="31" t="n">
+        <v>248.12</v>
+      </c>
+      <c r="AC22" s="31" t="n">
+        <v>248.1199951171875</v>
+      </c>
+      <c r="AD22" s="31" t="n">
+        <v>220.52</v>
+      </c>
+      <c r="AE22" s="31" t="n">
+        <v>229.52</v>
+      </c>
+      <c r="AF22" s="31" t="n">
+        <v>213.769</v>
+      </c>
+      <c r="AG22" s="31" t="n">
+        <v>-13.84</v>
+      </c>
+      <c r="AH22" s="31" t="n">
+        <v>243.0216</v>
+      </c>
+      <c r="AI22" s="31" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="AJ22" s="31" t="n">
+        <v>260.0331120000001</v>
+      </c>
+      <c r="AK22" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AL22" s="31" t="n">
+        <v>248.79</v>
+      </c>
+      <c r="AM22" s="31" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="AN22" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" s="31" t="n"/>
+      <c r="AP22" s="31" t="n"/>
+      <c r="AQ22" s="31" t="n"/>
+      <c r="AR22" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS22" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT22" s="31" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="AU22" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-10 05:42</t>
+        </is>
+      </c>
+      <c r="AV22" s="31" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW22" s="31" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX22" s="31" t="n"/>
+      <c r="AY22" s="31" t="inlineStr"/>
+      <c r="AZ22" s="31" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA22" s="31" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB22" s="31" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC22" s="31" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD22" s="31" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE22" s="31" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 213.77</t>
+        </is>
+      </c>
+      <c r="BF22" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="BG22" s="31" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>AAPL_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B23" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D23" s="31" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E23" s="31" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="F23" s="31" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="G23" s="31" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H23" s="31" t="n"/>
+      <c r="I23" s="31" t="n"/>
+      <c r="J23" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="K23" s="31" t="n"/>
+      <c r="L23" s="31" t="n"/>
+      <c r="M23" s="31" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="N23" s="31" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O23" s="31" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="P23" s="31" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q23" s="31" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R23" s="31" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #7 · Conf 50% · momentum → · band STRONG · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S23" s="31" t="n"/>
+      <c r="T23" s="31" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="U23" s="31" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V23" s="31" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="W23" s="31" t="n"/>
+      <c r="X23" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="31" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z23" s="31" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA23" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB23" s="31" t="n">
+        <v>311</v>
+      </c>
+      <c r="AC23" s="31" t="n">
+        <v>311</v>
+      </c>
+      <c r="AD23" s="31" t="n">
+        <v>327.07</v>
+      </c>
+      <c r="AE23" s="31" t="n">
+        <v>340.41</v>
+      </c>
+      <c r="AF23" s="31" t="n">
+        <v>317.053</v>
+      </c>
+      <c r="AG23" s="31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH23" s="31" t="n">
+        <v>360.4392</v>
+      </c>
+      <c r="AI23" s="31" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="AJ23" s="31" t="n">
+        <v>385.669944</v>
+      </c>
+      <c r="AK23" s="31" t="n">
+        <v>24.01</v>
+      </c>
+      <c r="AL23" s="31" t="n">
+        <v>309.38</v>
+      </c>
+      <c r="AM23" s="31" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AN23" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" s="31" t="n"/>
+      <c r="AP23" s="31" t="n"/>
+      <c r="AQ23" s="31" t="n"/>
+      <c r="AR23" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS23" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT23" s="31" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="AU23" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-10 05:42</t>
+        </is>
+      </c>
+      <c r="AV23" s="31" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW23" s="31" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX23" s="31" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="AY23" s="31" t="inlineStr">
+        <is>
+          <t>🏆 QUALITY</t>
+        </is>
+      </c>
+      <c r="AZ23" s="31" t="inlineStr">
+        <is>
+          <t>🟢 HOLD</t>
+        </is>
+      </c>
+      <c r="BA23" s="31" t="inlineStr">
+        <is>
+          <t>🟢 LOW</t>
+        </is>
+      </c>
+      <c r="BB23" s="31" t="inlineStr">
+        <is>
+          <t>Compounder</t>
+        </is>
+      </c>
+      <c r="BC23" s="31" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="BD23" s="31" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="BE23" s="31" t="inlineStr">
+        <is>
+          <t>Watching @ 360.44</t>
+        </is>
+      </c>
+      <c r="BF23" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="BG23" s="31" t="inlineStr">
+        <is>
+          <t>⚪ No immediate execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>JPM_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B24" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D24" s="31" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E24" s="31" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="F24" s="31" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase</t>
+        </is>
+      </c>
+      <c r="G24" s="31" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H24" s="31" t="n"/>
+      <c r="I24" s="31" t="n"/>
+      <c r="J24" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="K24" s="31" t="n"/>
+      <c r="L24" s="31" t="n"/>
+      <c r="M24" s="31" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="N24" s="31" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O24" s="31" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="P24" s="31" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q24" s="31" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 18 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R24" s="31" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #8 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S24" s="31" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-5.0% ≤ -5.0% · exit</t>
+        </is>
+      </c>
+      <c r="T24" s="31" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="U24" s="31" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V24" s="31" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="W24" s="31" t="n"/>
+      <c r="X24" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="31" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z24" s="31" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA24" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB24" s="31" t="n">
+        <v>359.24</v>
+      </c>
+      <c r="AC24" s="31" t="n">
+        <v>359.239990234375</v>
+      </c>
+      <c r="AD24" s="31" t="n">
+        <v>334.28</v>
+      </c>
+      <c r="AE24" s="31" t="n">
+        <v>347.92</v>
+      </c>
+      <c r="AF24" s="31" t="n">
+        <v>324.045</v>
+      </c>
+      <c r="AG24" s="31" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="AH24" s="31" t="n">
+        <v>368.388</v>
+      </c>
+      <c r="AI24" s="31" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AJ24" s="31" t="n">
+        <v>394.1751600000001</v>
+      </c>
+      <c r="AK24" s="31" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="AL24" s="31" t="n">
+        <v>357.52</v>
+      </c>
+      <c r="AM24" s="31" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AN24" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" s="31" t="n"/>
+      <c r="AP24" s="31" t="n"/>
+      <c r="AQ24" s="31" t="n"/>
+      <c r="AR24" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS24" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT24" s="31" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU24" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-10 05:42</t>
+        </is>
+      </c>
+      <c r="AV24" s="31" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW24" s="31" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX24" s="31" t="n"/>
+      <c r="AY24" s="31" t="inlineStr"/>
+      <c r="AZ24" s="31" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA24" s="31" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB24" s="31" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC24" s="31" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD24" s="31" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE24" s="31" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 324.05</t>
+        </is>
+      </c>
+      <c r="BF24" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="BG24" s="31" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="31" t="inlineStr">
+        <is>
+          <t>GS_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B25" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D25" s="31" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E25" s="31" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="F25" s="31" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="G25" s="31" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H25" s="31" t="n"/>
+      <c r="I25" s="31" t="n"/>
+      <c r="J25" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="K25" s="31" t="n"/>
+      <c r="L25" s="31" t="n"/>
+      <c r="M25" s="31" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="N25" s="31" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O25" s="31" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="P25" s="31" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q25" s="31" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 9 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R25" s="31" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #9 · Conf 51% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S25" s="31" t="n"/>
+      <c r="T25" s="31" t="n">
+        <v>51</v>
+      </c>
+      <c r="U25" s="31" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V25" s="31" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="W25" s="31" t="n"/>
+      <c r="X25" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="31" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z25" s="31" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA25" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB25" s="31" t="n">
+        <v>1060.38</v>
+      </c>
+      <c r="AC25" s="31" t="n">
+        <v>1060.380004882812</v>
+      </c>
+      <c r="AD25" s="31" t="n">
+        <v>1043.92</v>
+      </c>
+      <c r="AE25" s="31" t="n">
+        <v>1086.52</v>
+      </c>
+      <c r="AF25" s="31" t="n">
+        <v>1011.959</v>
+      </c>
+      <c r="AG25" s="31" t="n">
+        <v>-4.57</v>
+      </c>
+      <c r="AH25" s="31" t="n">
+        <v>1150.4376</v>
+      </c>
+      <c r="AI25" s="31" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="AJ25" s="31" t="n">
+        <v>1230.968232</v>
+      </c>
+      <c r="AK25" s="31" t="n">
+        <v>16.09</v>
+      </c>
+      <c r="AL25" s="31" t="n">
+        <v>1052.98</v>
+      </c>
+      <c r="AM25" s="31" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AN25" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="31" t="n"/>
+      <c r="AP25" s="31" t="n"/>
+      <c r="AQ25" s="31" t="n"/>
+      <c r="AR25" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS25" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT25" s="31" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="AU25" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-10 05:42</t>
+        </is>
+      </c>
+      <c r="AV25" s="31" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW25" s="31" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX25" s="31" t="n"/>
+      <c r="AY25" s="31" t="inlineStr"/>
+      <c r="AZ25" s="31" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA25" s="31" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB25" s="31" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC25" s="31" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD25" s="31" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE25" s="31" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 1011.96</t>
+        </is>
+      </c>
+      <c r="BF25" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="BG25" s="31" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="31" t="inlineStr">
+        <is>
+          <t>MMM_USA_20260810</t>
+        </is>
+      </c>
+      <c r="B26" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D26" s="31" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E26" s="31" t="inlineStr">
+        <is>
+          <t>MMM</t>
+        </is>
+      </c>
+      <c r="F26" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="G26" s="31" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H26" s="31" t="n"/>
+      <c r="I26" s="31" t="n"/>
+      <c r="J26" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="K26" s="31" t="n"/>
+      <c r="L26" s="31" t="n"/>
+      <c r="M26" s="31" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="N26" s="31" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O26" s="31" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="P26" s="31" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q26" s="31" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 15 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R26" s="31" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 54% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S26" s="31" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-12.2% ≤ -8.0% · EXIT URGENT</t>
+        </is>
+      </c>
+      <c r="T26" s="31" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="U26" s="31" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V26" s="31" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="W26" s="31" t="n"/>
+      <c r="X26" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="31" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z26" s="31" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA26" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="AB26" s="31" t="n">
+        <v>182.08</v>
+      </c>
+      <c r="AC26" s="31" t="n">
+        <v>182.0800018310547</v>
+      </c>
+      <c r="AD26" s="31" t="n">
+        <v>156.64</v>
+      </c>
+      <c r="AE26" s="31" t="n">
+        <v>163.04</v>
+      </c>
+      <c r="AF26" s="31" t="n">
+        <v>151.848</v>
+      </c>
+      <c r="AG26" s="31" t="n">
+        <v>-16.6</v>
+      </c>
+      <c r="AH26" s="31" t="n">
+        <v>172.6272</v>
+      </c>
+      <c r="AI26" s="31" t="n">
+        <v>-5.19</v>
+      </c>
+      <c r="AJ26" s="31" t="n">
+        <v>184.711104</v>
+      </c>
+      <c r="AK26" s="31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AL26" s="31" t="n">
+        <v>181.45</v>
+      </c>
+      <c r="AM26" s="31" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AN26" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" s="31" t="n"/>
+      <c r="AP26" s="31" t="n"/>
+      <c r="AQ26" s="31" t="n"/>
+      <c r="AR26" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS26" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT26" s="31" t="n">
+        <v>-5.19</v>
+      </c>
+      <c r="AU26" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-10 05:42</t>
+        </is>
+      </c>
+      <c r="AV26" s="31" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW26" s="31" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX26" s="31" t="n"/>
+      <c r="AY26" s="31" t="inlineStr"/>
+      <c r="AZ26" s="31" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA26" s="31" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB26" s="31" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC26" s="31" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD26" s="31" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE26" s="31" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 151.85</t>
+        </is>
+      </c>
+      <c r="BF26" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="BG26" s="31" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -4154,13 +4154,13 @@
         <v>19.63</v>
       </c>
       <c r="AL2" s="30" t="n">
-        <v>377.15</v>
+        <v>382.45</v>
       </c>
       <c r="AM2" s="30" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AN2" s="30" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO2" s="30" t="n"/>
       <c r="AP2" s="30" t="n"/>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="AU2" s="30" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:01</t>
         </is>
       </c>
       <c r="AV2" s="30" t="inlineStr">
@@ -4369,13 +4369,13 @@
         <v>15</v>
       </c>
       <c r="AL3" s="31" t="n">
-        <v>369.59</v>
+        <v>368.54</v>
       </c>
       <c r="AM3" s="31" t="n">
-        <v>-0.28</v>
+        <v>0</v>
       </c>
       <c r="AN3" s="31" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO3" s="31" t="n"/>
       <c r="AP3" s="31" t="n"/>
@@ -4395,7 +4395,7 @@
       </c>
       <c r="AU3" s="31" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:01</t>
         </is>
       </c>
       <c r="AV3" s="31" t="inlineStr">
@@ -4562,7 +4562,7 @@
         </is>
       </c>
       <c r="AB4" s="32" t="n">
-        <v>202.81</v>
+        <v>219.22</v>
       </c>
       <c r="AC4" s="32" t="n">
         <v>219.2200012207031</v>
@@ -4592,13 +4592,13 @@
         <v>15</v>
       </c>
       <c r="AL4" s="32" t="n">
-        <v>211.94</v>
+        <v>219.22</v>
       </c>
       <c r="AM4" s="32" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="AN4" s="32" t="n">
-        <v>-7.49</v>
+        <v>-0</v>
       </c>
       <c r="AO4" s="32" t="n"/>
       <c r="AP4" s="32" t="n"/>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="AU4" s="32" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:01</t>
         </is>
       </c>
       <c r="AV4" s="32" t="inlineStr">
@@ -4773,7 +4773,7 @@
         </is>
       </c>
       <c r="AB5" s="32" t="n">
-        <v>341.1</v>
+        <v>359.24</v>
       </c>
       <c r="AC5" s="32" t="n">
         <v>359.239990234375</v>
@@ -4803,13 +4803,13 @@
         <v>15</v>
       </c>
       <c r="AL5" s="32" t="n">
-        <v>357.52</v>
+        <v>359.24</v>
       </c>
       <c r="AM5" s="32" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="AN5" s="32" t="n">
-        <v>-5.05</v>
+        <v>0</v>
       </c>
       <c r="AO5" s="32" t="n"/>
       <c r="AP5" s="32" t="n"/>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="AU5" s="32" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:01</t>
         </is>
       </c>
       <c r="AV5" s="32" t="inlineStr">
@@ -4984,7 +4984,7 @@
         </is>
       </c>
       <c r="AB6" s="32" t="n">
-        <v>225.02</v>
+        <v>248.12</v>
       </c>
       <c r="AC6" s="32" t="n">
         <v>248.1199951171875</v>
@@ -5014,13 +5014,13 @@
         <v>15</v>
       </c>
       <c r="AL6" s="32" t="n">
-        <v>248.79</v>
+        <v>248.12</v>
       </c>
       <c r="AM6" s="32" t="n">
-        <v>-0.27</v>
+        <v>0</v>
       </c>
       <c r="AN6" s="32" t="n">
-        <v>-9.31</v>
+        <v>0</v>
       </c>
       <c r="AO6" s="32" t="n"/>
       <c r="AP6" s="32" t="n"/>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="AU6" s="32" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:01</t>
         </is>
       </c>
       <c r="AV6" s="32" t="inlineStr">
@@ -5191,7 +5191,7 @@
         </is>
       </c>
       <c r="AB7" s="32" t="n">
-        <v>1065.22</v>
+        <v>1060.38</v>
       </c>
       <c r="AC7" s="32" t="n">
         <v>1060.380004882812</v>
@@ -5221,13 +5221,13 @@
         <v>15</v>
       </c>
       <c r="AL7" s="32" t="n">
-        <v>1052.98</v>
+        <v>1060.38</v>
       </c>
       <c r="AM7" s="32" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="AN7" s="32" t="n">
-        <v>0.46</v>
+        <v>-0</v>
       </c>
       <c r="AO7" s="32" t="n"/>
       <c r="AP7" s="32" t="n"/>
@@ -5247,7 +5247,7 @@
       </c>
       <c r="AU7" s="32" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:01</t>
         </is>
       </c>
       <c r="AV7" s="32" t="inlineStr">
@@ -5398,7 +5398,7 @@
         </is>
       </c>
       <c r="AB8" s="32" t="n">
-        <v>333.74</v>
+        <v>311</v>
       </c>
       <c r="AC8" s="32" t="n">
         <v>311</v>
@@ -5428,13 +5428,13 @@
         <v>15</v>
       </c>
       <c r="AL8" s="32" t="n">
-        <v>309.38</v>
+        <v>311</v>
       </c>
       <c r="AM8" s="32" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="AN8" s="32" t="n">
-        <v>7.31</v>
+        <v>0</v>
       </c>
       <c r="AO8" s="32" t="n"/>
       <c r="AP8" s="32" t="n"/>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AU8" s="32" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:01</t>
         </is>
       </c>
       <c r="AV8" s="32" t="inlineStr">
@@ -5627,7 +5627,7 @@
         </is>
       </c>
       <c r="AB9" s="32" t="n">
-        <v>393.82</v>
+        <v>487.46</v>
       </c>
       <c r="AC9" s="32" t="n">
         <v>487.4599914550781</v>
@@ -5657,13 +5657,13 @@
         <v>15</v>
       </c>
       <c r="AL9" s="32" t="n">
-        <v>492.81</v>
+        <v>487.46</v>
       </c>
       <c r="AM9" s="32" t="n">
-        <v>-1.09</v>
+        <v>0</v>
       </c>
       <c r="AN9" s="32" t="n">
-        <v>-19.21</v>
+        <v>0</v>
       </c>
       <c r="AO9" s="32" t="n"/>
       <c r="AP9" s="32" t="n"/>
@@ -5683,7 +5683,7 @@
       </c>
       <c r="AU9" s="32" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:01</t>
         </is>
       </c>
       <c r="AV9" s="32" t="inlineStr">
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="AB10" s="32" t="n">
-        <v>81.56</v>
+        <v>86.83</v>
       </c>
       <c r="AC10" s="32" t="n">
         <v>86.83000183105469</v>
@@ -5868,13 +5868,13 @@
         <v>14.99</v>
       </c>
       <c r="AL10" s="32" t="n">
-        <v>86.56</v>
+        <v>86.83</v>
       </c>
       <c r="AM10" s="32" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="AN10" s="32" t="n">
-        <v>-6.07</v>
+        <v>-0</v>
       </c>
       <c r="AO10" s="32" t="n"/>
       <c r="AP10" s="32" t="n"/>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="AU10" s="32" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:01</t>
         </is>
       </c>
       <c r="AV10" s="32" t="inlineStr">
@@ -6049,7 +6049,7 @@
         </is>
       </c>
       <c r="AB11" s="32" t="n">
-        <v>159.84</v>
+        <v>182.08</v>
       </c>
       <c r="AC11" s="32" t="n">
         <v>182.0800018310547</v>
@@ -6079,13 +6079,13 @@
         <v>15</v>
       </c>
       <c r="AL11" s="32" t="n">
-        <v>181.45</v>
+        <v>182.08</v>
       </c>
       <c r="AM11" s="32" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="AN11" s="32" t="n">
-        <v>-12.21</v>
+        <v>-0</v>
       </c>
       <c r="AO11" s="32" t="n"/>
       <c r="AP11" s="32" t="n"/>
@@ -6105,7 +6105,7 @@
       </c>
       <c r="AU11" s="32" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:01</t>
         </is>
       </c>
       <c r="AV11" s="32" t="inlineStr">
@@ -6260,7 +6260,7 @@
         </is>
       </c>
       <c r="AB12" s="32" t="n">
-        <v>95.04000000000001</v>
+        <v>101.06</v>
       </c>
       <c r="AC12" s="32" t="n">
         <v>101.0599975585938</v>
@@ -6290,13 +6290,13 @@
         <v>15</v>
       </c>
       <c r="AL12" s="32" t="n">
-        <v>100.86</v>
+        <v>101.06</v>
       </c>
       <c r="AM12" s="32" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="AN12" s="32" t="n">
-        <v>-5.96</v>
+        <v>0</v>
       </c>
       <c r="AO12" s="32" t="n"/>
       <c r="AP12" s="32" t="n"/>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="AU12" s="32" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:01</t>
         </is>
       </c>
       <c r="AV12" s="32" t="inlineStr">
@@ -6471,7 +6471,7 @@
         </is>
       </c>
       <c r="AB13" s="32" t="n">
-        <v>214.03</v>
+        <v>240.19</v>
       </c>
       <c r="AC13" s="32" t="n">
         <v>240.1900024414062</v>
@@ -6501,13 +6501,13 @@
         <v>15</v>
       </c>
       <c r="AL13" s="32" t="n">
-        <v>237.16</v>
+        <v>240.19</v>
       </c>
       <c r="AM13" s="32" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN13" s="32" t="n">
-        <v>-10.89</v>
+        <v>-0</v>
       </c>
       <c r="AO13" s="32" t="n"/>
       <c r="AP13" s="32" t="n"/>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="AU13" s="32" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:01</t>
         </is>
       </c>
       <c r="AV13" s="32" t="inlineStr">
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="AB14" s="32" t="n">
-        <v>338.87</v>
+        <v>353.14</v>
       </c>
       <c r="AC14" s="32" t="n">
         <v>353.1400146484375</v>
@@ -6708,13 +6708,13 @@
         <v>15</v>
       </c>
       <c r="AL14" s="32" t="n">
-        <v>348.24</v>
+        <v>353.14</v>
       </c>
       <c r="AM14" s="32" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AN14" s="32" t="n">
-        <v>-4.04</v>
+        <v>-0</v>
       </c>
       <c r="AO14" s="32" t="n"/>
       <c r="AP14" s="32" t="n"/>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="AU14" s="32" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:01</t>
         </is>
       </c>
       <c r="AV14" s="32" t="inlineStr">
@@ -6885,7 +6885,7 @@
         </is>
       </c>
       <c r="AB15" s="32" t="n">
-        <v>97.67</v>
+        <v>101.76</v>
       </c>
       <c r="AC15" s="32" t="n">
         <v>101.7600021362305</v>
@@ -6915,13 +6915,13 @@
         <v>15</v>
       </c>
       <c r="AL15" s="32" t="n">
-        <v>98.18000000000001</v>
+        <v>101.76</v>
       </c>
       <c r="AM15" s="32" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AN15" s="32" t="n">
-        <v>-4.02</v>
+        <v>-0</v>
       </c>
       <c r="AO15" s="32" t="n"/>
       <c r="AP15" s="32" t="n"/>
@@ -6941,7 +6941,7 @@
       </c>
       <c r="AU15" s="32" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:01</t>
         </is>
       </c>
       <c r="AV15" s="32" t="inlineStr">
@@ -7092,7 +7092,7 @@
         </is>
       </c>
       <c r="AB16" s="32" t="n">
-        <v>267.71</v>
+        <v>274</v>
       </c>
       <c r="AC16" s="32" t="n">
         <v>274</v>
@@ -7122,13 +7122,13 @@
         <v>15</v>
       </c>
       <c r="AL16" s="32" t="n">
-        <v>268.34</v>
+        <v>274</v>
       </c>
       <c r="AM16" s="32" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AN16" s="32" t="n">
-        <v>-2.3</v>
+        <v>0</v>
       </c>
       <c r="AO16" s="32" t="n"/>
       <c r="AP16" s="32" t="n"/>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="AU16" s="32" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:01</t>
         </is>
       </c>
       <c r="AV16" s="32" t="inlineStr">
@@ -7317,13 +7317,13 @@
         <v>12.43</v>
       </c>
       <c r="AL17" s="30" t="n">
-        <v>369.59</v>
+        <v>368.54</v>
       </c>
       <c r="AM17" s="30" t="n">
-        <v>-0.28</v>
+        <v>0</v>
       </c>
       <c r="AN17" s="30" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO17" s="30" t="n"/>
       <c r="AP17" s="30" t="n"/>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="AU17" s="30" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:01</t>
         </is>
       </c>
       <c r="AV17" s="30" t="inlineStr">
@@ -7522,13 +7522,13 @@
         <v>15.62</v>
       </c>
       <c r="AL18" s="30" t="n">
-        <v>377.15</v>
+        <v>382.45</v>
       </c>
       <c r="AM18" s="30" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AN18" s="30" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO18" s="30" t="n"/>
       <c r="AP18" s="30" t="n"/>
@@ -7546,7 +7546,7 @@
       </c>
       <c r="AU18" s="30" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:01</t>
         </is>
       </c>
       <c r="AV18" s="30" t="inlineStr">
@@ -7731,13 +7731,13 @@
         <v>6.91</v>
       </c>
       <c r="AL19" s="30" t="n">
-        <v>211.94</v>
+        <v>219.22</v>
       </c>
       <c r="AM19" s="30" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="AN19" s="30" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO19" s="30" t="n"/>
       <c r="AP19" s="30" t="n"/>
@@ -7755,7 +7755,7 @@
       </c>
       <c r="AU19" s="30" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:01</t>
         </is>
       </c>
       <c r="AV19" s="30" t="inlineStr">
@@ -7940,10 +7940,10 @@
         <v>-6.64</v>
       </c>
       <c r="AL20" s="30" t="n">
-        <v>492.81</v>
+        <v>487.46</v>
       </c>
       <c r="AM20" s="30" t="n">
-        <v>-1.09</v>
+        <v>0</v>
       </c>
       <c r="AN20" s="30" t="n">
         <v>0</v>
@@ -7964,7 +7964,7 @@
       </c>
       <c r="AU20" s="30" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:01</t>
         </is>
       </c>
       <c r="AV20" s="30" t="inlineStr">
@@ -8149,13 +8149,13 @@
         <v>8.550000000000001</v>
       </c>
       <c r="AL21" s="31" t="n">
-        <v>86.56</v>
+        <v>86.83</v>
       </c>
       <c r="AM21" s="31" t="n">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="AN21" s="31" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO21" s="31" t="n"/>
       <c r="AP21" s="31" t="n"/>
@@ -8173,7 +8173,7 @@
       </c>
       <c r="AU21" s="31" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:01</t>
         </is>
       </c>
       <c r="AV21" s="31" t="inlineStr">
@@ -8358,10 +8358,10 @@
         <v>4.8</v>
       </c>
       <c r="AL22" s="31" t="n">
-        <v>248.79</v>
+        <v>248.12</v>
       </c>
       <c r="AM22" s="31" t="n">
-        <v>-0.27</v>
+        <v>0</v>
       </c>
       <c r="AN22" s="31" t="n">
         <v>0</v>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="AU22" s="31" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:01</t>
         </is>
       </c>
       <c r="AV22" s="31" t="inlineStr">
@@ -8563,10 +8563,10 @@
         <v>24.01</v>
       </c>
       <c r="AL23" s="31" t="n">
-        <v>309.38</v>
+        <v>311</v>
       </c>
       <c r="AM23" s="31" t="n">
-        <v>0.52</v>
+        <v>0</v>
       </c>
       <c r="AN23" s="31" t="n">
         <v>0</v>
@@ -8587,7 +8587,7 @@
       </c>
       <c r="AU23" s="31" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:01</t>
         </is>
       </c>
       <c r="AV23" s="31" t="inlineStr">
@@ -8778,10 +8778,10 @@
         <v>9.720000000000001</v>
       </c>
       <c r="AL24" s="31" t="n">
-        <v>357.52</v>
+        <v>359.24</v>
       </c>
       <c r="AM24" s="31" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="AN24" s="31" t="n">
         <v>0</v>
@@ -8802,7 +8802,7 @@
       </c>
       <c r="AU24" s="31" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:01</t>
         </is>
       </c>
       <c r="AV24" s="31" t="inlineStr">
@@ -8983,13 +8983,13 @@
         <v>16.09</v>
       </c>
       <c r="AL25" s="31" t="n">
-        <v>1052.98</v>
+        <v>1060.38</v>
       </c>
       <c r="AM25" s="31" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="AN25" s="31" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO25" s="31" t="n"/>
       <c r="AP25" s="31" t="n"/>
@@ -9007,7 +9007,7 @@
       </c>
       <c r="AU25" s="31" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:01</t>
         </is>
       </c>
       <c r="AV25" s="31" t="inlineStr">
@@ -9192,13 +9192,13 @@
         <v>1.45</v>
       </c>
       <c r="AL26" s="31" t="n">
-        <v>181.45</v>
+        <v>182.08</v>
       </c>
       <c r="AM26" s="31" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="AN26" s="31" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO26" s="31" t="n"/>
       <c r="AP26" s="31" t="n"/>
@@ -9216,7 +9216,7 @@
       </c>
       <c r="AU26" s="31" t="inlineStr">
         <is>
-          <t>2026-08-10 05:42</t>
+          <t>2026-08-10 06:01</t>
         </is>
       </c>
       <c r="AV26" s="31" t="inlineStr">

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -86,12 +86,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFCC66"/>
-        <bgColor rgb="00FFCC66"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D6DCE4"/>
         <bgColor rgb="00D6DCE4"/>
       </patternFill>
@@ -100,6 +94,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E7E6E6"/>
         <bgColor rgb="00E7E6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCC66"/>
+        <bgColor rgb="00FFCC66"/>
       </patternFill>
     </fill>
     <fill>
@@ -841,12 +841,12 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>🟠 REVIEW</t>
+          <t>🟢 HOLD</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>🟢 ACTIVE</t>
+          <t>🟡 REVIEWING</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -965,12 +965,12 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
           <t>⚪ CLOSED</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>🔒 CLOSED</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr"/>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
           <t>⚪ CLOSED</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>🔒 CLOSED</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr"/>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
           <t>⚪ CLOSED</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>🔒 CLOSED</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr"/>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
           <t>⚪ CLOSED</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>🔒 CLOSED</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr"/>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
           <t>⚪ CLOSED</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>🔒 CLOSED</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr"/>
@@ -1499,12 +1499,12 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
           <t>⚪ CLOSED</t>
-        </is>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>🔒 CLOSED</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr"/>
@@ -1609,12 +1609,12 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
           <t>⚪ CLOSED</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>🔒 CLOSED</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr"/>
@@ -1719,12 +1719,12 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
           <t>⚪ CLOSED</t>
-        </is>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
-        <is>
-          <t>🔒 CLOSED</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr"/>
@@ -1829,12 +1829,12 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
           <t>⚪ CLOSED</t>
-        </is>
-      </c>
-      <c r="C17" s="9" t="inlineStr">
-        <is>
-          <t>🔒 CLOSED</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr"/>
@@ -1939,12 +1939,12 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
           <t>⚪ CLOSED</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>🔒 CLOSED</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr"/>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
           <t>⚪ CLOSED</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>🔒 CLOSED</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr"/>
@@ -2159,12 +2159,12 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
           <t>⚪ CLOSED</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>🔒 CLOSED</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr"/>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="AU2" s="30" t="inlineStr">
         <is>
-          <t>2026-08-10 06:01</t>
+          <t>2026-08-10 06:14</t>
         </is>
       </c>
       <c r="AV2" s="30" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="AU3" s="31" t="inlineStr">
         <is>
-          <t>2026-08-10 06:01</t>
+          <t>2026-08-10 06:14</t>
         </is>
       </c>
       <c r="AV3" s="31" t="inlineStr">
@@ -4635,7 +4635,7 @@
       <c r="AY4" s="32" t="inlineStr"/>
       <c r="AZ4" s="32" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA4" s="32" t="inlineStr">
@@ -4846,7 +4846,7 @@
       <c r="AY5" s="32" t="inlineStr"/>
       <c r="AZ5" s="32" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA5" s="32" t="inlineStr">
@@ -5057,7 +5057,7 @@
       <c r="AY6" s="32" t="inlineStr"/>
       <c r="AZ6" s="32" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA6" s="32" t="inlineStr">
@@ -5264,7 +5264,7 @@
       <c r="AY7" s="32" t="inlineStr"/>
       <c r="AZ7" s="32" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA7" s="32" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="AZ8" s="32" t="inlineStr">
         <is>
-          <t>🟠 REVIEW</t>
+          <t>🟢 HOLD</t>
         </is>
       </c>
       <c r="BA8" s="32" t="inlineStr">
@@ -5700,7 +5700,7 @@
       <c r="AY9" s="32" t="inlineStr"/>
       <c r="AZ9" s="32" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA9" s="32" t="inlineStr">
@@ -5911,7 +5911,7 @@
       <c r="AY10" s="32" t="inlineStr"/>
       <c r="AZ10" s="32" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA10" s="32" t="inlineStr">
@@ -6122,7 +6122,7 @@
       <c r="AY11" s="32" t="inlineStr"/>
       <c r="AZ11" s="32" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA11" s="32" t="inlineStr">
@@ -6333,7 +6333,7 @@
       <c r="AY12" s="32" t="inlineStr"/>
       <c r="AZ12" s="32" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA12" s="32" t="inlineStr">
@@ -6544,7 +6544,7 @@
       <c r="AY13" s="32" t="inlineStr"/>
       <c r="AZ13" s="32" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA13" s="32" t="inlineStr">
@@ -6751,7 +6751,7 @@
       <c r="AY14" s="32" t="inlineStr"/>
       <c r="AZ14" s="32" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA14" s="32" t="inlineStr">
@@ -6958,7 +6958,7 @@
       <c r="AY15" s="32" t="inlineStr"/>
       <c r="AZ15" s="32" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA15" s="32" t="inlineStr">
@@ -7165,7 +7165,7 @@
       <c r="AY16" s="32" t="inlineStr"/>
       <c r="AZ16" s="32" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>—</t>
         </is>
       </c>
       <c r="BA16" s="32" t="inlineStr">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="AU17" s="30" t="inlineStr">
         <is>
-          <t>2026-08-10 06:01</t>
+          <t>2026-08-10 06:14</t>
         </is>
       </c>
       <c r="AV17" s="30" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="AU18" s="30" t="inlineStr">
         <is>
-          <t>2026-08-10 06:01</t>
+          <t>2026-08-10 06:14</t>
         </is>
       </c>
       <c r="AV18" s="30" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="AU19" s="30" t="inlineStr">
         <is>
-          <t>2026-08-10 06:01</t>
+          <t>2026-08-10 06:14</t>
         </is>
       </c>
       <c r="AV19" s="30" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="AU20" s="30" t="inlineStr">
         <is>
-          <t>2026-08-10 06:01</t>
+          <t>2026-08-10 06:14</t>
         </is>
       </c>
       <c r="AV20" s="30" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="AU21" s="31" t="inlineStr">
         <is>
-          <t>2026-08-10 06:01</t>
+          <t>2026-08-10 06:14</t>
         </is>
       </c>
       <c r="AV21" s="31" t="inlineStr">
@@ -8382,7 +8382,7 @@
       </c>
       <c r="AU22" s="31" t="inlineStr">
         <is>
-          <t>2026-08-10 06:01</t>
+          <t>2026-08-10 06:14</t>
         </is>
       </c>
       <c r="AV22" s="31" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="AU23" s="31" t="inlineStr">
         <is>
-          <t>2026-08-10 06:01</t>
+          <t>2026-08-10 06:14</t>
         </is>
       </c>
       <c r="AV23" s="31" t="inlineStr">
@@ -8802,7 +8802,7 @@
       </c>
       <c r="AU24" s="31" t="inlineStr">
         <is>
-          <t>2026-08-10 06:01</t>
+          <t>2026-08-10 06:14</t>
         </is>
       </c>
       <c r="AV24" s="31" t="inlineStr">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="AU25" s="31" t="inlineStr">
         <is>
-          <t>2026-08-10 06:01</t>
+          <t>2026-08-10 06:14</t>
         </is>
       </c>
       <c r="AV25" s="31" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="AU26" s="31" t="inlineStr">
         <is>
-          <t>2026-08-10 06:01</t>
+          <t>2026-08-10 06:14</t>
         </is>
       </c>
       <c r="AV26" s="31" t="inlineStr">

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -4182,7 +4182,7 @@
       </c>
       <c r="AU2" s="30" t="inlineStr">
         <is>
-          <t>2026-08-10 06:14</t>
+          <t>2026-08-10 06:18</t>
         </is>
       </c>
       <c r="AV2" s="30" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="AU3" s="31" t="inlineStr">
         <is>
-          <t>2026-08-10 06:14</t>
+          <t>2026-08-10 06:18</t>
         </is>
       </c>
       <c r="AV3" s="31" t="inlineStr">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="AU17" s="30" t="inlineStr">
         <is>
-          <t>2026-08-10 06:14</t>
+          <t>2026-08-10 06:18</t>
         </is>
       </c>
       <c r="AV17" s="30" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="AU18" s="30" t="inlineStr">
         <is>
-          <t>2026-08-10 06:14</t>
+          <t>2026-08-10 06:18</t>
         </is>
       </c>
       <c r="AV18" s="30" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="AU19" s="30" t="inlineStr">
         <is>
-          <t>2026-08-10 06:14</t>
+          <t>2026-08-10 06:18</t>
         </is>
       </c>
       <c r="AV19" s="30" t="inlineStr">
@@ -7964,7 +7964,7 @@
       </c>
       <c r="AU20" s="30" t="inlineStr">
         <is>
-          <t>2026-08-10 06:14</t>
+          <t>2026-08-10 06:18</t>
         </is>
       </c>
       <c r="AV20" s="30" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="AU21" s="31" t="inlineStr">
         <is>
-          <t>2026-08-10 06:14</t>
+          <t>2026-08-10 06:18</t>
         </is>
       </c>
       <c r="AV21" s="31" t="inlineStr">
@@ -8382,7 +8382,7 @@
       </c>
       <c r="AU22" s="31" t="inlineStr">
         <is>
-          <t>2026-08-10 06:14</t>
+          <t>2026-08-10 06:18</t>
         </is>
       </c>
       <c r="AV22" s="31" t="inlineStr">
@@ -8587,7 +8587,7 @@
       </c>
       <c r="AU23" s="31" t="inlineStr">
         <is>
-          <t>2026-08-10 06:14</t>
+          <t>2026-08-10 06:18</t>
         </is>
       </c>
       <c r="AV23" s="31" t="inlineStr">
@@ -8802,7 +8802,7 @@
       </c>
       <c r="AU24" s="31" t="inlineStr">
         <is>
-          <t>2026-08-10 06:14</t>
+          <t>2026-08-10 06:18</t>
         </is>
       </c>
       <c r="AV24" s="31" t="inlineStr">
@@ -9007,7 +9007,7 @@
       </c>
       <c r="AU25" s="31" t="inlineStr">
         <is>
-          <t>2026-08-10 06:14</t>
+          <t>2026-08-10 06:18</t>
         </is>
       </c>
       <c r="AV25" s="31" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="AU26" s="31" t="inlineStr">
         <is>
-          <t>2026-08-10 06:14</t>
+          <t>2026-08-10 06:18</t>
         </is>
       </c>
       <c r="AV26" s="31" t="inlineStr">

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -965,7 +965,7 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -4064,12 +4064,8 @@
       <c r="J2" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="K2" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" s="30" t="n">
-        <v>0</v>
-      </c>
+      <c r="K2" s="30" t="n"/>
+      <c r="L2" s="30" t="n"/>
       <c r="M2" s="30" t="n">
         <v>79.3</v>
       </c>
@@ -4091,7 +4087,7 @@
       </c>
       <c r="R2" s="30" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 1→1 · Conf 57% · band HOLD · 14d left · → BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank #1 · Conf 57% · band HOLD · 14d left · → BUY</t>
         </is>
       </c>
       <c r="S2" s="30" t="n"/>
@@ -4182,7 +4178,7 @@
       </c>
       <c r="AU2" s="30" t="inlineStr">
         <is>
-          <t>2026-08-10 06:18</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
       <c r="AV2" s="30" t="inlineStr">
@@ -4279,12 +4275,8 @@
       <c r="J3" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="K3" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" s="31" t="n">
-        <v>0</v>
-      </c>
+      <c r="K3" s="31" t="n"/>
+      <c r="L3" s="31" t="n"/>
       <c r="M3" s="31" t="n">
         <v>86.5</v>
       </c>
@@ -4306,7 +4298,7 @@
       </c>
       <c r="R3" s="31" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-3.7%) · Rank → 2→2 · Conf 54% · band STRONG · 14d left · → HOLD</t>
+          <t>🟢 BUY (Δ-3.7%) · Rank #2 · Conf 54% · band STRONG · 14d left · → HOLD</t>
         </is>
       </c>
       <c r="S3" s="31" t="n"/>
@@ -4395,7 +4387,7 @@
       </c>
       <c r="AU3" s="31" t="inlineStr">
         <is>
-          <t>2026-08-10 06:18</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
       <c r="AV3" s="31" t="inlineStr">
@@ -4498,12 +4490,8 @@
       <c r="J4" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="K4" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="L4" s="32" t="n">
-        <v>0</v>
-      </c>
+      <c r="K4" s="32" t="n"/>
+      <c r="L4" s="32" t="n"/>
       <c r="M4" s="32" t="n">
         <v>67.5</v>
       </c>
@@ -4525,7 +4513,7 @@
       </c>
       <c r="R4" s="32" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 3→3 · Conf 47% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+          <t>🔴 AVOID · Rank #3 · Conf 47% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="S4" s="32" t="inlineStr">
@@ -4618,7 +4606,7 @@
       </c>
       <c r="AU4" s="32" t="inlineStr">
         <is>
-          <t>2026-08-10 06:01</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
       <c r="AV4" s="32" t="inlineStr">
@@ -4635,7 +4623,7 @@
       <c r="AY4" s="32" t="inlineStr"/>
       <c r="AZ4" s="32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="BA4" s="32" t="inlineStr">
@@ -4709,12 +4697,8 @@
       <c r="J5" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="K5" s="32" t="n">
-        <v>4</v>
-      </c>
-      <c r="L5" s="32" t="n">
-        <v>0</v>
-      </c>
+      <c r="K5" s="32" t="n"/>
+      <c r="L5" s="32" t="n"/>
       <c r="M5" s="32" t="n">
         <v>78.40000000000001</v>
       </c>
@@ -4736,7 +4720,7 @@
       </c>
       <c r="R5" s="32" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 4→4 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+          <t>🔴 AVOID · Rank #4 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="S5" s="32" t="inlineStr">
@@ -4829,7 +4813,7 @@
       </c>
       <c r="AU5" s="32" t="inlineStr">
         <is>
-          <t>2026-08-10 06:01</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
       <c r="AV5" s="32" t="inlineStr">
@@ -4846,7 +4830,7 @@
       <c r="AY5" s="32" t="inlineStr"/>
       <c r="AZ5" s="32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="BA5" s="32" t="inlineStr">
@@ -4920,12 +4904,8 @@
       <c r="J6" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="K6" s="32" t="n">
-        <v>5</v>
-      </c>
-      <c r="L6" s="32" t="n">
-        <v>0</v>
-      </c>
+      <c r="K6" s="32" t="n"/>
+      <c r="L6" s="32" t="n"/>
       <c r="M6" s="32" t="n">
         <v>76</v>
       </c>
@@ -4947,7 +4927,7 @@
       </c>
       <c r="R6" s="32" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 5→5 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+          <t>🔴 AVOID · Rank #5 · Conf 50% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="S6" s="32" t="inlineStr">
@@ -5040,7 +5020,7 @@
       </c>
       <c r="AU6" s="32" t="inlineStr">
         <is>
-          <t>2026-08-10 06:01</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
       <c r="AV6" s="32" t="inlineStr">
@@ -5057,7 +5037,7 @@
       <c r="AY6" s="32" t="inlineStr"/>
       <c r="AZ6" s="32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="BA6" s="32" t="inlineStr">
@@ -5131,12 +5111,8 @@
       <c r="J7" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="K7" s="32" t="n">
-        <v>6</v>
-      </c>
-      <c r="L7" s="32" t="n">
-        <v>0</v>
-      </c>
+      <c r="K7" s="32" t="n"/>
+      <c r="L7" s="32" t="n"/>
       <c r="M7" s="32" t="n">
         <v>66.3</v>
       </c>
@@ -5158,7 +5134,7 @@
       </c>
       <c r="R7" s="32" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 6→6 · Conf 51% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
+          <t>🔴 AVOID · Rank #6 · Conf 51% · band HOLD · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="S7" s="32" t="n"/>
@@ -5247,7 +5223,7 @@
       </c>
       <c r="AU7" s="32" t="inlineStr">
         <is>
-          <t>2026-08-10 06:01</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
       <c r="AV7" s="32" t="inlineStr">
@@ -5264,7 +5240,7 @@
       <c r="AY7" s="32" t="inlineStr"/>
       <c r="AZ7" s="32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="BA7" s="32" t="inlineStr">
@@ -5338,12 +5314,8 @@
       <c r="J8" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="K8" s="32" t="n">
-        <v>7</v>
-      </c>
-      <c r="L8" s="32" t="n">
-        <v>0</v>
-      </c>
+      <c r="K8" s="32" t="n"/>
+      <c r="L8" s="32" t="n"/>
       <c r="M8" s="32" t="n">
         <v>83.5</v>
       </c>
@@ -5365,7 +5337,7 @@
       </c>
       <c r="R8" s="32" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 7→7 · Conf 50% · band STRONG · 6d left · → EXIT (rotate to TRV)</t>
+          <t>🔴 AVOID · Rank #7 · Conf 50% · band STRONG · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="S8" s="32" t="n"/>
@@ -5454,7 +5426,7 @@
       </c>
       <c r="AU8" s="32" t="inlineStr">
         <is>
-          <t>2026-08-10 06:01</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
       <c r="AV8" s="32" t="inlineStr">
@@ -5563,12 +5535,8 @@
       <c r="J9" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="K9" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="L9" s="32" t="n">
-        <v>0</v>
-      </c>
+      <c r="K9" s="32" t="n"/>
+      <c r="L9" s="32" t="n"/>
       <c r="M9" s="32" t="n">
         <v>79.5</v>
       </c>
@@ -5590,7 +5558,7 @@
       </c>
       <c r="R9" s="32" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 8→8 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
+          <t>🔴 AVOID · Rank #8 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="S9" s="32" t="inlineStr">
@@ -5683,7 +5651,7 @@
       </c>
       <c r="AU9" s="32" t="inlineStr">
         <is>
-          <t>2026-08-10 06:01</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
       <c r="AV9" s="32" t="inlineStr">
@@ -5700,7 +5668,7 @@
       <c r="AY9" s="32" t="inlineStr"/>
       <c r="AZ9" s="32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="BA9" s="32" t="inlineStr">
@@ -5774,12 +5742,8 @@
       <c r="J10" s="32" t="n">
         <v>9</v>
       </c>
-      <c r="K10" s="32" t="n">
-        <v>9</v>
-      </c>
-      <c r="L10" s="32" t="n">
-        <v>0</v>
-      </c>
+      <c r="K10" s="32" t="n"/>
+      <c r="L10" s="32" t="n"/>
       <c r="M10" s="32" t="n">
         <v>84.09999999999999</v>
       </c>
@@ -5801,7 +5765,7 @@
       </c>
       <c r="R10" s="32" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 9→9 · Conf 50% · band STRONG · 6d left · → EXIT (rotate to TRV)</t>
+          <t>🔴 AVOID · Rank #9 · Conf 50% · band STRONG · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="S10" s="32" t="inlineStr">
@@ -5894,7 +5858,7 @@
       </c>
       <c r="AU10" s="32" t="inlineStr">
         <is>
-          <t>2026-08-10 06:01</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
       <c r="AV10" s="32" t="inlineStr">
@@ -5911,7 +5875,7 @@
       <c r="AY10" s="32" t="inlineStr"/>
       <c r="AZ10" s="32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="BA10" s="32" t="inlineStr">
@@ -5985,12 +5949,8 @@
       <c r="J11" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="K11" s="32" t="n">
-        <v>10</v>
-      </c>
-      <c r="L11" s="32" t="n">
-        <v>0</v>
-      </c>
+      <c r="K11" s="32" t="n"/>
+      <c r="L11" s="32" t="n"/>
       <c r="M11" s="32" t="n">
         <v>76.2</v>
       </c>
@@ -6012,7 +5972,7 @@
       </c>
       <c r="R11" s="32" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 10→10 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
+          <t>🔴 AVOID · Rank #10 · Conf 54% · band HOLD · 58d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="S11" s="32" t="inlineStr">
@@ -6105,7 +6065,7 @@
       </c>
       <c r="AU11" s="32" t="inlineStr">
         <is>
-          <t>2026-08-10 06:01</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
       <c r="AV11" s="32" t="inlineStr">
@@ -6122,7 +6082,7 @@
       <c r="AY11" s="32" t="inlineStr"/>
       <c r="AZ11" s="32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="BA11" s="32" t="inlineStr">
@@ -6196,12 +6156,8 @@
       <c r="J12" s="32" t="n">
         <v>11</v>
       </c>
-      <c r="K12" s="32" t="n">
-        <v>11</v>
-      </c>
-      <c r="L12" s="32" t="n">
-        <v>0</v>
-      </c>
+      <c r="K12" s="32" t="n"/>
+      <c r="L12" s="32" t="n"/>
       <c r="M12" s="32" t="n">
         <v>52.5</v>
       </c>
@@ -6223,7 +6179,7 @@
       </c>
       <c r="R12" s="32" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 11→11 · Conf 29% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+          <t>🔴 AVOID · Rank #11 · Conf 29% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="S12" s="32" t="inlineStr">
@@ -6316,7 +6272,7 @@
       </c>
       <c r="AU12" s="32" t="inlineStr">
         <is>
-          <t>2026-08-10 06:01</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
       <c r="AV12" s="32" t="inlineStr">
@@ -6333,7 +6289,7 @@
       <c r="AY12" s="32" t="inlineStr"/>
       <c r="AZ12" s="32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="BA12" s="32" t="inlineStr">
@@ -6407,12 +6363,8 @@
       <c r="J13" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="K13" s="32" t="n">
-        <v>12</v>
-      </c>
-      <c r="L13" s="32" t="n">
-        <v>0</v>
-      </c>
+      <c r="K13" s="32" t="n"/>
+      <c r="L13" s="32" t="n"/>
       <c r="M13" s="32" t="n">
         <v>52.6</v>
       </c>
@@ -6434,7 +6386,7 @@
       </c>
       <c r="R13" s="32" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 12→12 · Conf 31% · band EXIT · 58d left · → EXIT (rotate to TRV)</t>
+          <t>🔴 AVOID · Rank #12 · Conf 31% · band EXIT · 58d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="S13" s="32" t="inlineStr">
@@ -6527,7 +6479,7 @@
       </c>
       <c r="AU13" s="32" t="inlineStr">
         <is>
-          <t>2026-08-10 06:01</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
       <c r="AV13" s="32" t="inlineStr">
@@ -6544,7 +6496,7 @@
       <c r="AY13" s="32" t="inlineStr"/>
       <c r="AZ13" s="32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="BA13" s="32" t="inlineStr">
@@ -6618,12 +6570,8 @@
       <c r="J14" s="32" t="n">
         <v>13</v>
       </c>
-      <c r="K14" s="32" t="n">
-        <v>13</v>
-      </c>
-      <c r="L14" s="32" t="n">
-        <v>0</v>
-      </c>
+      <c r="K14" s="32" t="n"/>
+      <c r="L14" s="32" t="n"/>
       <c r="M14" s="32" t="n">
         <v>52.8</v>
       </c>
@@ -6645,7 +6593,7 @@
       </c>
       <c r="R14" s="32" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 13→13 · Conf 35% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+          <t>🔴 AVOID · Rank #13 · Conf 35% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="S14" s="32" t="n"/>
@@ -6734,7 +6682,7 @@
       </c>
       <c r="AU14" s="32" t="inlineStr">
         <is>
-          <t>2026-08-10 06:01</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
       <c r="AV14" s="32" t="inlineStr">
@@ -6751,7 +6699,7 @@
       <c r="AY14" s="32" t="inlineStr"/>
       <c r="AZ14" s="32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="BA14" s="32" t="inlineStr">
@@ -6825,12 +6773,8 @@
       <c r="J15" s="32" t="n">
         <v>14</v>
       </c>
-      <c r="K15" s="32" t="n">
-        <v>14</v>
-      </c>
-      <c r="L15" s="32" t="n">
-        <v>0</v>
-      </c>
+      <c r="K15" s="32" t="n"/>
+      <c r="L15" s="32" t="n"/>
       <c r="M15" s="32" t="n">
         <v>52.8</v>
       </c>
@@ -6852,7 +6796,7 @@
       </c>
       <c r="R15" s="32" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 14→14 · Conf 35% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+          <t>🔴 AVOID · Rank #14 · Conf 35% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="S15" s="32" t="n"/>
@@ -6941,7 +6885,7 @@
       </c>
       <c r="AU15" s="32" t="inlineStr">
         <is>
-          <t>2026-08-10 06:01</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
       <c r="AV15" s="32" t="inlineStr">
@@ -6958,7 +6902,7 @@
       <c r="AY15" s="32" t="inlineStr"/>
       <c r="AZ15" s="32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="BA15" s="32" t="inlineStr">
@@ -7032,12 +6976,8 @@
       <c r="J16" s="32" t="n">
         <v>15</v>
       </c>
-      <c r="K16" s="32" t="n">
-        <v>15</v>
-      </c>
-      <c r="L16" s="32" t="n">
-        <v>0</v>
-      </c>
+      <c r="K16" s="32" t="n"/>
+      <c r="L16" s="32" t="n"/>
       <c r="M16" s="32" t="n">
         <v>52.5</v>
       </c>
@@ -7059,7 +6999,7 @@
       </c>
       <c r="R16" s="32" t="inlineStr">
         <is>
-          <t>🔴 AVOID · Rank → 15→15 · Conf 28% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
+          <t>🔴 AVOID · Rank #15 · Conf 28% · band EXIT · 6d left · → EXIT (rotate to TRV)</t>
         </is>
       </c>
       <c r="S16" s="32" t="n"/>
@@ -7148,7 +7088,7 @@
       </c>
       <c r="AU16" s="32" t="inlineStr">
         <is>
-          <t>2026-08-10 06:01</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
       <c r="AV16" s="32" t="inlineStr">
@@ -7165,7 +7105,7 @@
       <c r="AY16" s="32" t="inlineStr"/>
       <c r="AZ16" s="32" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="BA16" s="32" t="inlineStr">
@@ -7341,7 +7281,7 @@
       </c>
       <c r="AU17" s="30" t="inlineStr">
         <is>
-          <t>2026-08-10 06:18</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
       <c r="AV17" s="30" t="inlineStr">
@@ -7546,7 +7486,7 @@
       </c>
       <c r="AU18" s="30" t="inlineStr">
         <is>
-          <t>2026-08-10 06:18</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
       <c r="AV18" s="30" t="inlineStr">
@@ -7755,7 +7695,7 @@
       </c>
       <c r="AU19" s="30" t="inlineStr">
         <is>
-          <t>2026-08-10 06:18</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
       <c r="AV19" s="30" t="inlineStr">
@@ -7964,7 +7904,7 @@
       </c>
       <c r="AU20" s="30" t="inlineStr">
         <is>
-          <t>2026-08-10 06:18</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
       <c r="AV20" s="30" t="inlineStr">
@@ -8173,7 +8113,7 @@
       </c>
       <c r="AU21" s="31" t="inlineStr">
         <is>
-          <t>2026-08-10 06:18</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
       <c r="AV21" s="31" t="inlineStr">
@@ -8382,7 +8322,7 @@
       </c>
       <c r="AU22" s="31" t="inlineStr">
         <is>
-          <t>2026-08-10 06:18</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
       <c r="AV22" s="31" t="inlineStr">
@@ -8587,7 +8527,7 @@
       </c>
       <c r="AU23" s="31" t="inlineStr">
         <is>
-          <t>2026-08-10 06:18</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
       <c r="AV23" s="31" t="inlineStr">
@@ -8802,7 +8742,7 @@
       </c>
       <c r="AU24" s="31" t="inlineStr">
         <is>
-          <t>2026-08-10 06:18</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
       <c r="AV24" s="31" t="inlineStr">
@@ -9007,7 +8947,7 @@
       </c>
       <c r="AU25" s="31" t="inlineStr">
         <is>
-          <t>2026-08-10 06:18</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
       <c r="AV25" s="31" t="inlineStr">
@@ -9216,7 +9156,7 @@
       </c>
       <c r="AU26" s="31" t="inlineStr">
         <is>
-          <t>2026-08-10 06:18</t>
+          <t>2026-08-10 06:27</t>
         </is>
       </c>
       <c r="AV26" s="31" t="inlineStr">

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -86,14 +86,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D6DCE4"/>
-        <bgColor rgb="00D6DCE4"/>
+        <fgColor rgb="00E7E6E6"/>
+        <bgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E7E6E6"/>
-        <bgColor rgb="00E7E6E6"/>
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -602,7 +602,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS USA PORTFOLIO · as of 2026-08-10</t>
+          <t>AEGIS USA PORTFOLIO · as of 2026-08-11</t>
         </is>
       </c>
     </row>
@@ -841,29 +841,17 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>🟢 HOLD</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>🟡 REVIEWING</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>Review @ 333.74</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>🟠 No execution · investigate + decide</t>
-        </is>
-      </c>
+          <t>⚪ ARTIFACT</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr"/>
+      <c r="E8" s="9" t="inlineStr"/>
+      <c r="F8" s="9" t="inlineStr"/>
       <c r="G8" s="9" t="inlineStr">
         <is>
           <t>R2</t>
@@ -899,22 +887,22 @@
       </c>
       <c r="N8" s="9" t="inlineStr">
         <is>
-          <t>🟡 MEDIUM</t>
+          <t>⚪ CLOSED</t>
         </is>
       </c>
       <c r="O8" s="9" t="inlineStr">
         <is>
-          <t>Premature Exit?</t>
+          <t>Artifact</t>
         </is>
       </c>
       <c r="P8" s="9" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="Q8" s="9" t="inlineStr">
         <is>
-          <t>5 DAYS</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="R8" s="9" t="inlineStr">
@@ -965,12 +953,12 @@
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr"/>
@@ -1016,12 +1004,12 @@
       </c>
       <c r="O9" s="9" t="inlineStr">
         <is>
-          <t>Clean Exit</t>
+          <t>Artifact</t>
         </is>
       </c>
       <c r="P9" s="9" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="Q9" s="9" t="inlineStr">
@@ -1071,12 +1059,12 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr"/>
@@ -1122,12 +1110,12 @@
       </c>
       <c r="O10" s="9" t="inlineStr">
         <is>
-          <t>Clean Exit</t>
+          <t>Artifact</t>
         </is>
       </c>
       <c r="P10" s="9" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="Q10" s="9" t="inlineStr">
@@ -1177,12 +1165,12 @@
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr"/>
@@ -1228,12 +1216,12 @@
       </c>
       <c r="O11" s="9" t="inlineStr">
         <is>
-          <t>Clean Exit</t>
+          <t>Artifact</t>
         </is>
       </c>
       <c r="P11" s="9" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="Q11" s="9" t="inlineStr">
@@ -1283,12 +1271,12 @@
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr"/>
@@ -1334,12 +1322,12 @@
       </c>
       <c r="O12" s="9" t="inlineStr">
         <is>
-          <t>Clean Exit</t>
+          <t>Artifact</t>
         </is>
       </c>
       <c r="P12" s="9" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="Q12" s="9" t="inlineStr">
@@ -1389,12 +1377,12 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr"/>
@@ -1440,12 +1428,12 @@
       </c>
       <c r="O13" s="9" t="inlineStr">
         <is>
-          <t>Clean Exit</t>
+          <t>Artifact</t>
         </is>
       </c>
       <c r="P13" s="9" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="Q13" s="9" t="inlineStr">
@@ -1499,12 +1487,12 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr"/>
@@ -1550,12 +1538,12 @@
       </c>
       <c r="O14" s="9" t="inlineStr">
         <is>
-          <t>Clean Exit</t>
+          <t>Artifact</t>
         </is>
       </c>
       <c r="P14" s="9" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="Q14" s="9" t="inlineStr">
@@ -1609,12 +1597,12 @@
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="D15" s="9" t="inlineStr"/>
@@ -1660,12 +1648,12 @@
       </c>
       <c r="O15" s="9" t="inlineStr">
         <is>
-          <t>Clean Exit</t>
+          <t>Artifact</t>
         </is>
       </c>
       <c r="P15" s="9" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="Q15" s="9" t="inlineStr">
@@ -1719,12 +1707,12 @@
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="D16" s="9" t="inlineStr"/>
@@ -1770,12 +1758,12 @@
       </c>
       <c r="O16" s="9" t="inlineStr">
         <is>
-          <t>Clean Exit</t>
+          <t>Artifact</t>
         </is>
       </c>
       <c r="P16" s="9" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="Q16" s="9" t="inlineStr">
@@ -1829,12 +1817,12 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="D17" s="9" t="inlineStr"/>
@@ -1880,12 +1868,12 @@
       </c>
       <c r="O17" s="9" t="inlineStr">
         <is>
-          <t>Clean Exit</t>
+          <t>Artifact</t>
         </is>
       </c>
       <c r="P17" s="9" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="Q17" s="9" t="inlineStr">
@@ -1939,12 +1927,12 @@
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="D18" s="9" t="inlineStr"/>
@@ -1990,12 +1978,12 @@
       </c>
       <c r="O18" s="9" t="inlineStr">
         <is>
-          <t>Clean Exit</t>
+          <t>Artifact</t>
         </is>
       </c>
       <c r="P18" s="9" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="Q18" s="9" t="inlineStr">
@@ -2049,12 +2037,12 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="D19" s="9" t="inlineStr"/>
@@ -2100,12 +2088,12 @@
       </c>
       <c r="O19" s="9" t="inlineStr">
         <is>
-          <t>Clean Exit</t>
+          <t>Artifact</t>
         </is>
       </c>
       <c r="P19" s="9" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="Q19" s="9" t="inlineStr">
@@ -2159,12 +2147,12 @@
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>⚪ CLOSED</t>
+          <t>⚪ ARTIFACT</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr"/>
@@ -2210,12 +2198,12 @@
       </c>
       <c r="O20" s="9" t="inlineStr">
         <is>
-          <t>Clean Exit</t>
+          <t>Artifact</t>
         </is>
       </c>
       <c r="P20" s="9" t="inlineStr">
         <is>
-          <t>CLOSED</t>
+          <t>IGNORE</t>
         </is>
       </c>
       <c r="Q20" s="9" t="inlineStr">
@@ -2284,37 +2272,37 @@
       </c>
       <c r="E21" s="16" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F21" s="16" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+      <c r="G21" s="16" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="H21" s="16" t="inlineStr">
+        <is>
+          <t>✅ AGREE</t>
+        </is>
+      </c>
+      <c r="I21" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J21" s="16" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K21" s="16" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>✅ AGREE</t>
-        </is>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="K21" s="16" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L21" s="16" t="n"/>
@@ -2398,37 +2386,37 @@
       </c>
       <c r="E22" s="22" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+      <c r="G22" s="22" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>✅ AGREE</t>
+        </is>
+      </c>
+      <c r="I22" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J22" s="22" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K22" s="22" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F22" s="22" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-      <c r="G22" s="22" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="H22" s="22" t="inlineStr">
-        <is>
-          <t>✅ AGREE</t>
-        </is>
-      </c>
-      <c r="I22" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J22" s="22" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="K22" s="22" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L22" s="22" t="n"/>
@@ -2512,37 +2500,37 @@
       </c>
       <c r="E23" s="16" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+      <c r="G23" s="16" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H23" s="16" t="inlineStr">
+        <is>
+          <t>✅ AGREE</t>
+        </is>
+      </c>
+      <c r="I23" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J23" s="16" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K23" s="16" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="H23" s="16" t="inlineStr">
-        <is>
-          <t>✅ AGREE</t>
-        </is>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J23" s="16" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="K23" s="16" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L23" s="16" t="n"/>
@@ -2626,37 +2614,37 @@
       </c>
       <c r="E24" s="16" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+      <c r="G24" s="16" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H24" s="16" t="inlineStr">
+        <is>
+          <t>✅ AGREE</t>
+        </is>
+      </c>
+      <c r="I24" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J24" s="16" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K24" s="16" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>✅ AGREE</t>
-        </is>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J24" s="16" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="K24" s="16" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L24" s="16" t="n"/>
@@ -2740,37 +2728,37 @@
       </c>
       <c r="E25" s="16" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F25" s="16" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+      <c r="G25" s="16" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H25" s="16" t="inlineStr">
+        <is>
+          <t>✅ AGREE</t>
+        </is>
+      </c>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J25" s="16" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K25" s="16" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="H25" s="16" t="inlineStr">
-        <is>
-          <t>✅ AGREE</t>
-        </is>
-      </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J25" s="16" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="K25" s="16" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L25" s="16" t="n"/>
@@ -2858,37 +2846,37 @@
       </c>
       <c r="E26" s="16" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+      <c r="G26" s="16" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H26" s="16" t="inlineStr">
+        <is>
+          <t>✅ AGREE</t>
+        </is>
+      </c>
+      <c r="I26" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J26" s="16" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K26" s="16" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>✅ AGREE</t>
-        </is>
-      </c>
-      <c r="I26" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J26" s="16" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="K26" s="16" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L26" s="16" t="n"/>
@@ -2976,37 +2964,37 @@
       </c>
       <c r="E27" s="22" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>✅ AGREE</t>
+        </is>
+      </c>
+      <c r="I27" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J27" s="22" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K27" s="22" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F27" s="22" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-      <c r="G27" s="22" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="H27" s="22" t="inlineStr">
-        <is>
-          <t>✅ AGREE</t>
-        </is>
-      </c>
-      <c r="I27" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J27" s="22" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="K27" s="22" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L27" s="22" t="n"/>
@@ -3094,37 +3082,37 @@
       </c>
       <c r="E28" s="22" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>✅ AGREE</t>
+        </is>
+      </c>
+      <c r="I28" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J28" s="22" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K28" s="22" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F28" s="22" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-      <c r="G28" s="22" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="H28" s="22" t="inlineStr">
-        <is>
-          <t>✅ AGREE</t>
-        </is>
-      </c>
-      <c r="I28" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J28" s="22" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="K28" s="22" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L28" s="22" t="n"/>
@@ -3212,7 +3200,7 @@
       </c>
       <c r="E29" s="22" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -3242,7 +3230,7 @@
       </c>
       <c r="K29" s="22" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="L29" s="22" t="n"/>
@@ -3332,37 +3320,37 @@
       </c>
       <c r="E30" s="22" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+      <c r="G30" s="22" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H30" s="22" t="inlineStr">
+        <is>
+          <t>✅ AGREE</t>
+        </is>
+      </c>
+      <c r="I30" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J30" s="22" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K30" s="22" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F30" s="22" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-      <c r="G30" s="22" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="H30" s="22" t="inlineStr">
-        <is>
-          <t>✅ AGREE</t>
-        </is>
-      </c>
-      <c r="I30" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J30" s="22" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="K30" s="22" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L30" s="22" t="n"/>
@@ -3450,37 +3438,37 @@
       </c>
       <c r="E31" s="22" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+      <c r="G31" s="22" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H31" s="22" t="inlineStr">
+        <is>
+          <t>✅ AGREE</t>
+        </is>
+      </c>
+      <c r="I31" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J31" s="22" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K31" s="22" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F31" s="22" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-      <c r="G31" s="22" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="H31" s="22" t="inlineStr">
-        <is>
-          <t>✅ AGREE</t>
-        </is>
-      </c>
-      <c r="I31" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J31" s="22" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="K31" s="22" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L31" s="22" t="n"/>
@@ -3564,37 +3552,37 @@
       </c>
       <c r="E32" s="22" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+      <c r="G32" s="22" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="H32" s="22" t="inlineStr">
+        <is>
+          <t>✅ AGREE</t>
+        </is>
+      </c>
+      <c r="I32" s="22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J32" s="22" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="K32" s="22" t="inlineStr">
+        <is>
           <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="F32" s="22" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-      <c r="G32" s="22" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="H32" s="22" t="inlineStr">
-        <is>
-          <t>✅ AGREE</t>
-        </is>
-      </c>
-      <c r="I32" s="22" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J32" s="22" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="K32" s="22" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L32" s="22" t="n"/>
@@ -3673,7 +3661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG26"/>
+  <dimension ref="A1:BG38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -9212,6 +9200,2514 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="30" t="inlineStr">
+        <is>
+          <t>TRV_USA_20260811</t>
+        </is>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C27" s="30" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D27" s="30" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E27" s="30" t="inlineStr">
+        <is>
+          <t>TRV</t>
+        </is>
+      </c>
+      <c r="F27" s="30" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="G27" s="30" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H27" s="30" t="n"/>
+      <c r="I27" s="30" t="n"/>
+      <c r="J27" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="30" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="N27" s="30" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O27" s="30" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="P27" s="30" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q27" s="30" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R27" s="30" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 1→1 · Conf 57% · band HOLD · 14d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S27" s="30" t="n"/>
+      <c r="T27" s="30" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="U27" s="30" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V27" s="30" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="W27" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="X27" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="30" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z27" s="30" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA27" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB27" s="30" t="n">
+        <v>382.45</v>
+      </c>
+      <c r="AC27" s="30" t="n">
+        <v>382.4500122070312</v>
+      </c>
+      <c r="AD27" s="30" t="n">
+        <v>365.29</v>
+      </c>
+      <c r="AE27" s="30" t="n">
+        <v>372.67</v>
+      </c>
+      <c r="AF27" s="30" t="n">
+        <v>346.84</v>
+      </c>
+      <c r="AG27" s="30" t="n">
+        <v>-9.31</v>
+      </c>
+      <c r="AH27" s="30" t="n">
+        <v>413.26</v>
+      </c>
+      <c r="AI27" s="30" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="AJ27" s="30" t="n">
+        <v>457.54</v>
+      </c>
+      <c r="AK27" s="30" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="AL27" s="30" t="n">
+        <v>382.45</v>
+      </c>
+      <c r="AM27" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" s="30" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO27" s="30" t="n"/>
+      <c r="AP27" s="30" t="n"/>
+      <c r="AQ27" s="30" t="inlineStr">
+        <is>
+          <t>Momentum · Value · Trend</t>
+        </is>
+      </c>
+      <c r="AR27" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS27" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT27" s="30" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="AU27" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:16</t>
+        </is>
+      </c>
+      <c r="AV27" s="30" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW27" s="30" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX27" s="30" t="n"/>
+      <c r="AY27" s="30" t="inlineStr"/>
+      <c r="AZ27" s="30" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA27" s="30" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB27" s="30" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC27" s="30" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD27" s="30" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE27" s="30" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 346.84</t>
+        </is>
+      </c>
+      <c r="BF27" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="BG27" s="30" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="31" t="inlineStr">
+        <is>
+          <t>V_USA_20260811</t>
+        </is>
+      </c>
+      <c r="B28" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D28" s="31" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E28" s="31" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F28" s="31" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="G28" s="31" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H28" s="31" t="n"/>
+      <c r="I28" s="31" t="n"/>
+      <c r="J28" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="31" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="N28" s="31" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O28" s="31" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="P28" s="31" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q28" s="31" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R28" s="31" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-3.7%) · Rank → 2→2 · Conf 54% · band STRONG · 14d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S28" s="31" t="n"/>
+      <c r="T28" s="31" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="U28" s="31" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V28" s="31" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="W28" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="X28" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="31" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z28" s="31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA28" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB28" s="31" t="n">
+        <v>368.54</v>
+      </c>
+      <c r="AC28" s="31" t="n">
+        <v>368.5400085449219</v>
+      </c>
+      <c r="AD28" s="31" t="n">
+        <v>364.85</v>
+      </c>
+      <c r="AE28" s="31" t="n">
+        <v>372.23</v>
+      </c>
+      <c r="AF28" s="31" t="n">
+        <v>350.11</v>
+      </c>
+      <c r="AG28" s="31" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH28" s="31" t="n">
+        <v>398.02</v>
+      </c>
+      <c r="AI28" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ28" s="31" t="n">
+        <v>423.82</v>
+      </c>
+      <c r="AK28" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL28" s="31" t="n">
+        <v>368.54</v>
+      </c>
+      <c r="AM28" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" s="31" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO28" s="31" t="n"/>
+      <c r="AP28" s="31" t="n"/>
+      <c r="AQ28" s="31" t="inlineStr">
+        <is>
+          <t>Momentum · Trend · Quality</t>
+        </is>
+      </c>
+      <c r="AR28" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS28" s="31" t="n"/>
+      <c r="AT28" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:16</t>
+        </is>
+      </c>
+      <c r="AV28" s="31" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW28" s="31" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX28" s="31" t="n"/>
+      <c r="AY28" s="31" t="inlineStr"/>
+      <c r="AZ28" s="31" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA28" s="31" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB28" s="31" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC28" s="31" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD28" s="31" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE28" s="31" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 350.11</t>
+        </is>
+      </c>
+      <c r="BF28" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="BG28" s="31" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="30" t="inlineStr">
+        <is>
+          <t>V_USA_20260811</t>
+        </is>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C29" s="30" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D29" s="30" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E29" s="30" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F29" s="30" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="G29" s="30" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H29" s="30" t="n"/>
+      <c r="I29" s="30" t="n"/>
+      <c r="J29" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" s="30" t="n"/>
+      <c r="L29" s="30" t="n"/>
+      <c r="M29" s="30" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="N29" s="30" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O29" s="30" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="P29" s="30" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q29" s="30" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R29" s="30" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #1 · Conf 54% · momentum → · band STRONG · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S29" s="30" t="n"/>
+      <c r="T29" s="30" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="U29" s="30" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V29" s="30" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="W29" s="30" t="n"/>
+      <c r="X29" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="30" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z29" s="30" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA29" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB29" s="30" t="n">
+        <v>368.54</v>
+      </c>
+      <c r="AC29" s="30" t="n">
+        <v>368.5400085449219</v>
+      </c>
+      <c r="AD29" s="30" t="n">
+        <v>351.39</v>
+      </c>
+      <c r="AE29" s="30" t="n">
+        <v>365.73</v>
+      </c>
+      <c r="AF29" s="30" t="n">
+        <v>340.632</v>
+      </c>
+      <c r="AG29" s="30" t="n">
+        <v>-7.57</v>
+      </c>
+      <c r="AH29" s="30" t="n">
+        <v>387.2448000000001</v>
+      </c>
+      <c r="AI29" s="30" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="AJ29" s="30" t="n">
+        <v>414.3519360000001</v>
+      </c>
+      <c r="AK29" s="30" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="AL29" s="30" t="n">
+        <v>368.54</v>
+      </c>
+      <c r="AM29" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" s="30" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO29" s="30" t="n"/>
+      <c r="AP29" s="30" t="n"/>
+      <c r="AQ29" s="30" t="n"/>
+      <c r="AR29" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS29" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT29" s="30" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="AU29" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:16</t>
+        </is>
+      </c>
+      <c r="AV29" s="30" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW29" s="30" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX29" s="30" t="n"/>
+      <c r="AY29" s="30" t="inlineStr"/>
+      <c r="AZ29" s="30" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA29" s="30" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB29" s="30" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC29" s="30" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD29" s="30" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE29" s="30" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 340.63</t>
+        </is>
+      </c>
+      <c r="BF29" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="BG29" s="30" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="30" t="inlineStr">
+        <is>
+          <t>TRV_USA_20260811</t>
+        </is>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C30" s="30" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D30" s="30" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E30" s="30" t="inlineStr">
+        <is>
+          <t>TRV</t>
+        </is>
+      </c>
+      <c r="F30" s="30" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="G30" s="30" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H30" s="30" t="n"/>
+      <c r="I30" s="30" t="n"/>
+      <c r="J30" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" s="30" t="n"/>
+      <c r="L30" s="30" t="n"/>
+      <c r="M30" s="30" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="N30" s="30" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O30" s="30" t="n">
+        <v>56.1</v>
+      </c>
+      <c r="P30" s="30" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q30" s="30" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R30" s="30" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 57% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S30" s="30" t="n"/>
+      <c r="T30" s="30" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="U30" s="30" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V30" s="30" t="n">
+        <v>58.8</v>
+      </c>
+      <c r="W30" s="30" t="n"/>
+      <c r="X30" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="30" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z30" s="30" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA30" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB30" s="30" t="n">
+        <v>382.45</v>
+      </c>
+      <c r="AC30" s="30" t="n">
+        <v>382.4500122070312</v>
+      </c>
+      <c r="AD30" s="30" t="n">
+        <v>365.29</v>
+      </c>
+      <c r="AE30" s="30" t="n">
+        <v>372.67</v>
+      </c>
+      <c r="AF30" s="30" t="n">
+        <v>350.531</v>
+      </c>
+      <c r="AG30" s="30" t="n">
+        <v>-8.35</v>
+      </c>
+      <c r="AH30" s="30" t="n">
+        <v>413.26</v>
+      </c>
+      <c r="AI30" s="30" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="AJ30" s="30" t="n">
+        <v>442.1882</v>
+      </c>
+      <c r="AK30" s="30" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="AL30" s="30" t="n">
+        <v>382.45</v>
+      </c>
+      <c r="AM30" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" s="30" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO30" s="30" t="n"/>
+      <c r="AP30" s="30" t="n"/>
+      <c r="AQ30" s="30" t="n"/>
+      <c r="AR30" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS30" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT30" s="30" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="AU30" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:16</t>
+        </is>
+      </c>
+      <c r="AV30" s="30" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW30" s="30" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX30" s="30" t="n"/>
+      <c r="AY30" s="30" t="inlineStr"/>
+      <c r="AZ30" s="30" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA30" s="30" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB30" s="30" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC30" s="30" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD30" s="30" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE30" s="30" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 350.53</t>
+        </is>
+      </c>
+      <c r="BF30" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="BG30" s="30" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t>NVDA_USA_20260811</t>
+        </is>
+      </c>
+      <c r="B31" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C31" s="30" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D31" s="30" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E31" s="30" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="F31" s="30" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="G31" s="30" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H31" s="30" t="n"/>
+      <c r="I31" s="30" t="n"/>
+      <c r="J31" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="K31" s="30" t="n"/>
+      <c r="L31" s="30" t="n"/>
+      <c r="M31" s="30" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="N31" s="30" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O31" s="30" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="P31" s="30" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q31" s="30" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 21 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R31" s="30" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #3 · Conf 47% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S31" s="30" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-7.5% ≤ -5.0% · exit</t>
+        </is>
+      </c>
+      <c r="T31" s="30" t="n">
+        <v>47.3</v>
+      </c>
+      <c r="U31" s="30" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V31" s="30" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="W31" s="30" t="n"/>
+      <c r="X31" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="30" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z31" s="30" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA31" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB31" s="30" t="n">
+        <v>219.22</v>
+      </c>
+      <c r="AC31" s="30" t="n">
+        <v>219.2200012207031</v>
+      </c>
+      <c r="AD31" s="30" t="n">
+        <v>198.75</v>
+      </c>
+      <c r="AE31" s="30" t="n">
+        <v>206.87</v>
+      </c>
+      <c r="AF31" s="30" t="n">
+        <v>192.6695</v>
+      </c>
+      <c r="AG31" s="30" t="n">
+        <v>-12.11</v>
+      </c>
+      <c r="AH31" s="30" t="n">
+        <v>219.0348</v>
+      </c>
+      <c r="AI31" s="30" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AJ31" s="30" t="n">
+        <v>234.367236</v>
+      </c>
+      <c r="AK31" s="30" t="n">
+        <v>6.91</v>
+      </c>
+      <c r="AL31" s="30" t="n">
+        <v>219.22</v>
+      </c>
+      <c r="AM31" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" s="30" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO31" s="30" t="n"/>
+      <c r="AP31" s="30" t="n"/>
+      <c r="AQ31" s="30" t="n"/>
+      <c r="AR31" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS31" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT31" s="30" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AU31" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:16</t>
+        </is>
+      </c>
+      <c r="AV31" s="30" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW31" s="30" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX31" s="30" t="n"/>
+      <c r="AY31" s="30" t="inlineStr"/>
+      <c r="AZ31" s="30" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA31" s="30" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB31" s="30" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC31" s="30" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD31" s="30" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE31" s="30" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 192.67</t>
+        </is>
+      </c>
+      <c r="BF31" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="BG31" s="30" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="30" t="inlineStr">
+        <is>
+          <t>MSFT_USA_20260811</t>
+        </is>
+      </c>
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C32" s="30" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D32" s="30" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E32" s="30" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="F32" s="30" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="G32" s="30" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="H32" s="30" t="n"/>
+      <c r="I32" s="30" t="n"/>
+      <c r="J32" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="K32" s="30" t="n"/>
+      <c r="L32" s="30" t="n"/>
+      <c r="M32" s="30" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="N32" s="30" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O32" s="30" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="P32" s="30" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q32" s="30" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R32" s="30" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #4 · Conf 54% · momentum → · band HOLD · 91d left · → BUY</t>
+        </is>
+      </c>
+      <c r="S32" s="30" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-19.2% ≤ -8.0% · EXIT URGENT</t>
+        </is>
+      </c>
+      <c r="T32" s="30" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="U32" s="30" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V32" s="30" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="W32" s="30" t="n"/>
+      <c r="X32" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="30" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z32" s="30" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA32" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB32" s="30" t="n">
+        <v>487.46</v>
+      </c>
+      <c r="AC32" s="30" t="n">
+        <v>487.4599914550781</v>
+      </c>
+      <c r="AD32" s="30" t="n">
+        <v>385.94</v>
+      </c>
+      <c r="AE32" s="30" t="n">
+        <v>401.7</v>
+      </c>
+      <c r="AF32" s="30" t="n">
+        <v>374.129</v>
+      </c>
+      <c r="AG32" s="30" t="n">
+        <v>-23.25</v>
+      </c>
+      <c r="AH32" s="30" t="n">
+        <v>425.3256</v>
+      </c>
+      <c r="AI32" s="30" t="n">
+        <v>-12.75</v>
+      </c>
+      <c r="AJ32" s="30" t="n">
+        <v>455.098392</v>
+      </c>
+      <c r="AK32" s="30" t="n">
+        <v>-6.64</v>
+      </c>
+      <c r="AL32" s="30" t="n">
+        <v>487.46</v>
+      </c>
+      <c r="AM32" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" s="30" t="n"/>
+      <c r="AP32" s="30" t="n"/>
+      <c r="AQ32" s="30" t="n"/>
+      <c r="AR32" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS32" s="30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT32" s="30" t="n">
+        <v>-12.75</v>
+      </c>
+      <c r="AU32" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:16</t>
+        </is>
+      </c>
+      <c r="AV32" s="30" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW32" s="30" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX32" s="30" t="n"/>
+      <c r="AY32" s="30" t="inlineStr"/>
+      <c r="AZ32" s="30" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA32" s="30" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB32" s="30" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC32" s="30" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD32" s="30" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE32" s="30" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 374.13</t>
+        </is>
+      </c>
+      <c r="BF32" s="30" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="BG32" s="30" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="31" t="inlineStr">
+        <is>
+          <t>KO_USA_20260811</t>
+        </is>
+      </c>
+      <c r="B33" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C33" s="31" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D33" s="31" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E33" s="31" t="inlineStr">
+        <is>
+          <t>KO</t>
+        </is>
+      </c>
+      <c r="F33" s="31" t="inlineStr">
+        <is>
+          <t>Coca-Cola</t>
+        </is>
+      </c>
+      <c r="G33" s="31" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H33" s="31" t="n"/>
+      <c r="I33" s="31" t="n"/>
+      <c r="J33" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="K33" s="31" t="n"/>
+      <c r="L33" s="31" t="n"/>
+      <c r="M33" s="31" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="N33" s="31" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O33" s="31" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="P33" s="31" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q33" s="31" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 11 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R33" s="31" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #5 · Conf 50% · momentum → · band STRONG · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S33" s="31" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-6.1% ≤ -5.0% · exit</t>
+        </is>
+      </c>
+      <c r="T33" s="31" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="U33" s="31" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V33" s="31" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="W33" s="31" t="n"/>
+      <c r="X33" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="31" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z33" s="31" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA33" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB33" s="31" t="n">
+        <v>86.83</v>
+      </c>
+      <c r="AC33" s="31" t="n">
+        <v>86.83000183105469</v>
+      </c>
+      <c r="AD33" s="31" t="n">
+        <v>79.93000000000001</v>
+      </c>
+      <c r="AE33" s="31" t="n">
+        <v>83.19</v>
+      </c>
+      <c r="AF33" s="31" t="n">
+        <v>77.482</v>
+      </c>
+      <c r="AG33" s="31" t="n">
+        <v>-10.77</v>
+      </c>
+      <c r="AH33" s="31" t="n">
+        <v>88.0848</v>
+      </c>
+      <c r="AI33" s="31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AJ33" s="31" t="n">
+        <v>94.250736</v>
+      </c>
+      <c r="AK33" s="31" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="AL33" s="31" t="n">
+        <v>86.83</v>
+      </c>
+      <c r="AM33" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" s="31" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO33" s="31" t="n"/>
+      <c r="AP33" s="31" t="n"/>
+      <c r="AQ33" s="31" t="n"/>
+      <c r="AR33" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS33" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT33" s="31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AU33" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:16</t>
+        </is>
+      </c>
+      <c r="AV33" s="31" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW33" s="31" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX33" s="31" t="n"/>
+      <c r="AY33" s="31" t="inlineStr"/>
+      <c r="AZ33" s="31" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA33" s="31" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB33" s="31" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC33" s="31" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD33" s="31" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE33" s="31" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 77.48</t>
+        </is>
+      </c>
+      <c r="BF33" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="BG33" s="31" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="31" t="inlineStr">
+        <is>
+          <t>HON_USA_20260811</t>
+        </is>
+      </c>
+      <c r="B34" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C34" s="31" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D34" s="31" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E34" s="31" t="inlineStr">
+        <is>
+          <t>HON</t>
+        </is>
+      </c>
+      <c r="F34" s="31" t="inlineStr">
+        <is>
+          <t>Honeywell</t>
+        </is>
+      </c>
+      <c r="G34" s="31" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H34" s="31" t="n"/>
+      <c r="I34" s="31" t="n"/>
+      <c r="J34" s="31" t="n">
+        <v>6</v>
+      </c>
+      <c r="K34" s="31" t="n"/>
+      <c r="L34" s="31" t="n"/>
+      <c r="M34" s="31" t="n">
+        <v>76</v>
+      </c>
+      <c r="N34" s="31" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O34" s="31" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="P34" s="31" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q34" s="31" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 48 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R34" s="31" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #6 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S34" s="31" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-9.3% ≤ -8.0% · EXIT URGENT</t>
+        </is>
+      </c>
+      <c r="T34" s="31" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="U34" s="31" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V34" s="31" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="W34" s="31" t="n"/>
+      <c r="X34" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="31" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z34" s="31" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA34" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB34" s="31" t="n">
+        <v>248.12</v>
+      </c>
+      <c r="AC34" s="31" t="n">
+        <v>248.1199951171875</v>
+      </c>
+      <c r="AD34" s="31" t="n">
+        <v>220.52</v>
+      </c>
+      <c r="AE34" s="31" t="n">
+        <v>229.52</v>
+      </c>
+      <c r="AF34" s="31" t="n">
+        <v>213.769</v>
+      </c>
+      <c r="AG34" s="31" t="n">
+        <v>-13.84</v>
+      </c>
+      <c r="AH34" s="31" t="n">
+        <v>243.0216</v>
+      </c>
+      <c r="AI34" s="31" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="AJ34" s="31" t="n">
+        <v>260.0331120000001</v>
+      </c>
+      <c r="AK34" s="31" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AL34" s="31" t="n">
+        <v>248.12</v>
+      </c>
+      <c r="AM34" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="31" t="n"/>
+      <c r="AP34" s="31" t="n"/>
+      <c r="AQ34" s="31" t="n"/>
+      <c r="AR34" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS34" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT34" s="31" t="n">
+        <v>-2.05</v>
+      </c>
+      <c r="AU34" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:16</t>
+        </is>
+      </c>
+      <c r="AV34" s="31" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW34" s="31" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX34" s="31" t="n"/>
+      <c r="AY34" s="31" t="inlineStr"/>
+      <c r="AZ34" s="31" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA34" s="31" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB34" s="31" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC34" s="31" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD34" s="31" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE34" s="31" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 213.77</t>
+        </is>
+      </c>
+      <c r="BF34" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="BG34" s="31" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="31" t="inlineStr">
+        <is>
+          <t>AAPL_USA_20260811</t>
+        </is>
+      </c>
+      <c r="B35" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C35" s="31" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D35" s="31" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E35" s="31" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="F35" s="31" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="G35" s="31" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H35" s="31" t="n"/>
+      <c r="I35" s="31" t="n"/>
+      <c r="J35" s="31" t="n">
+        <v>7</v>
+      </c>
+      <c r="K35" s="31" t="n"/>
+      <c r="L35" s="31" t="n"/>
+      <c r="M35" s="31" t="n">
+        <v>83.5</v>
+      </c>
+      <c r="N35" s="31" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O35" s="31" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="P35" s="31" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q35" s="31" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R35" s="31" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #7 · Conf 50% · momentum → · band STRONG · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S35" s="31" t="n"/>
+      <c r="T35" s="31" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="U35" s="31" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V35" s="31" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="W35" s="31" t="n"/>
+      <c r="X35" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="31" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z35" s="31" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA35" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB35" s="31" t="n">
+        <v>311</v>
+      </c>
+      <c r="AC35" s="31" t="n">
+        <v>311</v>
+      </c>
+      <c r="AD35" s="31" t="n">
+        <v>327.07</v>
+      </c>
+      <c r="AE35" s="31" t="n">
+        <v>340.41</v>
+      </c>
+      <c r="AF35" s="31" t="n">
+        <v>317.053</v>
+      </c>
+      <c r="AG35" s="31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH35" s="31" t="n">
+        <v>360.4392</v>
+      </c>
+      <c r="AI35" s="31" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="AJ35" s="31" t="n">
+        <v>385.669944</v>
+      </c>
+      <c r="AK35" s="31" t="n">
+        <v>24.01</v>
+      </c>
+      <c r="AL35" s="31" t="n">
+        <v>311</v>
+      </c>
+      <c r="AM35" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" s="31" t="n"/>
+      <c r="AP35" s="31" t="n"/>
+      <c r="AQ35" s="31" t="n"/>
+      <c r="AR35" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS35" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT35" s="31" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="AU35" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:16</t>
+        </is>
+      </c>
+      <c r="AV35" s="31" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW35" s="31" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX35" s="31" t="n">
+        <v>82.59999999999999</v>
+      </c>
+      <c r="AY35" s="31" t="inlineStr">
+        <is>
+          <t>🏆 QUALITY</t>
+        </is>
+      </c>
+      <c r="AZ35" s="31" t="inlineStr">
+        <is>
+          <t>🟢 HOLD</t>
+        </is>
+      </c>
+      <c r="BA35" s="31" t="inlineStr">
+        <is>
+          <t>🟢 LOW</t>
+        </is>
+      </c>
+      <c r="BB35" s="31" t="inlineStr">
+        <is>
+          <t>Compounder</t>
+        </is>
+      </c>
+      <c r="BC35" s="31" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="BD35" s="31" t="inlineStr">
+        <is>
+          <t>30 DAYS</t>
+        </is>
+      </c>
+      <c r="BE35" s="31" t="inlineStr">
+        <is>
+          <t>Watching @ 360.44</t>
+        </is>
+      </c>
+      <c r="BF35" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="BG35" s="31" t="inlineStr">
+        <is>
+          <t>⚪ No immediate execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="31" t="inlineStr">
+        <is>
+          <t>JPM_USA_20260811</t>
+        </is>
+      </c>
+      <c r="B36" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C36" s="31" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D36" s="31" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E36" s="31" t="inlineStr">
+        <is>
+          <t>JPM</t>
+        </is>
+      </c>
+      <c r="F36" s="31" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase</t>
+        </is>
+      </c>
+      <c r="G36" s="31" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H36" s="31" t="n"/>
+      <c r="I36" s="31" t="n"/>
+      <c r="J36" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="K36" s="31" t="n"/>
+      <c r="L36" s="31" t="n"/>
+      <c r="M36" s="31" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="N36" s="31" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O36" s="31" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="P36" s="31" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q36" s="31" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 18 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R36" s="31" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #8 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S36" s="31" t="inlineStr">
+        <is>
+          <t>WARNING·STOP_LOSS_HIT·-5.0% ≤ -5.0% · exit</t>
+        </is>
+      </c>
+      <c r="T36" s="31" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="U36" s="31" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V36" s="31" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="W36" s="31" t="n"/>
+      <c r="X36" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="31" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z36" s="31" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA36" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB36" s="31" t="n">
+        <v>359.24</v>
+      </c>
+      <c r="AC36" s="31" t="n">
+        <v>359.239990234375</v>
+      </c>
+      <c r="AD36" s="31" t="n">
+        <v>334.28</v>
+      </c>
+      <c r="AE36" s="31" t="n">
+        <v>347.92</v>
+      </c>
+      <c r="AF36" s="31" t="n">
+        <v>324.045</v>
+      </c>
+      <c r="AG36" s="31" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="AH36" s="31" t="n">
+        <v>368.388</v>
+      </c>
+      <c r="AI36" s="31" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AJ36" s="31" t="n">
+        <v>394.1751600000001</v>
+      </c>
+      <c r="AK36" s="31" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="AL36" s="31" t="n">
+        <v>359.24</v>
+      </c>
+      <c r="AM36" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="31" t="n"/>
+      <c r="AP36" s="31" t="n"/>
+      <c r="AQ36" s="31" t="n"/>
+      <c r="AR36" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS36" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT36" s="31" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU36" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:16</t>
+        </is>
+      </c>
+      <c r="AV36" s="31" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW36" s="31" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX36" s="31" t="n"/>
+      <c r="AY36" s="31" t="inlineStr"/>
+      <c r="AZ36" s="31" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA36" s="31" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB36" s="31" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC36" s="31" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD36" s="31" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE36" s="31" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 324.05</t>
+        </is>
+      </c>
+      <c r="BF36" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="BG36" s="31" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="31" t="inlineStr">
+        <is>
+          <t>GS_USA_20260811</t>
+        </is>
+      </c>
+      <c r="B37" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C37" s="31" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D37" s="31" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E37" s="31" t="inlineStr">
+        <is>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="F37" s="31" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="G37" s="31" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H37" s="31" t="n"/>
+      <c r="I37" s="31" t="n"/>
+      <c r="J37" s="31" t="n">
+        <v>9</v>
+      </c>
+      <c r="K37" s="31" t="n"/>
+      <c r="L37" s="31" t="n"/>
+      <c r="M37" s="31" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="N37" s="31" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O37" s="31" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="P37" s="31" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q37" s="31" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 9 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R37" s="31" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #9 · Conf 51% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S37" s="31" t="n"/>
+      <c r="T37" s="31" t="n">
+        <v>51</v>
+      </c>
+      <c r="U37" s="31" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V37" s="31" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="W37" s="31" t="n"/>
+      <c r="X37" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="31" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z37" s="31" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA37" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB37" s="31" t="n">
+        <v>1060.38</v>
+      </c>
+      <c r="AC37" s="31" t="n">
+        <v>1060.380004882812</v>
+      </c>
+      <c r="AD37" s="31" t="n">
+        <v>1043.92</v>
+      </c>
+      <c r="AE37" s="31" t="n">
+        <v>1086.52</v>
+      </c>
+      <c r="AF37" s="31" t="n">
+        <v>1011.959</v>
+      </c>
+      <c r="AG37" s="31" t="n">
+        <v>-4.57</v>
+      </c>
+      <c r="AH37" s="31" t="n">
+        <v>1150.4376</v>
+      </c>
+      <c r="AI37" s="31" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="AJ37" s="31" t="n">
+        <v>1230.968232</v>
+      </c>
+      <c r="AK37" s="31" t="n">
+        <v>16.09</v>
+      </c>
+      <c r="AL37" s="31" t="n">
+        <v>1060.38</v>
+      </c>
+      <c r="AM37" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" s="31" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO37" s="31" t="n"/>
+      <c r="AP37" s="31" t="n"/>
+      <c r="AQ37" s="31" t="n"/>
+      <c r="AR37" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS37" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT37" s="31" t="n">
+        <v>8.49</v>
+      </c>
+      <c r="AU37" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:16</t>
+        </is>
+      </c>
+      <c r="AV37" s="31" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW37" s="31" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX37" s="31" t="n"/>
+      <c r="AY37" s="31" t="inlineStr"/>
+      <c r="AZ37" s="31" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA37" s="31" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB37" s="31" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC37" s="31" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD37" s="31" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE37" s="31" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 1011.96</t>
+        </is>
+      </c>
+      <c r="BF37" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="BG37" s="31" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="31" t="inlineStr">
+        <is>
+          <t>MMM_USA_20260811</t>
+        </is>
+      </c>
+      <c r="B38" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C38" s="31" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="D38" s="31" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="E38" s="31" t="inlineStr">
+        <is>
+          <t>MMM</t>
+        </is>
+      </c>
+      <c r="F38" s="31" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="G38" s="31" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H38" s="31" t="n"/>
+      <c r="I38" s="31" t="n"/>
+      <c r="J38" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="K38" s="31" t="n"/>
+      <c r="L38" s="31" t="n"/>
+      <c r="M38" s="31" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="N38" s="31" t="inlineStr">
+        <is>
+          <t>🟢</t>
+        </is>
+      </c>
+      <c r="O38" s="31" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="P38" s="31" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="Q38" s="31" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 15 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R38" s="31" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 54% · momentum → · band HOLD · 91d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S38" s="31" t="inlineStr">
+        <is>
+          <t>CRITICAL·DEEP_LOSS·-12.2% ≤ -8.0% · EXIT URGENT</t>
+        </is>
+      </c>
+      <c r="T38" s="31" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="U38" s="31" t="inlineStr">
+        <is>
+          <t>Calibrated</t>
+        </is>
+      </c>
+      <c r="V38" s="31" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="W38" s="31" t="n"/>
+      <c r="X38" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="31" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z38" s="31" t="n">
+        <v>91</v>
+      </c>
+      <c r="AA38" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB38" s="31" t="n">
+        <v>182.08</v>
+      </c>
+      <c r="AC38" s="31" t="n">
+        <v>182.0800018310547</v>
+      </c>
+      <c r="AD38" s="31" t="n">
+        <v>156.64</v>
+      </c>
+      <c r="AE38" s="31" t="n">
+        <v>163.04</v>
+      </c>
+      <c r="AF38" s="31" t="n">
+        <v>151.848</v>
+      </c>
+      <c r="AG38" s="31" t="n">
+        <v>-16.6</v>
+      </c>
+      <c r="AH38" s="31" t="n">
+        <v>172.6272</v>
+      </c>
+      <c r="AI38" s="31" t="n">
+        <v>-5.19</v>
+      </c>
+      <c r="AJ38" s="31" t="n">
+        <v>184.711104</v>
+      </c>
+      <c r="AK38" s="31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AL38" s="31" t="n">
+        <v>182.08</v>
+      </c>
+      <c r="AM38" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" s="31" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AO38" s="31" t="n"/>
+      <c r="AP38" s="31" t="n"/>
+      <c r="AQ38" s="31" t="n"/>
+      <c r="AR38" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS38" s="31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT38" s="31" t="n">
+        <v>-5.19</v>
+      </c>
+      <c r="AU38" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:16</t>
+        </is>
+      </c>
+      <c r="AV38" s="31" t="inlineStr">
+        <is>
+          <t>LargeCap (S&amp;P 500)</t>
+        </is>
+      </c>
+      <c r="AW38" s="31" t="inlineStr">
+        <is>
+          <t>🆕 NEW</t>
+        </is>
+      </c>
+      <c r="AX38" s="31" t="n"/>
+      <c r="AY38" s="31" t="inlineStr"/>
+      <c r="AZ38" s="31" t="inlineStr">
+        <is>
+          <t>🟠 PROTECT</t>
+        </is>
+      </c>
+      <c r="BA38" s="31" t="inlineStr">
+        <is>
+          <t>🟡 MEDIUM</t>
+        </is>
+      </c>
+      <c r="BB38" s="31" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="BC38" s="31" t="inlineStr">
+        <is>
+          <t>TIGHTEN STOP</t>
+        </is>
+      </c>
+      <c r="BD38" s="31" t="inlineStr">
+        <is>
+          <t>TOMORROW</t>
+        </is>
+      </c>
+      <c r="BE38" s="31" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 151.85</t>
+        </is>
+      </c>
+      <c r="BF38" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="BG38" s="31" t="inlineStr">
+        <is>
+          <t>🟡 Normal window · 10:00-14:30 IST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -4014,7 +4014,7 @@
     <row r="2">
       <c r="A2" s="30" t="inlineStr">
         <is>
-          <t>TRV_USA_20260810</t>
+          <t>USA-R2-TRV-20260810-9cd25d</t>
         </is>
       </c>
       <c r="B2" s="30" t="inlineStr">
@@ -4144,7 +4144,7 @@
         <v>0</v>
       </c>
       <c r="AN2" s="30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO2" s="30" t="n"/>
       <c r="AP2" s="30" t="n"/>
@@ -4225,7 +4225,7 @@
     <row r="3">
       <c r="A3" s="31" t="inlineStr">
         <is>
-          <t>V_USA_20260810</t>
+          <t>USA-R2-V-20260810-69160d</t>
         </is>
       </c>
       <c r="B3" s="31" t="inlineStr">
@@ -4355,7 +4355,7 @@
         <v>0</v>
       </c>
       <c r="AN3" s="31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO3" s="31" t="n"/>
       <c r="AP3" s="31" t="n"/>
@@ -4434,7 +4434,7 @@
     <row r="4">
       <c r="A4" s="32" t="inlineStr">
         <is>
-          <t>NVDA_USA_20260810</t>
+          <t>USA-R2-NVDA-20260810-99ffda</t>
         </is>
       </c>
       <c r="B4" s="32" t="inlineStr">
@@ -4574,7 +4574,7 @@
         <v>0</v>
       </c>
       <c r="AN4" s="32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO4" s="32" t="n"/>
       <c r="AP4" s="32" t="n"/>
@@ -4641,7 +4641,7 @@
     <row r="5">
       <c r="A5" s="32" t="inlineStr">
         <is>
-          <t>JPM_USA_20260810</t>
+          <t>USA-R2-JPM-20260810-9d795f</t>
         </is>
       </c>
       <c r="B5" s="32" t="inlineStr">
@@ -4848,7 +4848,7 @@
     <row r="6">
       <c r="A6" s="32" t="inlineStr">
         <is>
-          <t>HON_USA_20260810</t>
+          <t>USA-R2-HON-20260810-ab1167</t>
         </is>
       </c>
       <c r="B6" s="32" t="inlineStr">
@@ -5055,7 +5055,7 @@
     <row r="7">
       <c r="A7" s="32" t="inlineStr">
         <is>
-          <t>GS_USA_20260810</t>
+          <t>USA-R2-GS-20260810-69e512</t>
         </is>
       </c>
       <c r="B7" s="32" t="inlineStr">
@@ -5191,7 +5191,7 @@
         <v>0</v>
       </c>
       <c r="AN7" s="32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO7" s="32" t="n"/>
       <c r="AP7" s="32" t="n"/>
@@ -5258,7 +5258,7 @@
     <row r="8">
       <c r="A8" s="32" t="inlineStr">
         <is>
-          <t>AAPL_USA_20260810</t>
+          <t>USA-R2-AAPL-20260810-25a640</t>
         </is>
       </c>
       <c r="B8" s="32" t="inlineStr">
@@ -5479,7 +5479,7 @@
     <row r="9">
       <c r="A9" s="32" t="inlineStr">
         <is>
-          <t>MSFT_USA_20260810</t>
+          <t>USA-R2-MSFT-20260810-686f62</t>
         </is>
       </c>
       <c r="B9" s="32" t="inlineStr">
@@ -5686,7 +5686,7 @@
     <row r="10">
       <c r="A10" s="32" t="inlineStr">
         <is>
-          <t>KO_USA_20260810</t>
+          <t>USA-R2-KO-20260810-5fbe6b</t>
         </is>
       </c>
       <c r="B10" s="32" t="inlineStr">
@@ -5826,7 +5826,7 @@
         <v>0</v>
       </c>
       <c r="AN10" s="32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO10" s="32" t="n"/>
       <c r="AP10" s="32" t="n"/>
@@ -5893,7 +5893,7 @@
     <row r="11">
       <c r="A11" s="32" t="inlineStr">
         <is>
-          <t>MMM_USA_20260810</t>
+          <t>USA-R2-MMM-20260810-ff304e</t>
         </is>
       </c>
       <c r="B11" s="32" t="inlineStr">
@@ -6033,7 +6033,7 @@
         <v>0</v>
       </c>
       <c r="AN11" s="32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO11" s="32" t="n"/>
       <c r="AP11" s="32" t="n"/>
@@ -6100,7 +6100,7 @@
     <row r="12">
       <c r="A12" s="32" t="inlineStr">
         <is>
-          <t>INTC_USA_20260810</t>
+          <t>USA-R2-INTC-20260810-a06dd2</t>
         </is>
       </c>
       <c r="B12" s="32" t="inlineStr">
@@ -6307,7 +6307,7 @@
     <row r="13">
       <c r="A13" s="32" t="inlineStr">
         <is>
-          <t>BA_USA_20260810</t>
+          <t>USA-R2-BA-20260810-e0c250</t>
         </is>
       </c>
       <c r="B13" s="32" t="inlineStr">
@@ -6447,7 +6447,7 @@
         <v>0</v>
       </c>
       <c r="AN13" s="32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO13" s="32" t="n"/>
       <c r="AP13" s="32" t="n"/>
@@ -6514,7 +6514,7 @@
     <row r="14">
       <c r="A14" s="32" t="inlineStr">
         <is>
-          <t>HD_USA_20260810</t>
+          <t>USA-R2-HD-20260810-cf005a</t>
         </is>
       </c>
       <c r="B14" s="32" t="inlineStr">
@@ -6650,7 +6650,7 @@
         <v>0</v>
       </c>
       <c r="AN14" s="32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO14" s="32" t="n"/>
       <c r="AP14" s="32" t="n"/>
@@ -6717,7 +6717,7 @@
     <row r="15">
       <c r="A15" s="32" t="inlineStr">
         <is>
-          <t>DIS_USA_20260810</t>
+          <t>USA-R2-DIS-20260810-1ab349</t>
         </is>
       </c>
       <c r="B15" s="32" t="inlineStr">
@@ -6853,7 +6853,7 @@
         <v>0</v>
       </c>
       <c r="AN15" s="32" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO15" s="32" t="n"/>
       <c r="AP15" s="32" t="n"/>
@@ -6920,7 +6920,7 @@
     <row r="16">
       <c r="A16" s="32" t="inlineStr">
         <is>
-          <t>MCD_USA_20260810</t>
+          <t>USA-R2-MCD-20260810-06f359</t>
         </is>
       </c>
       <c r="B16" s="32" t="inlineStr">
@@ -7123,7 +7123,7 @@
     <row r="17">
       <c r="A17" s="30" t="inlineStr">
         <is>
-          <t>V_USA_20260810</t>
+          <t>USA-R1-V-20260810-4d75a7</t>
         </is>
       </c>
       <c r="B17" s="30" t="inlineStr">
@@ -7251,7 +7251,7 @@
         <v>0</v>
       </c>
       <c r="AN17" s="30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO17" s="30" t="n"/>
       <c r="AP17" s="30" t="n"/>
@@ -7328,7 +7328,7 @@
     <row r="18">
       <c r="A18" s="30" t="inlineStr">
         <is>
-          <t>TRV_USA_20260810</t>
+          <t>USA-R1-TRV-20260810-6f873c</t>
         </is>
       </c>
       <c r="B18" s="30" t="inlineStr">
@@ -7456,7 +7456,7 @@
         <v>0</v>
       </c>
       <c r="AN18" s="30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO18" s="30" t="n"/>
       <c r="AP18" s="30" t="n"/>
@@ -7533,7 +7533,7 @@
     <row r="19">
       <c r="A19" s="30" t="inlineStr">
         <is>
-          <t>NVDA_USA_20260810</t>
+          <t>USA-R1-NVDA-20260810-2aa027</t>
         </is>
       </c>
       <c r="B19" s="30" t="inlineStr">
@@ -7665,7 +7665,7 @@
         <v>0</v>
       </c>
       <c r="AN19" s="30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO19" s="30" t="n"/>
       <c r="AP19" s="30" t="n"/>
@@ -7742,7 +7742,7 @@
     <row r="20">
       <c r="A20" s="30" t="inlineStr">
         <is>
-          <t>MSFT_USA_20260810</t>
+          <t>USA-R1-MSFT-20260810-6110fc</t>
         </is>
       </c>
       <c r="B20" s="30" t="inlineStr">
@@ -7951,7 +7951,7 @@
     <row r="21">
       <c r="A21" s="31" t="inlineStr">
         <is>
-          <t>KO_USA_20260810</t>
+          <t>USA-R1-KO-20260810-af15a9</t>
         </is>
       </c>
       <c r="B21" s="31" t="inlineStr">
@@ -8083,7 +8083,7 @@
         <v>0</v>
       </c>
       <c r="AN21" s="31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO21" s="31" t="n"/>
       <c r="AP21" s="31" t="n"/>
@@ -8160,7 +8160,7 @@
     <row r="22">
       <c r="A22" s="31" t="inlineStr">
         <is>
-          <t>HON_USA_20260810</t>
+          <t>USA-R1-HON-20260810-0b8118</t>
         </is>
       </c>
       <c r="B22" s="31" t="inlineStr">
@@ -8369,7 +8369,7 @@
     <row r="23">
       <c r="A23" s="31" t="inlineStr">
         <is>
-          <t>AAPL_USA_20260810</t>
+          <t>USA-R1-AAPL-20260810-d82b13</t>
         </is>
       </c>
       <c r="B23" s="31" t="inlineStr">
@@ -8580,7 +8580,7 @@
     <row r="24">
       <c r="A24" s="31" t="inlineStr">
         <is>
-          <t>JPM_USA_20260810</t>
+          <t>USA-R1-JPM-20260810-a6a394</t>
         </is>
       </c>
       <c r="B24" s="31" t="inlineStr">
@@ -8789,7 +8789,7 @@
     <row r="25">
       <c r="A25" s="31" t="inlineStr">
         <is>
-          <t>GS_USA_20260810</t>
+          <t>USA-R1-GS-20260810-c6e885</t>
         </is>
       </c>
       <c r="B25" s="31" t="inlineStr">
@@ -8917,7 +8917,7 @@
         <v>0</v>
       </c>
       <c r="AN25" s="31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO25" s="31" t="n"/>
       <c r="AP25" s="31" t="n"/>
@@ -8994,7 +8994,7 @@
     <row r="26">
       <c r="A26" s="31" t="inlineStr">
         <is>
-          <t>MMM_USA_20260810</t>
+          <t>USA-R1-MMM-20260810-0649c0</t>
         </is>
       </c>
       <c r="B26" s="31" t="inlineStr">
@@ -9126,7 +9126,7 @@
         <v>0</v>
       </c>
       <c r="AN26" s="31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO26" s="31" t="n"/>
       <c r="AP26" s="31" t="n"/>
@@ -9203,7 +9203,7 @@
     <row r="27">
       <c r="A27" s="30" t="inlineStr">
         <is>
-          <t>TRV_USA_20260811</t>
+          <t>USA-R2-TRV-20260810-9cd25d</t>
         </is>
       </c>
       <c r="B27" s="30" t="inlineStr">
@@ -9337,7 +9337,7 @@
         <v>0</v>
       </c>
       <c r="AN27" s="30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO27" s="30" t="n"/>
       <c r="AP27" s="30" t="n"/>
@@ -9418,7 +9418,7 @@
     <row r="28">
       <c r="A28" s="31" t="inlineStr">
         <is>
-          <t>V_USA_20260811</t>
+          <t>USA-R2-V-20260810-69160d</t>
         </is>
       </c>
       <c r="B28" s="31" t="inlineStr">
@@ -9552,7 +9552,7 @@
         <v>0</v>
       </c>
       <c r="AN28" s="31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO28" s="31" t="n"/>
       <c r="AP28" s="31" t="n"/>
@@ -9631,7 +9631,7 @@
     <row r="29">
       <c r="A29" s="30" t="inlineStr">
         <is>
-          <t>V_USA_20260811</t>
+          <t>USA-R1-V-20260810-4d75a7</t>
         </is>
       </c>
       <c r="B29" s="30" t="inlineStr">
@@ -9759,7 +9759,7 @@
         <v>0</v>
       </c>
       <c r="AN29" s="30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO29" s="30" t="n"/>
       <c r="AP29" s="30" t="n"/>
@@ -9836,7 +9836,7 @@
     <row r="30">
       <c r="A30" s="30" t="inlineStr">
         <is>
-          <t>TRV_USA_20260811</t>
+          <t>USA-R1-TRV-20260810-6f873c</t>
         </is>
       </c>
       <c r="B30" s="30" t="inlineStr">
@@ -9964,7 +9964,7 @@
         <v>0</v>
       </c>
       <c r="AN30" s="30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO30" s="30" t="n"/>
       <c r="AP30" s="30" t="n"/>
@@ -10041,7 +10041,7 @@
     <row r="31">
       <c r="A31" s="30" t="inlineStr">
         <is>
-          <t>NVDA_USA_20260811</t>
+          <t>USA-R1-NVDA-20260810-2aa027</t>
         </is>
       </c>
       <c r="B31" s="30" t="inlineStr">
@@ -10173,7 +10173,7 @@
         <v>0</v>
       </c>
       <c r="AN31" s="30" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO31" s="30" t="n"/>
       <c r="AP31" s="30" t="n"/>
@@ -10250,7 +10250,7 @@
     <row r="32">
       <c r="A32" s="30" t="inlineStr">
         <is>
-          <t>MSFT_USA_20260811</t>
+          <t>USA-R1-MSFT-20260810-6110fc</t>
         </is>
       </c>
       <c r="B32" s="30" t="inlineStr">
@@ -10459,7 +10459,7 @@
     <row r="33">
       <c r="A33" s="31" t="inlineStr">
         <is>
-          <t>KO_USA_20260811</t>
+          <t>USA-R1-KO-20260810-af15a9</t>
         </is>
       </c>
       <c r="B33" s="31" t="inlineStr">
@@ -10591,7 +10591,7 @@
         <v>0</v>
       </c>
       <c r="AN33" s="31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO33" s="31" t="n"/>
       <c r="AP33" s="31" t="n"/>
@@ -10668,7 +10668,7 @@
     <row r="34">
       <c r="A34" s="31" t="inlineStr">
         <is>
-          <t>HON_USA_20260811</t>
+          <t>USA-R1-HON-20260810-0b8118</t>
         </is>
       </c>
       <c r="B34" s="31" t="inlineStr">
@@ -10877,7 +10877,7 @@
     <row r="35">
       <c r="A35" s="31" t="inlineStr">
         <is>
-          <t>AAPL_USA_20260811</t>
+          <t>USA-R1-AAPL-20260810-d82b13</t>
         </is>
       </c>
       <c r="B35" s="31" t="inlineStr">
@@ -11088,7 +11088,7 @@
     <row r="36">
       <c r="A36" s="31" t="inlineStr">
         <is>
-          <t>JPM_USA_20260811</t>
+          <t>USA-R1-JPM-20260810-a6a394</t>
         </is>
       </c>
       <c r="B36" s="31" t="inlineStr">
@@ -11297,7 +11297,7 @@
     <row r="37">
       <c r="A37" s="31" t="inlineStr">
         <is>
-          <t>GS_USA_20260811</t>
+          <t>USA-R1-GS-20260810-c6e885</t>
         </is>
       </c>
       <c r="B37" s="31" t="inlineStr">
@@ -11425,7 +11425,7 @@
         <v>0</v>
       </c>
       <c r="AN37" s="31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO37" s="31" t="n"/>
       <c r="AP37" s="31" t="n"/>
@@ -11502,7 +11502,7 @@
     <row r="38">
       <c r="A38" s="31" t="inlineStr">
         <is>
-          <t>MMM_USA_20260811</t>
+          <t>USA-R1-MMM-20260810-0649c0</t>
         </is>
       </c>
       <c r="B38" s="31" t="inlineStr">
@@ -11634,7 +11634,7 @@
         <v>0</v>
       </c>
       <c r="AN38" s="31" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO38" s="31" t="n"/>
       <c r="AP38" s="31" t="n"/>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -1725,6 +1725,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
@@ -31444,6 +31445,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
@@ -31530,7 +31532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG38"/>
+  <dimension ref="A1:BG18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -34992,12 +34994,12 @@
     <row r="17">
       <c r="A17" s="30" t="inlineStr">
         <is>
-          <t>USA-R1-V-20260810-4d75a7</t>
+          <t>USA-R2-TRV-20260810-9cd25d</t>
         </is>
       </c>
       <c r="B17" s="30" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="C17" s="30" t="inlineStr">
@@ -35007,17 +35009,17 @@
       </c>
       <c r="D17" s="30" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="E17" s="30" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="F17" s="30" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="G17" s="30" t="inlineStr">
@@ -35030,10 +35032,14 @@
       <c r="J17" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="K17" s="30" t="n"/>
-      <c r="L17" s="30" t="n"/>
+      <c r="K17" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="30" t="n">
+        <v>0</v>
+      </c>
       <c r="M17" s="30" t="n">
-        <v>86.5</v>
+        <v>79.3</v>
       </c>
       <c r="N17" s="30" t="inlineStr">
         <is>
@@ -35041,24 +35047,24 @@
         </is>
       </c>
       <c r="O17" s="30" t="n">
-        <v>52.9</v>
+        <v>56.1</v>
       </c>
       <c r="P17" s="30" t="n">
         <v>-0.8</v>
       </c>
       <c r="Q17" s="30" t="inlineStr">
         <is>
-          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
         </is>
       </c>
       <c r="R17" s="30" t="inlineStr">
         <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #1 · Conf 54% · momentum → · band STRONG · 91d left · → BUY</t>
+          <t>🟢 BUY (Δ-1.0%) · Rank → 1→1 · Conf 57% · band HOLD · 14d left · → BUY</t>
         </is>
       </c>
       <c r="S17" s="30" t="n"/>
       <c r="T17" s="30" t="n">
-        <v>53.6</v>
+        <v>56.8</v>
       </c>
       <c r="U17" s="30" t="inlineStr">
         <is>
@@ -35066,55 +35072,57 @@
         </is>
       </c>
       <c r="V17" s="30" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="W17" s="30" t="n"/>
+        <v>29.2</v>
+      </c>
+      <c r="W17" s="30" t="n">
+        <v>4</v>
+      </c>
       <c r="X17" s="30" t="n">
         <v>0</v>
       </c>
       <c r="Y17" s="30" t="n">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="Z17" s="30" t="n">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="AA17" s="30" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AB17" s="30" t="n">
-        <v>368.54</v>
+        <v>382.45</v>
       </c>
       <c r="AC17" s="30" t="n">
-        <v>368.5400085449219</v>
+        <v>382.4500122070312</v>
       </c>
       <c r="AD17" s="30" t="n">
-        <v>351.39</v>
+        <v>365.29</v>
       </c>
       <c r="AE17" s="30" t="n">
-        <v>365.73</v>
+        <v>372.67</v>
       </c>
       <c r="AF17" s="30" t="n">
-        <v>340.632</v>
+        <v>346.84</v>
       </c>
       <c r="AG17" s="30" t="n">
-        <v>-7.57</v>
+        <v>-9.31</v>
       </c>
       <c r="AH17" s="30" t="n">
-        <v>387.2448000000001</v>
+        <v>413.26</v>
       </c>
       <c r="AI17" s="30" t="n">
-        <v>5.08</v>
+        <v>8.06</v>
       </c>
       <c r="AJ17" s="30" t="n">
-        <v>414.3519360000001</v>
+        <v>457.54</v>
       </c>
       <c r="AK17" s="30" t="n">
-        <v>12.43</v>
+        <v>19.63</v>
       </c>
       <c r="AL17" s="30" t="n">
-        <v>368.54</v>
+        <v>382.45</v>
       </c>
       <c r="AM17" s="30" t="n">
         <v>0</v>
@@ -35124,21 +35132,25 @@
       </c>
       <c r="AO17" s="30" t="n"/>
       <c r="AP17" s="30" t="n"/>
-      <c r="AQ17" s="30" t="n"/>
+      <c r="AQ17" s="30" t="inlineStr">
+        <is>
+          <t>Momentum · Value · Trend</t>
+        </is>
+      </c>
       <c r="AR17" s="30" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
       <c r="AS17" s="30" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AT17" s="30" t="n">
-        <v>5.08</v>
+        <v>8.06</v>
       </c>
       <c r="AU17" s="30" t="inlineStr">
         <is>
-          <t>2026-08-10 06:27</t>
+          <t>2026-08-11 04:16</t>
         </is>
       </c>
       <c r="AV17" s="30" t="inlineStr">
@@ -35180,12 +35192,12 @@
       </c>
       <c r="BE17" s="30" t="inlineStr">
         <is>
-          <t>Trailing Stop @ 340.63</t>
+          <t>Trailing Stop @ 346.84</t>
         </is>
       </c>
       <c r="BF17" s="30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="BG17" s="30" t="inlineStr">
@@ -35195,4383 +35207,213 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="30" t="inlineStr">
-        <is>
-          <t>USA-R1-TRV-20260810-6f873c</t>
-        </is>
-      </c>
-      <c r="B18" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="C18" s="30" t="inlineStr">
+      <c r="A18" s="31" t="inlineStr">
+        <is>
+          <t>USA-R2-V-20260810-69160d</t>
+        </is>
+      </c>
+      <c r="B18" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="D18" s="30" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E18" s="30" t="inlineStr">
-        <is>
-          <t>TRV</t>
-        </is>
-      </c>
-      <c r="F18" s="30" t="inlineStr">
-        <is>
-          <t>Travelers</t>
-        </is>
-      </c>
-      <c r="G18" s="30" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="H18" s="30" t="n"/>
-      <c r="I18" s="30" t="n"/>
-      <c r="J18" s="30" t="n">
+      <c r="D18" s="31" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="E18" s="31" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="F18" s="31" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="G18" s="31" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="H18" s="31" t="n"/>
+      <c r="I18" s="31" t="n"/>
+      <c r="J18" s="31" t="n">
         <v>2</v>
       </c>
-      <c r="K18" s="30" t="n"/>
-      <c r="L18" s="30" t="n"/>
-      <c r="M18" s="30" t="n">
-        <v>79.3</v>
-      </c>
-      <c r="N18" s="30" t="inlineStr">
+      <c r="K18" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="31" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="N18" s="31" t="inlineStr">
         <is>
           <t>🟢</t>
         </is>
       </c>
-      <c r="O18" s="30" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="P18" s="30" t="n">
+      <c r="O18" s="31" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="P18" s="31" t="n">
         <v>-0.8</v>
       </c>
-      <c r="Q18" s="30" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R18" s="30" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 57% · momentum → · band HOLD · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="S18" s="30" t="n"/>
-      <c r="T18" s="30" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="U18" s="30" t="inlineStr">
+      <c r="Q18" s="31" t="inlineStr">
+        <is>
+          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
+        </is>
+      </c>
+      <c r="R18" s="31" t="inlineStr">
+        <is>
+          <t>🟢 BUY (Δ-3.7%) · Rank → 2→2 · Conf 54% · band STRONG · 14d left · → HOLD</t>
+        </is>
+      </c>
+      <c r="S18" s="31" t="n"/>
+      <c r="T18" s="31" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="U18" s="31" t="inlineStr">
         <is>
           <t>Calibrated</t>
         </is>
       </c>
-      <c r="V18" s="30" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="W18" s="30" t="n"/>
-      <c r="X18" s="30" t="n">
+      <c r="V18" s="31" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="W18" s="31" t="n">
+        <v>4</v>
+      </c>
+      <c r="X18" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="Y18" s="30" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z18" s="30" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA18" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AB18" s="30" t="n">
-        <v>382.45</v>
-      </c>
-      <c r="AC18" s="30" t="n">
-        <v>382.4500122070312</v>
-      </c>
-      <c r="AD18" s="30" t="n">
-        <v>365.29</v>
-      </c>
-      <c r="AE18" s="30" t="n">
-        <v>372.67</v>
-      </c>
-      <c r="AF18" s="30" t="n">
-        <v>350.531</v>
-      </c>
-      <c r="AG18" s="30" t="n">
-        <v>-8.35</v>
-      </c>
-      <c r="AH18" s="30" t="n">
-        <v>413.26</v>
-      </c>
-      <c r="AI18" s="30" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="AJ18" s="30" t="n">
-        <v>442.1882</v>
-      </c>
-      <c r="AK18" s="30" t="n">
-        <v>15.62</v>
-      </c>
-      <c r="AL18" s="30" t="n">
-        <v>382.45</v>
-      </c>
-      <c r="AM18" s="30" t="n">
+      <c r="Y18" s="31" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z18" s="31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA18" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AB18" s="31" t="n">
+        <v>368.54</v>
+      </c>
+      <c r="AC18" s="31" t="n">
+        <v>368.5400085449219</v>
+      </c>
+      <c r="AD18" s="31" t="n">
+        <v>364.85</v>
+      </c>
+      <c r="AE18" s="31" t="n">
+        <v>372.23</v>
+      </c>
+      <c r="AF18" s="31" t="n">
+        <v>350.11</v>
+      </c>
+      <c r="AG18" s="31" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH18" s="31" t="n">
+        <v>398.02</v>
+      </c>
+      <c r="AI18" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ18" s="31" t="n">
+        <v>423.82</v>
+      </c>
+      <c r="AK18" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL18" s="31" t="n">
+        <v>368.54</v>
+      </c>
+      <c r="AM18" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="AN18" s="30" t="n">
+      <c r="AN18" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="AO18" s="30" t="n"/>
-      <c r="AP18" s="30" t="n"/>
-      <c r="AQ18" s="30" t="n"/>
-      <c r="AR18" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS18" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT18" s="30" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="AU18" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-10 06:27</t>
-        </is>
-      </c>
-      <c r="AV18" s="30" t="inlineStr">
+      <c r="AO18" s="31" t="n"/>
+      <c r="AP18" s="31" t="n"/>
+      <c r="AQ18" s="31" t="inlineStr">
+        <is>
+          <t>Momentum · Trend · Quality</t>
+        </is>
+      </c>
+      <c r="AR18" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AS18" s="31" t="n"/>
+      <c r="AT18" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-11 04:16</t>
+        </is>
+      </c>
+      <c r="AV18" s="31" t="inlineStr">
         <is>
           <t>LargeCap (S&amp;P 500)</t>
         </is>
       </c>
-      <c r="AW18" s="30" t="inlineStr">
+      <c r="AW18" s="31" t="inlineStr">
         <is>
           <t>🆕 NEW</t>
         </is>
       </c>
-      <c r="AX18" s="30" t="n"/>
-      <c r="AY18" s="30" t="inlineStr"/>
-      <c r="AZ18" s="30" t="inlineStr">
+      <c r="AX18" s="31" t="n"/>
+      <c r="AY18" s="31" t="inlineStr"/>
+      <c r="AZ18" s="31" t="inlineStr">
         <is>
           <t>🟠 PROTECT</t>
         </is>
       </c>
-      <c r="BA18" s="30" t="inlineStr">
+      <c r="BA18" s="31" t="inlineStr">
         <is>
           <t>🟡 MEDIUM</t>
         </is>
       </c>
-      <c r="BB18" s="30" t="inlineStr">
+      <c r="BB18" s="31" t="inlineStr">
         <is>
           <t>Watch</t>
         </is>
       </c>
-      <c r="BC18" s="30" t="inlineStr">
+      <c r="BC18" s="31" t="inlineStr">
         <is>
           <t>TIGHTEN STOP</t>
         </is>
       </c>
-      <c r="BD18" s="30" t="inlineStr">
+      <c r="BD18" s="31" t="inlineStr">
         <is>
           <t>TOMORROW</t>
         </is>
       </c>
-      <c r="BE18" s="30" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 350.53</t>
-        </is>
-      </c>
-      <c r="BF18" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="BG18" s="30" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="30" t="inlineStr">
-        <is>
-          <t>USA-R1-NVDA-20260810-2aa027</t>
-        </is>
-      </c>
-      <c r="B19" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="C19" s="30" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D19" s="30" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E19" s="30" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="F19" s="30" t="inlineStr">
-        <is>
-          <t>NVIDIA</t>
-        </is>
-      </c>
-      <c r="G19" s="30" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="H19" s="30" t="n"/>
-      <c r="I19" s="30" t="n"/>
-      <c r="J19" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="K19" s="30" t="n"/>
-      <c r="L19" s="30" t="n"/>
-      <c r="M19" s="30" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="N19" s="30" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O19" s="30" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="P19" s="30" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q19" s="30" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 21 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R19" s="30" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #3 · Conf 47% · momentum → · band HOLD · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="S19" s="30" t="inlineStr">
-        <is>
-          <t>WARNING·STOP_LOSS_HIT·-7.5% ≤ -5.0% · exit</t>
-        </is>
-      </c>
-      <c r="T19" s="30" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="U19" s="30" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V19" s="30" t="n">
-        <v>55.7</v>
-      </c>
-      <c r="W19" s="30" t="n"/>
-      <c r="X19" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="30" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z19" s="30" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA19" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AB19" s="30" t="n">
-        <v>219.22</v>
-      </c>
-      <c r="AC19" s="30" t="n">
-        <v>219.2200012207031</v>
-      </c>
-      <c r="AD19" s="30" t="n">
-        <v>198.75</v>
-      </c>
-      <c r="AE19" s="30" t="n">
-        <v>206.87</v>
-      </c>
-      <c r="AF19" s="30" t="n">
-        <v>192.6695</v>
-      </c>
-      <c r="AG19" s="30" t="n">
-        <v>-12.11</v>
-      </c>
-      <c r="AH19" s="30" t="n">
-        <v>219.0348</v>
-      </c>
-      <c r="AI19" s="30" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AJ19" s="30" t="n">
-        <v>234.367236</v>
-      </c>
-      <c r="AK19" s="30" t="n">
-        <v>6.91</v>
-      </c>
-      <c r="AL19" s="30" t="n">
-        <v>219.22</v>
-      </c>
-      <c r="AM19" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN19" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO19" s="30" t="n"/>
-      <c r="AP19" s="30" t="n"/>
-      <c r="AQ19" s="30" t="n"/>
-      <c r="AR19" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS19" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT19" s="30" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AU19" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-10 06:27</t>
-        </is>
-      </c>
-      <c r="AV19" s="30" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW19" s="30" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX19" s="30" t="n"/>
-      <c r="AY19" s="30" t="inlineStr"/>
-      <c r="AZ19" s="30" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA19" s="30" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB19" s="30" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC19" s="30" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD19" s="30" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE19" s="30" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 192.67</t>
-        </is>
-      </c>
-      <c r="BF19" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="BG19" s="30" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="30" t="inlineStr">
-        <is>
-          <t>USA-R1-MSFT-20260810-6110fc</t>
-        </is>
-      </c>
-      <c r="B20" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="C20" s="30" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D20" s="30" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E20" s="30" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="F20" s="30" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="G20" s="30" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="H20" s="30" t="n"/>
-      <c r="I20" s="30" t="n"/>
-      <c r="J20" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="K20" s="30" t="n"/>
-      <c r="L20" s="30" t="n"/>
-      <c r="M20" s="30" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="N20" s="30" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O20" s="30" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="P20" s="30" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q20" s="30" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R20" s="30" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #4 · Conf 54% · momentum → · band HOLD · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="S20" s="30" t="inlineStr">
-        <is>
-          <t>CRITICAL·DEEP_LOSS·-19.2% ≤ -8.0% · EXIT URGENT</t>
-        </is>
-      </c>
-      <c r="T20" s="30" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="U20" s="30" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V20" s="30" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="W20" s="30" t="n"/>
-      <c r="X20" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="30" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z20" s="30" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA20" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AB20" s="30" t="n">
-        <v>487.46</v>
-      </c>
-      <c r="AC20" s="30" t="n">
-        <v>487.4599914550781</v>
-      </c>
-      <c r="AD20" s="30" t="n">
-        <v>385.94</v>
-      </c>
-      <c r="AE20" s="30" t="n">
-        <v>401.7</v>
-      </c>
-      <c r="AF20" s="30" t="n">
-        <v>374.129</v>
-      </c>
-      <c r="AG20" s="30" t="n">
-        <v>-23.25</v>
-      </c>
-      <c r="AH20" s="30" t="n">
-        <v>425.3256</v>
-      </c>
-      <c r="AI20" s="30" t="n">
-        <v>-12.75</v>
-      </c>
-      <c r="AJ20" s="30" t="n">
-        <v>455.098392</v>
-      </c>
-      <c r="AK20" s="30" t="n">
-        <v>-6.64</v>
-      </c>
-      <c r="AL20" s="30" t="n">
-        <v>487.46</v>
-      </c>
-      <c r="AM20" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN20" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO20" s="30" t="n"/>
-      <c r="AP20" s="30" t="n"/>
-      <c r="AQ20" s="30" t="n"/>
-      <c r="AR20" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS20" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT20" s="30" t="n">
-        <v>-12.75</v>
-      </c>
-      <c r="AU20" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-10 06:27</t>
-        </is>
-      </c>
-      <c r="AV20" s="30" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW20" s="30" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX20" s="30" t="n"/>
-      <c r="AY20" s="30" t="inlineStr"/>
-      <c r="AZ20" s="30" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA20" s="30" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB20" s="30" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC20" s="30" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD20" s="30" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE20" s="30" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 374.13</t>
-        </is>
-      </c>
-      <c r="BF20" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="BG20" s="30" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="31" t="inlineStr">
-        <is>
-          <t>USA-R1-KO-20260810-af15a9</t>
-        </is>
-      </c>
-      <c r="B21" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="C21" s="31" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D21" s="31" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E21" s="31" t="inlineStr">
-        <is>
-          <t>KO</t>
-        </is>
-      </c>
-      <c r="F21" s="31" t="inlineStr">
-        <is>
-          <t>Coca-Cola</t>
-        </is>
-      </c>
-      <c r="G21" s="31" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H21" s="31" t="n"/>
-      <c r="I21" s="31" t="n"/>
-      <c r="J21" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="K21" s="31" t="n"/>
-      <c r="L21" s="31" t="n"/>
-      <c r="M21" s="31" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="N21" s="31" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O21" s="31" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="P21" s="31" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q21" s="31" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 11 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R21" s="31" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #5 · Conf 50% · momentum → · band STRONG · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S21" s="31" t="inlineStr">
-        <is>
-          <t>WARNING·STOP_LOSS_HIT·-6.1% ≤ -5.0% · exit</t>
-        </is>
-      </c>
-      <c r="T21" s="31" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="U21" s="31" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V21" s="31" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="W21" s="31" t="n"/>
-      <c r="X21" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="31" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z21" s="31" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA21" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AB21" s="31" t="n">
-        <v>86.83</v>
-      </c>
-      <c r="AC21" s="31" t="n">
-        <v>86.83000183105469</v>
-      </c>
-      <c r="AD21" s="31" t="n">
-        <v>79.93000000000001</v>
-      </c>
-      <c r="AE21" s="31" t="n">
-        <v>83.19</v>
-      </c>
-      <c r="AF21" s="31" t="n">
-        <v>77.482</v>
-      </c>
-      <c r="AG21" s="31" t="n">
-        <v>-10.77</v>
-      </c>
-      <c r="AH21" s="31" t="n">
-        <v>88.0848</v>
-      </c>
-      <c r="AI21" s="31" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AJ21" s="31" t="n">
-        <v>94.250736</v>
-      </c>
-      <c r="AK21" s="31" t="n">
-        <v>8.550000000000001</v>
-      </c>
-      <c r="AL21" s="31" t="n">
-        <v>86.83</v>
-      </c>
-      <c r="AM21" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN21" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO21" s="31" t="n"/>
-      <c r="AP21" s="31" t="n"/>
-      <c r="AQ21" s="31" t="n"/>
-      <c r="AR21" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS21" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT21" s="31" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AU21" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10 06:27</t>
-        </is>
-      </c>
-      <c r="AV21" s="31" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW21" s="31" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX21" s="31" t="n"/>
-      <c r="AY21" s="31" t="inlineStr"/>
-      <c r="AZ21" s="31" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA21" s="31" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB21" s="31" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC21" s="31" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD21" s="31" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE21" s="31" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 77.48</t>
-        </is>
-      </c>
-      <c r="BF21" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="BG21" s="31" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="31" t="inlineStr">
-        <is>
-          <t>USA-R1-HON-20260810-0b8118</t>
-        </is>
-      </c>
-      <c r="B22" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="C22" s="31" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D22" s="31" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E22" s="31" t="inlineStr">
-        <is>
-          <t>HON</t>
-        </is>
-      </c>
-      <c r="F22" s="31" t="inlineStr">
-        <is>
-          <t>Honeywell</t>
-        </is>
-      </c>
-      <c r="G22" s="31" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H22" s="31" t="n"/>
-      <c r="I22" s="31" t="n"/>
-      <c r="J22" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="K22" s="31" t="n"/>
-      <c r="L22" s="31" t="n"/>
-      <c r="M22" s="31" t="n">
-        <v>76</v>
-      </c>
-      <c r="N22" s="31" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O22" s="31" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="P22" s="31" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q22" s="31" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 48 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R22" s="31" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #6 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S22" s="31" t="inlineStr">
-        <is>
-          <t>CRITICAL·DEEP_LOSS·-9.3% ≤ -8.0% · EXIT URGENT</t>
-        </is>
-      </c>
-      <c r="T22" s="31" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="U22" s="31" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V22" s="31" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="W22" s="31" t="n"/>
-      <c r="X22" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="31" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z22" s="31" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA22" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AB22" s="31" t="n">
-        <v>248.12</v>
-      </c>
-      <c r="AC22" s="31" t="n">
-        <v>248.1199951171875</v>
-      </c>
-      <c r="AD22" s="31" t="n">
-        <v>220.52</v>
-      </c>
-      <c r="AE22" s="31" t="n">
-        <v>229.52</v>
-      </c>
-      <c r="AF22" s="31" t="n">
-        <v>213.769</v>
-      </c>
-      <c r="AG22" s="31" t="n">
-        <v>-13.84</v>
-      </c>
-      <c r="AH22" s="31" t="n">
-        <v>243.0216</v>
-      </c>
-      <c r="AI22" s="31" t="n">
-        <v>-2.05</v>
-      </c>
-      <c r="AJ22" s="31" t="n">
-        <v>260.0331120000001</v>
-      </c>
-      <c r="AK22" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AL22" s="31" t="n">
-        <v>248.12</v>
-      </c>
-      <c r="AM22" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN22" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO22" s="31" t="n"/>
-      <c r="AP22" s="31" t="n"/>
-      <c r="AQ22" s="31" t="n"/>
-      <c r="AR22" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS22" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT22" s="31" t="n">
-        <v>-2.05</v>
-      </c>
-      <c r="AU22" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10 06:27</t>
-        </is>
-      </c>
-      <c r="AV22" s="31" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW22" s="31" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX22" s="31" t="n"/>
-      <c r="AY22" s="31" t="inlineStr"/>
-      <c r="AZ22" s="31" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA22" s="31" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB22" s="31" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC22" s="31" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD22" s="31" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE22" s="31" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 213.77</t>
-        </is>
-      </c>
-      <c r="BF22" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="BG22" s="31" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="31" t="inlineStr">
-        <is>
-          <t>USA-R1-AAPL-20260810-d82b13</t>
-        </is>
-      </c>
-      <c r="B23" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="C23" s="31" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D23" s="31" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E23" s="31" t="inlineStr">
-        <is>
-          <t>AAPL</t>
-        </is>
-      </c>
-      <c r="F23" s="31" t="inlineStr">
-        <is>
-          <t>Apple</t>
-        </is>
-      </c>
-      <c r="G23" s="31" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H23" s="31" t="n"/>
-      <c r="I23" s="31" t="n"/>
-      <c r="J23" s="31" t="n">
-        <v>7</v>
-      </c>
-      <c r="K23" s="31" t="n"/>
-      <c r="L23" s="31" t="n"/>
-      <c r="M23" s="31" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="N23" s="31" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O23" s="31" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="P23" s="31" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q23" s="31" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R23" s="31" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #7 · Conf 50% · momentum → · band STRONG · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S23" s="31" t="n"/>
-      <c r="T23" s="31" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="U23" s="31" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V23" s="31" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="W23" s="31" t="n"/>
-      <c r="X23" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="31" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z23" s="31" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA23" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AB23" s="31" t="n">
-        <v>311</v>
-      </c>
-      <c r="AC23" s="31" t="n">
-        <v>311</v>
-      </c>
-      <c r="AD23" s="31" t="n">
-        <v>327.07</v>
-      </c>
-      <c r="AE23" s="31" t="n">
-        <v>340.41</v>
-      </c>
-      <c r="AF23" s="31" t="n">
-        <v>317.053</v>
-      </c>
-      <c r="AG23" s="31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH23" s="31" t="n">
-        <v>360.4392</v>
-      </c>
-      <c r="AI23" s="31" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="AJ23" s="31" t="n">
-        <v>385.669944</v>
-      </c>
-      <c r="AK23" s="31" t="n">
-        <v>24.01</v>
-      </c>
-      <c r="AL23" s="31" t="n">
-        <v>311</v>
-      </c>
-      <c r="AM23" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN23" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO23" s="31" t="n"/>
-      <c r="AP23" s="31" t="n"/>
-      <c r="AQ23" s="31" t="n"/>
-      <c r="AR23" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS23" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT23" s="31" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="AU23" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10 06:27</t>
-        </is>
-      </c>
-      <c r="AV23" s="31" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW23" s="31" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX23" s="31" t="n">
-        <v>82.59999999999999</v>
-      </c>
-      <c r="AY23" s="31" t="inlineStr">
-        <is>
-          <t>🏆 QUALITY</t>
-        </is>
-      </c>
-      <c r="AZ23" s="31" t="inlineStr">
-        <is>
-          <t>🟢 HOLD</t>
-        </is>
-      </c>
-      <c r="BA23" s="31" t="inlineStr">
-        <is>
-          <t>🟢 LOW</t>
-        </is>
-      </c>
-      <c r="BB23" s="31" t="inlineStr">
-        <is>
-          <t>Compounder</t>
-        </is>
-      </c>
-      <c r="BC23" s="31" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="BD23" s="31" t="inlineStr">
-        <is>
-          <t>30 DAYS</t>
-        </is>
-      </c>
-      <c r="BE23" s="31" t="inlineStr">
-        <is>
-          <t>Watching @ 360.44</t>
-        </is>
-      </c>
-      <c r="BF23" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="BG23" s="31" t="inlineStr">
-        <is>
-          <t>⚪ No immediate execution</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="31" t="inlineStr">
-        <is>
-          <t>USA-R1-JPM-20260810-a6a394</t>
-        </is>
-      </c>
-      <c r="B24" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="C24" s="31" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D24" s="31" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E24" s="31" t="inlineStr">
-        <is>
-          <t>JPM</t>
-        </is>
-      </c>
-      <c r="F24" s="31" t="inlineStr">
-        <is>
-          <t>JPMorgan Chase</t>
-        </is>
-      </c>
-      <c r="G24" s="31" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H24" s="31" t="n"/>
-      <c r="I24" s="31" t="n"/>
-      <c r="J24" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="K24" s="31" t="n"/>
-      <c r="L24" s="31" t="n"/>
-      <c r="M24" s="31" t="n">
-        <v>78.40000000000001</v>
-      </c>
-      <c r="N24" s="31" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O24" s="31" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="P24" s="31" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q24" s="31" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 18 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R24" s="31" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #8 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S24" s="31" t="inlineStr">
-        <is>
-          <t>WARNING·STOP_LOSS_HIT·-5.0% ≤ -5.0% · exit</t>
-        </is>
-      </c>
-      <c r="T24" s="31" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="U24" s="31" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V24" s="31" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="W24" s="31" t="n"/>
-      <c r="X24" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="31" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z24" s="31" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA24" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AB24" s="31" t="n">
-        <v>359.24</v>
-      </c>
-      <c r="AC24" s="31" t="n">
-        <v>359.239990234375</v>
-      </c>
-      <c r="AD24" s="31" t="n">
-        <v>334.28</v>
-      </c>
-      <c r="AE24" s="31" t="n">
-        <v>347.92</v>
-      </c>
-      <c r="AF24" s="31" t="n">
-        <v>324.045</v>
-      </c>
-      <c r="AG24" s="31" t="n">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="AH24" s="31" t="n">
-        <v>368.388</v>
-      </c>
-      <c r="AI24" s="31" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AJ24" s="31" t="n">
-        <v>394.1751600000001</v>
-      </c>
-      <c r="AK24" s="31" t="n">
-        <v>9.720000000000001</v>
-      </c>
-      <c r="AL24" s="31" t="n">
-        <v>359.24</v>
-      </c>
-      <c r="AM24" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN24" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO24" s="31" t="n"/>
-      <c r="AP24" s="31" t="n"/>
-      <c r="AQ24" s="31" t="n"/>
-      <c r="AR24" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS24" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT24" s="31" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU24" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10 06:27</t>
-        </is>
-      </c>
-      <c r="AV24" s="31" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW24" s="31" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX24" s="31" t="n"/>
-      <c r="AY24" s="31" t="inlineStr"/>
-      <c r="AZ24" s="31" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA24" s="31" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB24" s="31" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC24" s="31" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD24" s="31" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE24" s="31" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 324.05</t>
-        </is>
-      </c>
-      <c r="BF24" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="BG24" s="31" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="31" t="inlineStr">
-        <is>
-          <t>USA-R1-GS-20260810-c6e885</t>
-        </is>
-      </c>
-      <c r="B25" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="C25" s="31" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D25" s="31" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E25" s="31" t="inlineStr">
-        <is>
-          <t>GS</t>
-        </is>
-      </c>
-      <c r="F25" s="31" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="G25" s="31" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H25" s="31" t="n"/>
-      <c r="I25" s="31" t="n"/>
-      <c r="J25" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="K25" s="31" t="n"/>
-      <c r="L25" s="31" t="n"/>
-      <c r="M25" s="31" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="N25" s="31" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O25" s="31" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="P25" s="31" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q25" s="31" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 9 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R25" s="31" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #9 · Conf 51% · momentum → · band HOLD · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S25" s="31" t="n"/>
-      <c r="T25" s="31" t="n">
-        <v>51</v>
-      </c>
-      <c r="U25" s="31" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V25" s="31" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="W25" s="31" t="n"/>
-      <c r="X25" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" s="31" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z25" s="31" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA25" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AB25" s="31" t="n">
-        <v>1060.38</v>
-      </c>
-      <c r="AC25" s="31" t="n">
-        <v>1060.380004882812</v>
-      </c>
-      <c r="AD25" s="31" t="n">
-        <v>1043.92</v>
-      </c>
-      <c r="AE25" s="31" t="n">
-        <v>1086.52</v>
-      </c>
-      <c r="AF25" s="31" t="n">
-        <v>1011.959</v>
-      </c>
-      <c r="AG25" s="31" t="n">
-        <v>-4.57</v>
-      </c>
-      <c r="AH25" s="31" t="n">
-        <v>1150.4376</v>
-      </c>
-      <c r="AI25" s="31" t="n">
-        <v>8.49</v>
-      </c>
-      <c r="AJ25" s="31" t="n">
-        <v>1230.968232</v>
-      </c>
-      <c r="AK25" s="31" t="n">
-        <v>16.09</v>
-      </c>
-      <c r="AL25" s="31" t="n">
-        <v>1060.38</v>
-      </c>
-      <c r="AM25" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN25" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO25" s="31" t="n"/>
-      <c r="AP25" s="31" t="n"/>
-      <c r="AQ25" s="31" t="n"/>
-      <c r="AR25" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS25" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT25" s="31" t="n">
-        <v>8.49</v>
-      </c>
-      <c r="AU25" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10 06:27</t>
-        </is>
-      </c>
-      <c r="AV25" s="31" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW25" s="31" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX25" s="31" t="n"/>
-      <c r="AY25" s="31" t="inlineStr"/>
-      <c r="AZ25" s="31" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA25" s="31" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB25" s="31" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC25" s="31" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD25" s="31" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE25" s="31" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 1011.96</t>
-        </is>
-      </c>
-      <c r="BF25" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="BG25" s="31" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="31" t="inlineStr">
-        <is>
-          <t>USA-R1-MMM-20260810-0649c0</t>
-        </is>
-      </c>
-      <c r="B26" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="C26" s="31" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D26" s="31" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E26" s="31" t="inlineStr">
-        <is>
-          <t>MMM</t>
-        </is>
-      </c>
-      <c r="F26" s="31" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
-      <c r="G26" s="31" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H26" s="31" t="n"/>
-      <c r="I26" s="31" t="n"/>
-      <c r="J26" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="K26" s="31" t="n"/>
-      <c r="L26" s="31" t="n"/>
-      <c r="M26" s="31" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="N26" s="31" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O26" s="31" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="P26" s="31" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q26" s="31" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 2d (high) (+17 more) → -1.0pts · crude +19.8% (rising) → +1.0pts · 15 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R26" s="31" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 54% · momentum → · band HOLD · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S26" s="31" t="inlineStr">
-        <is>
-          <t>CRITICAL·DEEP_LOSS·-12.2% ≤ -8.0% · EXIT URGENT</t>
-        </is>
-      </c>
-      <c r="T26" s="31" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="U26" s="31" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V26" s="31" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="W26" s="31" t="n"/>
-      <c r="X26" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="31" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z26" s="31" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA26" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="AB26" s="31" t="n">
-        <v>182.08</v>
-      </c>
-      <c r="AC26" s="31" t="n">
-        <v>182.0800018310547</v>
-      </c>
-      <c r="AD26" s="31" t="n">
-        <v>156.64</v>
-      </c>
-      <c r="AE26" s="31" t="n">
-        <v>163.04</v>
-      </c>
-      <c r="AF26" s="31" t="n">
-        <v>151.848</v>
-      </c>
-      <c r="AG26" s="31" t="n">
-        <v>-16.6</v>
-      </c>
-      <c r="AH26" s="31" t="n">
-        <v>172.6272</v>
-      </c>
-      <c r="AI26" s="31" t="n">
-        <v>-5.19</v>
-      </c>
-      <c r="AJ26" s="31" t="n">
-        <v>184.711104</v>
-      </c>
-      <c r="AK26" s="31" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AL26" s="31" t="n">
-        <v>182.08</v>
-      </c>
-      <c r="AM26" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN26" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO26" s="31" t="n"/>
-      <c r="AP26" s="31" t="n"/>
-      <c r="AQ26" s="31" t="n"/>
-      <c r="AR26" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS26" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT26" s="31" t="n">
-        <v>-5.19</v>
-      </c>
-      <c r="AU26" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-10 06:27</t>
-        </is>
-      </c>
-      <c r="AV26" s="31" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW26" s="31" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX26" s="31" t="n"/>
-      <c r="AY26" s="31" t="inlineStr"/>
-      <c r="AZ26" s="31" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA26" s="31" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB26" s="31" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC26" s="31" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD26" s="31" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE26" s="31" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 151.85</t>
-        </is>
-      </c>
-      <c r="BF26" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="BG26" s="31" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="30" t="inlineStr">
-        <is>
-          <t>USA-R2-TRV-20260810-9cd25d</t>
-        </is>
-      </c>
-      <c r="B27" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="C27" s="30" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D27" s="30" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E27" s="30" t="inlineStr">
-        <is>
-          <t>TRV</t>
-        </is>
-      </c>
-      <c r="F27" s="30" t="inlineStr">
-        <is>
-          <t>Travelers</t>
-        </is>
-      </c>
-      <c r="G27" s="30" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="H27" s="30" t="n"/>
-      <c r="I27" s="30" t="n"/>
-      <c r="J27" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="L27" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="30" t="n">
-        <v>79.3</v>
-      </c>
-      <c r="N27" s="30" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O27" s="30" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="P27" s="30" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q27" s="30" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R27" s="30" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank → 1→1 · Conf 57% · band HOLD · 14d left · → BUY</t>
-        </is>
-      </c>
-      <c r="S27" s="30" t="n"/>
-      <c r="T27" s="30" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="U27" s="30" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V27" s="30" t="n">
-        <v>29.2</v>
-      </c>
-      <c r="W27" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="X27" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="30" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z27" s="30" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA27" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB27" s="30" t="n">
-        <v>382.45</v>
-      </c>
-      <c r="AC27" s="30" t="n">
-        <v>382.4500122070312</v>
-      </c>
-      <c r="AD27" s="30" t="n">
-        <v>365.29</v>
-      </c>
-      <c r="AE27" s="30" t="n">
-        <v>372.67</v>
-      </c>
-      <c r="AF27" s="30" t="n">
-        <v>346.84</v>
-      </c>
-      <c r="AG27" s="30" t="n">
-        <v>-9.31</v>
-      </c>
-      <c r="AH27" s="30" t="n">
-        <v>413.26</v>
-      </c>
-      <c r="AI27" s="30" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="AJ27" s="30" t="n">
-        <v>457.54</v>
-      </c>
-      <c r="AK27" s="30" t="n">
-        <v>19.63</v>
-      </c>
-      <c r="AL27" s="30" t="n">
-        <v>382.45</v>
-      </c>
-      <c r="AM27" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN27" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO27" s="30" t="n"/>
-      <c r="AP27" s="30" t="n"/>
-      <c r="AQ27" s="30" t="inlineStr">
-        <is>
-          <t>Momentum · Value · Trend</t>
-        </is>
-      </c>
-      <c r="AR27" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS27" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT27" s="30" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="AU27" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11 04:16</t>
-        </is>
-      </c>
-      <c r="AV27" s="30" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW27" s="30" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX27" s="30" t="n"/>
-      <c r="AY27" s="30" t="inlineStr"/>
-      <c r="AZ27" s="30" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA27" s="30" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB27" s="30" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC27" s="30" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD27" s="30" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE27" s="30" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 346.84</t>
-        </is>
-      </c>
-      <c r="BF27" s="30" t="inlineStr">
+      <c r="BE18" s="31" t="inlineStr">
+        <is>
+          <t>Trailing Stop @ 350.11</t>
+        </is>
+      </c>
+      <c r="BF18" s="31" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="BG27" s="30" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="31" t="inlineStr">
-        <is>
-          <t>USA-R2-V-20260810-69160d</t>
-        </is>
-      </c>
-      <c r="B28" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="C28" s="31" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D28" s="31" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="E28" s="31" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="F28" s="31" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="G28" s="31" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H28" s="31" t="n"/>
-      <c r="I28" s="31" t="n"/>
-      <c r="J28" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="K28" s="31" t="n">
-        <v>2</v>
-      </c>
-      <c r="L28" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="31" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="N28" s="31" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O28" s="31" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="P28" s="31" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q28" s="31" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R28" s="31" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-3.7%) · Rank → 2→2 · Conf 54% · band STRONG · 14d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S28" s="31" t="n"/>
-      <c r="T28" s="31" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="U28" s="31" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V28" s="31" t="n">
-        <v>27.8</v>
-      </c>
-      <c r="W28" s="31" t="n">
-        <v>4</v>
-      </c>
-      <c r="X28" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" s="31" t="n">
-        <v>17</v>
-      </c>
-      <c r="Z28" s="31" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA28" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB28" s="31" t="n">
-        <v>368.54</v>
-      </c>
-      <c r="AC28" s="31" t="n">
-        <v>368.5400085449219</v>
-      </c>
-      <c r="AD28" s="31" t="n">
-        <v>364.85</v>
-      </c>
-      <c r="AE28" s="31" t="n">
-        <v>372.23</v>
-      </c>
-      <c r="AF28" s="31" t="n">
-        <v>350.11</v>
-      </c>
-      <c r="AG28" s="31" t="n">
-        <v>-5</v>
-      </c>
-      <c r="AH28" s="31" t="n">
-        <v>398.02</v>
-      </c>
-      <c r="AI28" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ28" s="31" t="n">
-        <v>423.82</v>
-      </c>
-      <c r="AK28" s="31" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL28" s="31" t="n">
-        <v>368.54</v>
-      </c>
-      <c r="AM28" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN28" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO28" s="31" t="n"/>
-      <c r="AP28" s="31" t="n"/>
-      <c r="AQ28" s="31" t="inlineStr">
-        <is>
-          <t>Momentum · Trend · Quality</t>
-        </is>
-      </c>
-      <c r="AR28" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS28" s="31" t="n"/>
-      <c r="AT28" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11 04:16</t>
-        </is>
-      </c>
-      <c r="AV28" s="31" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW28" s="31" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX28" s="31" t="n"/>
-      <c r="AY28" s="31" t="inlineStr"/>
-      <c r="AZ28" s="31" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA28" s="31" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB28" s="31" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC28" s="31" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD28" s="31" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE28" s="31" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 350.11</t>
-        </is>
-      </c>
-      <c r="BF28" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="BG28" s="31" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="30" t="inlineStr">
-        <is>
-          <t>USA-R1-V-20260810-4d75a7</t>
-        </is>
-      </c>
-      <c r="B29" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="C29" s="30" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D29" s="30" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E29" s="30" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="F29" s="30" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="G29" s="30" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="H29" s="30" t="n"/>
-      <c r="I29" s="30" t="n"/>
-      <c r="J29" s="30" t="n">
-        <v>1</v>
-      </c>
-      <c r="K29" s="30" t="n"/>
-      <c r="L29" s="30" t="n"/>
-      <c r="M29" s="30" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="N29" s="30" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O29" s="30" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="P29" s="30" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q29" s="30" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R29" s="30" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #1 · Conf 54% · momentum → · band STRONG · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="S29" s="30" t="n"/>
-      <c r="T29" s="30" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="U29" s="30" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V29" s="30" t="n">
-        <v>64.3</v>
-      </c>
-      <c r="W29" s="30" t="n"/>
-      <c r="X29" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="30" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z29" s="30" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA29" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB29" s="30" t="n">
-        <v>368.54</v>
-      </c>
-      <c r="AC29" s="30" t="n">
-        <v>368.5400085449219</v>
-      </c>
-      <c r="AD29" s="30" t="n">
-        <v>351.39</v>
-      </c>
-      <c r="AE29" s="30" t="n">
-        <v>365.73</v>
-      </c>
-      <c r="AF29" s="30" t="n">
-        <v>340.632</v>
-      </c>
-      <c r="AG29" s="30" t="n">
-        <v>-7.57</v>
-      </c>
-      <c r="AH29" s="30" t="n">
-        <v>387.2448000000001</v>
-      </c>
-      <c r="AI29" s="30" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="AJ29" s="30" t="n">
-        <v>414.3519360000001</v>
-      </c>
-      <c r="AK29" s="30" t="n">
-        <v>12.43</v>
-      </c>
-      <c r="AL29" s="30" t="n">
-        <v>368.54</v>
-      </c>
-      <c r="AM29" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN29" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO29" s="30" t="n"/>
-      <c r="AP29" s="30" t="n"/>
-      <c r="AQ29" s="30" t="n"/>
-      <c r="AR29" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS29" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT29" s="30" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="AU29" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11 04:16</t>
-        </is>
-      </c>
-      <c r="AV29" s="30" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW29" s="30" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX29" s="30" t="n"/>
-      <c r="AY29" s="30" t="inlineStr"/>
-      <c r="AZ29" s="30" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA29" s="30" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB29" s="30" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC29" s="30" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD29" s="30" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE29" s="30" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 340.63</t>
-        </is>
-      </c>
-      <c r="BF29" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="BG29" s="30" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="30" t="inlineStr">
-        <is>
-          <t>USA-R1-TRV-20260810-6f873c</t>
-        </is>
-      </c>
-      <c r="B30" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="C30" s="30" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D30" s="30" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E30" s="30" t="inlineStr">
-        <is>
-          <t>TRV</t>
-        </is>
-      </c>
-      <c r="F30" s="30" t="inlineStr">
-        <is>
-          <t>Travelers</t>
-        </is>
-      </c>
-      <c r="G30" s="30" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="H30" s="30" t="n"/>
-      <c r="I30" s="30" t="n"/>
-      <c r="J30" s="30" t="n">
-        <v>2</v>
-      </c>
-      <c r="K30" s="30" t="n"/>
-      <c r="L30" s="30" t="n"/>
-      <c r="M30" s="30" t="n">
-        <v>79.3</v>
-      </c>
-      <c r="N30" s="30" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O30" s="30" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="P30" s="30" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q30" s="30" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 12 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R30" s="30" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-1.0%) · Rank #2 · Conf 57% · momentum → · band HOLD · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="S30" s="30" t="n"/>
-      <c r="T30" s="30" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="U30" s="30" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V30" s="30" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="W30" s="30" t="n"/>
-      <c r="X30" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" s="30" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z30" s="30" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA30" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB30" s="30" t="n">
-        <v>382.45</v>
-      </c>
-      <c r="AC30" s="30" t="n">
-        <v>382.4500122070312</v>
-      </c>
-      <c r="AD30" s="30" t="n">
-        <v>365.29</v>
-      </c>
-      <c r="AE30" s="30" t="n">
-        <v>372.67</v>
-      </c>
-      <c r="AF30" s="30" t="n">
-        <v>350.531</v>
-      </c>
-      <c r="AG30" s="30" t="n">
-        <v>-8.35</v>
-      </c>
-      <c r="AH30" s="30" t="n">
-        <v>413.26</v>
-      </c>
-      <c r="AI30" s="30" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="AJ30" s="30" t="n">
-        <v>442.1882</v>
-      </c>
-      <c r="AK30" s="30" t="n">
-        <v>15.62</v>
-      </c>
-      <c r="AL30" s="30" t="n">
-        <v>382.45</v>
-      </c>
-      <c r="AM30" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO30" s="30" t="n"/>
-      <c r="AP30" s="30" t="n"/>
-      <c r="AQ30" s="30" t="n"/>
-      <c r="AR30" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS30" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT30" s="30" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="AU30" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11 04:16</t>
-        </is>
-      </c>
-      <c r="AV30" s="30" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW30" s="30" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX30" s="30" t="n"/>
-      <c r="AY30" s="30" t="inlineStr"/>
-      <c r="AZ30" s="30" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA30" s="30" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB30" s="30" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC30" s="30" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD30" s="30" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE30" s="30" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 350.53</t>
-        </is>
-      </c>
-      <c r="BF30" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="BG30" s="30" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="30" t="inlineStr">
-        <is>
-          <t>USA-R1-NVDA-20260810-2aa027</t>
-        </is>
-      </c>
-      <c r="B31" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="C31" s="30" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D31" s="30" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E31" s="30" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="F31" s="30" t="inlineStr">
-        <is>
-          <t>NVIDIA</t>
-        </is>
-      </c>
-      <c r="G31" s="30" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="H31" s="30" t="n"/>
-      <c r="I31" s="30" t="n"/>
-      <c r="J31" s="30" t="n">
-        <v>3</v>
-      </c>
-      <c r="K31" s="30" t="n"/>
-      <c r="L31" s="30" t="n"/>
-      <c r="M31" s="30" t="n">
-        <v>67.5</v>
-      </c>
-      <c r="N31" s="30" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O31" s="30" t="n">
-        <v>46.6</v>
-      </c>
-      <c r="P31" s="30" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q31" s="30" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 21 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R31" s="30" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #3 · Conf 47% · momentum → · band HOLD · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="S31" s="30" t="inlineStr">
-        <is>
-          <t>WARNING·STOP_LOSS_HIT·-7.5% ≤ -5.0% · exit</t>
-        </is>
-      </c>
-      <c r="T31" s="30" t="n">
-        <v>47.3</v>
-      </c>
-      <c r="U31" s="30" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V31" s="30" t="n">
-        <v>55.7</v>
-      </c>
-      <c r="W31" s="30" t="n"/>
-      <c r="X31" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" s="30" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z31" s="30" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA31" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB31" s="30" t="n">
-        <v>219.22</v>
-      </c>
-      <c r="AC31" s="30" t="n">
-        <v>219.2200012207031</v>
-      </c>
-      <c r="AD31" s="30" t="n">
-        <v>198.75</v>
-      </c>
-      <c r="AE31" s="30" t="n">
-        <v>206.87</v>
-      </c>
-      <c r="AF31" s="30" t="n">
-        <v>192.6695</v>
-      </c>
-      <c r="AG31" s="30" t="n">
-        <v>-12.11</v>
-      </c>
-      <c r="AH31" s="30" t="n">
-        <v>219.0348</v>
-      </c>
-      <c r="AI31" s="30" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AJ31" s="30" t="n">
-        <v>234.367236</v>
-      </c>
-      <c r="AK31" s="30" t="n">
-        <v>6.91</v>
-      </c>
-      <c r="AL31" s="30" t="n">
-        <v>219.22</v>
-      </c>
-      <c r="AM31" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN31" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO31" s="30" t="n"/>
-      <c r="AP31" s="30" t="n"/>
-      <c r="AQ31" s="30" t="n"/>
-      <c r="AR31" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS31" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT31" s="30" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="AU31" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11 04:16</t>
-        </is>
-      </c>
-      <c r="AV31" s="30" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW31" s="30" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX31" s="30" t="n"/>
-      <c r="AY31" s="30" t="inlineStr"/>
-      <c r="AZ31" s="30" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA31" s="30" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB31" s="30" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC31" s="30" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD31" s="30" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE31" s="30" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 192.67</t>
-        </is>
-      </c>
-      <c r="BF31" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="BG31" s="30" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="30" t="inlineStr">
-        <is>
-          <t>USA-R1-MSFT-20260810-6110fc</t>
-        </is>
-      </c>
-      <c r="B32" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="C32" s="30" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D32" s="30" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E32" s="30" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="F32" s="30" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="G32" s="30" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="H32" s="30" t="n"/>
-      <c r="I32" s="30" t="n"/>
-      <c r="J32" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="K32" s="30" t="n"/>
-      <c r="L32" s="30" t="n"/>
-      <c r="M32" s="30" t="n">
-        <v>79.5</v>
-      </c>
-      <c r="N32" s="30" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O32" s="30" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="P32" s="30" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q32" s="30" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 33 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R32" s="30" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #4 · Conf 54% · momentum → · band HOLD · 91d left · → BUY</t>
-        </is>
-      </c>
-      <c r="S32" s="30" t="inlineStr">
-        <is>
-          <t>CRITICAL·DEEP_LOSS·-19.2% ≤ -8.0% · EXIT URGENT</t>
-        </is>
-      </c>
-      <c r="T32" s="30" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="U32" s="30" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V32" s="30" t="n">
-        <v>51.8</v>
-      </c>
-      <c r="W32" s="30" t="n"/>
-      <c r="X32" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="30" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z32" s="30" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA32" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB32" s="30" t="n">
-        <v>487.46</v>
-      </c>
-      <c r="AC32" s="30" t="n">
-        <v>487.4599914550781</v>
-      </c>
-      <c r="AD32" s="30" t="n">
-        <v>385.94</v>
-      </c>
-      <c r="AE32" s="30" t="n">
-        <v>401.7</v>
-      </c>
-      <c r="AF32" s="30" t="n">
-        <v>374.129</v>
-      </c>
-      <c r="AG32" s="30" t="n">
-        <v>-23.25</v>
-      </c>
-      <c r="AH32" s="30" t="n">
-        <v>425.3256</v>
-      </c>
-      <c r="AI32" s="30" t="n">
-        <v>-12.75</v>
-      </c>
-      <c r="AJ32" s="30" t="n">
-        <v>455.098392</v>
-      </c>
-      <c r="AK32" s="30" t="n">
-        <v>-6.64</v>
-      </c>
-      <c r="AL32" s="30" t="n">
-        <v>487.46</v>
-      </c>
-      <c r="AM32" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN32" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO32" s="30" t="n"/>
-      <c r="AP32" s="30" t="n"/>
-      <c r="AQ32" s="30" t="n"/>
-      <c r="AR32" s="30" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS32" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT32" s="30" t="n">
-        <v>-12.75</v>
-      </c>
-      <c r="AU32" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-11 04:16</t>
-        </is>
-      </c>
-      <c r="AV32" s="30" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW32" s="30" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX32" s="30" t="n"/>
-      <c r="AY32" s="30" t="inlineStr"/>
-      <c r="AZ32" s="30" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA32" s="30" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB32" s="30" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC32" s="30" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD32" s="30" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE32" s="30" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 374.13</t>
-        </is>
-      </c>
-      <c r="BF32" s="30" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="BG32" s="30" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="31" t="inlineStr">
-        <is>
-          <t>USA-R1-KO-20260810-af15a9</t>
-        </is>
-      </c>
-      <c r="B33" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="C33" s="31" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D33" s="31" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E33" s="31" t="inlineStr">
-        <is>
-          <t>KO</t>
-        </is>
-      </c>
-      <c r="F33" s="31" t="inlineStr">
-        <is>
-          <t>Coca-Cola</t>
-        </is>
-      </c>
-      <c r="G33" s="31" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H33" s="31" t="n"/>
-      <c r="I33" s="31" t="n"/>
-      <c r="J33" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="K33" s="31" t="n"/>
-      <c r="L33" s="31" t="n"/>
-      <c r="M33" s="31" t="n">
-        <v>84.09999999999999</v>
-      </c>
-      <c r="N33" s="31" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O33" s="31" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="P33" s="31" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q33" s="31" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 11 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R33" s="31" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #5 · Conf 50% · momentum → · band STRONG · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S33" s="31" t="inlineStr">
-        <is>
-          <t>WARNING·STOP_LOSS_HIT·-6.1% ≤ -5.0% · exit</t>
-        </is>
-      </c>
-      <c r="T33" s="31" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="U33" s="31" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V33" s="31" t="n">
-        <v>46.7</v>
-      </c>
-      <c r="W33" s="31" t="n"/>
-      <c r="X33" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" s="31" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z33" s="31" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA33" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB33" s="31" t="n">
-        <v>86.83</v>
-      </c>
-      <c r="AC33" s="31" t="n">
-        <v>86.83000183105469</v>
-      </c>
-      <c r="AD33" s="31" t="n">
-        <v>79.93000000000001</v>
-      </c>
-      <c r="AE33" s="31" t="n">
-        <v>83.19</v>
-      </c>
-      <c r="AF33" s="31" t="n">
-        <v>77.482</v>
-      </c>
-      <c r="AG33" s="31" t="n">
-        <v>-10.77</v>
-      </c>
-      <c r="AH33" s="31" t="n">
-        <v>88.0848</v>
-      </c>
-      <c r="AI33" s="31" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AJ33" s="31" t="n">
-        <v>94.250736</v>
-      </c>
-      <c r="AK33" s="31" t="n">
-        <v>8.550000000000001</v>
-      </c>
-      <c r="AL33" s="31" t="n">
-        <v>86.83</v>
-      </c>
-      <c r="AM33" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN33" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO33" s="31" t="n"/>
-      <c r="AP33" s="31" t="n"/>
-      <c r="AQ33" s="31" t="n"/>
-      <c r="AR33" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS33" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT33" s="31" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AU33" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11 04:16</t>
-        </is>
-      </c>
-      <c r="AV33" s="31" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW33" s="31" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX33" s="31" t="n"/>
-      <c r="AY33" s="31" t="inlineStr"/>
-      <c r="AZ33" s="31" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA33" s="31" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB33" s="31" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC33" s="31" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD33" s="31" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE33" s="31" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 77.48</t>
-        </is>
-      </c>
-      <c r="BF33" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="BG33" s="31" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="31" t="inlineStr">
-        <is>
-          <t>USA-R1-HON-20260810-0b8118</t>
-        </is>
-      </c>
-      <c r="B34" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="C34" s="31" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D34" s="31" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E34" s="31" t="inlineStr">
-        <is>
-          <t>HON</t>
-        </is>
-      </c>
-      <c r="F34" s="31" t="inlineStr">
-        <is>
-          <t>Honeywell</t>
-        </is>
-      </c>
-      <c r="G34" s="31" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H34" s="31" t="n"/>
-      <c r="I34" s="31" t="n"/>
-      <c r="J34" s="31" t="n">
-        <v>6</v>
-      </c>
-      <c r="K34" s="31" t="n"/>
-      <c r="L34" s="31" t="n"/>
-      <c r="M34" s="31" t="n">
-        <v>76</v>
-      </c>
-      <c r="N34" s="31" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O34" s="31" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="P34" s="31" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q34" s="31" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 48 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R34" s="31" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #6 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S34" s="31" t="inlineStr">
-        <is>
-          <t>CRITICAL·DEEP_LOSS·-9.3% ≤ -8.0% · EXIT URGENT</t>
-        </is>
-      </c>
-      <c r="T34" s="31" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="U34" s="31" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V34" s="31" t="n">
-        <v>46.5</v>
-      </c>
-      <c r="W34" s="31" t="n"/>
-      <c r="X34" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" s="31" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z34" s="31" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA34" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB34" s="31" t="n">
-        <v>248.12</v>
-      </c>
-      <c r="AC34" s="31" t="n">
-        <v>248.1199951171875</v>
-      </c>
-      <c r="AD34" s="31" t="n">
-        <v>220.52</v>
-      </c>
-      <c r="AE34" s="31" t="n">
-        <v>229.52</v>
-      </c>
-      <c r="AF34" s="31" t="n">
-        <v>213.769</v>
-      </c>
-      <c r="AG34" s="31" t="n">
-        <v>-13.84</v>
-      </c>
-      <c r="AH34" s="31" t="n">
-        <v>243.0216</v>
-      </c>
-      <c r="AI34" s="31" t="n">
-        <v>-2.05</v>
-      </c>
-      <c r="AJ34" s="31" t="n">
-        <v>260.0331120000001</v>
-      </c>
-      <c r="AK34" s="31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AL34" s="31" t="n">
-        <v>248.12</v>
-      </c>
-      <c r="AM34" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN34" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO34" s="31" t="n"/>
-      <c r="AP34" s="31" t="n"/>
-      <c r="AQ34" s="31" t="n"/>
-      <c r="AR34" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS34" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT34" s="31" t="n">
-        <v>-2.05</v>
-      </c>
-      <c r="AU34" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11 04:16</t>
-        </is>
-      </c>
-      <c r="AV34" s="31" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW34" s="31" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX34" s="31" t="n"/>
-      <c r="AY34" s="31" t="inlineStr"/>
-      <c r="AZ34" s="31" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA34" s="31" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB34" s="31" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC34" s="31" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD34" s="31" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE34" s="31" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 213.77</t>
-        </is>
-      </c>
-      <c r="BF34" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="BG34" s="31" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="31" t="inlineStr">
-        <is>
-          <t>USA-R1-AAPL-20260810-d82b13</t>
-        </is>
-      </c>
-      <c r="B35" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="C35" s="31" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D35" s="31" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E35" s="31" t="inlineStr">
-        <is>
-          <t>AAPL</t>
-        </is>
-      </c>
-      <c r="F35" s="31" t="inlineStr">
-        <is>
-          <t>Apple</t>
-        </is>
-      </c>
-      <c r="G35" s="31" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H35" s="31" t="n"/>
-      <c r="I35" s="31" t="n"/>
-      <c r="J35" s="31" t="n">
-        <v>7</v>
-      </c>
-      <c r="K35" s="31" t="n"/>
-      <c r="L35" s="31" t="n"/>
-      <c r="M35" s="31" t="n">
-        <v>83.5</v>
-      </c>
-      <c r="N35" s="31" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O35" s="31" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="P35" s="31" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q35" s="31" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 5 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R35" s="31" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #7 · Conf 50% · momentum → · band STRONG · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S35" s="31" t="n"/>
-      <c r="T35" s="31" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="U35" s="31" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V35" s="31" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="W35" s="31" t="n"/>
-      <c r="X35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" s="31" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z35" s="31" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA35" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB35" s="31" t="n">
-        <v>311</v>
-      </c>
-      <c r="AC35" s="31" t="n">
-        <v>311</v>
-      </c>
-      <c r="AD35" s="31" t="n">
-        <v>327.07</v>
-      </c>
-      <c r="AE35" s="31" t="n">
-        <v>340.41</v>
-      </c>
-      <c r="AF35" s="31" t="n">
-        <v>317.053</v>
-      </c>
-      <c r="AG35" s="31" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH35" s="31" t="n">
-        <v>360.4392</v>
-      </c>
-      <c r="AI35" s="31" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="AJ35" s="31" t="n">
-        <v>385.669944</v>
-      </c>
-      <c r="AK35" s="31" t="n">
-        <v>24.01</v>
-      </c>
-      <c r="AL35" s="31" t="n">
-        <v>311</v>
-      </c>
-      <c r="AM35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN35" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO35" s="31" t="n"/>
-      <c r="AP35" s="31" t="n"/>
-      <c r="AQ35" s="31" t="n"/>
-      <c r="AR35" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS35" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT35" s="31" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="AU35" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11 04:16</t>
-        </is>
-      </c>
-      <c r="AV35" s="31" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW35" s="31" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX35" s="31" t="n">
-        <v>82.59999999999999</v>
-      </c>
-      <c r="AY35" s="31" t="inlineStr">
-        <is>
-          <t>🏆 QUALITY</t>
-        </is>
-      </c>
-      <c r="AZ35" s="31" t="inlineStr">
-        <is>
-          <t>🟢 HOLD</t>
-        </is>
-      </c>
-      <c r="BA35" s="31" t="inlineStr">
-        <is>
-          <t>🟢 LOW</t>
-        </is>
-      </c>
-      <c r="BB35" s="31" t="inlineStr">
-        <is>
-          <t>Compounder</t>
-        </is>
-      </c>
-      <c r="BC35" s="31" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="BD35" s="31" t="inlineStr">
-        <is>
-          <t>30 DAYS</t>
-        </is>
-      </c>
-      <c r="BE35" s="31" t="inlineStr">
-        <is>
-          <t>Watching @ 360.44</t>
-        </is>
-      </c>
-      <c r="BF35" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="BG35" s="31" t="inlineStr">
-        <is>
-          <t>⚪ No immediate execution</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="31" t="inlineStr">
-        <is>
-          <t>USA-R1-JPM-20260810-a6a394</t>
-        </is>
-      </c>
-      <c r="B36" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="C36" s="31" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D36" s="31" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E36" s="31" t="inlineStr">
-        <is>
-          <t>JPM</t>
-        </is>
-      </c>
-      <c r="F36" s="31" t="inlineStr">
-        <is>
-          <t>JPMorgan Chase</t>
-        </is>
-      </c>
-      <c r="G36" s="31" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H36" s="31" t="n"/>
-      <c r="I36" s="31" t="n"/>
-      <c r="J36" s="31" t="n">
-        <v>8</v>
-      </c>
-      <c r="K36" s="31" t="n"/>
-      <c r="L36" s="31" t="n"/>
-      <c r="M36" s="31" t="n">
-        <v>78.40000000000001</v>
-      </c>
-      <c r="N36" s="31" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O36" s="31" t="n">
-        <v>48.9</v>
-      </c>
-      <c r="P36" s="31" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q36" s="31" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 18 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R36" s="31" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #8 · Conf 50% · momentum → · band HOLD · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S36" s="31" t="inlineStr">
-        <is>
-          <t>WARNING·STOP_LOSS_HIT·-5.0% ≤ -5.0% · exit</t>
-        </is>
-      </c>
-      <c r="T36" s="31" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="U36" s="31" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V36" s="31" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="W36" s="31" t="n"/>
-      <c r="X36" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" s="31" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z36" s="31" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA36" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB36" s="31" t="n">
-        <v>359.24</v>
-      </c>
-      <c r="AC36" s="31" t="n">
-        <v>359.239990234375</v>
-      </c>
-      <c r="AD36" s="31" t="n">
-        <v>334.28</v>
-      </c>
-      <c r="AE36" s="31" t="n">
-        <v>347.92</v>
-      </c>
-      <c r="AF36" s="31" t="n">
-        <v>324.045</v>
-      </c>
-      <c r="AG36" s="31" t="n">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="AH36" s="31" t="n">
-        <v>368.388</v>
-      </c>
-      <c r="AI36" s="31" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AJ36" s="31" t="n">
-        <v>394.1751600000001</v>
-      </c>
-      <c r="AK36" s="31" t="n">
-        <v>9.720000000000001</v>
-      </c>
-      <c r="AL36" s="31" t="n">
-        <v>359.24</v>
-      </c>
-      <c r="AM36" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN36" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO36" s="31" t="n"/>
-      <c r="AP36" s="31" t="n"/>
-      <c r="AQ36" s="31" t="n"/>
-      <c r="AR36" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS36" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT36" s="31" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU36" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11 04:16</t>
-        </is>
-      </c>
-      <c r="AV36" s="31" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW36" s="31" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX36" s="31" t="n"/>
-      <c r="AY36" s="31" t="inlineStr"/>
-      <c r="AZ36" s="31" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA36" s="31" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB36" s="31" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC36" s="31" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD36" s="31" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE36" s="31" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 324.05</t>
-        </is>
-      </c>
-      <c r="BF36" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="BG36" s="31" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="31" t="inlineStr">
-        <is>
-          <t>USA-R1-GS-20260810-c6e885</t>
-        </is>
-      </c>
-      <c r="B37" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="C37" s="31" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D37" s="31" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E37" s="31" t="inlineStr">
-        <is>
-          <t>GS</t>
-        </is>
-      </c>
-      <c r="F37" s="31" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="G37" s="31" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H37" s="31" t="n"/>
-      <c r="I37" s="31" t="n"/>
-      <c r="J37" s="31" t="n">
-        <v>9</v>
-      </c>
-      <c r="K37" s="31" t="n"/>
-      <c r="L37" s="31" t="n"/>
-      <c r="M37" s="31" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="N37" s="31" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O37" s="31" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="P37" s="31" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q37" s="31" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 9 insider Form 4 filings last 90d → +1.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R37" s="31" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #9 · Conf 51% · momentum → · band HOLD · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S37" s="31" t="n"/>
-      <c r="T37" s="31" t="n">
-        <v>51</v>
-      </c>
-      <c r="U37" s="31" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V37" s="31" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="W37" s="31" t="n"/>
-      <c r="X37" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" s="31" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z37" s="31" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA37" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB37" s="31" t="n">
-        <v>1060.38</v>
-      </c>
-      <c r="AC37" s="31" t="n">
-        <v>1060.380004882812</v>
-      </c>
-      <c r="AD37" s="31" t="n">
-        <v>1043.92</v>
-      </c>
-      <c r="AE37" s="31" t="n">
-        <v>1086.52</v>
-      </c>
-      <c r="AF37" s="31" t="n">
-        <v>1011.959</v>
-      </c>
-      <c r="AG37" s="31" t="n">
-        <v>-4.57</v>
-      </c>
-      <c r="AH37" s="31" t="n">
-        <v>1150.4376</v>
-      </c>
-      <c r="AI37" s="31" t="n">
-        <v>8.49</v>
-      </c>
-      <c r="AJ37" s="31" t="n">
-        <v>1230.968232</v>
-      </c>
-      <c r="AK37" s="31" t="n">
-        <v>16.09</v>
-      </c>
-      <c r="AL37" s="31" t="n">
-        <v>1060.38</v>
-      </c>
-      <c r="AM37" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN37" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO37" s="31" t="n"/>
-      <c r="AP37" s="31" t="n"/>
-      <c r="AQ37" s="31" t="n"/>
-      <c r="AR37" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS37" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT37" s="31" t="n">
-        <v>8.49</v>
-      </c>
-      <c r="AU37" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11 04:16</t>
-        </is>
-      </c>
-      <c r="AV37" s="31" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW37" s="31" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX37" s="31" t="n"/>
-      <c r="AY37" s="31" t="inlineStr"/>
-      <c r="AZ37" s="31" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA37" s="31" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB37" s="31" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC37" s="31" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD37" s="31" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE37" s="31" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 1011.96</t>
-        </is>
-      </c>
-      <c r="BF37" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="BG37" s="31" t="inlineStr">
-        <is>
-          <t>🟡 Normal window · 10:00-14:30 IST</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="31" t="inlineStr">
-        <is>
-          <t>USA-R1-MMM-20260810-0649c0</t>
-        </is>
-      </c>
-      <c r="B38" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="C38" s="31" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="D38" s="31" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="E38" s="31" t="inlineStr">
-        <is>
-          <t>MMM</t>
-        </is>
-      </c>
-      <c r="F38" s="31" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
-      <c r="G38" s="31" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="H38" s="31" t="n"/>
-      <c r="I38" s="31" t="n"/>
-      <c r="J38" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="K38" s="31" t="n"/>
-      <c r="L38" s="31" t="n"/>
-      <c r="M38" s="31" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="N38" s="31" t="inlineStr">
-        <is>
-          <t>🟢</t>
-        </is>
-      </c>
-      <c r="O38" s="31" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="P38" s="31" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="Q38" s="31" t="inlineStr">
-        <is>
-          <t>FOMC Rate Decision in 1d (high) (+26 more) → -2.0pts · crude +19.8% (rising) → +1.0pts · 15 insider Form 4 filings last 90d → +2.0pts (note: buy/sell parse pending)</t>
-        </is>
-      </c>
-      <c r="R38" s="31" t="inlineStr">
-        <is>
-          <t>🟢 BUY (Δ-2.0%) · Rank #10 · Conf 54% · momentum → · band HOLD · 91d left · → HOLD</t>
-        </is>
-      </c>
-      <c r="S38" s="31" t="inlineStr">
-        <is>
-          <t>CRITICAL·DEEP_LOSS·-12.2% ≤ -8.0% · EXIT URGENT</t>
-        </is>
-      </c>
-      <c r="T38" s="31" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="U38" s="31" t="inlineStr">
-        <is>
-          <t>Calibrated</t>
-        </is>
-      </c>
-      <c r="V38" s="31" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="W38" s="31" t="n"/>
-      <c r="X38" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" s="31" t="n">
-        <v>90</v>
-      </c>
-      <c r="Z38" s="31" t="n">
-        <v>91</v>
-      </c>
-      <c r="AA38" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="AB38" s="31" t="n">
-        <v>182.08</v>
-      </c>
-      <c r="AC38" s="31" t="n">
-        <v>182.0800018310547</v>
-      </c>
-      <c r="AD38" s="31" t="n">
-        <v>156.64</v>
-      </c>
-      <c r="AE38" s="31" t="n">
-        <v>163.04</v>
-      </c>
-      <c r="AF38" s="31" t="n">
-        <v>151.848</v>
-      </c>
-      <c r="AG38" s="31" t="n">
-        <v>-16.6</v>
-      </c>
-      <c r="AH38" s="31" t="n">
-        <v>172.6272</v>
-      </c>
-      <c r="AI38" s="31" t="n">
-        <v>-5.19</v>
-      </c>
-      <c r="AJ38" s="31" t="n">
-        <v>184.711104</v>
-      </c>
-      <c r="AK38" s="31" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AL38" s="31" t="n">
-        <v>182.08</v>
-      </c>
-      <c r="AM38" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN38" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO38" s="31" t="n"/>
-      <c r="AP38" s="31" t="n"/>
-      <c r="AQ38" s="31" t="n"/>
-      <c r="AR38" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AS38" s="31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT38" s="31" t="n">
-        <v>-5.19</v>
-      </c>
-      <c r="AU38" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-11 04:16</t>
-        </is>
-      </c>
-      <c r="AV38" s="31" t="inlineStr">
-        <is>
-          <t>LargeCap (S&amp;P 500)</t>
-        </is>
-      </c>
-      <c r="AW38" s="31" t="inlineStr">
-        <is>
-          <t>🆕 NEW</t>
-        </is>
-      </c>
-      <c r="AX38" s="31" t="n"/>
-      <c r="AY38" s="31" t="inlineStr"/>
-      <c r="AZ38" s="31" t="inlineStr">
-        <is>
-          <t>🟠 PROTECT</t>
-        </is>
-      </c>
-      <c r="BA38" s="31" t="inlineStr">
-        <is>
-          <t>🟡 MEDIUM</t>
-        </is>
-      </c>
-      <c r="BB38" s="31" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="BC38" s="31" t="inlineStr">
-        <is>
-          <t>TIGHTEN STOP</t>
-        </is>
-      </c>
-      <c r="BD38" s="31" t="inlineStr">
-        <is>
-          <t>TOMORROW</t>
-        </is>
-      </c>
-      <c r="BE38" s="31" t="inlineStr">
-        <is>
-          <t>Trailing Stop @ 151.85</t>
-        </is>
-      </c>
-      <c r="BF38" s="31" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="BG38" s="31" t="inlineStr">
+      <c r="BG18" s="31" t="inlineStr">
         <is>
           <t>🟡 Normal window · 10:00-14:30 IST</t>
         </is>
@@ -40112,7 +35954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -40207,50 +36049,46 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RETIRED_DORMANT</t>
+          <t>ACTIVE_PRODUCTION</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>R1 formally retired per configs/aegis_retirement.yaml · DORMANT_BY_DESIGN · historical records preserved</t>
+          <t>runner produced signals and/or opened positions in window</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38</v>
+        <v>508</v>
       </c>
       <c r="E4" t="n">
-        <v>38</v>
+        <v>508</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>26</v>
+        <v>502</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
+        <v>5.66</v>
+      </c>
+      <c r="J4" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-3.45</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>INSUFFICIENT (n=0 · minimum 30 for stable statistics)</t>
+          <t>INSUFFICIENT (n=9 · minimum 30 for stable statistics)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -40262,104 +36100,53 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>COMBINED</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ACTIVE_PRODUCTION</t>
+          <t>PIPELINE_FAILURE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>runner produced signals and/or opened positions in window</t>
+          <t>0 signals AND 0 opened positions in window AND no recent engine activity in aegis_daily_v2_history · investigate engine health</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>508</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>508</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>502</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>5.66</v>
-      </c>
-      <c r="J5" t="n">
-        <v>33.3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-3.45</v>
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>INSUFFICIENT (n=9 · minimum 30 for stable statistics)</t>
+          <t>INSUFFICIENT (n=0 · minimum 30 for stable statistics)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
-        <is>
-          <t>canonical:runner_accountability</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>COMBINED</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>PIPELINE_FAILURE</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0 signals AND 0 opened positions in window AND no recent engine activity in aegis_daily_v2_history · investigate engine health</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>INSUFFICIENT (n=0 · minimum 30 for stable statistics)</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
         <is>
           <t>canonical:runner_accountability</t>
         </is>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -2990,7 +2990,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M5" s="4" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -3558,7 +3558,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -3617,7 +3617,7 @@
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M28" s="4" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -4443,7 +4443,7 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -4502,7 +4502,7 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M30" s="4" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M34" s="4" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M36" s="4" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -4915,7 +4915,7 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M38" s="4" t="inlineStr">
@@ -4996,7 +4996,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -5210,7 +5210,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M42" s="4" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -5269,7 +5269,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M43" s="4" t="inlineStr">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M44" s="4" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
@@ -5409,7 +5409,7 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M46" s="4" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -5505,7 +5505,7 @@
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M47" s="4" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M48" s="4" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M49" s="4" t="inlineStr">
@@ -5645,7 +5645,7 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M50" s="4" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M51" s="4" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M52" s="4" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M53" s="4" t="inlineStr">
@@ -5881,7 +5881,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M54" s="4" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M55" s="4" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M56" s="4" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M57" s="4" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M58" s="4" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M59" s="4" t="inlineStr">
@@ -6235,7 +6235,7 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -6272,7 +6272,7 @@
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M60" s="4" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M61" s="4" t="inlineStr">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M62" s="4" t="inlineStr">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -6449,7 +6449,7 @@
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M63" s="4" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M64" s="4" t="inlineStr">
@@ -6530,7 +6530,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M65" s="4" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -6626,7 +6626,7 @@
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M66" s="4" t="inlineStr">
@@ -6648,7 +6648,7 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -6685,7 +6685,7 @@
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M67" s="4" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M68" s="4" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M69" s="4" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M70" s="4" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M71" s="4" t="inlineStr">
@@ -6943,7 +6943,7 @@
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M72" s="4" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M73" s="4" t="inlineStr">
@@ -7061,7 +7061,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M74" s="4" t="inlineStr">
@@ -7120,7 +7120,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M75" s="4" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M76" s="4" t="inlineStr">
@@ -7238,7 +7238,7 @@
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M77" s="4" t="inlineStr">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M78" s="4" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M79" s="4" t="inlineStr">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M80" s="4" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M81" s="4" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M82" s="4" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M83" s="4" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M84" s="4" t="inlineStr">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M85" s="4" t="inlineStr">
@@ -7769,7 +7769,7 @@
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M86" s="4" t="inlineStr">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -7865,7 +7865,7 @@
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M87" s="4" t="inlineStr">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M88" s="4" t="inlineStr">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M89" s="4" t="inlineStr">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M90" s="4" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M91" s="4" t="inlineStr">
@@ -8123,7 +8123,7 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M92" s="4" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -8219,7 +8219,7 @@
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M93" s="4" t="inlineStr">
@@ -8241,7 +8241,7 @@
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -8278,7 +8278,7 @@
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M94" s="4" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
@@ -8337,7 +8337,7 @@
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M95" s="4" t="inlineStr">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M96" s="4" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M97" s="4" t="inlineStr">
@@ -8477,7 +8477,7 @@
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M98" s="4" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -8573,7 +8573,7 @@
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M99" s="4" t="inlineStr">
@@ -8595,7 +8595,7 @@
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M100" s="4" t="inlineStr">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M101" s="4" t="inlineStr">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M102" s="4" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -8809,7 +8809,7 @@
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M103" s="4" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M104" s="4" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -8927,7 +8927,7 @@
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M105" s="4" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
@@ -8986,7 +8986,7 @@
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M106" s="4" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
@@ -9045,7 +9045,7 @@
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M107" s="4" t="inlineStr">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M108" s="4" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -9163,7 +9163,7 @@
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M109" s="4" t="inlineStr">
@@ -9185,7 +9185,7 @@
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M110" s="4" t="inlineStr">
@@ -9244,7 +9244,7 @@
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M111" s="4" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M112" s="4" t="inlineStr">
@@ -9362,7 +9362,7 @@
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -9399,7 +9399,7 @@
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M113" s="4" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
@@ -9458,7 +9458,7 @@
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M114" s="4" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M115" s="4" t="inlineStr">
@@ -9539,7 +9539,7 @@
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
@@ -9576,7 +9576,7 @@
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M116" s="4" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
@@ -9635,7 +9635,7 @@
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M117" s="4" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
@@ -9694,7 +9694,7 @@
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M118" s="4" t="inlineStr">
@@ -9716,7 +9716,7 @@
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
@@ -9753,7 +9753,7 @@
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M119" s="4" t="inlineStr">
@@ -9775,7 +9775,7 @@
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
@@ -9812,7 +9812,7 @@
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M120" s="4" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M121" s="4" t="inlineStr">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
@@ -9930,7 +9930,7 @@
       </c>
       <c r="L122" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M122" s="4" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="L123" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M123" s="4" t="inlineStr">
@@ -10011,7 +10011,7 @@
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
@@ -10048,7 +10048,7 @@
       </c>
       <c r="L124" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M124" s="4" t="inlineStr">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
@@ -10107,7 +10107,7 @@
       </c>
       <c r="L125" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M125" s="4" t="inlineStr">
@@ -10129,7 +10129,7 @@
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="L126" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M126" s="4" t="inlineStr">
@@ -10188,7 +10188,7 @@
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
@@ -10225,7 +10225,7 @@
       </c>
       <c r="L127" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M127" s="4" t="inlineStr">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
@@ -10284,7 +10284,7 @@
       </c>
       <c r="L128" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M128" s="4" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="L129" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M129" s="4" t="inlineStr">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
@@ -10402,7 +10402,7 @@
       </c>
       <c r="L130" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M130" s="4" t="inlineStr">
@@ -10424,7 +10424,7 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
@@ -10461,7 +10461,7 @@
       </c>
       <c r="L131" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M131" s="4" t="inlineStr">
@@ -10483,7 +10483,7 @@
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
@@ -10520,7 +10520,7 @@
       </c>
       <c r="L132" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M132" s="4" t="inlineStr">
@@ -10542,7 +10542,7 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
@@ -10579,7 +10579,7 @@
       </c>
       <c r="L133" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M133" s="4" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
@@ -10638,7 +10638,7 @@
       </c>
       <c r="L134" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M134" s="4" t="inlineStr">
@@ -10660,7 +10660,7 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="L135" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M135" s="4" t="inlineStr">
@@ -10719,7 +10719,7 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="L136" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M136" s="4" t="inlineStr">
@@ -10778,7 +10778,7 @@
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
@@ -10815,7 +10815,7 @@
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M137" s="4" t="inlineStr">
@@ -10837,7 +10837,7 @@
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M138" s="4" t="inlineStr">
@@ -10896,7 +10896,7 @@
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
@@ -10933,7 +10933,7 @@
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M139" s="4" t="inlineStr">
@@ -10955,7 +10955,7 @@
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
@@ -10992,7 +10992,7 @@
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M140" s="4" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="L141" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M141" s="4" t="inlineStr">
@@ -11073,7 +11073,7 @@
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
@@ -11110,7 +11110,7 @@
       </c>
       <c r="L142" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M142" s="4" t="inlineStr">
@@ -11132,7 +11132,7 @@
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
@@ -11169,7 +11169,7 @@
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M143" s="4" t="inlineStr">
@@ -11191,7 +11191,7 @@
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M144" s="4" t="inlineStr">
@@ -11250,7 +11250,7 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
@@ -11287,7 +11287,7 @@
       </c>
       <c r="L145" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M145" s="4" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M146" s="4" t="inlineStr">
@@ -11368,7 +11368,7 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
@@ -11405,7 +11405,7 @@
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M147" s="4" t="inlineStr">
@@ -11427,7 +11427,7 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="L148" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M148" s="4" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
@@ -11523,7 +11523,7 @@
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M149" s="4" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M150" s="4" t="inlineStr">
@@ -11604,7 +11604,7 @@
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
@@ -11641,7 +11641,7 @@
       </c>
       <c r="L151" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M151" s="4" t="inlineStr">
@@ -11663,7 +11663,7 @@
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
@@ -11700,7 +11700,7 @@
       </c>
       <c r="L152" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M152" s="4" t="inlineStr">
@@ -11722,7 +11722,7 @@
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
@@ -11759,7 +11759,7 @@
       </c>
       <c r="L153" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M153" s="4" t="inlineStr">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
@@ -11818,7 +11818,7 @@
       </c>
       <c r="L154" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M154" s="4" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
@@ -11877,7 +11877,7 @@
       </c>
       <c r="L155" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M155" s="4" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
@@ -11936,7 +11936,7 @@
       </c>
       <c r="L156" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M156" s="4" t="inlineStr">
@@ -11958,7 +11958,7 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
@@ -11995,7 +11995,7 @@
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M157" s="4" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="L158" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M158" s="4" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
@@ -12113,7 +12113,7 @@
       </c>
       <c r="L159" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M159" s="4" t="inlineStr">
@@ -12135,7 +12135,7 @@
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
@@ -12172,7 +12172,7 @@
       </c>
       <c r="L160" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M160" s="4" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
@@ -12231,7 +12231,7 @@
       </c>
       <c r="L161" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M161" s="4" t="inlineStr">
@@ -12253,7 +12253,7 @@
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="L162" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M162" s="4" t="inlineStr">
@@ -12312,7 +12312,7 @@
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
@@ -12349,7 +12349,7 @@
       </c>
       <c r="L163" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M163" s="4" t="inlineStr">
@@ -12371,7 +12371,7 @@
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="L164" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M164" s="4" t="inlineStr">
@@ -12430,7 +12430,7 @@
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
@@ -12467,7 +12467,7 @@
       </c>
       <c r="L165" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M165" s="4" t="inlineStr">
@@ -12489,7 +12489,7 @@
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="L166" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M166" s="4" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
@@ -12585,7 +12585,7 @@
       </c>
       <c r="L167" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M167" s="4" t="inlineStr">
@@ -12607,7 +12607,7 @@
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="L168" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M168" s="4" t="inlineStr">
@@ -12666,7 +12666,7 @@
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
@@ -12703,7 +12703,7 @@
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M169" s="4" t="inlineStr">
@@ -12725,7 +12725,7 @@
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
@@ -12762,7 +12762,7 @@
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M170" s="4" t="inlineStr">
@@ -12784,7 +12784,7 @@
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
@@ -12821,7 +12821,7 @@
       </c>
       <c r="L171" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M171" s="4" t="inlineStr">
@@ -12843,7 +12843,7 @@
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="L172" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M172" s="4" t="inlineStr">
@@ -12902,7 +12902,7 @@
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="L173" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M173" s="4" t="inlineStr">
@@ -12961,7 +12961,7 @@
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
@@ -12998,7 +12998,7 @@
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M174" s="4" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
@@ -13057,7 +13057,7 @@
       </c>
       <c r="L175" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M175" s="4" t="inlineStr">
@@ -13079,7 +13079,7 @@
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
@@ -13116,7 +13116,7 @@
       </c>
       <c r="L176" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M176" s="4" t="inlineStr">
@@ -13175,7 +13175,7 @@
       </c>
       <c r="L177" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M177" s="4" t="inlineStr">
@@ -13197,7 +13197,7 @@
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
@@ -13234,7 +13234,7 @@
       </c>
       <c r="L178" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M178" s="4" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
@@ -13293,7 +13293,7 @@
       </c>
       <c r="L179" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M179" s="4" t="inlineStr">
@@ -13315,7 +13315,7 @@
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="L180" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M180" s="4" t="inlineStr">
@@ -13374,7 +13374,7 @@
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
@@ -13411,7 +13411,7 @@
       </c>
       <c r="L181" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M181" s="4" t="inlineStr">
@@ -13433,7 +13433,7 @@
       </c>
       <c r="C182" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D182" s="4" t="inlineStr">
@@ -13470,7 +13470,7 @@
       </c>
       <c r="L182" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M182" s="4" t="inlineStr">
@@ -13492,7 +13492,7 @@
       </c>
       <c r="C183" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D183" s="4" t="inlineStr">
@@ -13529,7 +13529,7 @@
       </c>
       <c r="L183" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M183" s="4" t="inlineStr">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="C184" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D184" s="4" t="inlineStr">
@@ -13588,7 +13588,7 @@
       </c>
       <c r="L184" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M184" s="4" t="inlineStr">
@@ -13610,7 +13610,7 @@
       </c>
       <c r="C185" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D185" s="4" t="inlineStr">
@@ -13647,7 +13647,7 @@
       </c>
       <c r="L185" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M185" s="4" t="inlineStr">
@@ -13669,7 +13669,7 @@
       </c>
       <c r="C186" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D186" s="4" t="inlineStr">
@@ -13706,7 +13706,7 @@
       </c>
       <c r="L186" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M186" s="4" t="inlineStr">
@@ -13728,7 +13728,7 @@
       </c>
       <c r="C187" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D187" s="4" t="inlineStr">
@@ -13765,7 +13765,7 @@
       </c>
       <c r="L187" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M187" s="4" t="inlineStr">
@@ -13787,7 +13787,7 @@
       </c>
       <c r="C188" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D188" s="4" t="inlineStr">
@@ -13824,7 +13824,7 @@
       </c>
       <c r="L188" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M188" s="4" t="inlineStr">
@@ -13846,7 +13846,7 @@
       </c>
       <c r="C189" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D189" s="4" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="L189" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M189" s="4" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="C190" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D190" s="4" t="inlineStr">
@@ -13942,7 +13942,7 @@
       </c>
       <c r="L190" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M190" s="4" t="inlineStr">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="C191" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D191" s="4" t="inlineStr">
@@ -14001,7 +14001,7 @@
       </c>
       <c r="L191" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M191" s="4" t="inlineStr">
@@ -14023,7 +14023,7 @@
       </c>
       <c r="C192" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D192" s="4" t="inlineStr">
@@ -14060,7 +14060,7 @@
       </c>
       <c r="L192" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M192" s="4" t="inlineStr">
@@ -14082,7 +14082,7 @@
       </c>
       <c r="C193" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D193" s="4" t="inlineStr">
@@ -14119,7 +14119,7 @@
       </c>
       <c r="L193" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M193" s="4" t="inlineStr">
@@ -14141,7 +14141,7 @@
       </c>
       <c r="C194" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D194" s="4" t="inlineStr">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="L194" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M194" s="4" t="inlineStr">
@@ -14200,7 +14200,7 @@
       </c>
       <c r="C195" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D195" s="4" t="inlineStr">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="L195" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M195" s="4" t="inlineStr">
@@ -14259,7 +14259,7 @@
       </c>
       <c r="C196" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr">
@@ -14296,7 +14296,7 @@
       </c>
       <c r="L196" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M196" s="4" t="inlineStr">
@@ -14318,7 +14318,7 @@
       </c>
       <c r="C197" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D197" s="4" t="inlineStr">
@@ -14355,7 +14355,7 @@
       </c>
       <c r="L197" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M197" s="4" t="inlineStr">
@@ -14377,7 +14377,7 @@
       </c>
       <c r="C198" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D198" s="4" t="inlineStr">
@@ -14414,7 +14414,7 @@
       </c>
       <c r="L198" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M198" s="4" t="inlineStr">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C199" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D199" s="4" t="inlineStr">
@@ -14473,7 +14473,7 @@
       </c>
       <c r="L199" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M199" s="4" t="inlineStr">
@@ -14495,7 +14495,7 @@
       </c>
       <c r="C200" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D200" s="4" t="inlineStr">
@@ -14532,7 +14532,7 @@
       </c>
       <c r="L200" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M200" s="4" t="inlineStr">
@@ -14554,7 +14554,7 @@
       </c>
       <c r="C201" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D201" s="4" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="L201" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M201" s="4" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="C202" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D202" s="4" t="inlineStr">
@@ -14650,7 +14650,7 @@
       </c>
       <c r="L202" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M202" s="4" t="inlineStr">
@@ -14672,7 +14672,7 @@
       </c>
       <c r="C203" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D203" s="4" t="inlineStr">
@@ -14709,7 +14709,7 @@
       </c>
       <c r="L203" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M203" s="4" t="inlineStr">
@@ -14731,7 +14731,7 @@
       </c>
       <c r="C204" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D204" s="4" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="L204" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M204" s="4" t="inlineStr">
@@ -14790,7 +14790,7 @@
       </c>
       <c r="C205" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D205" s="4" t="inlineStr">
@@ -14827,7 +14827,7 @@
       </c>
       <c r="L205" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M205" s="4" t="inlineStr">
@@ -14849,7 +14849,7 @@
       </c>
       <c r="C206" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D206" s="4" t="inlineStr">
@@ -14886,7 +14886,7 @@
       </c>
       <c r="L206" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M206" s="4" t="inlineStr">
@@ -14908,7 +14908,7 @@
       </c>
       <c r="C207" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D207" s="4" t="inlineStr">
@@ -14945,7 +14945,7 @@
       </c>
       <c r="L207" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M207" s="4" t="inlineStr">
@@ -14967,7 +14967,7 @@
       </c>
       <c r="C208" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D208" s="4" t="inlineStr">
@@ -15004,7 +15004,7 @@
       </c>
       <c r="L208" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M208" s="4" t="inlineStr">
@@ -15026,7 +15026,7 @@
       </c>
       <c r="C209" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D209" s="4" t="inlineStr">
@@ -15063,7 +15063,7 @@
       </c>
       <c r="L209" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M209" s="4" t="inlineStr">
@@ -15085,7 +15085,7 @@
       </c>
       <c r="C210" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D210" s="4" t="inlineStr">
@@ -15122,7 +15122,7 @@
       </c>
       <c r="L210" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M210" s="4" t="inlineStr">
@@ -15144,7 +15144,7 @@
       </c>
       <c r="C211" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D211" s="4" t="inlineStr">
@@ -15181,7 +15181,7 @@
       </c>
       <c r="L211" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M211" s="4" t="inlineStr">
@@ -15203,7 +15203,7 @@
       </c>
       <c r="C212" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D212" s="4" t="inlineStr">
@@ -15240,7 +15240,7 @@
       </c>
       <c r="L212" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M212" s="4" t="inlineStr">
@@ -15262,7 +15262,7 @@
       </c>
       <c r="C213" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D213" s="4" t="inlineStr">
@@ -15299,7 +15299,7 @@
       </c>
       <c r="L213" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M213" s="4" t="inlineStr">
@@ -15321,7 +15321,7 @@
       </c>
       <c r="C214" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D214" s="4" t="inlineStr">
@@ -15358,7 +15358,7 @@
       </c>
       <c r="L214" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M214" s="4" t="inlineStr">
@@ -15380,7 +15380,7 @@
       </c>
       <c r="C215" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D215" s="4" t="inlineStr">
@@ -15417,7 +15417,7 @@
       </c>
       <c r="L215" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M215" s="4" t="inlineStr">
@@ -15439,7 +15439,7 @@
       </c>
       <c r="C216" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D216" s="4" t="inlineStr">
@@ -15476,7 +15476,7 @@
       </c>
       <c r="L216" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M216" s="4" t="inlineStr">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="C217" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr">
@@ -15535,7 +15535,7 @@
       </c>
       <c r="L217" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M217" s="4" t="inlineStr">
@@ -15557,7 +15557,7 @@
       </c>
       <c r="C218" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D218" s="4" t="inlineStr">
@@ -15594,7 +15594,7 @@
       </c>
       <c r="L218" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M218" s="4" t="inlineStr">
@@ -15616,7 +15616,7 @@
       </c>
       <c r="C219" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D219" s="4" t="inlineStr">
@@ -15653,7 +15653,7 @@
       </c>
       <c r="L219" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M219" s="4" t="inlineStr">
@@ -15675,7 +15675,7 @@
       </c>
       <c r="C220" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D220" s="4" t="inlineStr">
@@ -15712,7 +15712,7 @@
       </c>
       <c r="L220" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M220" s="4" t="inlineStr">
@@ -15734,7 +15734,7 @@
       </c>
       <c r="C221" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D221" s="4" t="inlineStr">
@@ -15771,7 +15771,7 @@
       </c>
       <c r="L221" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M221" s="4" t="inlineStr">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="C222" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D222" s="4" t="inlineStr">
@@ -15830,7 +15830,7 @@
       </c>
       <c r="L222" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M222" s="4" t="inlineStr">
@@ -15852,7 +15852,7 @@
       </c>
       <c r="C223" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D223" s="4" t="inlineStr">
@@ -15889,7 +15889,7 @@
       </c>
       <c r="L223" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M223" s="4" t="inlineStr">
@@ -15911,7 +15911,7 @@
       </c>
       <c r="C224" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D224" s="4" t="inlineStr">
@@ -15948,7 +15948,7 @@
       </c>
       <c r="L224" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M224" s="4" t="inlineStr">
@@ -15970,7 +15970,7 @@
       </c>
       <c r="C225" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D225" s="4" t="inlineStr">
@@ -16007,7 +16007,7 @@
       </c>
       <c r="L225" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M225" s="4" t="inlineStr">
@@ -16029,7 +16029,7 @@
       </c>
       <c r="C226" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D226" s="4" t="inlineStr">
@@ -16066,7 +16066,7 @@
       </c>
       <c r="L226" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M226" s="4" t="inlineStr">
@@ -16088,7 +16088,7 @@
       </c>
       <c r="C227" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D227" s="4" t="inlineStr">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="L227" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M227" s="4" t="inlineStr">
@@ -16147,7 +16147,7 @@
       </c>
       <c r="C228" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D228" s="4" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="L228" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M228" s="4" t="inlineStr">
@@ -16206,7 +16206,7 @@
       </c>
       <c r="C229" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D229" s="4" t="inlineStr">
@@ -16243,7 +16243,7 @@
       </c>
       <c r="L229" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M229" s="4" t="inlineStr">
@@ -16265,7 +16265,7 @@
       </c>
       <c r="C230" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D230" s="4" t="inlineStr">
@@ -16302,7 +16302,7 @@
       </c>
       <c r="L230" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M230" s="4" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="C231" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D231" s="4" t="inlineStr">
@@ -16361,7 +16361,7 @@
       </c>
       <c r="L231" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M231" s="4" t="inlineStr">
@@ -16383,7 +16383,7 @@
       </c>
       <c r="C232" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D232" s="4" t="inlineStr">
@@ -16420,7 +16420,7 @@
       </c>
       <c r="L232" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M232" s="4" t="inlineStr">
@@ -16442,7 +16442,7 @@
       </c>
       <c r="C233" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D233" s="4" t="inlineStr">
@@ -16479,7 +16479,7 @@
       </c>
       <c r="L233" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M233" s="4" t="inlineStr">
@@ -16501,7 +16501,7 @@
       </c>
       <c r="C234" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D234" s="4" t="inlineStr">
@@ -16538,7 +16538,7 @@
       </c>
       <c r="L234" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M234" s="4" t="inlineStr">
@@ -16560,7 +16560,7 @@
       </c>
       <c r="C235" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D235" s="4" t="inlineStr">
@@ -16597,7 +16597,7 @@
       </c>
       <c r="L235" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M235" s="4" t="inlineStr">
@@ -16619,7 +16619,7 @@
       </c>
       <c r="C236" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D236" s="4" t="inlineStr">
@@ -16656,7 +16656,7 @@
       </c>
       <c r="L236" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M236" s="4" t="inlineStr">
@@ -16678,7 +16678,7 @@
       </c>
       <c r="C237" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D237" s="4" t="inlineStr">
@@ -16715,7 +16715,7 @@
       </c>
       <c r="L237" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M237" s="4" t="inlineStr">
@@ -16737,7 +16737,7 @@
       </c>
       <c r="C238" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D238" s="4" t="inlineStr">
@@ -16774,7 +16774,7 @@
       </c>
       <c r="L238" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M238" s="4" t="inlineStr">
@@ -16796,7 +16796,7 @@
       </c>
       <c r="C239" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D239" s="4" t="inlineStr">
@@ -16833,7 +16833,7 @@
       </c>
       <c r="L239" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M239" s="4" t="inlineStr">
@@ -16855,7 +16855,7 @@
       </c>
       <c r="C240" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D240" s="4" t="inlineStr">
@@ -16892,7 +16892,7 @@
       </c>
       <c r="L240" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M240" s="4" t="inlineStr">
@@ -16914,7 +16914,7 @@
       </c>
       <c r="C241" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D241" s="4" t="inlineStr">
@@ -16951,7 +16951,7 @@
       </c>
       <c r="L241" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M241" s="4" t="inlineStr">
@@ -16973,7 +16973,7 @@
       </c>
       <c r="C242" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D242" s="4" t="inlineStr">
@@ -17010,7 +17010,7 @@
       </c>
       <c r="L242" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M242" s="4" t="inlineStr">
@@ -17032,7 +17032,7 @@
       </c>
       <c r="C243" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D243" s="4" t="inlineStr">
@@ -17069,7 +17069,7 @@
       </c>
       <c r="L243" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M243" s="4" t="inlineStr">
@@ -17091,7 +17091,7 @@
       </c>
       <c r="C244" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D244" s="4" t="inlineStr">
@@ -17128,7 +17128,7 @@
       </c>
       <c r="L244" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M244" s="4" t="inlineStr">
@@ -17150,7 +17150,7 @@
       </c>
       <c r="C245" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D245" s="4" t="inlineStr">
@@ -17187,7 +17187,7 @@
       </c>
       <c r="L245" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M245" s="4" t="inlineStr">
@@ -17209,7 +17209,7 @@
       </c>
       <c r="C246" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D246" s="4" t="inlineStr">
@@ -17246,7 +17246,7 @@
       </c>
       <c r="L246" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M246" s="4" t="inlineStr">
@@ -17268,7 +17268,7 @@
       </c>
       <c r="C247" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D247" s="4" t="inlineStr">
@@ -17305,7 +17305,7 @@
       </c>
       <c r="L247" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M247" s="4" t="inlineStr">
@@ -17327,7 +17327,7 @@
       </c>
       <c r="C248" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D248" s="4" t="inlineStr">
@@ -17364,7 +17364,7 @@
       </c>
       <c r="L248" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M248" s="4" t="inlineStr">
@@ -17386,7 +17386,7 @@
       </c>
       <c r="C249" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D249" s="4" t="inlineStr">
@@ -17423,7 +17423,7 @@
       </c>
       <c r="L249" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M249" s="4" t="inlineStr">
@@ -17445,7 +17445,7 @@
       </c>
       <c r="C250" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D250" s="4" t="inlineStr">
@@ -17482,7 +17482,7 @@
       </c>
       <c r="L250" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M250" s="4" t="inlineStr">
@@ -17504,7 +17504,7 @@
       </c>
       <c r="C251" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D251" s="4" t="inlineStr">
@@ -17541,7 +17541,7 @@
       </c>
       <c r="L251" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M251" s="4" t="inlineStr">
@@ -17563,7 +17563,7 @@
       </c>
       <c r="C252" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D252" s="4" t="inlineStr">
@@ -17600,7 +17600,7 @@
       </c>
       <c r="L252" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M252" s="4" t="inlineStr">
@@ -17622,7 +17622,7 @@
       </c>
       <c r="C253" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D253" s="4" t="inlineStr">
@@ -17659,7 +17659,7 @@
       </c>
       <c r="L253" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M253" s="4" t="inlineStr">
@@ -17681,7 +17681,7 @@
       </c>
       <c r="C254" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D254" s="4" t="inlineStr">
@@ -17718,7 +17718,7 @@
       </c>
       <c r="L254" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M254" s="4" t="inlineStr">
@@ -17740,7 +17740,7 @@
       </c>
       <c r="C255" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D255" s="4" t="inlineStr">
@@ -17777,7 +17777,7 @@
       </c>
       <c r="L255" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M255" s="4" t="inlineStr">
@@ -17799,7 +17799,7 @@
       </c>
       <c r="C256" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D256" s="4" t="inlineStr">
@@ -17836,7 +17836,7 @@
       </c>
       <c r="L256" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M256" s="4" t="inlineStr">
@@ -17858,7 +17858,7 @@
       </c>
       <c r="C257" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D257" s="4" t="inlineStr">
@@ -17895,7 +17895,7 @@
       </c>
       <c r="L257" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M257" s="4" t="inlineStr">
@@ -17917,7 +17917,7 @@
       </c>
       <c r="C258" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D258" s="4" t="inlineStr">
@@ -17954,7 +17954,7 @@
       </c>
       <c r="L258" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M258" s="4" t="inlineStr">
@@ -17976,7 +17976,7 @@
       </c>
       <c r="C259" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D259" s="4" t="inlineStr">
@@ -18013,7 +18013,7 @@
       </c>
       <c r="L259" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M259" s="4" t="inlineStr">
@@ -18035,7 +18035,7 @@
       </c>
       <c r="C260" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D260" s="4" t="inlineStr">
@@ -18072,7 +18072,7 @@
       </c>
       <c r="L260" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M260" s="4" t="inlineStr">
@@ -18094,7 +18094,7 @@
       </c>
       <c r="C261" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D261" s="4" t="inlineStr">
@@ -18131,7 +18131,7 @@
       </c>
       <c r="L261" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M261" s="4" t="inlineStr">
@@ -18153,7 +18153,7 @@
       </c>
       <c r="C262" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D262" s="4" t="inlineStr">
@@ -18190,7 +18190,7 @@
       </c>
       <c r="L262" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M262" s="4" t="inlineStr">
@@ -18212,7 +18212,7 @@
       </c>
       <c r="C263" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D263" s="4" t="inlineStr">
@@ -18249,7 +18249,7 @@
       </c>
       <c r="L263" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M263" s="4" t="inlineStr">
@@ -18271,7 +18271,7 @@
       </c>
       <c r="C264" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D264" s="4" t="inlineStr">
@@ -18308,7 +18308,7 @@
       </c>
       <c r="L264" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M264" s="4" t="inlineStr">
@@ -18330,7 +18330,7 @@
       </c>
       <c r="C265" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D265" s="4" t="inlineStr">
@@ -18367,7 +18367,7 @@
       </c>
       <c r="L265" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M265" s="4" t="inlineStr">
@@ -18389,7 +18389,7 @@
       </c>
       <c r="C266" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D266" s="4" t="inlineStr">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="L266" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M266" s="4" t="inlineStr">
@@ -18448,7 +18448,7 @@
       </c>
       <c r="C267" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D267" s="4" t="inlineStr">
@@ -18485,7 +18485,7 @@
       </c>
       <c r="L267" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M267" s="4" t="inlineStr">
@@ -18507,7 +18507,7 @@
       </c>
       <c r="C268" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D268" s="4" t="inlineStr">
@@ -18544,7 +18544,7 @@
       </c>
       <c r="L268" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M268" s="4" t="inlineStr">
@@ -18566,7 +18566,7 @@
       </c>
       <c r="C269" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D269" s="4" t="inlineStr">
@@ -18603,7 +18603,7 @@
       </c>
       <c r="L269" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M269" s="4" t="inlineStr">
@@ -18625,7 +18625,7 @@
       </c>
       <c r="C270" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D270" s="4" t="inlineStr">
@@ -18662,7 +18662,7 @@
       </c>
       <c r="L270" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M270" s="4" t="inlineStr">
@@ -18684,7 +18684,7 @@
       </c>
       <c r="C271" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D271" s="4" t="inlineStr">
@@ -18721,7 +18721,7 @@
       </c>
       <c r="L271" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M271" s="4" t="inlineStr">
@@ -18743,7 +18743,7 @@
       </c>
       <c r="C272" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D272" s="4" t="inlineStr">
@@ -18780,7 +18780,7 @@
       </c>
       <c r="L272" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M272" s="4" t="inlineStr">
@@ -18802,7 +18802,7 @@
       </c>
       <c r="C273" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D273" s="4" t="inlineStr">
@@ -18839,7 +18839,7 @@
       </c>
       <c r="L273" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M273" s="4" t="inlineStr">
@@ -18861,7 +18861,7 @@
       </c>
       <c r="C274" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D274" s="4" t="inlineStr">
@@ -18898,7 +18898,7 @@
       </c>
       <c r="L274" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M274" s="4" t="inlineStr">
@@ -18920,7 +18920,7 @@
       </c>
       <c r="C275" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D275" s="4" t="inlineStr">
@@ -18957,7 +18957,7 @@
       </c>
       <c r="L275" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M275" s="4" t="inlineStr">
@@ -18979,7 +18979,7 @@
       </c>
       <c r="C276" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D276" s="4" t="inlineStr">
@@ -19016,7 +19016,7 @@
       </c>
       <c r="L276" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M276" s="4" t="inlineStr">
@@ -19038,7 +19038,7 @@
       </c>
       <c r="C277" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D277" s="4" t="inlineStr">
@@ -19075,7 +19075,7 @@
       </c>
       <c r="L277" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M277" s="4" t="inlineStr">
@@ -19097,7 +19097,7 @@
       </c>
       <c r="C278" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D278" s="4" t="inlineStr">
@@ -19134,7 +19134,7 @@
       </c>
       <c r="L278" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M278" s="4" t="inlineStr">
@@ -19156,7 +19156,7 @@
       </c>
       <c r="C279" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D279" s="4" t="inlineStr">
@@ -19193,7 +19193,7 @@
       </c>
       <c r="L279" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M279" s="4" t="inlineStr">
@@ -19215,7 +19215,7 @@
       </c>
       <c r="C280" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D280" s="4" t="inlineStr">
@@ -19252,7 +19252,7 @@
       </c>
       <c r="L280" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M280" s="4" t="inlineStr">
@@ -19274,7 +19274,7 @@
       </c>
       <c r="C281" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D281" s="4" t="inlineStr">
@@ -19311,7 +19311,7 @@
       </c>
       <c r="L281" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M281" s="4" t="inlineStr">
@@ -19333,7 +19333,7 @@
       </c>
       <c r="C282" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D282" s="4" t="inlineStr">
@@ -19370,7 +19370,7 @@
       </c>
       <c r="L282" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M282" s="4" t="inlineStr">
@@ -19392,7 +19392,7 @@
       </c>
       <c r="C283" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D283" s="4" t="inlineStr">
@@ -19429,7 +19429,7 @@
       </c>
       <c r="L283" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M283" s="4" t="inlineStr">
@@ -19451,7 +19451,7 @@
       </c>
       <c r="C284" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D284" s="4" t="inlineStr">
@@ -19488,7 +19488,7 @@
       </c>
       <c r="L284" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M284" s="4" t="inlineStr">
@@ -19510,7 +19510,7 @@
       </c>
       <c r="C285" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D285" s="4" t="inlineStr">
@@ -19547,7 +19547,7 @@
       </c>
       <c r="L285" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M285" s="4" t="inlineStr">
@@ -19569,7 +19569,7 @@
       </c>
       <c r="C286" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D286" s="4" t="inlineStr">
@@ -19606,7 +19606,7 @@
       </c>
       <c r="L286" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M286" s="4" t="inlineStr">
@@ -19628,7 +19628,7 @@
       </c>
       <c r="C287" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D287" s="4" t="inlineStr">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="L287" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M287" s="4" t="inlineStr">
@@ -19687,7 +19687,7 @@
       </c>
       <c r="C288" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D288" s="4" t="inlineStr">
@@ -19724,7 +19724,7 @@
       </c>
       <c r="L288" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M288" s="4" t="inlineStr">
@@ -19746,7 +19746,7 @@
       </c>
       <c r="C289" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D289" s="4" t="inlineStr">
@@ -19783,7 +19783,7 @@
       </c>
       <c r="L289" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M289" s="4" t="inlineStr">
@@ -19805,7 +19805,7 @@
       </c>
       <c r="C290" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D290" s="4" t="inlineStr">
@@ -19842,7 +19842,7 @@
       </c>
       <c r="L290" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M290" s="4" t="inlineStr">
@@ -19864,7 +19864,7 @@
       </c>
       <c r="C291" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D291" s="4" t="inlineStr">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="L291" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M291" s="4" t="inlineStr">
@@ -19923,7 +19923,7 @@
       </c>
       <c r="C292" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D292" s="4" t="inlineStr">
@@ -19960,7 +19960,7 @@
       </c>
       <c r="L292" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M292" s="4" t="inlineStr">
@@ -19982,7 +19982,7 @@
       </c>
       <c r="C293" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D293" s="4" t="inlineStr">
@@ -20019,7 +20019,7 @@
       </c>
       <c r="L293" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M293" s="4" t="inlineStr">
@@ -20041,7 +20041,7 @@
       </c>
       <c r="C294" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D294" s="4" t="inlineStr">
@@ -20078,7 +20078,7 @@
       </c>
       <c r="L294" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M294" s="4" t="inlineStr">
@@ -20100,7 +20100,7 @@
       </c>
       <c r="C295" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D295" s="4" t="inlineStr">
@@ -20137,7 +20137,7 @@
       </c>
       <c r="L295" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M295" s="4" t="inlineStr">
@@ -20159,7 +20159,7 @@
       </c>
       <c r="C296" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D296" s="4" t="inlineStr">
@@ -20196,7 +20196,7 @@
       </c>
       <c r="L296" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M296" s="4" t="inlineStr">
@@ -20218,7 +20218,7 @@
       </c>
       <c r="C297" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D297" s="4" t="inlineStr">
@@ -20255,7 +20255,7 @@
       </c>
       <c r="L297" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M297" s="4" t="inlineStr">
@@ -20277,7 +20277,7 @@
       </c>
       <c r="C298" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D298" s="4" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="L298" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M298" s="4" t="inlineStr">
@@ -20336,7 +20336,7 @@
       </c>
       <c r="C299" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D299" s="4" t="inlineStr">
@@ -20373,7 +20373,7 @@
       </c>
       <c r="L299" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M299" s="4" t="inlineStr">
@@ -20395,7 +20395,7 @@
       </c>
       <c r="C300" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D300" s="4" t="inlineStr">
@@ -20432,7 +20432,7 @@
       </c>
       <c r="L300" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M300" s="4" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="C301" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D301" s="4" t="inlineStr">
@@ -20491,7 +20491,7 @@
       </c>
       <c r="L301" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M301" s="4" t="inlineStr">
@@ -20513,7 +20513,7 @@
       </c>
       <c r="C302" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D302" s="4" t="inlineStr">
@@ -20550,7 +20550,7 @@
       </c>
       <c r="L302" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M302" s="4" t="inlineStr">
@@ -20572,7 +20572,7 @@
       </c>
       <c r="C303" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D303" s="4" t="inlineStr">
@@ -20609,7 +20609,7 @@
       </c>
       <c r="L303" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M303" s="4" t="inlineStr">
@@ -20631,7 +20631,7 @@
       </c>
       <c r="C304" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D304" s="4" t="inlineStr">
@@ -20668,7 +20668,7 @@
       </c>
       <c r="L304" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M304" s="4" t="inlineStr">
@@ -20690,7 +20690,7 @@
       </c>
       <c r="C305" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D305" s="4" t="inlineStr">
@@ -20727,7 +20727,7 @@
       </c>
       <c r="L305" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M305" s="4" t="inlineStr">
@@ -20749,7 +20749,7 @@
       </c>
       <c r="C306" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D306" s="4" t="inlineStr">
@@ -20786,7 +20786,7 @@
       </c>
       <c r="L306" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M306" s="4" t="inlineStr">
@@ -20808,7 +20808,7 @@
       </c>
       <c r="C307" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D307" s="4" t="inlineStr">
@@ -20845,7 +20845,7 @@
       </c>
       <c r="L307" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M307" s="4" t="inlineStr">
@@ -20867,7 +20867,7 @@
       </c>
       <c r="C308" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D308" s="4" t="inlineStr">
@@ -20904,7 +20904,7 @@
       </c>
       <c r="L308" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M308" s="4" t="inlineStr">
@@ -20926,7 +20926,7 @@
       </c>
       <c r="C309" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D309" s="4" t="inlineStr">
@@ -20963,7 +20963,7 @@
       </c>
       <c r="L309" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M309" s="4" t="inlineStr">
@@ -20985,7 +20985,7 @@
       </c>
       <c r="C310" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D310" s="4" t="inlineStr">
@@ -21022,7 +21022,7 @@
       </c>
       <c r="L310" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M310" s="4" t="inlineStr">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C311" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D311" s="4" t="inlineStr">
@@ -21081,7 +21081,7 @@
       </c>
       <c r="L311" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M311" s="4" t="inlineStr">
@@ -21103,7 +21103,7 @@
       </c>
       <c r="C312" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D312" s="4" t="inlineStr">
@@ -21140,7 +21140,7 @@
       </c>
       <c r="L312" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M312" s="4" t="inlineStr">
@@ -21162,7 +21162,7 @@
       </c>
       <c r="C313" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D313" s="4" t="inlineStr">
@@ -21199,7 +21199,7 @@
       </c>
       <c r="L313" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M313" s="4" t="inlineStr">
@@ -21221,7 +21221,7 @@
       </c>
       <c r="C314" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D314" s="4" t="inlineStr">
@@ -21258,7 +21258,7 @@
       </c>
       <c r="L314" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M314" s="4" t="inlineStr">
@@ -21280,7 +21280,7 @@
       </c>
       <c r="C315" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D315" s="4" t="inlineStr">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="L315" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M315" s="4" t="inlineStr">
@@ -21339,7 +21339,7 @@
       </c>
       <c r="C316" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D316" s="4" t="inlineStr">
@@ -21376,7 +21376,7 @@
       </c>
       <c r="L316" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M316" s="4" t="inlineStr">
@@ -21398,7 +21398,7 @@
       </c>
       <c r="C317" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D317" s="4" t="inlineStr">
@@ -21435,7 +21435,7 @@
       </c>
       <c r="L317" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M317" s="4" t="inlineStr">
@@ -21457,7 +21457,7 @@
       </c>
       <c r="C318" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D318" s="4" t="inlineStr">
@@ -21494,7 +21494,7 @@
       </c>
       <c r="L318" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M318" s="4" t="inlineStr">
@@ -21516,7 +21516,7 @@
       </c>
       <c r="C319" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D319" s="4" t="inlineStr">
@@ -21553,7 +21553,7 @@
       </c>
       <c r="L319" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M319" s="4" t="inlineStr">
@@ -21575,7 +21575,7 @@
       </c>
       <c r="C320" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D320" s="4" t="inlineStr">
@@ -21612,7 +21612,7 @@
       </c>
       <c r="L320" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M320" s="4" t="inlineStr">
@@ -21634,7 +21634,7 @@
       </c>
       <c r="C321" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D321" s="4" t="inlineStr">
@@ -21671,7 +21671,7 @@
       </c>
       <c r="L321" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M321" s="4" t="inlineStr">
@@ -21693,7 +21693,7 @@
       </c>
       <c r="C322" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D322" s="4" t="inlineStr">
@@ -21730,7 +21730,7 @@
       </c>
       <c r="L322" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M322" s="4" t="inlineStr">
@@ -21752,7 +21752,7 @@
       </c>
       <c r="C323" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D323" s="4" t="inlineStr">
@@ -21789,7 +21789,7 @@
       </c>
       <c r="L323" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M323" s="4" t="inlineStr">
@@ -21811,7 +21811,7 @@
       </c>
       <c r="C324" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D324" s="4" t="inlineStr">
@@ -21848,7 +21848,7 @@
       </c>
       <c r="L324" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M324" s="4" t="inlineStr">
@@ -21870,7 +21870,7 @@
       </c>
       <c r="C325" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D325" s="4" t="inlineStr">
@@ -21907,7 +21907,7 @@
       </c>
       <c r="L325" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M325" s="4" t="inlineStr">
@@ -21929,7 +21929,7 @@
       </c>
       <c r="C326" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D326" s="4" t="inlineStr">
@@ -21966,7 +21966,7 @@
       </c>
       <c r="L326" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M326" s="4" t="inlineStr">
@@ -21988,7 +21988,7 @@
       </c>
       <c r="C327" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D327" s="4" t="inlineStr">
@@ -22025,7 +22025,7 @@
       </c>
       <c r="L327" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M327" s="4" t="inlineStr">
@@ -22047,7 +22047,7 @@
       </c>
       <c r="C328" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D328" s="4" t="inlineStr">
@@ -22084,7 +22084,7 @@
       </c>
       <c r="L328" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M328" s="4" t="inlineStr">
@@ -22106,7 +22106,7 @@
       </c>
       <c r="C329" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D329" s="4" t="inlineStr">
@@ -22143,7 +22143,7 @@
       </c>
       <c r="L329" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M329" s="4" t="inlineStr">
@@ -22165,7 +22165,7 @@
       </c>
       <c r="C330" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D330" s="4" t="inlineStr">
@@ -22202,7 +22202,7 @@
       </c>
       <c r="L330" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M330" s="4" t="inlineStr">
@@ -22224,7 +22224,7 @@
       </c>
       <c r="C331" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D331" s="4" t="inlineStr">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="L331" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M331" s="4" t="inlineStr">
@@ -22283,7 +22283,7 @@
       </c>
       <c r="C332" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D332" s="4" t="inlineStr">
@@ -22320,7 +22320,7 @@
       </c>
       <c r="L332" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M332" s="4" t="inlineStr">
@@ -22342,7 +22342,7 @@
       </c>
       <c r="C333" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D333" s="4" t="inlineStr">
@@ -22379,7 +22379,7 @@
       </c>
       <c r="L333" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M333" s="4" t="inlineStr">
@@ -22401,7 +22401,7 @@
       </c>
       <c r="C334" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D334" s="4" t="inlineStr">
@@ -22438,7 +22438,7 @@
       </c>
       <c r="L334" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M334" s="4" t="inlineStr">
@@ -22460,7 +22460,7 @@
       </c>
       <c r="C335" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D335" s="4" t="inlineStr">
@@ -22497,7 +22497,7 @@
       </c>
       <c r="L335" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M335" s="4" t="inlineStr">
@@ -22519,7 +22519,7 @@
       </c>
       <c r="C336" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D336" s="4" t="inlineStr">
@@ -22556,7 +22556,7 @@
       </c>
       <c r="L336" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M336" s="4" t="inlineStr">
@@ -22578,7 +22578,7 @@
       </c>
       <c r="C337" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D337" s="4" t="inlineStr">
@@ -22615,7 +22615,7 @@
       </c>
       <c r="L337" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M337" s="4" t="inlineStr">
@@ -22637,7 +22637,7 @@
       </c>
       <c r="C338" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D338" s="4" t="inlineStr">
@@ -22674,7 +22674,7 @@
       </c>
       <c r="L338" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M338" s="4" t="inlineStr">
@@ -22696,7 +22696,7 @@
       </c>
       <c r="C339" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D339" s="4" t="inlineStr">
@@ -22733,7 +22733,7 @@
       </c>
       <c r="L339" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M339" s="4" t="inlineStr">
@@ -22755,7 +22755,7 @@
       </c>
       <c r="C340" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D340" s="4" t="inlineStr">
@@ -22792,7 +22792,7 @@
       </c>
       <c r="L340" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M340" s="4" t="inlineStr">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="C341" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D341" s="4" t="inlineStr">
@@ -22851,7 +22851,7 @@
       </c>
       <c r="L341" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M341" s="4" t="inlineStr">
@@ -22873,7 +22873,7 @@
       </c>
       <c r="C342" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D342" s="4" t="inlineStr">
@@ -22910,7 +22910,7 @@
       </c>
       <c r="L342" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M342" s="4" t="inlineStr">
@@ -22932,7 +22932,7 @@
       </c>
       <c r="C343" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D343" s="4" t="inlineStr">
@@ -22969,7 +22969,7 @@
       </c>
       <c r="L343" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M343" s="4" t="inlineStr">
@@ -22991,7 +22991,7 @@
       </c>
       <c r="C344" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D344" s="4" t="inlineStr">
@@ -23028,7 +23028,7 @@
       </c>
       <c r="L344" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M344" s="4" t="inlineStr">
@@ -23050,7 +23050,7 @@
       </c>
       <c r="C345" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D345" s="4" t="inlineStr">
@@ -23087,7 +23087,7 @@
       </c>
       <c r="L345" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M345" s="4" t="inlineStr">
@@ -23109,7 +23109,7 @@
       </c>
       <c r="C346" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D346" s="4" t="inlineStr">
@@ -23146,7 +23146,7 @@
       </c>
       <c r="L346" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M346" s="4" t="inlineStr">
@@ -23168,7 +23168,7 @@
       </c>
       <c r="C347" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D347" s="4" t="inlineStr">
@@ -23205,7 +23205,7 @@
       </c>
       <c r="L347" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M347" s="4" t="inlineStr">
@@ -23227,7 +23227,7 @@
       </c>
       <c r="C348" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D348" s="4" t="inlineStr">
@@ -23264,7 +23264,7 @@
       </c>
       <c r="L348" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M348" s="4" t="inlineStr">
@@ -23286,7 +23286,7 @@
       </c>
       <c r="C349" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D349" s="4" t="inlineStr">
@@ -23323,7 +23323,7 @@
       </c>
       <c r="L349" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M349" s="4" t="inlineStr">
@@ -23345,7 +23345,7 @@
       </c>
       <c r="C350" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D350" s="4" t="inlineStr">
@@ -23382,7 +23382,7 @@
       </c>
       <c r="L350" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M350" s="4" t="inlineStr">
@@ -23404,7 +23404,7 @@
       </c>
       <c r="C351" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D351" s="4" t="inlineStr">
@@ -23441,7 +23441,7 @@
       </c>
       <c r="L351" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M351" s="4" t="inlineStr">
@@ -23463,7 +23463,7 @@
       </c>
       <c r="C352" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D352" s="4" t="inlineStr">
@@ -23500,7 +23500,7 @@
       </c>
       <c r="L352" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M352" s="4" t="inlineStr">
@@ -23522,7 +23522,7 @@
       </c>
       <c r="C353" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D353" s="4" t="inlineStr">
@@ -23559,7 +23559,7 @@
       </c>
       <c r="L353" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M353" s="4" t="inlineStr">
@@ -23581,7 +23581,7 @@
       </c>
       <c r="C354" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D354" s="4" t="inlineStr">
@@ -23618,7 +23618,7 @@
       </c>
       <c r="L354" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M354" s="4" t="inlineStr">
@@ -23640,7 +23640,7 @@
       </c>
       <c r="C355" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D355" s="4" t="inlineStr">
@@ -23677,7 +23677,7 @@
       </c>
       <c r="L355" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M355" s="4" t="inlineStr">
@@ -23699,7 +23699,7 @@
       </c>
       <c r="C356" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D356" s="4" t="inlineStr">
@@ -23736,7 +23736,7 @@
       </c>
       <c r="L356" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M356" s="4" t="inlineStr">
@@ -23758,7 +23758,7 @@
       </c>
       <c r="C357" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D357" s="4" t="inlineStr">
@@ -23795,7 +23795,7 @@
       </c>
       <c r="L357" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M357" s="4" t="inlineStr">
@@ -23817,7 +23817,7 @@
       </c>
       <c r="C358" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D358" s="4" t="inlineStr">
@@ -23854,7 +23854,7 @@
       </c>
       <c r="L358" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M358" s="4" t="inlineStr">
@@ -23876,7 +23876,7 @@
       </c>
       <c r="C359" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D359" s="4" t="inlineStr">
@@ -23913,7 +23913,7 @@
       </c>
       <c r="L359" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M359" s="4" t="inlineStr">
@@ -23935,7 +23935,7 @@
       </c>
       <c r="C360" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D360" s="4" t="inlineStr">
@@ -23972,7 +23972,7 @@
       </c>
       <c r="L360" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M360" s="4" t="inlineStr">
@@ -23994,7 +23994,7 @@
       </c>
       <c r="C361" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D361" s="4" t="inlineStr">
@@ -24031,7 +24031,7 @@
       </c>
       <c r="L361" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M361" s="4" t="inlineStr">
@@ -24053,7 +24053,7 @@
       </c>
       <c r="C362" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D362" s="4" t="inlineStr">
@@ -24090,7 +24090,7 @@
       </c>
       <c r="L362" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M362" s="4" t="inlineStr">
@@ -24112,7 +24112,7 @@
       </c>
       <c r="C363" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D363" s="4" t="inlineStr">
@@ -24149,7 +24149,7 @@
       </c>
       <c r="L363" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M363" s="4" t="inlineStr">
@@ -24171,7 +24171,7 @@
       </c>
       <c r="C364" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D364" s="4" t="inlineStr">
@@ -24208,7 +24208,7 @@
       </c>
       <c r="L364" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M364" s="4" t="inlineStr">
@@ -24230,7 +24230,7 @@
       </c>
       <c r="C365" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D365" s="4" t="inlineStr">
@@ -24267,7 +24267,7 @@
       </c>
       <c r="L365" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M365" s="4" t="inlineStr">
@@ -24289,7 +24289,7 @@
       </c>
       <c r="C366" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D366" s="4" t="inlineStr">
@@ -24326,7 +24326,7 @@
       </c>
       <c r="L366" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M366" s="4" t="inlineStr">
@@ -24348,7 +24348,7 @@
       </c>
       <c r="C367" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D367" s="4" t="inlineStr">
@@ -24385,7 +24385,7 @@
       </c>
       <c r="L367" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M367" s="4" t="inlineStr">
@@ -24407,7 +24407,7 @@
       </c>
       <c r="C368" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D368" s="4" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="L368" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M368" s="4" t="inlineStr">
@@ -24466,7 +24466,7 @@
       </c>
       <c r="C369" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D369" s="4" t="inlineStr">
@@ -24503,7 +24503,7 @@
       </c>
       <c r="L369" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M369" s="4" t="inlineStr">
@@ -24525,7 +24525,7 @@
       </c>
       <c r="C370" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D370" s="4" t="inlineStr">
@@ -24562,7 +24562,7 @@
       </c>
       <c r="L370" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M370" s="4" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="C371" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D371" s="4" t="inlineStr">
@@ -24621,7 +24621,7 @@
       </c>
       <c r="L371" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M371" s="4" t="inlineStr">
@@ -24643,7 +24643,7 @@
       </c>
       <c r="C372" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D372" s="4" t="inlineStr">
@@ -24680,7 +24680,7 @@
       </c>
       <c r="L372" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M372" s="4" t="inlineStr">
@@ -24702,7 +24702,7 @@
       </c>
       <c r="C373" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D373" s="4" t="inlineStr">
@@ -24739,7 +24739,7 @@
       </c>
       <c r="L373" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M373" s="4" t="inlineStr">
@@ -24761,7 +24761,7 @@
       </c>
       <c r="C374" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D374" s="4" t="inlineStr">
@@ -24798,7 +24798,7 @@
       </c>
       <c r="L374" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M374" s="4" t="inlineStr">
@@ -24820,7 +24820,7 @@
       </c>
       <c r="C375" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D375" s="4" t="inlineStr">
@@ -24857,7 +24857,7 @@
       </c>
       <c r="L375" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M375" s="4" t="inlineStr">
@@ -24879,7 +24879,7 @@
       </c>
       <c r="C376" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D376" s="4" t="inlineStr">
@@ -24916,7 +24916,7 @@
       </c>
       <c r="L376" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M376" s="4" t="inlineStr">
@@ -24938,7 +24938,7 @@
       </c>
       <c r="C377" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D377" s="4" t="inlineStr">
@@ -24975,7 +24975,7 @@
       </c>
       <c r="L377" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M377" s="4" t="inlineStr">
@@ -24997,7 +24997,7 @@
       </c>
       <c r="C378" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D378" s="4" t="inlineStr">
@@ -25034,7 +25034,7 @@
       </c>
       <c r="L378" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M378" s="4" t="inlineStr">
@@ -25056,7 +25056,7 @@
       </c>
       <c r="C379" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D379" s="4" t="inlineStr">
@@ -25093,7 +25093,7 @@
       </c>
       <c r="L379" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M379" s="4" t="inlineStr">
@@ -25115,7 +25115,7 @@
       </c>
       <c r="C380" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D380" s="4" t="inlineStr">
@@ -25152,7 +25152,7 @@
       </c>
       <c r="L380" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M380" s="4" t="inlineStr">
@@ -25174,7 +25174,7 @@
       </c>
       <c r="C381" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D381" s="4" t="inlineStr">
@@ -25211,7 +25211,7 @@
       </c>
       <c r="L381" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M381" s="4" t="inlineStr">
@@ -25233,7 +25233,7 @@
       </c>
       <c r="C382" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D382" s="4" t="inlineStr">
@@ -25270,7 +25270,7 @@
       </c>
       <c r="L382" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M382" s="4" t="inlineStr">
@@ -25292,7 +25292,7 @@
       </c>
       <c r="C383" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D383" s="4" t="inlineStr">
@@ -25329,7 +25329,7 @@
       </c>
       <c r="L383" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M383" s="4" t="inlineStr">
@@ -25351,7 +25351,7 @@
       </c>
       <c r="C384" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D384" s="4" t="inlineStr">
@@ -25388,7 +25388,7 @@
       </c>
       <c r="L384" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M384" s="4" t="inlineStr">
@@ -25410,7 +25410,7 @@
       </c>
       <c r="C385" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D385" s="4" t="inlineStr">
@@ -25447,7 +25447,7 @@
       </c>
       <c r="L385" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M385" s="4" t="inlineStr">
@@ -25469,7 +25469,7 @@
       </c>
       <c r="C386" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D386" s="4" t="inlineStr">
@@ -25506,7 +25506,7 @@
       </c>
       <c r="L386" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M386" s="4" t="inlineStr">
@@ -25528,7 +25528,7 @@
       </c>
       <c r="C387" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D387" s="4" t="inlineStr">
@@ -25565,7 +25565,7 @@
       </c>
       <c r="L387" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M387" s="4" t="inlineStr">
@@ -25587,7 +25587,7 @@
       </c>
       <c r="C388" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D388" s="4" t="inlineStr">
@@ -25624,7 +25624,7 @@
       </c>
       <c r="L388" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M388" s="4" t="inlineStr">
@@ -25646,7 +25646,7 @@
       </c>
       <c r="C389" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D389" s="4" t="inlineStr">
@@ -25683,7 +25683,7 @@
       </c>
       <c r="L389" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M389" s="4" t="inlineStr">
@@ -25705,7 +25705,7 @@
       </c>
       <c r="C390" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D390" s="4" t="inlineStr">
@@ -25742,7 +25742,7 @@
       </c>
       <c r="L390" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M390" s="4" t="inlineStr">
@@ -25764,7 +25764,7 @@
       </c>
       <c r="C391" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D391" s="4" t="inlineStr">
@@ -25801,7 +25801,7 @@
       </c>
       <c r="L391" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M391" s="4" t="inlineStr">
@@ -25823,7 +25823,7 @@
       </c>
       <c r="C392" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D392" s="4" t="inlineStr">
@@ -25860,7 +25860,7 @@
       </c>
       <c r="L392" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M392" s="4" t="inlineStr">
@@ -25882,7 +25882,7 @@
       </c>
       <c r="C393" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D393" s="4" t="inlineStr">
@@ -25919,7 +25919,7 @@
       </c>
       <c r="L393" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M393" s="4" t="inlineStr">
@@ -25941,7 +25941,7 @@
       </c>
       <c r="C394" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D394" s="4" t="inlineStr">
@@ -25978,7 +25978,7 @@
       </c>
       <c r="L394" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M394" s="4" t="inlineStr">
@@ -26000,7 +26000,7 @@
       </c>
       <c r="C395" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D395" s="4" t="inlineStr">
@@ -26037,7 +26037,7 @@
       </c>
       <c r="L395" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M395" s="4" t="inlineStr">
@@ -26059,7 +26059,7 @@
       </c>
       <c r="C396" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D396" s="4" t="inlineStr">
@@ -26096,7 +26096,7 @@
       </c>
       <c r="L396" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M396" s="4" t="inlineStr">
@@ -26118,7 +26118,7 @@
       </c>
       <c r="C397" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D397" s="4" t="inlineStr">
@@ -26155,7 +26155,7 @@
       </c>
       <c r="L397" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M397" s="4" t="inlineStr">
@@ -26177,7 +26177,7 @@
       </c>
       <c r="C398" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D398" s="4" t="inlineStr">
@@ -26214,7 +26214,7 @@
       </c>
       <c r="L398" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M398" s="4" t="inlineStr">
@@ -26236,7 +26236,7 @@
       </c>
       <c r="C399" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D399" s="4" t="inlineStr">
@@ -26273,7 +26273,7 @@
       </c>
       <c r="L399" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M399" s="4" t="inlineStr">
@@ -26295,7 +26295,7 @@
       </c>
       <c r="C400" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D400" s="4" t="inlineStr">
@@ -26332,7 +26332,7 @@
       </c>
       <c r="L400" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M400" s="4" t="inlineStr">
@@ -26354,7 +26354,7 @@
       </c>
       <c r="C401" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D401" s="4" t="inlineStr">
@@ -26391,7 +26391,7 @@
       </c>
       <c r="L401" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M401" s="4" t="inlineStr">
@@ -26413,7 +26413,7 @@
       </c>
       <c r="C402" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D402" s="4" t="inlineStr">
@@ -26450,7 +26450,7 @@
       </c>
       <c r="L402" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M402" s="4" t="inlineStr">
@@ -26472,7 +26472,7 @@
       </c>
       <c r="C403" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D403" s="4" t="inlineStr">
@@ -26509,7 +26509,7 @@
       </c>
       <c r="L403" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M403" s="4" t="inlineStr">
@@ -26531,7 +26531,7 @@
       </c>
       <c r="C404" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D404" s="4" t="inlineStr">
@@ -26568,7 +26568,7 @@
       </c>
       <c r="L404" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M404" s="4" t="inlineStr">
@@ -26590,7 +26590,7 @@
       </c>
       <c r="C405" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D405" s="4" t="inlineStr">
@@ -26627,7 +26627,7 @@
       </c>
       <c r="L405" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M405" s="4" t="inlineStr">
@@ -26649,7 +26649,7 @@
       </c>
       <c r="C406" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D406" s="4" t="inlineStr">
@@ -26686,7 +26686,7 @@
       </c>
       <c r="L406" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M406" s="4" t="inlineStr">
@@ -26708,7 +26708,7 @@
       </c>
       <c r="C407" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D407" s="4" t="inlineStr">
@@ -26745,7 +26745,7 @@
       </c>
       <c r="L407" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M407" s="4" t="inlineStr">
@@ -26767,7 +26767,7 @@
       </c>
       <c r="C408" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D408" s="4" t="inlineStr">
@@ -26804,7 +26804,7 @@
       </c>
       <c r="L408" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M408" s="4" t="inlineStr">
@@ -26826,7 +26826,7 @@
       </c>
       <c r="C409" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D409" s="4" t="inlineStr">
@@ -26863,7 +26863,7 @@
       </c>
       <c r="L409" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M409" s="4" t="inlineStr">
@@ -26885,7 +26885,7 @@
       </c>
       <c r="C410" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D410" s="4" t="inlineStr">
@@ -26922,7 +26922,7 @@
       </c>
       <c r="L410" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M410" s="4" t="inlineStr">
@@ -26944,7 +26944,7 @@
       </c>
       <c r="C411" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D411" s="4" t="inlineStr">
@@ -26981,7 +26981,7 @@
       </c>
       <c r="L411" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M411" s="4" t="inlineStr">
@@ -27003,7 +27003,7 @@
       </c>
       <c r="C412" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D412" s="4" t="inlineStr">
@@ -27040,7 +27040,7 @@
       </c>
       <c r="L412" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M412" s="4" t="inlineStr">
@@ -27062,7 +27062,7 @@
       </c>
       <c r="C413" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D413" s="4" t="inlineStr">
@@ -27099,7 +27099,7 @@
       </c>
       <c r="L413" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M413" s="4" t="inlineStr">
@@ -27121,7 +27121,7 @@
       </c>
       <c r="C414" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D414" s="4" t="inlineStr">
@@ -27158,7 +27158,7 @@
       </c>
       <c r="L414" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M414" s="4" t="inlineStr">
@@ -27180,7 +27180,7 @@
       </c>
       <c r="C415" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D415" s="4" t="inlineStr">
@@ -27217,7 +27217,7 @@
       </c>
       <c r="L415" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M415" s="4" t="inlineStr">
@@ -27239,7 +27239,7 @@
       </c>
       <c r="C416" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D416" s="4" t="inlineStr">
@@ -27276,7 +27276,7 @@
       </c>
       <c r="L416" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M416" s="4" t="inlineStr">
@@ -27298,7 +27298,7 @@
       </c>
       <c r="C417" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D417" s="4" t="inlineStr">
@@ -27335,7 +27335,7 @@
       </c>
       <c r="L417" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M417" s="4" t="inlineStr">
@@ -27357,7 +27357,7 @@
       </c>
       <c r="C418" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D418" s="4" t="inlineStr">
@@ -27394,7 +27394,7 @@
       </c>
       <c r="L418" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M418" s="4" t="inlineStr">
@@ -27416,7 +27416,7 @@
       </c>
       <c r="C419" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D419" s="4" t="inlineStr">
@@ -27453,7 +27453,7 @@
       </c>
       <c r="L419" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M419" s="4" t="inlineStr">
@@ -27475,7 +27475,7 @@
       </c>
       <c r="C420" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D420" s="4" t="inlineStr">
@@ -27512,7 +27512,7 @@
       </c>
       <c r="L420" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M420" s="4" t="inlineStr">
@@ -27534,7 +27534,7 @@
       </c>
       <c r="C421" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D421" s="4" t="inlineStr">
@@ -27571,7 +27571,7 @@
       </c>
       <c r="L421" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M421" s="4" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="C422" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D422" s="4" t="inlineStr">
@@ -27630,7 +27630,7 @@
       </c>
       <c r="L422" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M422" s="4" t="inlineStr">
@@ -27652,7 +27652,7 @@
       </c>
       <c r="C423" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D423" s="4" t="inlineStr">
@@ -27689,7 +27689,7 @@
       </c>
       <c r="L423" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M423" s="4" t="inlineStr">
@@ -27711,7 +27711,7 @@
       </c>
       <c r="C424" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D424" s="4" t="inlineStr">
@@ -27748,7 +27748,7 @@
       </c>
       <c r="L424" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M424" s="4" t="inlineStr">
@@ -27770,7 +27770,7 @@
       </c>
       <c r="C425" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D425" s="4" t="inlineStr">
@@ -27807,7 +27807,7 @@
       </c>
       <c r="L425" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M425" s="4" t="inlineStr">
@@ -27829,7 +27829,7 @@
       </c>
       <c r="C426" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D426" s="4" t="inlineStr">
@@ -27866,7 +27866,7 @@
       </c>
       <c r="L426" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M426" s="4" t="inlineStr">
@@ -27888,7 +27888,7 @@
       </c>
       <c r="C427" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D427" s="4" t="inlineStr">
@@ -27925,7 +27925,7 @@
       </c>
       <c r="L427" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M427" s="4" t="inlineStr">
@@ -27947,7 +27947,7 @@
       </c>
       <c r="C428" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D428" s="4" t="inlineStr">
@@ -27984,7 +27984,7 @@
       </c>
       <c r="L428" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M428" s="4" t="inlineStr">
@@ -28006,7 +28006,7 @@
       </c>
       <c r="C429" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D429" s="4" t="inlineStr">
@@ -28043,7 +28043,7 @@
       </c>
       <c r="L429" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M429" s="4" t="inlineStr">
@@ -28065,7 +28065,7 @@
       </c>
       <c r="C430" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D430" s="4" t="inlineStr">
@@ -28102,7 +28102,7 @@
       </c>
       <c r="L430" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M430" s="4" t="inlineStr">
@@ -28124,7 +28124,7 @@
       </c>
       <c r="C431" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D431" s="4" t="inlineStr">
@@ -28161,7 +28161,7 @@
       </c>
       <c r="L431" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M431" s="4" t="inlineStr">
@@ -28183,7 +28183,7 @@
       </c>
       <c r="C432" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D432" s="4" t="inlineStr">
@@ -28220,7 +28220,7 @@
       </c>
       <c r="L432" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M432" s="4" t="inlineStr">
@@ -28242,7 +28242,7 @@
       </c>
       <c r="C433" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D433" s="4" t="inlineStr">
@@ -28279,7 +28279,7 @@
       </c>
       <c r="L433" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M433" s="4" t="inlineStr">
@@ -28301,7 +28301,7 @@
       </c>
       <c r="C434" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D434" s="4" t="inlineStr">
@@ -28338,7 +28338,7 @@
       </c>
       <c r="L434" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M434" s="4" t="inlineStr">
@@ -28360,7 +28360,7 @@
       </c>
       <c r="C435" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D435" s="4" t="inlineStr">
@@ -28397,7 +28397,7 @@
       </c>
       <c r="L435" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M435" s="4" t="inlineStr">
@@ -28419,7 +28419,7 @@
       </c>
       <c r="C436" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D436" s="4" t="inlineStr">
@@ -28456,7 +28456,7 @@
       </c>
       <c r="L436" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M436" s="4" t="inlineStr">
@@ -28478,7 +28478,7 @@
       </c>
       <c r="C437" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D437" s="4" t="inlineStr">
@@ -28515,7 +28515,7 @@
       </c>
       <c r="L437" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M437" s="4" t="inlineStr">
@@ -28537,7 +28537,7 @@
       </c>
       <c r="C438" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D438" s="4" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="L438" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M438" s="4" t="inlineStr">
@@ -28596,7 +28596,7 @@
       </c>
       <c r="C439" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D439" s="4" t="inlineStr">
@@ -28633,7 +28633,7 @@
       </c>
       <c r="L439" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M439" s="4" t="inlineStr">
@@ -28655,7 +28655,7 @@
       </c>
       <c r="C440" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D440" s="4" t="inlineStr">
@@ -28692,7 +28692,7 @@
       </c>
       <c r="L440" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M440" s="4" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="C441" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D441" s="4" t="inlineStr">
@@ -28751,7 +28751,7 @@
       </c>
       <c r="L441" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M441" s="4" t="inlineStr">
@@ -28773,7 +28773,7 @@
       </c>
       <c r="C442" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D442" s="4" t="inlineStr">
@@ -28810,7 +28810,7 @@
       </c>
       <c r="L442" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M442" s="4" t="inlineStr">
@@ -28832,7 +28832,7 @@
       </c>
       <c r="C443" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D443" s="4" t="inlineStr">
@@ -28869,7 +28869,7 @@
       </c>
       <c r="L443" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M443" s="4" t="inlineStr">
@@ -28891,7 +28891,7 @@
       </c>
       <c r="C444" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D444" s="4" t="inlineStr">
@@ -28928,7 +28928,7 @@
       </c>
       <c r="L444" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M444" s="4" t="inlineStr">
@@ -28950,7 +28950,7 @@
       </c>
       <c r="C445" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D445" s="4" t="inlineStr">
@@ -28987,7 +28987,7 @@
       </c>
       <c r="L445" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M445" s="4" t="inlineStr">
@@ -29009,7 +29009,7 @@
       </c>
       <c r="C446" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D446" s="4" t="inlineStr">
@@ -29046,7 +29046,7 @@
       </c>
       <c r="L446" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M446" s="4" t="inlineStr">
@@ -29068,7 +29068,7 @@
       </c>
       <c r="C447" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D447" s="4" t="inlineStr">
@@ -29105,7 +29105,7 @@
       </c>
       <c r="L447" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M447" s="4" t="inlineStr">
@@ -29127,7 +29127,7 @@
       </c>
       <c r="C448" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D448" s="4" t="inlineStr">
@@ -29164,7 +29164,7 @@
       </c>
       <c r="L448" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M448" s="4" t="inlineStr">
@@ -29186,7 +29186,7 @@
       </c>
       <c r="C449" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D449" s="4" t="inlineStr">
@@ -29223,7 +29223,7 @@
       </c>
       <c r="L449" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M449" s="4" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="C450" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D450" s="4" t="inlineStr">
@@ -29282,7 +29282,7 @@
       </c>
       <c r="L450" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M450" s="4" t="inlineStr">
@@ -29304,7 +29304,7 @@
       </c>
       <c r="C451" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D451" s="4" t="inlineStr">
@@ -29341,7 +29341,7 @@
       </c>
       <c r="L451" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M451" s="4" t="inlineStr">
@@ -29363,7 +29363,7 @@
       </c>
       <c r="C452" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D452" s="4" t="inlineStr">
@@ -29400,7 +29400,7 @@
       </c>
       <c r="L452" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M452" s="4" t="inlineStr">
@@ -29422,7 +29422,7 @@
       </c>
       <c r="C453" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D453" s="4" t="inlineStr">
@@ -29459,7 +29459,7 @@
       </c>
       <c r="L453" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M453" s="4" t="inlineStr">
@@ -29481,7 +29481,7 @@
       </c>
       <c r="C454" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D454" s="4" t="inlineStr">
@@ -29518,7 +29518,7 @@
       </c>
       <c r="L454" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M454" s="4" t="inlineStr">
@@ -29540,7 +29540,7 @@
       </c>
       <c r="C455" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D455" s="4" t="inlineStr">
@@ -29577,7 +29577,7 @@
       </c>
       <c r="L455" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M455" s="4" t="inlineStr">
@@ -29599,7 +29599,7 @@
       </c>
       <c r="C456" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D456" s="4" t="inlineStr">
@@ -29636,7 +29636,7 @@
       </c>
       <c r="L456" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M456" s="4" t="inlineStr">
@@ -29658,7 +29658,7 @@
       </c>
       <c r="C457" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D457" s="4" t="inlineStr">
@@ -29695,7 +29695,7 @@
       </c>
       <c r="L457" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M457" s="4" t="inlineStr">
@@ -29717,7 +29717,7 @@
       </c>
       <c r="C458" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D458" s="4" t="inlineStr">
@@ -29754,7 +29754,7 @@
       </c>
       <c r="L458" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M458" s="4" t="inlineStr">
@@ -29776,7 +29776,7 @@
       </c>
       <c r="C459" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D459" s="4" t="inlineStr">
@@ -29813,7 +29813,7 @@
       </c>
       <c r="L459" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M459" s="4" t="inlineStr">
@@ -29835,7 +29835,7 @@
       </c>
       <c r="C460" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D460" s="4" t="inlineStr">
@@ -29872,7 +29872,7 @@
       </c>
       <c r="L460" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M460" s="4" t="inlineStr">
@@ -29894,7 +29894,7 @@
       </c>
       <c r="C461" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D461" s="4" t="inlineStr">
@@ -29931,7 +29931,7 @@
       </c>
       <c r="L461" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M461" s="4" t="inlineStr">
@@ -29953,7 +29953,7 @@
       </c>
       <c r="C462" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D462" s="4" t="inlineStr">
@@ -29990,7 +29990,7 @@
       </c>
       <c r="L462" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M462" s="4" t="inlineStr">
@@ -30012,7 +30012,7 @@
       </c>
       <c r="C463" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D463" s="4" t="inlineStr">
@@ -30049,7 +30049,7 @@
       </c>
       <c r="L463" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M463" s="4" t="inlineStr">
@@ -30071,7 +30071,7 @@
       </c>
       <c r="C464" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D464" s="4" t="inlineStr">
@@ -30108,7 +30108,7 @@
       </c>
       <c r="L464" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M464" s="4" t="inlineStr">
@@ -30130,7 +30130,7 @@
       </c>
       <c r="C465" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D465" s="4" t="inlineStr">
@@ -30167,7 +30167,7 @@
       </c>
       <c r="L465" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M465" s="4" t="inlineStr">
@@ -30189,7 +30189,7 @@
       </c>
       <c r="C466" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D466" s="4" t="inlineStr">
@@ -30226,7 +30226,7 @@
       </c>
       <c r="L466" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M466" s="4" t="inlineStr">
@@ -30248,7 +30248,7 @@
       </c>
       <c r="C467" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D467" s="4" t="inlineStr">
@@ -30285,7 +30285,7 @@
       </c>
       <c r="L467" s="4" t="inlineStr">
         <is>
-          <t>ORPHAN_AUTO_CLOSE</t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M467" s="4" t="inlineStr">
@@ -30307,7 +30307,7 @@
       </c>
       <c r="C468" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D468" s="4" t="inlineStr">
@@ -30344,7 +30344,7 @@
       </c>
       <c r="L468" s="4" t="inlineStr">
         <is>
-          <t>Rotation → GOOGL (+57.4pp)</t>
+          <t>Rotation swap · +57.4 pp</t>
         </is>
       </c>
       <c r="M468" s="4" t="inlineStr">
@@ -30366,7 +30366,7 @@
       </c>
       <c r="C469" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D469" s="4" t="inlineStr">
@@ -30403,7 +30403,7 @@
       </c>
       <c r="L469" s="4" t="inlineStr">
         <is>
-          <t>Rotation → UBER (+60.6pp)</t>
+          <t>Rotation swap · +60.6 pp</t>
         </is>
       </c>
       <c r="M469" s="4" t="inlineStr">
@@ -30425,7 +30425,7 @@
       </c>
       <c r="C470" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D470" s="4" t="inlineStr">
@@ -30462,7 +30462,7 @@
       </c>
       <c r="L470" s="4" t="inlineStr">
         <is>
-          <t>Rotation → UBER (+60.5pp)</t>
+          <t>Rotation swap · +60.5 pp</t>
         </is>
       </c>
       <c r="M470" s="4" t="inlineStr">
@@ -30484,7 +30484,7 @@
       </c>
       <c r="C471" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D471" s="4" t="inlineStr">
@@ -30521,7 +30521,7 @@
       </c>
       <c r="L471" s="4" t="inlineStr">
         <is>
-          <t>Rotation → BMY (+59.4pp)</t>
+          <t>Rotation swap · +59.4 pp</t>
         </is>
       </c>
       <c r="M471" s="4" t="inlineStr">
@@ -30543,7 +30543,7 @@
       </c>
       <c r="C472" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D472" s="4" t="inlineStr">
@@ -30580,7 +30580,7 @@
       </c>
       <c r="L472" s="4" t="inlineStr">
         <is>
-          <t>→ BMY · +9.9pp alpha</t>
+          <t>Outperformance exit · +9.9 pp</t>
         </is>
       </c>
       <c r="M472" s="4" t="inlineStr">
@@ -30602,7 +30602,7 @@
       </c>
       <c r="C473" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D473" s="4" t="inlineStr">
@@ -30639,7 +30639,7 @@
       </c>
       <c r="L473" s="4" t="inlineStr">
         <is>
-          <t>→ BMY · +63.2pp alpha</t>
+          <t>Outperformance exit · +63.2 pp</t>
         </is>
       </c>
       <c r="M473" s="4" t="inlineStr">
@@ -30661,7 +30661,7 @@
       </c>
       <c r="C474" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D474" s="4" t="inlineStr">
@@ -30698,7 +30698,7 @@
       </c>
       <c r="L474" s="4" t="inlineStr">
         <is>
-          <t>→ BMY · +9.9pp alpha</t>
+          <t>Outperformance exit · +9.9 pp</t>
         </is>
       </c>
       <c r="M474" s="4" t="inlineStr">
@@ -30720,7 +30720,7 @@
       </c>
       <c r="C475" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D475" s="4" t="inlineStr">
@@ -30757,7 +30757,7 @@
       </c>
       <c r="L475" s="4" t="inlineStr">
         <is>
-          <t>→ BMY · +9.8pp alpha</t>
+          <t>Outperformance exit · +9.8 pp</t>
         </is>
       </c>
       <c r="M475" s="4" t="inlineStr">
@@ -30779,7 +30779,7 @@
       </c>
       <c r="C476" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D476" s="4" t="inlineStr">
@@ -30816,7 +30816,7 @@
       </c>
       <c r="L476" s="4" t="inlineStr">
         <is>
-          <t>→ MU · +61.4pp alpha</t>
+          <t>Outperformance exit · +61.4 pp</t>
         </is>
       </c>
       <c r="M476" s="4" t="inlineStr">
@@ -30838,7 +30838,7 @@
       </c>
       <c r="C477" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D477" s="4" t="inlineStr">
@@ -30875,7 +30875,7 @@
       </c>
       <c r="L477" s="4" t="inlineStr">
         <is>
-          <t>→ ADSK · +57.6pp alpha</t>
+          <t>Outperformance exit · +57.6 pp</t>
         </is>
       </c>
       <c r="M477" s="4" t="inlineStr">
@@ -30897,7 +30897,7 @@
       </c>
       <c r="C478" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D478" s="4" t="inlineStr">
@@ -30934,7 +30934,7 @@
       </c>
       <c r="L478" s="4" t="inlineStr">
         <is>
-          <t>→ MU · +5.7pp alpha</t>
+          <t>Outperformance exit · +5.7 pp</t>
         </is>
       </c>
       <c r="M478" s="4" t="inlineStr">
@@ -30956,7 +30956,7 @@
       </c>
       <c r="C479" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D479" s="4" t="inlineStr">
@@ -30993,7 +30993,7 @@
       </c>
       <c r="L479" s="4" t="inlineStr">
         <is>
-          <t>→ MU · +5.4pp alpha</t>
+          <t>Outperformance exit · +5.4 pp</t>
         </is>
       </c>
       <c r="M479" s="4" t="inlineStr">
@@ -31015,7 +31015,7 @@
       </c>
       <c r="C480" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D480" s="4" t="inlineStr">
@@ -31052,7 +31052,7 @@
       </c>
       <c r="L480" s="4" t="inlineStr">
         <is>
-          <t>→ ADSK · +59.4pp alpha</t>
+          <t>Outperformance exit · +59.4 pp</t>
         </is>
       </c>
       <c r="M480" s="4" t="inlineStr">
@@ -31074,7 +31074,7 @@
       </c>
       <c r="C481" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D481" s="4" t="inlineStr">
@@ -31111,7 +31111,7 @@
       </c>
       <c r="L481" s="4" t="inlineStr">
         <is>
-          <t>→ MU · +62.3pp alpha</t>
+          <t>Outperformance exit · +62.3 pp</t>
         </is>
       </c>
       <c r="M481" s="4" t="inlineStr">
@@ -31133,7 +31133,7 @@
       </c>
       <c r="C482" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D482" s="4" t="inlineStr">
@@ -31170,7 +31170,7 @@
       </c>
       <c r="L482" s="4" t="inlineStr">
         <is>
-          <t>→ MU · +5.1pp alpha</t>
+          <t>Outperformance exit · +5.1 pp</t>
         </is>
       </c>
       <c r="M482" s="4" t="inlineStr">
@@ -31192,7 +31192,7 @@
       </c>
       <c r="C483" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D483" s="4" t="inlineStr">
@@ -31229,7 +31229,7 @@
       </c>
       <c r="L483" s="4" t="inlineStr">
         <is>
-          <t>→ MU · +5.2pp alpha</t>
+          <t>Outperformance exit · +5.2 pp</t>
         </is>
       </c>
       <c r="M483" s="4" t="inlineStr">
@@ -31251,7 +31251,7 @@
       </c>
       <c r="C484" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D484" s="4" t="inlineStr">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="L484" s="4" t="inlineStr">
         <is>
-          <t>→ ADSK · +58.4pp alpha</t>
+          <t>Outperformance exit · +58.4 pp</t>
         </is>
       </c>
       <c r="M484" s="4" t="inlineStr">
@@ -31310,7 +31310,7 @@
       </c>
       <c r="C485" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D485" s="4" t="inlineStr">
@@ -31347,7 +31347,7 @@
       </c>
       <c r="L485" s="4" t="inlineStr">
         <is>
-          <t>→ MU · +5.7pp alpha</t>
+          <t>Outperformance exit · +5.7 pp</t>
         </is>
       </c>
       <c r="M485" s="4" t="inlineStr">
@@ -31369,7 +31369,7 @@
       </c>
       <c r="C486" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D486" s="4" t="inlineStr">
@@ -31406,7 +31406,7 @@
       </c>
       <c r="L486" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">ORPHAN_AUTO_CLOSE · CANONICAL_REPAIR v2 </t>
+          <t>Auto-close · orphaned position</t>
         </is>
       </c>
       <c r="M486" s="4" t="inlineStr">
@@ -31428,7 +31428,7 @@
       </c>
       <c r="C487" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D487" s="4" t="inlineStr">
@@ -31465,7 +31465,7 @@
       </c>
       <c r="L487" s="4" t="inlineStr">
         <is>
-          <t>→ TRV · +14.9pp alpha</t>
+          <t>Outperformance exit · +14.9 pp</t>
         </is>
       </c>
       <c r="M487" s="4" t="inlineStr">
@@ -31487,7 +31487,7 @@
       </c>
       <c r="C488" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D488" s="4" t="inlineStr">
@@ -31524,7 +31524,7 @@
       </c>
       <c r="L488" s="4" t="inlineStr">
         <is>
-          <t>→ PLTR · +58.1pp alpha</t>
+          <t>Outperformance exit · +58.1 pp</t>
         </is>
       </c>
       <c r="M488" s="4" t="inlineStr">
@@ -31546,7 +31546,7 @@
       </c>
       <c r="C489" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D489" s="4" t="inlineStr">
@@ -31583,7 +31583,7 @@
       </c>
       <c r="L489" s="4" t="inlineStr">
         <is>
-          <t>→ TRV · +37.8pp alpha</t>
+          <t>Outperformance exit · +37.8 pp</t>
         </is>
       </c>
       <c r="M489" s="4" t="inlineStr">
@@ -31605,7 +31605,7 @@
       </c>
       <c r="C490" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D490" s="4" t="inlineStr">
@@ -31642,7 +31642,7 @@
       </c>
       <c r="L490" s="4" t="inlineStr">
         <is>
-          <t>→ PLTR · +64.5pp alpha</t>
+          <t>Outperformance exit · +64.5 pp</t>
         </is>
       </c>
       <c r="M490" s="4" t="inlineStr">
@@ -31664,7 +31664,7 @@
       </c>
       <c r="C491" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D491" s="4" t="inlineStr">
@@ -31701,7 +31701,7 @@
       </c>
       <c r="L491" s="4" t="inlineStr">
         <is>
-          <t>→ PLTR · +6.0pp alpha</t>
+          <t>Outperformance exit · +6.0 pp</t>
         </is>
       </c>
       <c r="M491" s="4" t="inlineStr">
@@ -31723,7 +31723,7 @@
       </c>
       <c r="C492" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D492" s="4" t="inlineStr">
@@ -31760,7 +31760,7 @@
       </c>
       <c r="L492" s="4" t="inlineStr">
         <is>
-          <t>→ PLTR · +63.2pp alpha</t>
+          <t>Outperformance exit · +63.2 pp</t>
         </is>
       </c>
       <c r="M492" s="4" t="inlineStr">
@@ -31782,7 +31782,7 @@
       </c>
       <c r="C493" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D493" s="4" t="inlineStr">
@@ -31819,7 +31819,7 @@
       </c>
       <c r="L493" s="4" t="inlineStr">
         <is>
-          <t>→ PLTR · +58.2pp alpha</t>
+          <t>Outperformance exit · +58.2 pp</t>
         </is>
       </c>
       <c r="M493" s="4" t="inlineStr">
@@ -31841,7 +31841,7 @@
       </c>
       <c r="C494" s="4" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D494" s="4" t="inlineStr">
@@ -31878,7 +31878,7 @@
       </c>
       <c r="L494" s="4" t="inlineStr">
         <is>
-          <t>→ TRV · +45.6pp alpha</t>
+          <t>Outperformance exit · +45.6 pp</t>
         </is>
       </c>
       <c r="M494" s="4" t="inlineStr">
@@ -31900,7 +31900,7 @@
       </c>
       <c r="C495" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D495" s="4" t="inlineStr">
@@ -31937,7 +31937,7 @@
       </c>
       <c r="L495" s="4" t="inlineStr">
         <is>
-          <t>→ TRV · +14.8pp alpha</t>
+          <t>Outperformance exit · +14.8 pp</t>
         </is>
       </c>
       <c r="M495" s="4" t="inlineStr">
@@ -31959,7 +31959,7 @@
       </c>
       <c r="C496" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D496" s="4" t="inlineStr">
@@ -31996,7 +31996,7 @@
       </c>
       <c r="L496" s="4" t="inlineStr">
         <is>
-          <t>→ TRV · +43.9pp alpha</t>
+          <t>Outperformance exit · +43.9 pp</t>
         </is>
       </c>
       <c r="M496" s="4" t="inlineStr">
@@ -32018,7 +32018,7 @@
       </c>
       <c r="C497" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D497" s="4" t="inlineStr">
@@ -32055,7 +32055,7 @@
       </c>
       <c r="L497" s="4" t="inlineStr">
         <is>
-          <t>→ TRV · +14.4pp alpha</t>
+          <t>Outperformance exit · +14.4 pp</t>
         </is>
       </c>
       <c r="M497" s="4" t="inlineStr">
@@ -32077,7 +32077,7 @@
       </c>
       <c r="C498" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D498" s="4" t="inlineStr">
@@ -32114,7 +32114,7 @@
       </c>
       <c r="L498" s="4" t="inlineStr">
         <is>
-          <t>→ PLTR · +58.0pp alpha</t>
+          <t>Outperformance exit · +58.0 pp</t>
         </is>
       </c>
       <c r="M498" s="4" t="inlineStr">
@@ -32136,7 +32136,7 @@
       </c>
       <c r="C499" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D499" s="4" t="inlineStr">
@@ -32173,7 +32173,7 @@
       </c>
       <c r="L499" s="4" t="inlineStr">
         <is>
-          <t>→ TRV · +37.2pp alpha</t>
+          <t>Outperformance exit · +37.2 pp</t>
         </is>
       </c>
       <c r="M499" s="4" t="inlineStr">
@@ -32195,7 +32195,7 @@
       </c>
       <c r="C500" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D500" s="4" t="inlineStr">
@@ -32232,7 +32232,7 @@
       </c>
       <c r="L500" s="4" t="inlineStr">
         <is>
-          <t>→ TRV · +13.0pp alpha</t>
+          <t>Outperformance exit · +13.0 pp</t>
         </is>
       </c>
       <c r="M500" s="4" t="inlineStr">
@@ -32254,7 +32254,7 @@
       </c>
       <c r="C501" s="4" t="inlineStr">
         <is>
-          <t>Consumer Defensive</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D501" s="4" t="inlineStr">
@@ -32291,7 +32291,7 @@
       </c>
       <c r="L501" s="4" t="inlineStr">
         <is>
-          <t>→ TRV · +15.5pp alpha</t>
+          <t>Outperformance exit · +15.5 pp</t>
         </is>
       </c>
       <c r="M501" s="4" t="inlineStr">
@@ -32313,7 +32313,7 @@
       </c>
       <c r="C502" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D502" s="4" t="inlineStr">
@@ -32350,7 +32350,7 @@
       </c>
       <c r="L502" s="4" t="inlineStr">
         <is>
-          <t>→ TRV · +45.9pp alpha</t>
+          <t>Outperformance exit · +45.9 pp</t>
         </is>
       </c>
       <c r="M502" s="4" t="inlineStr">
@@ -32372,7 +32372,7 @@
       </c>
       <c r="C503" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D503" s="4" t="inlineStr">
@@ -32409,7 +32409,7 @@
       </c>
       <c r="L503" s="4" t="inlineStr">
         <is>
-          <t>→ TRV · +16.4pp alpha</t>
+          <t>Outperformance exit · +16.4 pp</t>
         </is>
       </c>
       <c r="M503" s="4" t="inlineStr">
@@ -32431,7 +32431,7 @@
       </c>
       <c r="C504" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D504" s="4" t="inlineStr">
@@ -32468,7 +32468,7 @@
       </c>
       <c r="L504" s="4" t="inlineStr">
         <is>
-          <t>→ TRV · +15.2pp alpha</t>
+          <t>Outperformance exit · +15.2 pp</t>
         </is>
       </c>
       <c r="M504" s="4" t="inlineStr">
@@ -32490,7 +32490,7 @@
       </c>
       <c r="C505" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D505" s="4" t="inlineStr">
@@ -32527,7 +32527,7 @@
       </c>
       <c r="L505" s="4" t="inlineStr">
         <is>
-          <t>→ TRV · +12.2pp alpha</t>
+          <t>Outperformance exit · +12.2 pp</t>
         </is>
       </c>
       <c r="M505" s="4" t="inlineStr">
@@ -32549,7 +32549,7 @@
       </c>
       <c r="C506" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D506" s="4" t="inlineStr">
@@ -32586,7 +32586,7 @@
       </c>
       <c r="L506" s="4" t="inlineStr">
         <is>
-          <t>→ PLTR · +6.6pp alpha</t>
+          <t>Outperformance exit · +6.6 pp</t>
         </is>
       </c>
       <c r="M506" s="4" t="inlineStr">

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P58"/>
+  <dimension ref="A1:P42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -518,7 +518,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Held: 17 · today's advisory BUY signals: 25 · needing review (stop breach or deep loss): 1</t>
+          <t>Held: 17 · today's advisory BUY signals: 9 · needing review (stop breach or deep loss): 1</t>
         </is>
       </c>
     </row>
@@ -653,12 +653,14 @@
           <t>REVIEW</t>
         </is>
       </c>
-      <c r="M6" s="4" t="n">
-        <v>98</v>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
@@ -721,12 +723,14 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="M7" s="4" t="n">
-        <v>79</v>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -789,12 +793,14 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="M8" s="4" t="n">
-        <v>63</v>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
@@ -858,7 +864,7 @@
         </is>
       </c>
       <c r="M9" s="4" t="n">
-        <v>81</v>
+        <v>59.4</v>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
@@ -925,12 +931,14 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="M10" s="4" t="n">
-        <v>91</v>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
@@ -993,12 +1001,14 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="M11" s="4" t="n">
-        <v>66</v>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
@@ -1061,12 +1071,14 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="M12" s="4" t="n">
-        <v>91</v>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
@@ -1129,12 +1141,14 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="M13" s="4" t="n">
-        <v>85</v>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
@@ -1197,12 +1211,14 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="M14" s="4" t="n">
-        <v>84</v>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
@@ -1265,12 +1281,14 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="M15" s="4" t="n">
-        <v>93</v>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
@@ -1333,12 +1351,14 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="M16" s="4" t="n">
-        <v>87</v>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
@@ -1402,7 +1422,7 @@
         </is>
       </c>
       <c r="M17" s="4" t="n">
-        <v>91</v>
+        <v>62.3</v>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
@@ -1470,7 +1490,7 @@
         </is>
       </c>
       <c r="M18" s="4" t="n">
-        <v>43</v>
+        <v>59.1</v>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
@@ -1537,12 +1557,14 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="M19" s="4" t="n">
-        <v>72</v>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
@@ -1605,12 +1627,14 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="M20" s="4" t="n">
-        <v>91</v>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
@@ -1674,7 +1698,7 @@
         </is>
       </c>
       <c r="M21" s="4" t="n">
-        <v>60</v>
+        <v>56.2</v>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
@@ -1742,7 +1766,7 @@
         </is>
       </c>
       <c r="M22" s="4" t="n">
-        <v>46</v>
+        <v>59.1</v>
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
@@ -1770,7 +1794,7 @@
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -1780,7 +1804,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1792,10 +1816,10 @@
         <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>208.7</v>
+        <v>38.72</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>208.7</v>
+        <v>38.72</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
@@ -1819,11 +1843,11 @@
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>NEW · BUY</t>
         </is>
       </c>
       <c r="M25" s="4" t="n">
-        <v>97</v>
+        <v>59.4</v>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
@@ -1832,7 +1856,7 @@
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:94.37 · positive_momentum:99.21</t>
+          <t>engine verdict NEW_POSITION</t>
         </is>
       </c>
       <c r="P25" s="4" t="inlineStr">
@@ -1844,7 +1868,7 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -1854,7 +1878,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1866,10 +1890,10 @@
         <v>0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>30.78</v>
+        <v>363.45</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>30.78</v>
+        <v>363.45</v>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
@@ -1893,11 +1917,11 @@
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>NEW · BUY</t>
         </is>
       </c>
       <c r="M26" s="4" t="n">
-        <v>99</v>
+        <v>62.3</v>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
@@ -1906,7 +1930,7 @@
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:93.55 · positive_momentum:85.17</t>
+          <t>engine verdict NEW_POSITION</t>
         </is>
       </c>
       <c r="P26" s="4" t="inlineStr">
@@ -1918,7 +1942,7 @@
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>RVTY</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -1928,7 +1952,7 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1940,10 +1964,10 @@
         <v>0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>130</v>
+        <v>126.89</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>130</v>
+        <v>126.89</v>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
@@ -1967,11 +1991,11 @@
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>NEW · BUY</t>
         </is>
       </c>
       <c r="M27" s="4" t="n">
-        <v>91</v>
+        <v>59.4</v>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
@@ -1980,7 +2004,7 @@
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:93.27 · positive_momentum:99.78</t>
+          <t>engine verdict NEW_POSITION</t>
         </is>
       </c>
       <c r="P27" s="4" t="inlineStr">
@@ -1992,7 +2016,7 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -2002,7 +2026,7 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -2014,10 +2038,10 @@
         <v>0</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>363.45</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>363.45</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
@@ -2041,11 +2065,11 @@
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>NEW · BUY</t>
         </is>
       </c>
       <c r="M28" s="4" t="n">
-        <v>91</v>
+        <v>59.4</v>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
@@ -2054,7 +2078,7 @@
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:92.67 · positive_momentum:100.0</t>
+          <t>engine verdict NEW_POSITION</t>
         </is>
       </c>
       <c r="P28" s="4" t="inlineStr">
@@ -2066,7 +2090,7 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>SOLV</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -2076,7 +2100,7 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -2088,10 +2112,10 @@
         <v>0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>92.28</v>
+        <v>59.9</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>92.28</v>
+        <v>59.9</v>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
@@ -2115,11 +2139,11 @@
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>NEW · BUY</t>
         </is>
       </c>
       <c r="M29" s="4" t="n">
-        <v>98</v>
+        <v>62.3</v>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
@@ -2128,7 +2152,7 @@
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:91.85 · positive_momentum:84.59</t>
+          <t>engine verdict NEW_POSITION</t>
         </is>
       </c>
       <c r="P29" s="4" t="inlineStr">
@@ -2140,7 +2164,7 @@
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -2150,7 +2174,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -2162,10 +2186,10 @@
         <v>0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>249.12</v>
+        <v>260.34</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>249.12</v>
+        <v>260.34</v>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
@@ -2189,11 +2213,11 @@
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>NEW · BUY</t>
         </is>
       </c>
       <c r="M30" s="4" t="n">
-        <v>90</v>
+        <v>59.1</v>
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
@@ -2202,7 +2226,7 @@
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:91.59 · positive_momentum:100.0</t>
+          <t>engine verdict NEW_POSITION</t>
         </is>
       </c>
       <c r="P30" s="4" t="inlineStr">
@@ -2214,7 +2238,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -2224,7 +2248,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -2236,10 +2260,10 @@
         <v>0</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>50.63</v>
+        <v>101.02</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>50.63</v>
+        <v>101.02</v>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
@@ -2263,11 +2287,11 @@
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>NEW · BUY</t>
         </is>
       </c>
       <c r="M31" s="4" t="n">
-        <v>98</v>
+        <v>56.2</v>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
@@ -2276,7 +2300,7 @@
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:91.59 · positive_momentum:81.58</t>
+          <t>engine verdict NEW_POSITION</t>
         </is>
       </c>
       <c r="P31" s="4" t="inlineStr">
@@ -2288,7 +2312,7 @@
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -2298,7 +2322,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -2310,10 +2334,10 @@
         <v>0</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>149.75</v>
+        <v>277.21</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>149.75</v>
+        <v>277.21</v>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
@@ -2337,11 +2361,11 @@
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>NEW · BUY</t>
         </is>
       </c>
       <c r="M32" s="4" t="n">
-        <v>97</v>
+        <v>59.1</v>
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
@@ -2350,7 +2374,7 @@
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:91.01 · positive_momentum:93.01</t>
+          <t>engine verdict NEW_POSITION</t>
         </is>
       </c>
       <c r="P32" s="4" t="inlineStr">
@@ -2362,7 +2386,7 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -2372,7 +2396,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -2384,10 +2408,10 @@
         <v>0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>379.86</v>
+        <v>120.38</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>379.86</v>
+        <v>120.38</v>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
@@ -2411,11 +2435,11 @@
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>NEW · BUY</t>
         </is>
       </c>
       <c r="M33" s="4" t="n">
-        <v>86</v>
+        <v>56.2</v>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
@@ -2424,7 +2448,7 @@
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:90.91 · positive_momentum:100.0</t>
+          <t>engine verdict NEW_POSITION</t>
         </is>
       </c>
       <c r="P33" s="4" t="inlineStr">
@@ -2433,1234 +2457,50 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>VRTX</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>554.4</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>554.4</v>
-      </c>
-      <c r="H34" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I34" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K34" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>NEW · STRONG-BUY</t>
-        </is>
-      </c>
-      <c r="M34" s="4" t="n">
-        <v>91</v>
-      </c>
-      <c r="N34" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O34" s="4" t="inlineStr">
-        <is>
-          <t>company_score_top_decile:89.84 · positive_momentum:91.12</t>
-        </is>
-      </c>
-      <c r="P34" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>COP</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="4" t="n">
-        <v>134.18</v>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>134.18</v>
-      </c>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K35" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>NEW · STRONG-BUY</t>
-        </is>
-      </c>
-      <c r="M35" s="4" t="n">
-        <v>95</v>
-      </c>
-      <c r="N35" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O35" s="4" t="inlineStr">
-        <is>
-          <t>company_score_top_decile:88.83 · positive_momentum:90.32</t>
-        </is>
-      </c>
-      <c r="P35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>SJM</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="4" t="n">
-        <v>128.86</v>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>128.86</v>
-      </c>
-      <c r="H36" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I36" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K36" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>NEW · STRONG-BUY</t>
-        </is>
-      </c>
-      <c r="M36" s="4" t="n">
-        <v>95</v>
-      </c>
-      <c r="N36" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O36" s="4" t="inlineStr">
-        <is>
-          <t>company_score_top_decile:88.19 · positive_momentum:90.78</t>
-        </is>
-      </c>
-      <c r="P36" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>R1 is RETIRED_ADVISORY · shown for operator awareness · it opens and closes nothing automatically.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>IQV</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>265.54</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>265.54</v>
-      </c>
-      <c r="H37" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I37" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K37" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>NEW · STRONG-BUY</t>
-        </is>
-      </c>
-      <c r="M37" s="4" t="n">
-        <v>96</v>
-      </c>
-      <c r="N37" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O37" s="4" t="inlineStr">
-        <is>
-          <t>company_score_top_decile:88.15 · positive_momentum:82.21</t>
-        </is>
-      </c>
-      <c r="P37" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Suggested Stop · Entry − 2×ATR14 at entry · a SUGGESTION · it is NOT the canonical dynamic_risk_v2 stop and is not enforced.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>NWS</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="4" t="n">
-        <v>34.38</v>
-      </c>
-      <c r="G38" s="4" t="n">
-        <v>34.38</v>
-      </c>
-      <c r="H38" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I38" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K38" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>NEW · STRONG-BUY</t>
-        </is>
-      </c>
-      <c r="M38" s="4" t="n">
-        <v>98</v>
-      </c>
-      <c r="N38" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O38" s="4" t="inlineStr">
-        <is>
-          <t>company_score_top_decile:86.97 · positive_momentum:74.64</t>
-        </is>
-      </c>
-      <c r="P38" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>Review State · 🟢 NORMAL · 🟡 WATCH (within 3.0% of stop or ≤-8.0% P&amp;L) · 🔴 STOP BREACH (price at/below suggested stop) · 🔴 DEEP LOSS (≤-15.0% P&amp;L).</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>PFE</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>28.56</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>28.56</v>
-      </c>
-      <c r="H39" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I39" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K39" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>NEW · STRONG-BUY</t>
-        </is>
-      </c>
-      <c r="M39" s="4" t="n">
-        <v>96</v>
-      </c>
-      <c r="N39" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O39" s="4" t="inlineStr">
-        <is>
-          <t>company_score_top_decile:86.74 · positive_momentum:75.94</t>
-        </is>
-      </c>
-      <c r="P39" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Action never exceeds REVIEW · R1 auto-exit is prohibited by V2 §18.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>BDX</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="4" t="n">
-        <v>186.56</v>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>186.56</v>
-      </c>
-      <c r="H40" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I40" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K40" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>NEW · STRONG-BUY</t>
-        </is>
-      </c>
-      <c r="M40" s="4" t="n">
-        <v>98</v>
-      </c>
-      <c r="N40" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O40" s="4" t="inlineStr">
-        <is>
-          <t>company_score_top_decile:86.13 · positive_momentum:78.02</t>
-        </is>
-      </c>
-      <c r="P40" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>R1 P&amp;L is never mixed into R2 production performance.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>ICE</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>161.81</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>161.81</v>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K41" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>NEW · STRONG-BUY</t>
-        </is>
-      </c>
-      <c r="M41" s="4" t="n">
-        <v>97</v>
-      </c>
-      <c r="N41" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O41" s="4" t="inlineStr">
-        <is>
-          <t>company_score_top_decile:85.91 · positive_momentum:82.87</t>
-        </is>
-      </c>
-      <c r="P41" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>Confidence % · from the canonical daily recommendation engine (recommendations.json) · NOT CAPTURED where no source scored the name. Distribution: range 0.323–0.623 · mean 0.507 · 0.0% of scored names sit at the maximum.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>TGT</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>163.02</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>163.02</v>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K42" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>NEW · STRONG-BUY</t>
-        </is>
-      </c>
-      <c r="M42" s="4" t="n">
-        <v>92</v>
-      </c>
-      <c r="N42" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O42" s="4" t="inlineStr">
-        <is>
-          <t>company_score_top_decile:85.78 · positive_momentum:82.73</t>
-        </is>
-      </c>
-      <c r="P42" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>JNJ</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="4" t="n">
-        <v>276.92</v>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>276.92</v>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K43" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
-        <is>
-          <t>NEW · STRONG-BUY</t>
-        </is>
-      </c>
-      <c r="M43" s="4" t="n">
-        <v>97</v>
-      </c>
-      <c r="N43" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O43" s="4" t="inlineStr">
-        <is>
-          <t>company_score_top_decile:85.63 · positive_momentum:85.74</t>
-        </is>
-      </c>
-      <c r="P43" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>MRK</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="4" t="n">
-        <v>151.25</v>
-      </c>
-      <c r="G44" s="4" t="n">
-        <v>151.25</v>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I44" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K44" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L44" s="4" t="inlineStr">
-        <is>
-          <t>NEW · STRONG-BUY</t>
-        </is>
-      </c>
-      <c r="M44" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="N44" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O44" s="4" t="inlineStr">
-        <is>
-          <t>company_score_top_decile:85.6 · positive_momentum:100.0</t>
-        </is>
-      </c>
-      <c r="P44" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="4" t="n">
-        <v>26.18</v>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>26.18</v>
-      </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I45" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K45" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L45" s="4" t="inlineStr">
-        <is>
-          <t>NEW · STRONG-BUY</t>
-        </is>
-      </c>
-      <c r="M45" s="4" t="n">
-        <v>97</v>
-      </c>
-      <c r="N45" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O45" s="4" t="inlineStr">
-        <is>
-          <t>company_score_top_decile:85.33 · positive_momentum:85.29</t>
-        </is>
-      </c>
-      <c r="P45" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>OKE</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="4" t="n">
-        <v>94.64</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>94.64</v>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I46" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K46" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>NEW · STRONG-BUY</t>
-        </is>
-      </c>
-      <c r="M46" s="4" t="n">
-        <v>97</v>
-      </c>
-      <c r="N46" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O46" s="4" t="inlineStr">
-        <is>
-          <t>company_score_top_decile:84.97 · positive_momentum:82.88</t>
-        </is>
-      </c>
-      <c r="P46" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>AMGN</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="4" t="n">
-        <v>439.45</v>
-      </c>
-      <c r="G47" s="4" t="n">
-        <v>439.45</v>
-      </c>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I47" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K47" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L47" s="4" t="inlineStr">
-        <is>
-          <t>NEW · STRONG-BUY</t>
-        </is>
-      </c>
-      <c r="M47" s="4" t="n">
-        <v>94</v>
-      </c>
-      <c r="N47" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O47" s="4" t="inlineStr">
-        <is>
-          <t>company_score_top_decile:84.75 · positive_momentum:70.19</t>
-        </is>
-      </c>
-      <c r="P47" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>CPAY</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C48" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="4" t="n">
-        <v>416.48</v>
-      </c>
-      <c r="G48" s="4" t="n">
-        <v>416.48</v>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I48" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K48" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L48" s="4" t="inlineStr">
-        <is>
-          <t>NEW · STRONG-BUY</t>
-        </is>
-      </c>
-      <c r="M48" s="4" t="n">
-        <v>94</v>
-      </c>
-      <c r="N48" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O48" s="4" t="inlineStr">
-        <is>
-          <t>company_score_top_decile:83.98 · positive_momentum:70.2</t>
-        </is>
-      </c>
-      <c r="P48" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>MDT</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="4" t="n">
-        <v>93.62</v>
-      </c>
-      <c r="G49" s="4" t="n">
-        <v>93.62</v>
-      </c>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I49" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K49" s="4" t="inlineStr">
-        <is>
-          <t>ADVISORY SIGNAL</t>
-        </is>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>NEW · STRONG-BUY</t>
-        </is>
-      </c>
-      <c r="M49" s="4" t="n">
-        <v>95</v>
-      </c>
-      <c r="N49" s="4" t="inlineStr">
-        <is>
-          <t>recommendations.json:confidence</t>
-        </is>
-      </c>
-      <c r="O49" s="4" t="inlineStr">
-        <is>
-          <t>company_score_top_decile:83.98 · positive_momentum:84.36</t>
-        </is>
-      </c>
-      <c r="P49" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>R1 is RETIRED_ADVISORY · shown for operator awareness · it opens and closes nothing automatically.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>Suggested Stop · Entry − 2×ATR14 at entry · a SUGGESTION · it is NOT the canonical dynamic_risk_v2 stop and is not enforced.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>Review State · 🟢 NORMAL · 🟡 WATCH (within 3.0% of stop or ≤-8.0% P&amp;L) · 🔴 STOP BREACH (price at/below suggested stop) · 🔴 DEEP LOSS (≤-15.0% P&amp;L).</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>Action never exceeds REVIEW · R1 auto-exit is prohibited by V2 §18.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>R1 P&amp;L is never mixed into R2 production performance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>Confidence % · from the canonical daily recommendation engine (recommendations.json) · NOT CAPTURED where no source scored the name. Distribution: range 0.35–0.99 · mean 0.801 · 0.0% of scored names sit at the maximum.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="7" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>Confidence Source · names exactly where the number came from · a value with no stated source is not trustworthy.</t>
         </is>
@@ -3668,15 +2508,15 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A42:P42"/>
+    <mergeCell ref="A41:P41"/>
+    <mergeCell ref="A36:P36"/>
     <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A56:P56"/>
-    <mergeCell ref="A58:P58"/>
-    <mergeCell ref="A53:P53"/>
-    <mergeCell ref="A55:P55"/>
+    <mergeCell ref="A37:P37"/>
+    <mergeCell ref="A40:P40"/>
+    <mergeCell ref="A39:P39"/>
     <mergeCell ref="A3:P3"/>
-    <mergeCell ref="A54:P54"/>
-    <mergeCell ref="A52:P52"/>
-    <mergeCell ref="A57:P57"/>
+    <mergeCell ref="A38:P38"/>
     <mergeCell ref="A24:P24"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
@@ -3907,12 +2747,14 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="Q6" s="4" t="n">
-        <v>63</v>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="R6" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="S6" s="4" t="inlineStr">
@@ -3994,12 +2836,14 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="Q7" s="4" t="n">
-        <v>91</v>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="R7" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="S7" s="4" t="inlineStr">
@@ -4081,12 +2925,14 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="Q8" s="4" t="n">
-        <v>74</v>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="S8" s="4" t="inlineStr">
@@ -4168,12 +3014,14 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="Q9" s="4" t="n">
-        <v>72</v>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="S9" s="4" t="inlineStr">
@@ -4255,12 +3103,14 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="Q10" s="4" t="n">
-        <v>96</v>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="S10" s="4" t="inlineStr">
@@ -4342,12 +3192,14 @@
           <t>HOLD</t>
         </is>
       </c>
-      <c r="Q11" s="4" t="n">
-        <v>91</v>
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
-          <t>recommendations.json:confidence</t>
+          <t>NOT CAPTURED</t>
         </is>
       </c>
       <c r="S11" s="4" t="inlineStr">
@@ -4418,7 +3270,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Confidence % · from the canonical daily recommendation engine (recommendations.json) · NOT CAPTURED where no source scored the name. Distribution: range 0.35–0.99 · mean 0.801 · 0.0% of scored names sit at the maximum.</t>
+          <t>Confidence % · from the canonical daily recommendation engine (recommendations.json) · NOT CAPTURED where no source scored the name. Distribution: range 0.323–0.623 · mean 0.507 · 0.0% of scored names sit at the maximum.</t>
         </is>
       </c>
     </row>
@@ -10086,7 +8938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -10114,14 +8966,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>56 row(s) · 1 position(s) need attention (stop breach or deep loss) · R2 production 6 · R1 advisory 17 · momentum candidates 15</t>
+          <t>36 row(s) · 1 position(s) need attention (stop breach or deep loss) · R2 production 6 · R1 advisory 17 · momentum candidates 15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Daily recommendations · as-of 2026-09-07 · 508 scored · 115 investable (NEW_POSITION) · 🟢 FRESH</t>
+          <t>Daily recommendations · as-of 2026-09-07 · 15 scored · 9 investable (NEW_POSITION) · 🟢 FRESH</t>
         </is>
       </c>
     </row>
@@ -10245,8 +9097,10 @@
           <t>R2 ACTIVE · held 28 d</t>
         </is>
       </c>
-      <c r="L6" s="4" t="n">
-        <v>63</v>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
@@ -10300,8 +9154,10 @@
           <t>R2 ACTIVE · held 27 d</t>
         </is>
       </c>
-      <c r="L7" s="4" t="n">
-        <v>91</v>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
@@ -10355,8 +9211,10 @@
           <t>R2 ACTIVE · held 28 d</t>
         </is>
       </c>
-      <c r="L8" s="4" t="n">
-        <v>74</v>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
@@ -10410,8 +9268,10 @@
           <t>R2 ACTIVE · held 28 d</t>
         </is>
       </c>
-      <c r="L9" s="4" t="n">
-        <v>72</v>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
@@ -10465,8 +9325,10 @@
           <t>R2 ACTIVE · held 28 d</t>
         </is>
       </c>
-      <c r="L10" s="4" t="n">
-        <v>96</v>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
@@ -10520,8 +9382,10 @@
           <t>R2 ACTIVE · held 27 d</t>
         </is>
       </c>
-      <c r="L11" s="4" t="n">
-        <v>91</v>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
@@ -10577,8 +9441,10 @@
           <t>R1 ADVISORY · held 24 d</t>
         </is>
       </c>
-      <c r="L12" s="4" t="n">
-        <v>98</v>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
@@ -10634,8 +9500,10 @@
           <t>R1 ADVISORY · held 6 d</t>
         </is>
       </c>
-      <c r="L13" s="4" t="n">
-        <v>79</v>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
@@ -10692,7 +9560,7 @@
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>81</v>
+        <v>59.4</v>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
@@ -10748,8 +9616,10 @@
           <t>R1 ADVISORY · held 28 d</t>
         </is>
       </c>
-      <c r="L15" s="4" t="n">
-        <v>66</v>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
@@ -10805,8 +9675,10 @@
           <t>R1 ADVISORY · held 19 d</t>
         </is>
       </c>
-      <c r="L16" s="4" t="n">
-        <v>91</v>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
@@ -10862,8 +9734,10 @@
           <t>R1 ADVISORY · held 19 d</t>
         </is>
       </c>
-      <c r="L17" s="4" t="n">
-        <v>85</v>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
@@ -10919,8 +9793,10 @@
           <t>R1 ADVISORY · held 24 d</t>
         </is>
       </c>
-      <c r="L18" s="4" t="n">
-        <v>84</v>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
@@ -10976,8 +9852,10 @@
           <t>R1 ADVISORY · held 6 d</t>
         </is>
       </c>
-      <c r="L19" s="4" t="n">
-        <v>93</v>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
@@ -11033,8 +9911,10 @@
           <t>R1 ADVISORY · held 28 d</t>
         </is>
       </c>
-      <c r="L20" s="4" t="n">
-        <v>87</v>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
@@ -11091,7 +9971,7 @@
         </is>
       </c>
       <c r="L21" s="4" t="n">
-        <v>91</v>
+        <v>62.3</v>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
@@ -11148,7 +10028,7 @@
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>43</v>
+        <v>59.1</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
@@ -11205,7 +10085,7 @@
         </is>
       </c>
       <c r="L23" s="4" t="n">
-        <v>60</v>
+        <v>56.2</v>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
@@ -11262,7 +10142,7 @@
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>46</v>
+        <v>59.1</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
@@ -11278,12 +10158,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -11292,7 +10172,7 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>208.7</v>
+        <v>38.72</v>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
@@ -11316,7 +10196,7 @@
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>NEW · BUY</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -11325,11 +10205,11 @@
         </is>
       </c>
       <c r="L25" s="4" t="n">
-        <v>97</v>
+        <v>59.4</v>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:94.37 · positive_momentum:99.21</t>
+          <t>engine verdict NEW_POSITION</t>
         </is>
       </c>
     </row>
@@ -11341,12 +10221,12 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -11355,7 +10235,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>30.78</v>
+        <v>126.89</v>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
@@ -11379,7 +10259,7 @@
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>NEW · BUY</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
@@ -11388,11 +10268,11 @@
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>99</v>
+        <v>59.4</v>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:93.55 · positive_momentum:85.17</t>
+          <t>engine verdict NEW_POSITION</t>
         </is>
       </c>
     </row>
@@ -11404,12 +10284,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>RVTY</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -11418,7 +10298,7 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>130</v>
+        <v>59.9</v>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
@@ -11442,7 +10322,7 @@
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>NEW · BUY</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
@@ -11451,11 +10331,11 @@
         </is>
       </c>
       <c r="L27" s="4" t="n">
-        <v>91</v>
+        <v>62.3</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:93.27 · positive_momentum:99.78</t>
+          <t>engine verdict NEW_POSITION</t>
         </is>
       </c>
     </row>
@@ -11467,12 +10347,12 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>SOLV</t>
+          <t>GDDY</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -11481,7 +10361,7 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>92.28</v>
+        <v>101.02</v>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
@@ -11505,7 +10385,7 @@
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>NEW · BUY</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
@@ -11514,37 +10394,39 @@
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>98</v>
+        <v>56.2</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:91.85 · positive_momentum:84.59</t>
+          <t>engine verdict NEW_POSITION</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>249.12</v>
+          <t>⚪ NO_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
@@ -11568,46 +10450,50 @@
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="n">
-        <v>90</v>
+          <t>Momentum candidate · upstream research · not an R2 entry</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:91.59 · positive_momentum:100.0</t>
+          <t>quality_band=UNKNOWN · cannot classify · engine says: unknown quality · watch but don't ac</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>50.63</v>
+          <t>⚪ NO_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
@@ -11631,46 +10517,50 @@
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="n">
-        <v>98</v>
+          <t>Momentum candidate · upstream research · not an R2 entry</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:91.59 · positive_momentum:81.58</t>
+          <t>quality_band=UNKNOWN · cannot classify · engine says: unknown quality · watch but don't ac</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>149.75</v>
+          <t>⚪ NO_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
@@ -11694,46 +10584,50 @@
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="n">
-        <v>97</v>
+          <t>Momentum candidate · upstream research · not an R2 entry</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:91.01 · positive_momentum:93.01</t>
+          <t>quality_band=UNKNOWN · cannot classify · engine says: unknown quality · watch but don't ac</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>379.86</v>
+          <t>⚪ NO_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
@@ -11757,46 +10651,50 @@
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L32" s="4" t="n">
-        <v>86</v>
+          <t>Momentum candidate · upstream research · not an R2 entry</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:90.91 · positive_momentum:100.0</t>
+          <t>quality_band=UNKNOWN · cannot classify · engine says: unknown quality · watch but don't ac</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>VRTX</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>554.4</v>
+          <t>⚪ NO_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
@@ -11820,46 +10718,50 @@
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L33" s="4" t="n">
-        <v>91</v>
+          <t>Momentum candidate · upstream research · not an R2 entry</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:89.84 · positive_momentum:91.12</t>
+          <t>quality_band=UNKNOWN · cannot classify · engine says: unknown quality + falling · not a va</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>134.18</v>
+          <t>⚪ NO_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
@@ -11883,46 +10785,50 @@
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L34" s="4" t="n">
-        <v>95</v>
+          <t>Momentum candidate · upstream research · not an R2 entry</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:88.83 · positive_momentum:90.32</t>
+          <t>quality_band=UNKNOWN · cannot classify · engine says: unknown quality + falling · not a va</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>SJM</t>
+          <t>NCLH</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>128.86</v>
+          <t>⚪ NO_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
@@ -11946,46 +10852,50 @@
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L35" s="4" t="n">
-        <v>95</v>
+          <t>Momentum candidate · upstream research · not an R2 entry</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:88.19 · positive_momentum:90.78</t>
+          <t>quality_band=UNKNOWN · cannot classify · engine says: unknown quality + falling · not a va</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>IQV</t>
+          <t>EFX</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>265.54</v>
+          <t>⚪ NO_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
@@ -12009,46 +10919,50 @@
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L36" s="4" t="n">
-        <v>96</v>
+          <t>Momentum candidate · upstream research · not an R2 entry</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:88.15 · positive_momentum:82.21</t>
+          <t>quality_band=UNKNOWN · cannot classify · engine says: unknown quality + falling · not a va</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>NWS</t>
+          <t>CIEN</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>34.38</v>
+          <t>⚪ NO_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
@@ -12072,46 +10986,50 @@
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L37" s="4" t="n">
-        <v>98</v>
+          <t>Momentum candidate · upstream research · not an R2 entry</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:86.97 · positive_momentum:74.64</t>
+          <t>quality_band=UNKNOWN · cannot classify · engine says: unknown quality + falling · not a va</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>PFE</t>
+          <t>LULU</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>28.56</v>
+          <t>⚪ NO_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
@@ -12135,46 +11053,50 @@
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L38" s="4" t="n">
-        <v>96</v>
+          <t>Momentum candidate · upstream research · not an R2 entry</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:86.74 · positive_momentum:75.94</t>
+          <t>quality_band=UNKNOWN · cannot classify · engine says: unknown quality + falling · not a va</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>BDX</t>
+          <t>PCG</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>186.56</v>
+          <t>⚪ NO_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
@@ -12198,46 +11120,50 @@
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L39" s="4" t="n">
-        <v>98</v>
+          <t>Momentum candidate · upstream research · not an R2 entry</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:86.13 · positive_momentum:78.02</t>
+          <t>quality_band=UNKNOWN · cannot classify · engine says: unknown quality + falling · not a va</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>161.81</v>
+          <t>⚪ NO_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
@@ -12261,46 +11187,50 @@
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L40" s="4" t="n">
-        <v>97</v>
+          <t>Momentum candidate · upstream research · not an R2 entry</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:85.91 · positive_momentum:82.87</t>
+          <t>quality_band=UNKNOWN · cannot classify · engine says: unknown quality + falling · not a va</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>Momentum</t>
         </is>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>TGT</t>
+          <t>APH</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>163.02</v>
+          <t>⚪ NO_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
@@ -12324,1535 +11254,225 @@
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>NEW · STRONG-BUY</t>
+          <t>WATCH</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L41" s="4" t="n">
-        <v>92</v>
+          <t>Momentum candidate · upstream research · not an R2 entry</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>company_score_top_decile:85.78 · positive_momentum:82.73</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>JNJ</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>276.92</v>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I42" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>NEW · STRONG-BUY</t>
-        </is>
-      </c>
-      <c r="K42" s="4" t="inlineStr">
-        <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L42" s="4" t="n">
-        <v>97</v>
-      </c>
-      <c r="M42" s="4" t="inlineStr">
-        <is>
-          <t>company_score_top_decile:85.63 · positive_momentum:85.74</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>MRK</t>
-        </is>
-      </c>
-      <c r="C43" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>151.25</v>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H43" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I43" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>NEW · STRONG-BUY</t>
-        </is>
-      </c>
-      <c r="K43" s="4" t="inlineStr">
-        <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L43" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="M43" s="4" t="inlineStr">
-        <is>
-          <t>company_score_top_decile:85.6 · positive_momentum:100.0</t>
+          <t>quality_band=UNKNOWN · cannot classify · engine says: unknown quality + falling · not a va</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="n">
-        <v>26.18</v>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I44" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>NEW · STRONG-BUY</t>
-        </is>
-      </c>
-      <c r="K44" s="4" t="inlineStr">
-        <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L44" s="4" t="n">
-        <v>97</v>
-      </c>
-      <c r="M44" s="4" t="inlineStr">
-        <is>
-          <t>company_score_top_decile:85.33 · positive_momentum:85.29</t>
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>MOMENTUM → R2 LIFECYCLE RECONCILIATION</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>OKE</t>
-        </is>
-      </c>
-      <c r="C45" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="n">
-        <v>94.64</v>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G45" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I45" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>NEW · STRONG-BUY</t>
-        </is>
-      </c>
-      <c r="K45" s="4" t="inlineStr">
-        <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L45" s="4" t="n">
-        <v>97</v>
-      </c>
-      <c r="M45" s="4" t="inlineStr">
-        <is>
-          <t>company_score_top_decile:84.97 · positive_momentum:82.88</t>
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>Where the rest went</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="inlineStr">
-        <is>
-          <t>AMGN</t>
-        </is>
-      </c>
-      <c r="C46" s="4" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>439.45</v>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G46" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I46" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>NEW · STRONG-BUY</t>
-        </is>
-      </c>
-      <c r="K46" s="4" t="inlineStr">
-        <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L46" s="4" t="n">
-        <v>94</v>
-      </c>
-      <c r="M46" s="4" t="inlineStr">
-        <is>
-          <t>company_score_top_decile:84.75 · positive_momentum:70.19</t>
-        </is>
-      </c>
+          <t>1 · Declared universe</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="n">
+        <v>908</v>
+      </c>
+      <c r="C46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>CPAY</t>
-        </is>
+          <t>2 · Actually evaluated</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="n">
+        <v>905</v>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>416.48</v>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I47" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>NEW · STRONG-BUY</t>
-        </is>
-      </c>
-      <c r="K47" s="4" t="inlineStr">
-        <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L47" s="4" t="n">
-        <v>94</v>
-      </c>
-      <c r="M47" s="4" t="inlineStr">
-        <is>
-          <t>company_score_top_decile:83.98 · positive_momentum:70.2</t>
+          <t>unreadable=0 · insufficient history=3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>MDT</t>
-        </is>
+          <t>3 · Momentum candidates</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>87</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NEW · INVESTABLE</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="n">
-        <v>93.62</v>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I48" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>NEW · STRONG-BUY</t>
-        </is>
-      </c>
-      <c r="K48" s="4" t="inlineStr">
-        <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L48" s="4" t="n">
-        <v>95</v>
-      </c>
-      <c r="M48" s="4" t="inlineStr">
-        <is>
-          <t>company_score_top_decile:83.98 · positive_momentum:84.36</t>
+          <t>818 evaluated tickers showed no momentum signal</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>Momentum</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>DELL</t>
-        </is>
+          <t>4 · In production universe</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>15</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr">
-        <is>
-          <t>⚪ NO_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I49" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="K49" s="4" t="inlineStr">
-        <is>
-          <t>Momentum candidate · upstream research · not an R2 entry</t>
-        </is>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
-      </c>
-      <c r="M49" s="4" t="inlineStr">
-        <is>
-          <t>quality_band=UNKNOWN · cannot classify · engine says: unknown quality · watch but don't ac</t>
+          <t>72 candidate(s) dropped as outside the 516-name production universe</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>Momentum</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>SNDK</t>
-        </is>
+          <t>5 · ACCEPTED by ledger</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>⚪ NO_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H50" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I50" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="K50" s="4" t="inlineStr">
-        <is>
-          <t>Momentum candidate · upstream research · not an R2 entry</t>
-        </is>
-      </c>
-      <c r="L50" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
-      </c>
-      <c r="M50" s="4" t="inlineStr">
-        <is>
-          <t>quality_band=UNKNOWN · cannot classify · engine says: unknown quality · watch but don't ac</t>
+          <t>WATCH=0 · REJECTED=0 · NO_EVIDENCE=15</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>Momentum</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>CF</t>
-        </is>
+          <t>6 · Registry R2 NEW today</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr">
-        <is>
-          <t>⚪ NO_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G51" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I51" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="K51" s="4" t="inlineStr">
-        <is>
-          <t>Momentum candidate · upstream research · not an R2 entry</t>
-        </is>
-      </c>
-      <c r="L51" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
-      </c>
-      <c r="M51" s="4" t="inlineStr">
-        <is>
-          <t>quality_band=UNKNOWN · cannot classify · engine says: unknown quality · watch but don't ac</t>
+          <t>accepted momentum tickers not opened: none</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>Momentum</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="inlineStr">
-        <is>
-          <t>MRNA</t>
-        </is>
-      </c>
-      <c r="C52" s="4" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr">
-        <is>
-          <t>⚪ NO_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F52" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G52" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I52" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="K52" s="4" t="inlineStr">
-        <is>
-          <t>Momentum candidate · upstream research · not an R2 entry</t>
-        </is>
-      </c>
-      <c r="L52" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
-      </c>
-      <c r="M52" s="4" t="inlineStr">
-        <is>
-          <t>quality_band=UNKNOWN · cannot classify · engine says: unknown quality · watch but don't ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>Momentum</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>RCL</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>⚪ NO_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G53" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H53" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I53" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="K53" s="4" t="inlineStr">
-        <is>
-          <t>Momentum candidate · upstream research · not an R2 entry</t>
-        </is>
-      </c>
-      <c r="L53" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
-      </c>
-      <c r="M53" s="4" t="inlineStr">
-        <is>
-          <t>quality_band=UNKNOWN · cannot classify · engine says: unknown quality + falling · not a va</t>
-        </is>
-      </c>
+          <t>7 · R2 sheet ACTIVE</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C52" s="4" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>Momentum</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>CCL</t>
-        </is>
-      </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr">
-        <is>
-          <t>⚪ NO_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G54" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I54" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="K54" s="4" t="inlineStr">
-        <is>
-          <t>Momentum candidate · upstream research · not an R2 entry</t>
-        </is>
-      </c>
-      <c r="L54" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
-      </c>
-      <c r="M54" s="4" t="inlineStr">
-        <is>
-          <t>quality_band=UNKNOWN · cannot classify · engine says: unknown quality + falling · not a va</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>Momentum</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>NCLH</t>
-        </is>
-      </c>
-      <c r="C55" s="4" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D55" s="4" t="inlineStr">
-        <is>
-          <t>⚪ NO_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I55" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="K55" s="4" t="inlineStr">
-        <is>
-          <t>Momentum candidate · upstream research · not an R2 entry</t>
-        </is>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
-      </c>
-      <c r="M55" s="4" t="inlineStr">
-        <is>
-          <t>quality_band=UNKNOWN · cannot classify · engine says: unknown quality + falling · not a va</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>Momentum</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>EFX</t>
-        </is>
-      </c>
-      <c r="C56" s="4" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D56" s="4" t="inlineStr">
-        <is>
-          <t>⚪ NO_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G56" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I56" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="K56" s="4" t="inlineStr">
-        <is>
-          <t>Momentum candidate · upstream research · not an R2 entry</t>
-        </is>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
-      </c>
-      <c r="M56" s="4" t="inlineStr">
-        <is>
-          <t>quality_band=UNKNOWN · cannot classify · engine says: unknown quality + falling · not a va</t>
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>✅ No unexplained losses between momentum and R2.</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>Momentum</t>
-        </is>
-      </c>
-      <c r="B57" s="4" t="inlineStr">
-        <is>
-          <t>CIEN</t>
-        </is>
-      </c>
-      <c r="C57" s="4" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D57" s="4" t="inlineStr">
-        <is>
-          <t>⚪ NO_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G57" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H57" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I57" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="K57" s="4" t="inlineStr">
-        <is>
-          <t>Momentum candidate · upstream research · not an R2 entry</t>
-        </is>
-      </c>
-      <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
-      </c>
-      <c r="M57" s="4" t="inlineStr">
-        <is>
-          <t>quality_band=UNKNOWN · cannot classify · engine says: unknown quality + falling · not a va</t>
+      <c r="A57" s="7" t="inlineStr">
+        <is>
+          <t>This is the primary daily sheet · one stock, one recommendation row.</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>Momentum</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="inlineStr">
-        <is>
-          <t>LULU</t>
-        </is>
-      </c>
-      <c r="C58" s="4" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>⚪ NO_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I58" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="K58" s="4" t="inlineStr">
-        <is>
-          <t>Momentum candidate · upstream research · not an R2 entry</t>
-        </is>
-      </c>
-      <c r="L58" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
-      </c>
-      <c r="M58" s="4" t="inlineStr">
-        <is>
-          <t>quality_band=UNKNOWN · cannot classify · engine says: unknown quality + falling · not a va</t>
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>Source · R2 production (real positions) · R1 advisory (no auto-exit) · Momentum upstream research (never a position).</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>Momentum</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>PCG</t>
-        </is>
-      </c>
-      <c r="C59" s="4" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D59" s="4" t="inlineStr">
-        <is>
-          <t>⚪ NO_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I59" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J59" s="4" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="K59" s="4" t="inlineStr">
-        <is>
-          <t>Momentum candidate · upstream research · not an R2 entry</t>
-        </is>
-      </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
-      </c>
-      <c r="M59" s="4" t="inlineStr">
-        <is>
-          <t>quality_band=UNKNOWN · cannot classify · engine says: unknown quality + falling · not a va</t>
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t>Stop for R2 rows is the canonical dynamic_risk_v2 value · identical to the R2 sheet by construction, not by convention.</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>Momentum</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>FICO</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="D60" s="4" t="inlineStr">
-        <is>
-          <t>⚪ NO_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F60" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G60" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I60" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="K60" s="4" t="inlineStr">
-        <is>
-          <t>Momentum candidate · upstream research · not an R2 entry</t>
-        </is>
-      </c>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
-      </c>
-      <c r="M60" s="4" t="inlineStr">
-        <is>
-          <t>quality_band=UNKNOWN · cannot classify · engine says: unknown quality + falling · not a va</t>
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>R1 rows show a SUGGESTED stop · advisory only · never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
-        <is>
-          <t>Momentum</t>
-        </is>
-      </c>
-      <c r="B61" s="4" t="inlineStr">
-        <is>
-          <t>APH</t>
-        </is>
-      </c>
-      <c r="C61" s="4" t="inlineStr">
-        <is>
-          <t>Tech</t>
-        </is>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>⚪ NO_EVIDENCE</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H61" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I61" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>WATCH</t>
-        </is>
-      </c>
-      <c r="K61" s="4" t="inlineStr">
-        <is>
-          <t>Momentum candidate · upstream research · not an R2 entry</t>
-        </is>
-      </c>
-      <c r="L61" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
-      </c>
-      <c r="M61" s="4" t="inlineStr">
-        <is>
-          <t>quality_band=UNKNOWN · cannot classify · engine says: unknown quality + falling · not a va</t>
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>Momentum ACCEPTED is not an R2 entry · R2 eligibility is a separate gate and is never bypassed by copying momentum into R2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>Reconciliation shows every stage from declared universe to R2 ACTIVE so a candidate can never disappear silently.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>NEW rows are the daily engine's INVESTABLE verdict (action = NEW_POSITION). They are candidates, NOT positions · nothing is opened automatically, and they never enter R2 without passing R2 eligibility.</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>MOMENTUM → R2 LIFECYCLE RECONCILIATION</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="3" t="inlineStr">
-        <is>
-          <t>Stage</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>Where the rest went</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="4" t="inlineStr">
-        <is>
-          <t>1 · Declared universe</t>
-        </is>
-      </c>
-      <c r="B66" s="4" t="n">
-        <v>908</v>
-      </c>
-      <c r="C66" s="4" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>2 · Actually evaluated</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="n">
-        <v>905</v>
-      </c>
-      <c r="C67" s="4" t="inlineStr">
-        <is>
-          <t>unreadable=0 · insufficient history=3</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>3 · Momentum candidates</t>
-        </is>
-      </c>
-      <c r="B68" s="4" t="n">
-        <v>87</v>
-      </c>
-      <c r="C68" s="4" t="inlineStr">
-        <is>
-          <t>818 evaluated tickers showed no momentum signal</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>4 · In production universe</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>72 candidate(s) dropped as outside the 516-name production universe</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>5 · ACCEPTED by ledger</t>
-        </is>
-      </c>
-      <c r="B70" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>WATCH=0 · REJECTED=0 · NO_EVIDENCE=15</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>6 · Registry R2 NEW today</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>accepted momentum tickers not opened: none</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
-        <is>
-          <t>7 · R2 sheet ACTIVE</t>
-        </is>
-      </c>
-      <c r="B72" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="C72" s="4" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>✅ No unexplained losses between momentum and R2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="7" t="inlineStr">
-        <is>
-          <t>This is the primary daily sheet · one stock, one recommendation row.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="7" t="inlineStr">
-        <is>
-          <t>Source · R2 production (real positions) · R1 advisory (no auto-exit) · Momentum upstream research (never a position).</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="7" t="inlineStr">
-        <is>
-          <t>Stop for R2 rows is the canonical dynamic_risk_v2 value · identical to the R2 sheet by construction, not by convention.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="7" t="inlineStr">
-        <is>
-          <t>R1 rows show a SUGGESTED stop · advisory only · never auto-exited.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="7" t="inlineStr">
-        <is>
-          <t>Momentum ACCEPTED is not an R2 entry · R2 eligibility is a separate gate and is never bypassed by copying momentum into R2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="7" t="inlineStr">
-        <is>
-          <t>Reconciliation shows every stage from declared universe to R2 ACTIVE so a candidate can never disappear silently.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="7" t="inlineStr">
-        <is>
-          <t>NEW rows are the daily engine's INVESTABLE verdict (action = NEW_POSITION). They are candidates, NOT positions · nothing is opened automatically, and they never enter R2 without passing R2 eligibility.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="7" t="inlineStr">
-        <is>
-          <t>Confidence % · from the canonical daily recommendation engine (recommendations.json) · NOT CAPTURED where no source scored the name. Distribution: range 0.35–0.99 · mean 0.801 · 0.0% of scored names sit at the maximum.</t>
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>Confidence % · from the canonical daily recommendation engine (recommendations.json) · NOT CAPTURED where no source scored the name. Distribution: range 0.323–0.623 · mean 0.507 · 0.0% of scored names sit at the maximum.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A84:M84"/>
+    <mergeCell ref="A60:M60"/>
+    <mergeCell ref="A44:M44"/>
     <mergeCell ref="A1:M1"/>
-    <mergeCell ref="A80:M80"/>
-    <mergeCell ref="A79:M79"/>
-    <mergeCell ref="A74:M74"/>
+    <mergeCell ref="A61:M61"/>
+    <mergeCell ref="A58:M58"/>
+    <mergeCell ref="A54:M54"/>
     <mergeCell ref="A4:M4"/>
+    <mergeCell ref="A62:M62"/>
     <mergeCell ref="A3:M3"/>
-    <mergeCell ref="A78:M78"/>
-    <mergeCell ref="A77:M77"/>
-    <mergeCell ref="A83:M83"/>
     <mergeCell ref="A64:M64"/>
-    <mergeCell ref="A81:M81"/>
+    <mergeCell ref="A59:M59"/>
+    <mergeCell ref="A57:M57"/>
     <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A82:M82"/>
+    <mergeCell ref="A63:M63"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -8970,7 +8970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9012,131 +9012,81 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>🔴 DATA FRESHNESS · 93 of 95 artifacts fresh · STALE 1 · MISSING 1 · 1 pipeline steps declare no artifact (unverifiable) · worst: usa/reports/macro_history.parquet (Nonetd) · usa/reports/news_sentiment_summary.json (10td)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
           <t>⚠ BLOCKERS: DAILY RECOMMENDATIONS STALE · /home/runner/work/NexaQuant/NexaQuant/usa/reports/recommendations.json is as-of 2026-09-07 but this report is as-of 2026-09-08 · today's new opportunities are NOT in this workbook. Producer: usa/research/recommendations/run.py (USA) · research/recommendations/run.py (India)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Stock</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>Current Price</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H6" s="3" t="inlineStr">
         <is>
           <t>Distance to Stop %</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K6" s="3" t="inlineStr">
         <is>
           <t>Lifecycle</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>Confidence %</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M6" s="3" t="inlineStr">
         <is>
           <t>Why</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>🟢 NORMAL</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>186.42</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>-3.49</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>174.3364</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>227.43</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>R2 ACTIVE · held 29 d</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
-      </c>
-      <c r="M6" s="4" t="inlineStr">
-        <is>
-          <t>canonical dynamic stop intact</t>
         </is>
       </c>
     </row>
@@ -9148,7 +9098,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -9162,19 +9112,19 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>87.90000000000001</v>
+        <v>186.42</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-1.82</v>
+        <v>-3.49</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>83.2157</v>
+        <v>174.3364</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>5.33</v>
+        <v>6.48</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>99.06</v>
+        <v>227.43</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -9183,7 +9133,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>R2 ACTIVE · held 28 d</t>
+          <t>R2 ACTIVE · held 29 d</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -9205,7 +9155,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -9219,19 +9169,19 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>369.35</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>-1.67</v>
+        <v>-1.82</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>356.8957</v>
+        <v>83.2157</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>3.37</v>
+        <v>5.33</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>402.23</v>
+        <v>99.06</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
@@ -9240,7 +9190,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>R2 ACTIVE · held 29 d</t>
+          <t>R2 ACTIVE · held 28 d</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -9262,7 +9212,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -9276,19 +9226,19 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>174.33</v>
+        <v>369.35</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>-0.51</v>
+        <v>-1.67</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>161.969</v>
+        <v>356.8957</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>7.09</v>
+        <v>3.37</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>204.13</v>
+        <v>402.23</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
@@ -9319,7 +9269,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -9333,19 +9283,19 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>375.07</v>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>4</v>
+        <v>174.33</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.51</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>362.4986</v>
+        <v>161.969</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3.35</v>
+        <v>7.09</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>384</v>
+        <v>204.13</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
@@ -9376,7 +9326,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -9390,19 +9340,19 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>66.81999999999999</v>
+        <v>375.07</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5.05</v>
+        <v>4</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>63.8043</v>
+        <v>362.4986</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4.51</v>
+        <v>3.35</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>69.45</v>
+        <v>384</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -9411,7 +9361,7 @@
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>R2 ACTIVE · held 28 d</t>
+          <t>R2 ACTIVE · held 29 d</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -9428,12 +9378,12 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>EIX</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -9443,34 +9393,32 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>🔴 DEEP LOSS</t>
+          <t>🟢 NORMAL</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>56.77</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>-20.5</v>
+        <v>66.81999999999999</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>5.05</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>66.33710000000001</v>
+        <v>63.8043</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-16.85</v>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>4.51</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>69.45</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>REVIEW</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 25 d</t>
+          <t>R2 ACTIVE · held 28 d</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -9480,7 +9428,7 @@
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>R1 deep unrealized loss · no auto-exit</t>
+          <t>canonical dynamic stop intact</t>
         </is>
       </c>
     </row>
@@ -9492,7 +9440,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>EIX</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -9502,20 +9450,20 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>🟢 NORMAL</t>
+          <t>🔴 DEEP LOSS</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>156.29</v>
+        <v>56.77</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>-3.44</v>
+        <v>-20.5</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>147.9529</v>
+        <v>66.33710000000001</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>5.33</v>
+        <v>-16.85</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
@@ -9524,12 +9472,12 @@
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>HOLD</t>
+          <t>REVIEW</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 7 d</t>
+          <t>R1 ADVISORY · held 25 d</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -9539,7 +9487,7 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>R1 advisory · within suggested stop</t>
+          <t>R1 deep unrealized loss · no auto-exit</t>
         </is>
       </c>
     </row>
@@ -9551,7 +9499,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -9565,16 +9513,16 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>75.76000000000001</v>
+        <v>156.29</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>-2.91</v>
+        <v>-3.44</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>72.40940000000001</v>
+        <v>147.9529</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.42</v>
+        <v>5.33</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
@@ -9588,11 +9536,13 @@
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 29 d</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v>59.4</v>
+          <t>R1 ADVISORY · held 7 d</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
@@ -9608,7 +9558,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -9622,16 +9572,16 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>58.42</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>-2.78</v>
+        <v>-2.91</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>56.6217</v>
+        <v>72.40940000000001</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>3.08</v>
+        <v>4.42</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
@@ -9645,13 +9595,11 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 20 d</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
+          <t>R1 ADVISORY · held 29 d</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>59.4</v>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
@@ -9667,12 +9615,12 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>FOX</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -9681,16 +9629,16 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>266.51</v>
+        <v>58.42</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-2.36</v>
+        <v>-2.78</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>247.1386</v>
+        <v>56.6217</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>7.27</v>
+        <v>3.08</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
@@ -9704,7 +9652,7 @@
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 29 d</t>
+          <t>R1 ADVISORY · held 20 d</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -9726,12 +9674,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -9740,16 +9688,16 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>338.46</v>
+        <v>266.51</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>-1.75</v>
+        <v>-2.36</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>323.138</v>
+        <v>247.1386</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>4.53</v>
+        <v>7.27</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
@@ -9763,11 +9711,13 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 20 d</t>
-        </is>
-      </c>
-      <c r="L17" s="4" t="n">
-        <v>55.8</v>
+          <t>R1 ADVISORY · held 29 d</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
@@ -9783,7 +9733,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -9797,16 +9747,16 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>499.7</v>
+        <v>338.46</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-1.07</v>
+        <v>-1.75</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>469.0698</v>
+        <v>323.138</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>6.13</v>
+        <v>4.53</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
@@ -9820,13 +9770,11 @@
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 29 d</t>
-        </is>
-      </c>
-      <c r="L18" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
+          <t>R1 ADVISORY · held 20 d</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>55.8</v>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
@@ -9842,7 +9790,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -9856,16 +9804,16 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>126.75</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>0.06</v>
+        <v>499.7</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-1.07</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>119.43</v>
+        <v>469.0698</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>5.78</v>
+        <v>6.13</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
@@ -9879,7 +9827,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 25 d</t>
+          <t>R1 ADVISORY · held 29 d</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -9901,7 +9849,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>SAIC</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -9915,16 +9863,16 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>188.8</v>
+        <v>126.75</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>0.59</v>
+        <v>0.06</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>180.8543</v>
+        <v>119.43</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>4.21</v>
+        <v>5.78</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
@@ -9938,7 +9886,7 @@
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 7 d</t>
+          <t>R1 ADVISORY · held 25 d</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -9960,7 +9908,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -9974,16 +9922,16 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>277.03</v>
+        <v>188.8</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.68</v>
+        <v>0.59</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>261.9314</v>
+        <v>180.8543</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>5.45</v>
+        <v>4.21</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
@@ -10000,8 +9948,10 @@
           <t>R1 ADVISORY · held 7 d</t>
         </is>
       </c>
-      <c r="L21" s="4" t="n">
-        <v>59.1</v>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
@@ -10017,7 +9967,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -10031,16 +9981,16 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>370.72</v>
+        <v>277.03</v>
       </c>
       <c r="F22" s="6" t="n">
-        <v>2.41</v>
+        <v>0.68</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>342.2271</v>
+        <v>261.9314</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>7.69</v>
+        <v>5.45</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
@@ -10058,7 +10008,7 @@
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>62.3</v>
+        <v>59.1</v>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
@@ -10074,7 +10024,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -10088,16 +10038,16 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>122.11</v>
+        <v>370.72</v>
       </c>
       <c r="F23" s="6" t="n">
-        <v>17.97</v>
+        <v>2.41</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>91.0157</v>
+        <v>342.2271</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>25.46</v>
+        <v>7.69</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
@@ -10115,7 +10065,7 @@
         </is>
       </c>
       <c r="L23" s="4" t="n">
-        <v>56.2</v>
+        <v>62.3</v>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
@@ -10131,7 +10081,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -10145,16 +10095,16 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>259.23</v>
+        <v>122.11</v>
       </c>
       <c r="F24" s="6" t="n">
-        <v>32.12</v>
+        <v>17.97</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>179.3029</v>
+        <v>91.0157</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>30.83</v>
+        <v>25.46</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
@@ -10168,13 +10118,11 @@
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · held 25 d</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
+          <t>R1 ADVISORY · held 7 d</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>56.2</v>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
@@ -10190,36 +10138,30 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>🟢 NEW · INVESTABLE</t>
+          <t>🟢 NORMAL</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>39.59</v>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>259.23</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>32.12</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>179.3029</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>30.83</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
@@ -10228,20 +10170,22 @@
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>NEW · BUY</t>
+          <t>HOLD</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>NEW CANDIDATE · not a position · no auto-entry</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="n">
-        <v>59.4</v>
+          <t>R1 ADVISORY · held 25 d</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>engine verdict NEW_POSITION</t>
+          <t>R1 advisory · within suggested stop</t>
         </is>
       </c>
     </row>
@@ -10253,7 +10197,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -10267,7 +10211,7 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>126.75</v>
+        <v>39.59</v>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
@@ -10316,7 +10260,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -10330,7 +10274,7 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>60.04</v>
+        <v>126.75</v>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
@@ -10363,7 +10307,7 @@
         </is>
       </c>
       <c r="L27" s="4" t="n">
-        <v>62.3</v>
+        <v>59.4</v>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
@@ -10374,28 +10318,26 @@
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Momentum</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>ADSK</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>🟡 WATCH</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>🟢 NEW · INVESTABLE</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>60.04</v>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
@@ -10419,22 +10361,20 @@
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>WATCH</t>
+          <t>NEW · BUY</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>Momentum candidate · upstream research · not an R2 entry</t>
-        </is>
-      </c>
-      <c r="L28" s="4" t="inlineStr">
-        <is>
-          <t>NOT CAPTURED</t>
-        </is>
+          <t>NEW CANDIDATE · not a position · no auto-entry</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>62.3</v>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>verdict=REBOUND_WATCH · quality=OK · quality on sale · watch for reversal signal</t>
+          <t>engine verdict NEW_POSITION</t>
         </is>
       </c>
     </row>
@@ -10446,17 +10386,17 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>⚪ NO_EVIDENCE</t>
+          <t>🟡 WATCH</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -10501,7 +10441,7 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>quality_band=UNKNOWN · cannot classify · engine says: unknown quality · watch but don't ac</t>
+          <t>verdict=REBOUND_WATCH · quality=OK · quality on sale · watch for reversal signal</t>
         </is>
       </c>
     </row>
@@ -10513,7 +10453,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>DELL</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -10580,7 +10520,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>DELL</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -10647,7 +10587,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -10714,7 +10654,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -10781,7 +10721,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -10848,7 +10788,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>MPC</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -10903,7 +10843,7 @@
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>quality_band=UNKNOWN · cannot classify · engine says: unknown quality + falling · not a va</t>
+          <t>quality_band=UNKNOWN · cannot classify · engine says: unknown quality · watch but don't ac</t>
         </is>
       </c>
     </row>
@@ -10915,7 +10855,7 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>RCL</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -10982,7 +10922,7 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>NCLH</t>
+          <t>RCL</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -11049,7 +10989,7 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>PCG</t>
+          <t>NCLH</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -11116,7 +11056,7 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>CIEN</t>
+          <t>PCG</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -11183,7 +11123,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>LULU</t>
+          <t>CIEN</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -11250,164 +11190,216 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
+          <t>LULU</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>⚪ NO_EVIDENCE</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>Momentum candidate · upstream research · not an R2 entry</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>NOT CAPTURED</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>quality_band=UNKNOWN · cannot classify · engine says: unknown quality + falling · not a va</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>Momentum</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
           <t>FICO</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C42" s="4" t="inlineStr">
         <is>
           <t>UNKNOWN</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D42" s="4" t="inlineStr">
         <is>
           <t>⚪ NO_EVIDENCE</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I41" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
         <is>
           <t>WATCH</t>
         </is>
       </c>
-      <c r="K41" s="4" t="inlineStr">
+      <c r="K42" s="4" t="inlineStr">
         <is>
           <t>Momentum candidate · upstream research · not an R2 entry</t>
         </is>
       </c>
-      <c r="L41" s="4" t="inlineStr">
+      <c r="L42" s="4" t="inlineStr">
         <is>
           <t>NOT CAPTURED</t>
         </is>
       </c>
-      <c r="M41" s="4" t="inlineStr">
+      <c r="M42" s="4" t="inlineStr">
         <is>
           <t>quality_band=UNKNOWN · cannot classify · engine says: unknown quality + falling · not a va</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>MOMENTUM → R2 LIFECYCLE RECONCILIATION</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>Stage</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B46" s="3" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>Where the rest went</t>
         </is>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>1 · Declared universe</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="n">
-        <v>908</v>
-      </c>
-      <c r="C46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>2 · Actually evaluated</t>
+          <t>1 · Declared universe</t>
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>905</v>
-      </c>
-      <c r="C47" s="4" t="inlineStr">
-        <is>
-          <t>unreadable=0 · insufficient history=3</t>
-        </is>
-      </c>
+        <v>908</v>
+      </c>
+      <c r="C47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>3 · Momentum candidates</t>
+          <t>2 · Actually evaluated</t>
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>90</v>
+        <v>905</v>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>815 evaluated tickers showed no momentum signal</t>
+          <t>unreadable=0 · insufficient history=3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>4 · In production universe</t>
+          <t>3 · Momentum candidates</t>
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>72 candidate(s) dropped as outside the 516-name production universe</t>
+          <t>815 evaluated tickers showed no momentum signal</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>5 · ACCEPTED by ledger</t>
+          <t>4 · In production universe</t>
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>WATCH=1 · REJECTED=0 · NO_EVIDENCE=17</t>
+          <t>72 candidate(s) dropped as outside the 516-name production universe</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>6 · Registry R2 NEW today</t>
+          <t>5 · ACCEPTED by ledger</t>
         </is>
       </c>
       <c r="B51" s="4" t="n">
@@ -11415,98 +11407,114 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>accepted momentum tickers not opened: none</t>
+          <t>WATCH=1 · REJECTED=0 · NO_EVIDENCE=17</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
+          <t>6 · Registry R2 NEW today</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>accepted momentum tickers not opened: none</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
           <t>7 · R2 sheet ACTIVE</t>
         </is>
       </c>
-      <c r="B52" s="4" t="n">
+      <c r="B53" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="C52" s="4" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>✅ No unexplained losses between momentum and R2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>This is the primary daily sheet · one stock, one recommendation row.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>Source · R2 production (real positions) · R1 advisory (no auto-exit) · Momentum upstream research (never a position).</t>
+          <t>This is the primary daily sheet · one stock, one recommendation row.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>Stop for R2 rows is the canonical dynamic_risk_v2 value · identical to the R2 sheet by construction, not by convention.</t>
+          <t>Source · R2 production (real positions) · R1 advisory (no auto-exit) · Momentum upstream research (never a position).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>R1 rows show a SUGGESTED stop · advisory only · never auto-exited.</t>
+          <t>Stop for R2 rows is the canonical dynamic_risk_v2 value · identical to the R2 sheet by construction, not by convention.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>Momentum ACCEPTED is not an R2 entry · R2 eligibility is a separate gate and is never bypassed by copying momentum into R2.</t>
+          <t>R1 rows show a SUGGESTED stop · advisory only · never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>Reconciliation shows every stage from declared universe to R2 ACTIVE so a candidate can never disappear silently.</t>
+          <t>Momentum ACCEPTED is not an R2 entry · R2 eligibility is a separate gate and is never bypassed by copying momentum into R2.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>NEW rows are the daily engine's INVESTABLE verdict (action = NEW_POSITION). They are candidates, NOT positions · nothing is opened automatically, and they never enter R2 without passing R2 eligibility.</t>
+          <t>Reconciliation shows every stage from declared universe to R2 ACTIVE so a candidate can never disappear silently.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
+          <t>NEW rows are the daily engine's INVESTABLE verdict (action = NEW_POSITION). They are candidates, NOT positions · nothing is opened automatically, and they never enter R2 without passing R2 eligibility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
           <t>Confidence % · from the canonical daily recommendation engine (recommendations.json) · NOT CAPTURED where no source scored the name. Distribution: range 0.323–0.623 · mean 0.5 · 0.0% of scored names sit at the maximum.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="15">
     <mergeCell ref="A60:M60"/>
-    <mergeCell ref="A44:M44"/>
     <mergeCell ref="A1:M1"/>
+    <mergeCell ref="A5:M5"/>
+    <mergeCell ref="A45:M45"/>
     <mergeCell ref="A61:M61"/>
     <mergeCell ref="A58:M58"/>
-    <mergeCell ref="A54:M54"/>
     <mergeCell ref="A4:M4"/>
     <mergeCell ref="A62:M62"/>
     <mergeCell ref="A3:M3"/>
+    <mergeCell ref="A55:M55"/>
     <mergeCell ref="A64:M64"/>
     <mergeCell ref="A59:M59"/>
-    <mergeCell ref="A57:M57"/>
+    <mergeCell ref="A65:M65"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A63:M63"/>
   </mergeCells>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P38"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -527,220 +527,98 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>🔎 WHY NEW=0 · 516 scored · 18 already in CURRENT · biggest blocker: model disagreement (397) · lost to the 15-name ensemble truncation: 2 · lifecycle defects: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>⛔ STALE INPUT · recommendations_v3 STALE (1 day(s) old) · ensemble STALE (1 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Market</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Engine</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Entry Date</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>Entry Price</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Current Price</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H7" s="3" t="inlineStr">
         <is>
           <t>P&amp;L %</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>Confidence %</t>
         </is>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>Stop</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K7" s="3" t="inlineStr">
         <is>
           <t>Stop State</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
+      <c r="L7" s="3" t="inlineStr">
         <is>
           <t>Dist to Stop %</t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="M7" s="3" t="inlineStr">
         <is>
           <t>Max Loss if Stop %</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="N7" s="3" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t>Position ID</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>Reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>PLTR</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>ACTIVE+</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>175.23</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>174.33</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>161.969</v>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>INTACT</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>7.09</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>-7.57</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>204.13</v>
-      </c>
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>USA-R2-PLTR-20260810-f9e975</t>
-        </is>
-      </c>
-      <c r="P6" s="4" t="inlineStr">
-        <is>
-          <t>STRONG BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>TRV</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>ACTIVE+</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>375.62</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>369.35</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>-1.67</v>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>356.8957</v>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>INTACT</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>-4.98</v>
-      </c>
-      <c r="N7" s="4" t="n">
-        <v>402.23</v>
-      </c>
-      <c r="O7" s="4" t="inlineStr">
-        <is>
-          <t>USA-R2-TRV-20260810-9cd25d</t>
-        </is>
-      </c>
-      <c r="P7" s="4" t="inlineStr">
-        <is>
-          <t>BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -752,7 +630,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -771,13 +649,13 @@
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>193.17</v>
+        <v>175.23</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>186.42</v>
+        <v>174.33</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>-3.49</v>
+        <v>-0.51</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
@@ -785,7 +663,7 @@
         </is>
       </c>
       <c r="J8" s="4" t="n">
-        <v>174.3364</v>
+        <v>161.969</v>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
@@ -793,17 +671,17 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>6.48</v>
+        <v>7.09</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-9.75</v>
+        <v>-7.57</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>227.43</v>
+        <v>204.13</v>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-IT-20260810-b5fd37</t>
+          <t>USA-R2-PLTR-20260810-f9e975</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
@@ -820,12 +698,12 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -835,17 +713,17 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>63.83</v>
+        <v>375.62</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>66.81999999999999</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>4.68</v>
+        <v>369.35</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>-1.67</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
@@ -853,7 +731,7 @@
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>60.0271</v>
+        <v>356.8957</v>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
@@ -861,22 +739,22 @@
         </is>
       </c>
       <c r="L9" s="4" t="n">
-        <v>10.17</v>
+        <v>3.37</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-5.96</v>
+        <v>-4.98</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>69.53</v>
+        <v>402.23</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-BMY-20260814-a3b600</t>
+          <t>USA-R2-TRV-20260810-9cd25d</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -888,12 +766,12 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -903,17 +781,17 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>275.17</v>
+        <v>193.17</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>277.03</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>0.68</v>
+        <v>186.42</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-3.49</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
@@ -921,7 +799,7 @@
         </is>
       </c>
       <c r="J10" s="4" t="n">
-        <v>261.9314</v>
+        <v>174.3364</v>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
@@ -929,22 +807,22 @@
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.45</v>
+        <v>6.48</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-4.81</v>
+        <v>-9.75</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>295.03</v>
+        <v>227.43</v>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-GRMN-20260901-4c77f2</t>
+          <t>USA-R2-IT-20260810-b5fd37</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>STRONG BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -956,7 +834,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -971,17 +849,17 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>175.23</v>
+        <v>63.83</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>174.33</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>-0.51</v>
+        <v>66.81999999999999</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>4.68</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
@@ -989,7 +867,7 @@
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>155.965</v>
+        <v>60.0271</v>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
@@ -997,17 +875,17 @@
         </is>
       </c>
       <c r="L11" s="4" t="n">
-        <v>10.53</v>
+        <v>10.17</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-10.99</v>
+        <v>-5.96</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>204.13</v>
+        <v>69.53</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-PLTR-20260810-5c4552</t>
+          <t>USA-R1-BMY-20260814-a3b600</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
@@ -1024,7 +902,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1039,17 +917,17 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>505.11</v>
+        <v>275.17</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>499.7</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>-1.07</v>
+        <v>277.03</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.68</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
@@ -1057,7 +935,7 @@
         </is>
       </c>
       <c r="J12" s="4" t="n">
-        <v>469.0698</v>
+        <v>261.9314</v>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
@@ -1065,17 +943,17 @@
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>6.13</v>
+        <v>5.45</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-7.13</v>
+        <v>-4.81</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>559.17</v>
+        <v>295.03</v>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-MSFT-20260810-6110fc</t>
+          <t>USA-R1-GRMN-20260901-4c77f2</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
@@ -1092,7 +970,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1111,13 +989,13 @@
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>272.96</v>
+        <v>175.23</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>266.51</v>
+        <v>174.33</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>-2.36</v>
+        <v>-0.51</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
@@ -1125,7 +1003,7 @@
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>247.1386</v>
+        <v>155.965</v>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
@@ -1133,17 +1011,17 @@
         </is>
       </c>
       <c r="L13" s="4" t="n">
-        <v>7.27</v>
+        <v>10.53</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-9.460000000000001</v>
+        <v>-10.99</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>311.69</v>
+        <v>204.13</v>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-ADBE-20260810-4ad164</t>
+          <t>USA-R1-PLTR-20260810-5c4552</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr">
@@ -1160,7 +1038,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1175,17 +1053,17 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>90.22</v>
+        <v>505.11</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>87.90000000000001</v>
+        <v>499.7</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>-2.57</v>
+        <v>-1.07</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
@@ -1193,7 +1071,7 @@
         </is>
       </c>
       <c r="J14" s="4" t="n">
-        <v>84.9543</v>
+        <v>469.0698</v>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
@@ -1201,17 +1079,17 @@
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>3.35</v>
+        <v>6.13</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-5.84</v>
+        <v>-7.13</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>98.12</v>
+        <v>559.17</v>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-DXCM-20260820-a0e45f</t>
+          <t>USA-R1-MSFT-20260810-6110fc</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr">
@@ -1228,7 +1106,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1247,13 +1125,13 @@
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>78.03</v>
+        <v>272.96</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>75.76000000000001</v>
+        <v>266.51</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>-2.91</v>
+        <v>-2.36</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
@@ -1261,7 +1139,7 @@
         </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v>72.40940000000001</v>
+        <v>247.1386</v>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
@@ -1269,17 +1147,17 @@
         </is>
       </c>
       <c r="L15" s="4" t="n">
-        <v>4.42</v>
+        <v>7.27</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-7.2</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>86.45999999999999</v>
+        <v>311.69</v>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-UBER-20260810-3f4c24</t>
+          <t>USA-R1-ADBE-20260810-4ad164</t>
         </is>
       </c>
       <c r="P15" s="4" t="inlineStr">
@@ -1296,7 +1174,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1311,17 +1189,17 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>193.17</v>
+        <v>90.22</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>186.42</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-3.49</v>
+        <v>-2.57</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
@@ -1329,7 +1207,7 @@
         </is>
       </c>
       <c r="J16" s="4" t="n">
-        <v>170.3286</v>
+        <v>84.9543</v>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
@@ -1337,17 +1215,17 @@
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>8.630000000000001</v>
+        <v>3.35</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-11.82</v>
+        <v>-5.84</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>227.43</v>
+        <v>98.12</v>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-IT-20260810-04dfbc</t>
+          <t>USA-R1-DXCM-20260820-a0e45f</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
@@ -1364,32 +1242,32 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>63.61</v>
+        <v>78.03</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>66.81999999999999</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>5.05</v>
+        <v>75.76000000000001</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-2.91</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
@@ -1397,7 +1275,7 @@
         </is>
       </c>
       <c r="J17" s="4" t="n">
-        <v>63.8043</v>
+        <v>72.40940000000001</v>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
@@ -1405,22 +1283,22 @@
         </is>
       </c>
       <c r="L17" s="4" t="n">
-        <v>4.51</v>
+        <v>4.42</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.31</v>
+        <v>-7.2</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>69.45</v>
+        <v>86.45999999999999</v>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-BMY-20260811-c99117</t>
+          <t>USA-R1-UBER-20260810-3f4c24</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -1432,17 +1310,17 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1451,13 +1329,13 @@
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>360.65</v>
+        <v>193.17</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>375.07</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>4</v>
+        <v>186.42</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>-3.49</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
@@ -1465,7 +1343,7 @@
         </is>
       </c>
       <c r="J18" s="4" t="n">
-        <v>362.4986</v>
+        <v>170.3286</v>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
@@ -1473,22 +1351,22 @@
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.35</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.51</v>
+        <v>-11.82</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>384</v>
+        <v>227.43</v>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-V-20260810-69160d</t>
+          <t>USA-R1-IT-20260810-04dfbc</t>
         </is>
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -1500,7 +1378,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1519,13 +1397,13 @@
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>89.53</v>
+        <v>63.61</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>-1.82</v>
+        <v>66.81999999999999</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>5.05</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
@@ -1533,7 +1411,7 @@
         </is>
       </c>
       <c r="J19" s="4" t="n">
-        <v>83.2157</v>
+        <v>63.8043</v>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
@@ -1541,17 +1419,17 @@
         </is>
       </c>
       <c r="L19" s="4" t="n">
-        <v>5.33</v>
+        <v>4.51</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-7.05</v>
+        <v>0.31</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>99.06</v>
+        <v>69.45</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-DXCM-20260811-b3de8c</t>
+          <t>USA-R2-BMY-20260811-c99117</t>
         </is>
       </c>
       <c r="P19" s="4" t="inlineStr">
@@ -1568,12 +1446,12 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1583,17 +1461,17 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>196.21</v>
+        <v>360.65</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>259.23</v>
+        <v>375.07</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>32.12</v>
+        <v>4</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
@@ -1601,7 +1479,7 @@
         </is>
       </c>
       <c r="J20" s="4" t="n">
-        <v>179.3029</v>
+        <v>362.4986</v>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
@@ -1609,22 +1487,22 @@
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>30.83</v>
+        <v>3.35</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-8.619999999999999</v>
+        <v>0.51</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>221.57</v>
+        <v>384</v>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-CRM-20260814-be7c1c</t>
+          <t>USA-R2-V-20260810-69160d</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>HOLD · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1636,12 +1514,12 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1651,17 +1529,17 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>103.51</v>
+        <v>89.53</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>122.11</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>17.97</v>
+        <v>87.90000000000001</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>-1.82</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
@@ -1669,7 +1547,7 @@
         </is>
       </c>
       <c r="J21" s="4" t="n">
-        <v>91.0157</v>
+        <v>83.2157</v>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
@@ -1677,22 +1555,22 @@
         </is>
       </c>
       <c r="L21" s="4" t="n">
-        <v>25.46</v>
+        <v>5.33</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-12.07</v>
+        <v>-7.05</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>122.25</v>
+        <v>99.06</v>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-HOOD-20260901-b8d64b</t>
+          <t>USA-R2-DXCM-20260811-b3de8c</t>
         </is>
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>HOLD · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1704,7 +1582,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1719,17 +1597,17 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>361.99</v>
+        <v>196.21</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>370.72</v>
+        <v>259.23</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>2.41</v>
+        <v>32.12</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
@@ -1737,7 +1615,7 @@
         </is>
       </c>
       <c r="J22" s="4" t="n">
-        <v>342.2271</v>
+        <v>179.3029</v>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
@@ -1745,17 +1623,17 @@
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>7.69</v>
+        <v>30.83</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-5.46</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>391.63</v>
+        <v>221.57</v>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-VLO-20260901-3c6acd</t>
+          <t>USA-R1-CRM-20260814-be7c1c</t>
         </is>
       </c>
       <c r="P22" s="4" t="inlineStr">
@@ -1772,7 +1650,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1791,13 +1669,13 @@
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>187.7</v>
+        <v>103.51</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>188.8</v>
+        <v>122.11</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.59</v>
+        <v>17.97</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
@@ -1805,7 +1683,7 @@
         </is>
       </c>
       <c r="J23" s="4" t="n">
-        <v>180.8543</v>
+        <v>91.0157</v>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
@@ -1813,17 +1691,17 @@
         </is>
       </c>
       <c r="L23" s="4" t="n">
-        <v>4.21</v>
+        <v>25.46</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-3.65</v>
+        <v>-12.07</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>197.97</v>
+        <v>122.25</v>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-EXPD-20260901-065905</t>
+          <t>USA-R1-HOOD-20260901-b8d64b</t>
         </is>
       </c>
       <c r="P23" s="4" t="inlineStr">
@@ -1840,7 +1718,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1855,17 +1733,17 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>126.68</v>
+        <v>361.99</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>126.75</v>
+        <v>370.72</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.06</v>
+        <v>2.41</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
@@ -1873,7 +1751,7 @@
         </is>
       </c>
       <c r="J24" s="4" t="n">
-        <v>119.43</v>
+        <v>342.2271</v>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
@@ -1881,17 +1759,17 @@
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>5.78</v>
+        <v>7.69</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-5.72</v>
+        <v>-5.46</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>137.55</v>
+        <v>391.63</v>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-SAIC-20260814-889ae8</t>
+          <t>USA-R1-VLO-20260901-3c6acd</t>
         </is>
       </c>
       <c r="P24" s="4" t="inlineStr">
@@ -1908,7 +1786,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1923,17 +1801,17 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>344.5</v>
+        <v>187.7</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>338.46</v>
-      </c>
-      <c r="H25" s="5" t="n">
-        <v>-1.75</v>
+        <v>188.8</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.59</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
@@ -1941,7 +1819,7 @@
         </is>
       </c>
       <c r="J25" s="4" t="n">
-        <v>323.138</v>
+        <v>180.8543</v>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
@@ -1949,17 +1827,17 @@
         </is>
       </c>
       <c r="L25" s="4" t="n">
-        <v>4.53</v>
+        <v>4.21</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-6.2</v>
+        <v>-3.65</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>376.54</v>
+        <v>197.97</v>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-GOOGL-20260819-1fce1a</t>
+          <t>USA-R1-EXPD-20260901-065905</t>
         </is>
       </c>
       <c r="P25" s="4" t="inlineStr">
@@ -1976,7 +1854,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>SAIC</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1991,17 +1869,17 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>60.09</v>
+        <v>126.68</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>58.42</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>-2.78</v>
+        <v>126.75</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>0.06</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
@@ -2009,7 +1887,7 @@
         </is>
       </c>
       <c r="J26" s="4" t="n">
-        <v>56.6217</v>
+        <v>119.43</v>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
@@ -2017,17 +1895,17 @@
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>3.08</v>
+        <v>5.78</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-5.78</v>
+        <v>-5.72</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>65.3</v>
+        <v>137.55</v>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-FOX-20260819-7b9e84</t>
+          <t>USA-R1-SAIC-20260814-889ae8</t>
         </is>
       </c>
       <c r="P26" s="4" t="inlineStr">
@@ -2044,143 +1922,289 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>344.5</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>338.46</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>323.138</v>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="M27" s="4" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="N27" s="4" t="n">
+        <v>376.54</v>
+      </c>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>USA-R1-GOOGL-20260819-1fce1a</t>
+        </is>
+      </c>
+      <c r="P27" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>FOX</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>60.09</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>58.42</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-2.78</v>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="n">
+        <v>56.6217</v>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="M28" s="4" t="n">
+        <v>-5.78</v>
+      </c>
+      <c r="N28" s="4" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>USA-R1-FOX-20260819-7b9e84</t>
+        </is>
+      </c>
+      <c r="P28" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
           <t>FTNT</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D29" s="4" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
+      <c r="E29" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="F29" s="4" t="n">
         <v>161.85</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="G29" s="4" t="n">
         <v>156.29</v>
       </c>
-      <c r="H27" s="5" t="n">
+      <c r="H29" s="5" t="n">
         <v>-3.44</v>
       </c>
-      <c r="I27" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J27" s="4" t="n">
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="n">
         <v>147.9529</v>
       </c>
-      <c r="K27" s="4" t="inlineStr">
+      <c r="K29" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L27" s="4" t="n">
+      <c r="L29" s="4" t="n">
         <v>5.33</v>
       </c>
-      <c r="M27" s="4" t="n">
+      <c r="M29" s="4" t="n">
         <v>-8.59</v>
       </c>
-      <c r="N27" s="4" t="n">
+      <c r="N29" s="4" t="n">
         <v>182.7</v>
       </c>
-      <c r="O27" s="4" t="inlineStr">
+      <c r="O29" s="4" t="inlineStr">
         <is>
           <t>USA-R1-FTNT-20260901-30d75e</t>
         </is>
       </c>
-      <c r="P27" s="4" t="inlineStr">
+      <c r="P29" s="4" t="inlineStr">
         <is>
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
+          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
+          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
           <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>The 🔎 line answers "why is NEW zero today?" from the lifecycle reconciler · every scored name gets exactly one verdict (reports/context/why_not_current_{market}.json). A zero here is never presented without its reason.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="16">
+    <mergeCell ref="A5:P5"/>
     <mergeCell ref="A32:P32"/>
     <mergeCell ref="A36:P36"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A37:P37"/>
-    <mergeCell ref="A31:P31"/>
+    <mergeCell ref="A40:P40"/>
+    <mergeCell ref="A6:P6"/>
+    <mergeCell ref="A39:P39"/>
     <mergeCell ref="A34:P34"/>
     <mergeCell ref="A35:P35"/>
     <mergeCell ref="A4:P4"/>
     <mergeCell ref="A3:P3"/>
-    <mergeCell ref="A30:P30"/>
+    <mergeCell ref="A38:P38"/>
     <mergeCell ref="A33:P33"/>
-    <mergeCell ref="A38:P38"/>
+    <mergeCell ref="A41:P41"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:P43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -508,14 +508,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>22 investable · NEW 0 · ACTIVE+ 11 · ACTIVE 11   ·   R2 6 · MOMENTUM 0 · R1 16 (advisory)</t>
+          <t>24 investable · NEW 2 · ACTIVE+ 11 · ACTIVE 11   ·   R2 8 · MOMENTUM 0 · R1 16 (advisory)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>🛡 DOWNSIDE · 22 position(s) with an INTACT stop · if all of them fired today the average outcome is -6.72% from entry, worst single -12.07%</t>
+          <t>🛡 DOWNSIDE · 24 position(s) with an INTACT stop · if all of them fired today the average outcome is -6.73% from entry, worst single -12.07%</t>
         </is>
       </c>
     </row>
@@ -529,7 +529,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 WHY NEW=0 · 516 scored · 18 already in CURRENT · biggest blocker: model disagreement (397) · lost to the 15-name ensemble truncation: 2 · lifecycle defects: 1</t>
+          <t>🔎 NEW=2 · 516 scored · 19 already in CURRENT · biggest blocker: model disagreement (397) · lost to the 15-name ensemble truncation: 2 · lifecycle defects: 1</t>
         </is>
       </c>
     </row>
@@ -630,7 +630,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -640,22 +640,22 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
-        <v>175.23</v>
+        <v>39.59</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>174.33</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>-0.51</v>
+        <v>39.59</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="J8" s="4" t="n">
-        <v>161.969</v>
+        <v>36.245</v>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
@@ -671,22 +671,22 @@
         </is>
       </c>
       <c r="L8" s="4" t="n">
-        <v>7.09</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-7.57</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>204.13</v>
+        <v>46.28</v>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-PLTR-20260810-f9e975</t>
+          <t>USA-R2-SMCI-20260908-c2c66b</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
-        <v>375.62</v>
+        <v>370.72</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>369.35</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>-1.67</v>
+        <v>370.72</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="J9" s="4" t="n">
-        <v>356.8957</v>
+        <v>350.9043</v>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
@@ -739,22 +739,22 @@
         </is>
       </c>
       <c r="L9" s="4" t="n">
-        <v>3.37</v>
+        <v>5.35</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-4.98</v>
+        <v>-5.35</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>402.23</v>
+        <v>400.44</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-TRV-20260810-9cd25d</t>
+          <t>USA-R2-VLO-20260908-e69cee</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -785,13 +785,13 @@
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>193.17</v>
+        <v>175.23</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>186.42</v>
+        <v>174.33</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-3.49</v>
+        <v>-0.51</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="J10" s="4" t="n">
-        <v>174.3364</v>
+        <v>161.969</v>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
@@ -807,17 +807,17 @@
         </is>
       </c>
       <c r="L10" s="4" t="n">
-        <v>6.48</v>
+        <v>7.09</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-9.75</v>
+        <v>-7.57</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>227.43</v>
+        <v>204.13</v>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-IT-20260810-b5fd37</t>
+          <t>USA-R2-PLTR-20260810-f9e975</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>63.83</v>
+        <v>375.62</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>66.81999999999999</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>4.68</v>
+        <v>369.35</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-1.67</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>60.0271</v>
+        <v>356.8957</v>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
@@ -875,22 +875,22 @@
         </is>
       </c>
       <c r="L11" s="4" t="n">
-        <v>10.17</v>
+        <v>3.37</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-5.96</v>
+        <v>-4.98</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>69.53</v>
+        <v>402.23</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-BMY-20260814-a3b600</t>
+          <t>USA-R2-TRV-20260810-9cd25d</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -902,12 +902,12 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -917,17 +917,17 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
-        <v>275.17</v>
+        <v>193.17</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>277.03</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>0.68</v>
+        <v>186.42</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>-3.49</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="J12" s="4" t="n">
-        <v>261.9314</v>
+        <v>174.3364</v>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
@@ -943,22 +943,22 @@
         </is>
       </c>
       <c r="L12" s="4" t="n">
-        <v>5.45</v>
+        <v>6.48</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-4.81</v>
+        <v>-9.75</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>295.03</v>
+        <v>227.43</v>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-GRMN-20260901-4c77f2</t>
+          <t>USA-R2-IT-20260810-b5fd37</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>STRONG BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F13" s="4" t="n">
-        <v>175.23</v>
+        <v>63.83</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>174.33</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>-0.51</v>
+        <v>66.81999999999999</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>4.68</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
@@ -1003,7 +1003,7 @@
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>155.965</v>
+        <v>60.0271</v>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
@@ -1011,17 +1011,17 @@
         </is>
       </c>
       <c r="L13" s="4" t="n">
-        <v>10.53</v>
+        <v>10.17</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-10.99</v>
+        <v>-5.96</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>204.13</v>
+        <v>69.53</v>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-PLTR-20260810-5c4552</t>
+          <t>USA-R1-BMY-20260814-a3b600</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
-        <v>505.11</v>
+        <v>275.17</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>499.7</v>
-      </c>
-      <c r="H14" s="5" t="n">
-        <v>-1.07</v>
+        <v>277.03</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>0.68</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="J14" s="4" t="n">
-        <v>469.0698</v>
+        <v>261.9314</v>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
@@ -1079,17 +1079,17 @@
         </is>
       </c>
       <c r="L14" s="4" t="n">
-        <v>6.13</v>
+        <v>5.45</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-7.13</v>
+        <v>-4.81</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>559.17</v>
+        <v>295.03</v>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-MSFT-20260810-6110fc</t>
+          <t>USA-R1-GRMN-20260901-4c77f2</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1125,13 +1125,13 @@
         </is>
       </c>
       <c r="F15" s="4" t="n">
-        <v>272.96</v>
+        <v>175.23</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>266.51</v>
+        <v>174.33</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>-2.36</v>
+        <v>-0.51</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v>247.1386</v>
+        <v>155.965</v>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
@@ -1147,17 +1147,17 @@
         </is>
       </c>
       <c r="L15" s="4" t="n">
-        <v>7.27</v>
+        <v>10.53</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-9.460000000000001</v>
+        <v>-10.99</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>311.69</v>
+        <v>204.13</v>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-ADBE-20260810-4ad164</t>
+          <t>USA-R1-PLTR-20260810-5c4552</t>
         </is>
       </c>
       <c r="P15" s="4" t="inlineStr">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>90.22</v>
+        <v>505.11</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>87.90000000000001</v>
+        <v>499.7</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-2.57</v>
+        <v>-1.07</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="J16" s="4" t="n">
-        <v>84.9543</v>
+        <v>469.0698</v>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
@@ -1215,17 +1215,17 @@
         </is>
       </c>
       <c r="L16" s="4" t="n">
-        <v>3.35</v>
+        <v>6.13</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-5.84</v>
+        <v>-7.13</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>98.12</v>
+        <v>559.17</v>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-DXCM-20260820-a0e45f</t>
+          <t>USA-R1-MSFT-20260810-6110fc</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>UBER</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1261,13 +1261,13 @@
         </is>
       </c>
       <c r="F17" s="4" t="n">
-        <v>78.03</v>
+        <v>272.96</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>75.76000000000001</v>
+        <v>266.51</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-2.91</v>
+        <v>-2.36</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="J17" s="4" t="n">
-        <v>72.40940000000001</v>
+        <v>247.1386</v>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
@@ -1283,17 +1283,17 @@
         </is>
       </c>
       <c r="L17" s="4" t="n">
-        <v>4.42</v>
+        <v>7.27</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-7.2</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>86.45999999999999</v>
+        <v>311.69</v>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-UBER-20260810-3f4c24</t>
+          <t>USA-R1-ADBE-20260810-4ad164</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
-        <v>193.17</v>
+        <v>90.22</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>186.42</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-3.49</v>
+        <v>-2.57</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="J18" s="4" t="n">
-        <v>170.3286</v>
+        <v>84.9543</v>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
@@ -1351,17 +1351,17 @@
         </is>
       </c>
       <c r="L18" s="4" t="n">
-        <v>8.630000000000001</v>
+        <v>3.35</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-11.82</v>
+        <v>-5.84</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>227.43</v>
+        <v>98.12</v>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-IT-20260810-04dfbc</t>
+          <t>USA-R1-DXCM-20260820-a0e45f</t>
         </is>
       </c>
       <c r="P18" s="4" t="inlineStr">
@@ -1378,32 +1378,32 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F19" s="4" t="n">
-        <v>63.61</v>
+        <v>78.03</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>66.81999999999999</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>5.05</v>
+        <v>75.76000000000001</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>-2.91</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="J19" s="4" t="n">
-        <v>63.8043</v>
+        <v>72.40940000000001</v>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
@@ -1419,22 +1419,22 @@
         </is>
       </c>
       <c r="L19" s="4" t="n">
-        <v>4.51</v>
+        <v>4.42</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.31</v>
+        <v>-7.2</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>69.45</v>
+        <v>86.45999999999999</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-BMY-20260811-c99117</t>
+          <t>USA-R1-UBER-20260810-3f4c24</t>
         </is>
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -1446,17 +1446,17 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1465,13 +1465,13 @@
         </is>
       </c>
       <c r="F20" s="4" t="n">
-        <v>360.65</v>
+        <v>193.17</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>375.07</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>4</v>
+        <v>186.42</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>-3.49</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
@@ -1479,7 +1479,7 @@
         </is>
       </c>
       <c r="J20" s="4" t="n">
-        <v>362.4986</v>
+        <v>170.3286</v>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
@@ -1487,22 +1487,22 @@
         </is>
       </c>
       <c r="L20" s="4" t="n">
-        <v>3.35</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.51</v>
+        <v>-11.82</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>384</v>
+        <v>227.43</v>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-V-20260810-69160d</t>
+          <t>USA-R1-IT-20260810-04dfbc</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="F21" s="4" t="n">
-        <v>89.53</v>
+        <v>63.61</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>87.90000000000001</v>
-      </c>
-      <c r="H21" s="5" t="n">
-        <v>-1.82</v>
+        <v>66.81999999999999</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>5.05</v>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="J21" s="4" t="n">
-        <v>83.2157</v>
+        <v>63.8043</v>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
@@ -1555,17 +1555,17 @@
         </is>
       </c>
       <c r="L21" s="4" t="n">
-        <v>5.33</v>
+        <v>4.51</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-7.05</v>
+        <v>0.31</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>99.06</v>
+        <v>69.45</v>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-DXCM-20260811-b3de8c</t>
+          <t>USA-R2-BMY-20260811-c99117</t>
         </is>
       </c>
       <c r="P21" s="4" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1597,17 +1597,17 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F22" s="4" t="n">
-        <v>196.21</v>
+        <v>360.65</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>259.23</v>
+        <v>375.07</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>32.12</v>
+        <v>4</v>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
@@ -1615,7 +1615,7 @@
         </is>
       </c>
       <c r="J22" s="4" t="n">
-        <v>179.3029</v>
+        <v>362.4986</v>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
@@ -1623,22 +1623,22 @@
         </is>
       </c>
       <c r="L22" s="4" t="n">
-        <v>30.83</v>
+        <v>3.35</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-8.619999999999999</v>
+        <v>0.51</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>221.57</v>
+        <v>384</v>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-CRM-20260814-be7c1c</t>
+          <t>USA-R2-V-20260810-69160d</t>
         </is>
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>HOLD · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="F23" s="4" t="n">
-        <v>103.51</v>
+        <v>89.53</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>122.11</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>17.97</v>
+        <v>87.90000000000001</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-1.82</v>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="J23" s="4" t="n">
-        <v>91.0157</v>
+        <v>83.2157</v>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
@@ -1691,22 +1691,22 @@
         </is>
       </c>
       <c r="L23" s="4" t="n">
-        <v>25.46</v>
+        <v>5.33</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-12.07</v>
+        <v>-7.05</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>122.25</v>
+        <v>99.06</v>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-HOOD-20260901-b8d64b</t>
+          <t>USA-R2-DXCM-20260811-b3de8c</t>
         </is>
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>HOLD · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -1733,17 +1733,17 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
-        <v>361.99</v>
+        <v>196.21</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>370.72</v>
+        <v>259.23</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>2.41</v>
+        <v>32.12</v>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         </is>
       </c>
       <c r="J24" s="4" t="n">
-        <v>342.2271</v>
+        <v>179.3029</v>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
@@ -1759,17 +1759,17 @@
         </is>
       </c>
       <c r="L24" s="4" t="n">
-        <v>7.69</v>
+        <v>30.83</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-5.46</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>391.63</v>
+        <v>221.57</v>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-VLO-20260901-3c6acd</t>
+          <t>USA-R1-CRM-20260814-be7c1c</t>
         </is>
       </c>
       <c r="P24" s="4" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -1805,13 +1805,13 @@
         </is>
       </c>
       <c r="F25" s="4" t="n">
-        <v>187.7</v>
+        <v>103.51</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>188.8</v>
+        <v>122.11</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.59</v>
+        <v>17.97</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
@@ -1819,7 +1819,7 @@
         </is>
       </c>
       <c r="J25" s="4" t="n">
-        <v>180.8543</v>
+        <v>91.0157</v>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
@@ -1827,17 +1827,17 @@
         </is>
       </c>
       <c r="L25" s="4" t="n">
-        <v>4.21</v>
+        <v>25.46</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-3.65</v>
+        <v>-12.07</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>197.97</v>
+        <v>122.25</v>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-EXPD-20260901-065905</t>
+          <t>USA-R1-HOOD-20260901-b8d64b</t>
         </is>
       </c>
       <c r="P25" s="4" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -1869,17 +1869,17 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F26" s="4" t="n">
-        <v>126.68</v>
+        <v>361.99</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>126.75</v>
+        <v>370.72</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.06</v>
+        <v>2.41</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="J26" s="4" t="n">
-        <v>119.43</v>
+        <v>342.2271</v>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
@@ -1895,17 +1895,17 @@
         </is>
       </c>
       <c r="L26" s="4" t="n">
-        <v>5.78</v>
+        <v>7.69</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-5.72</v>
+        <v>-5.46</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>137.55</v>
+        <v>391.63</v>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-SAIC-20260814-889ae8</t>
+          <t>USA-R1-VLO-20260901-3c6acd</t>
         </is>
       </c>
       <c r="P26" s="4" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F27" s="4" t="n">
-        <v>344.5</v>
+        <v>187.7</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>338.46</v>
-      </c>
-      <c r="H27" s="5" t="n">
-        <v>-1.75</v>
+        <v>188.8</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.59</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="J27" s="4" t="n">
-        <v>323.138</v>
+        <v>180.8543</v>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
@@ -1963,17 +1963,17 @@
         </is>
       </c>
       <c r="L27" s="4" t="n">
-        <v>4.53</v>
+        <v>4.21</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-6.2</v>
+        <v>-3.65</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>376.54</v>
+        <v>197.97</v>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-GOOGL-20260819-1fce1a</t>
+          <t>USA-R1-EXPD-20260901-065905</t>
         </is>
       </c>
       <c r="P27" s="4" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>SAIC</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2005,17 +2005,17 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="F28" s="4" t="n">
-        <v>60.09</v>
+        <v>126.68</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>58.42</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>-2.78</v>
+        <v>126.75</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>0.06</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="J28" s="4" t="n">
-        <v>56.6217</v>
+        <v>119.43</v>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
@@ -2031,17 +2031,17 @@
         </is>
       </c>
       <c r="L28" s="4" t="n">
-        <v>3.08</v>
+        <v>5.78</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-5.78</v>
+        <v>-5.72</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>65.3</v>
+        <v>137.55</v>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-FOX-20260819-7b9e84</t>
+          <t>USA-R1-SAIC-20260814-889ae8</t>
         </is>
       </c>
       <c r="P28" s="4" t="inlineStr">
@@ -2058,131 +2058,267 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>344.5</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>338.46</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>323.138</v>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="M29" s="4" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="N29" s="4" t="n">
+        <v>376.54</v>
+      </c>
+      <c r="O29" s="4" t="inlineStr">
+        <is>
+          <t>USA-R1-GOOGL-20260819-1fce1a</t>
+        </is>
+      </c>
+      <c r="P29" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>FOX</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>60.09</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>58.42</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>-2.78</v>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>56.6217</v>
+      </c>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>INTACT</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="M30" s="4" t="n">
+        <v>-5.78</v>
+      </c>
+      <c r="N30" s="4" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>USA-R1-FOX-20260819-7b9e84</t>
+        </is>
+      </c>
+      <c r="P30" s="4" t="inlineStr">
+        <is>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
           <t>FTNT</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="E31" s="4" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="F31" s="4" t="n">
         <v>161.85</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G31" s="4" t="n">
         <v>156.29</v>
       </c>
-      <c r="H29" s="5" t="n">
+      <c r="H31" s="5" t="n">
         <v>-3.44</v>
       </c>
-      <c r="I29" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J29" s="4" t="n">
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="n">
         <v>147.9529</v>
       </c>
-      <c r="K29" s="4" t="inlineStr">
+      <c r="K31" s="4" t="inlineStr">
         <is>
           <t>INTACT</t>
         </is>
       </c>
-      <c r="L29" s="4" t="n">
+      <c r="L31" s="4" t="n">
         <v>5.33</v>
       </c>
-      <c r="M29" s="4" t="n">
+      <c r="M31" s="4" t="n">
         <v>-8.59</v>
       </c>
-      <c r="N29" s="4" t="n">
+      <c r="N31" s="4" t="n">
         <v>182.7</v>
       </c>
-      <c r="O29" s="4" t="inlineStr">
+      <c r="O31" s="4" t="inlineStr">
         <is>
           <t>USA-R1-FTNT-20260901-30d75e</t>
         </is>
       </c>
-      <c r="P29" s="4" t="inlineStr">
+      <c r="P31" s="4" t="inlineStr">
         <is>
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
+          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>The 🔎 line answers "why is NEW zero today?" from the lifecycle reconciler · every scored name gets exactly one verdict (reports/context/why_not_current_{market}.json). A zero here is never presented without its reason.</t>
         </is>
@@ -2191,7 +2327,7 @@
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="A5:P5"/>
-    <mergeCell ref="A32:P32"/>
+    <mergeCell ref="A42:P42"/>
     <mergeCell ref="A36:P36"/>
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A37:P37"/>
@@ -2203,7 +2339,7 @@
     <mergeCell ref="A4:P4"/>
     <mergeCell ref="A3:P3"/>
     <mergeCell ref="A38:P38"/>
-    <mergeCell ref="A33:P33"/>
+    <mergeCell ref="A43:P43"/>
     <mergeCell ref="A41:P41"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P43"/>
+  <dimension ref="A1:AA49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -496,6 +496,17 @@
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="50" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="23" max="23"/>
+    <col width="34" customWidth="1" min="24" max="24"/>
+    <col width="60" customWidth="1" min="25" max="25"/>
+    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="27" max="27"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -536,7 +547,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>⛔ STALE INPUT · recommendations_v3 STALE (1 day(s) old) · ensemble STALE (1 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution</t>
+          <t>⛔ STALE INPUT · recommendations_v3 STALE (1 day(s) old) · ensemble STALE (1 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 = RESEARCH / SHADOW INTELLIGENCE · DOES NOT CHANGE R2 ACTION · 8 candidate(s) evaluated · every specialist is currently unvalidated, so every decision is ABSTAIN and every probability is withheld rather than guessed</t>
         </is>
       </c>
     </row>
@@ -621,6 +632,61 @@
           <t>Reason</t>
         </is>
       </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>R3 Decision</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>R3 Evidence</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>R3 Risk</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>R3 Fundamental</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>R3 Statistical</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>R3 Temporal</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>R3 Sector</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>R3 Uncertainty</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>R3 Reason</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>R3 As-of</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>R3 Model</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -689,6 +755,61 @@
           <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN</t>
+        </is>
+      </c>
+      <c r="R8" s="4" t="inlineStr">
+        <is>
+          <t>OBSERVATION</t>
+        </is>
+      </c>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>RESEARCH_ONLY</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_SUBSTRATE</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="inlineStr">
+        <is>
+          <t>NOT_AVAILABLE_AT_ASOF</t>
+        </is>
+      </c>
+      <c r="X8" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL · no validated specialist contributes</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+        </is>
+      </c>
+      <c r="Z8" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AA8" s="4" t="inlineStr">
+        <is>
+          <t>R3_FROZEN_2026-09-08</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -757,6 +878,61 @@
           <t>STRONG BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN</t>
+        </is>
+      </c>
+      <c r="R9" s="4" t="inlineStr">
+        <is>
+          <t>OBSERVATION</t>
+        </is>
+      </c>
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>RESEARCH_ONLY</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_SUBSTRATE</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="inlineStr">
+        <is>
+          <t>NOT_AVAILABLE_AT_ASOF</t>
+        </is>
+      </c>
+      <c r="X9" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL · no validated specialist contributes</t>
+        </is>
+      </c>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+        </is>
+      </c>
+      <c r="Z9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AA9" s="4" t="inlineStr">
+        <is>
+          <t>R3_FROZEN_2026-09-08</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -825,6 +1001,61 @@
           <t>STRONG BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN</t>
+        </is>
+      </c>
+      <c r="R10" s="4" t="inlineStr">
+        <is>
+          <t>OBSERVATION</t>
+        </is>
+      </c>
+      <c r="S10" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="U10" s="4" t="inlineStr">
+        <is>
+          <t>RESEARCH_ONLY</t>
+        </is>
+      </c>
+      <c r="V10" s="4" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_SUBSTRATE</t>
+        </is>
+      </c>
+      <c r="W10" s="4" t="inlineStr">
+        <is>
+          <t>NOT_AVAILABLE_AT_ASOF</t>
+        </is>
+      </c>
+      <c r="X10" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL · no validated specialist contributes</t>
+        </is>
+      </c>
+      <c r="Y10" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+        </is>
+      </c>
+      <c r="Z10" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AA10" s="4" t="inlineStr">
+        <is>
+          <t>R3_FROZEN_2026-09-08</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -893,6 +1124,61 @@
           <t>BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN</t>
+        </is>
+      </c>
+      <c r="R11" s="4" t="inlineStr">
+        <is>
+          <t>OBSERVATION</t>
+        </is>
+      </c>
+      <c r="S11" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="U11" s="4" t="inlineStr">
+        <is>
+          <t>RESEARCH_ONLY</t>
+        </is>
+      </c>
+      <c r="V11" s="4" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_SUBSTRATE</t>
+        </is>
+      </c>
+      <c r="W11" s="4" t="inlineStr">
+        <is>
+          <t>NOT_AVAILABLE_AT_ASOF</t>
+        </is>
+      </c>
+      <c r="X11" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL · no validated specialist contributes</t>
+        </is>
+      </c>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+        </is>
+      </c>
+      <c r="Z11" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AA11" s="4" t="inlineStr">
+        <is>
+          <t>R3_FROZEN_2026-09-08</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -961,6 +1247,61 @@
           <t>STRONG BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN</t>
+        </is>
+      </c>
+      <c r="R12" s="4" t="inlineStr">
+        <is>
+          <t>OBSERVATION</t>
+        </is>
+      </c>
+      <c r="S12" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="U12" s="4" t="inlineStr">
+        <is>
+          <t>RESEARCH_ONLY</t>
+        </is>
+      </c>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_SUBSTRATE</t>
+        </is>
+      </c>
+      <c r="W12" s="4" t="inlineStr">
+        <is>
+          <t>NOT_AVAILABLE_AT_ASOF</t>
+        </is>
+      </c>
+      <c r="X12" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL · no validated specialist contributes</t>
+        </is>
+      </c>
+      <c r="Y12" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+        </is>
+      </c>
+      <c r="Z12" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AA12" s="4" t="inlineStr">
+        <is>
+          <t>R3_FROZEN_2026-09-08</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1029,6 +1370,61 @@
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="R13" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="S13" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="U13" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="V13" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="W13" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="X13" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="Y13" s="4" t="inlineStr">
+        <is>
+          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
+        </is>
+      </c>
+      <c r="Z13" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA13" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1097,6 +1493,61 @@
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
+      <c r="Q14" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="R14" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="S14" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="U14" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="W14" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="X14" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="Y14" s="4" t="inlineStr">
+        <is>
+          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
+        </is>
+      </c>
+      <c r="Z14" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA14" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -1165,6 +1616,61 @@
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
+      <c r="Q15" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="R15" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="S15" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="U15" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="V15" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="W15" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="X15" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="Y15" s="4" t="inlineStr">
+        <is>
+          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
+        </is>
+      </c>
+      <c r="Z15" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA15" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1233,6 +1739,61 @@
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
+      <c r="Q16" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="R16" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="S16" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="U16" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="V16" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="W16" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="X16" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="Y16" s="4" t="inlineStr">
+        <is>
+          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
+        </is>
+      </c>
+      <c r="Z16" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA16" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1301,6 +1862,61 @@
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
+      <c r="Q17" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="R17" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="S17" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="U17" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="V17" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="W17" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="X17" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="Y17" s="4" t="inlineStr">
+        <is>
+          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
+        </is>
+      </c>
+      <c r="Z17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1369,6 +1985,61 @@
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
+      <c r="Q18" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="R18" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="S18" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="T18" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="U18" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="V18" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="W18" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="X18" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="Y18" s="4" t="inlineStr">
+        <is>
+          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
+        </is>
+      </c>
+      <c r="Z18" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA18" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1437,6 +2108,61 @@
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
+      <c r="Q19" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="R19" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="S19" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="T19" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="U19" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="V19" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="W19" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="X19" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="Y19" s="4" t="inlineStr">
+        <is>
+          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
+        </is>
+      </c>
+      <c r="Z19" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA19" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1505,6 +2231,61 @@
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
+      <c r="Q20" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="R20" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="S20" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="T20" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="U20" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="V20" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="W20" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="X20" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="Y20" s="4" t="inlineStr">
+        <is>
+          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
+        </is>
+      </c>
+      <c r="Z20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -1573,6 +2354,61 @@
           <t>HOLD · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
+      <c r="Q21" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN</t>
+        </is>
+      </c>
+      <c r="R21" s="4" t="inlineStr">
+        <is>
+          <t>OBSERVATION</t>
+        </is>
+      </c>
+      <c r="S21" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="T21" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="U21" s="4" t="inlineStr">
+        <is>
+          <t>RESEARCH_ONLY</t>
+        </is>
+      </c>
+      <c r="V21" s="4" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_SUBSTRATE</t>
+        </is>
+      </c>
+      <c r="W21" s="4" t="inlineStr">
+        <is>
+          <t>NOT_AVAILABLE_AT_ASOF</t>
+        </is>
+      </c>
+      <c r="X21" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL · no validated specialist contributes</t>
+        </is>
+      </c>
+      <c r="Y21" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+        </is>
+      </c>
+      <c r="Z21" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AA21" s="4" t="inlineStr">
+        <is>
+          <t>R3_FROZEN_2026-09-08</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -1641,6 +2477,61 @@
           <t>HOLD · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
+      <c r="Q22" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN</t>
+        </is>
+      </c>
+      <c r="R22" s="4" t="inlineStr">
+        <is>
+          <t>OBSERVATION</t>
+        </is>
+      </c>
+      <c r="S22" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="T22" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="U22" s="4" t="inlineStr">
+        <is>
+          <t>RESEARCH_ONLY</t>
+        </is>
+      </c>
+      <c r="V22" s="4" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_SUBSTRATE</t>
+        </is>
+      </c>
+      <c r="W22" s="4" t="inlineStr">
+        <is>
+          <t>NOT_AVAILABLE_AT_ASOF</t>
+        </is>
+      </c>
+      <c r="X22" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL · no validated specialist contributes</t>
+        </is>
+      </c>
+      <c r="Y22" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+        </is>
+      </c>
+      <c r="Z22" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AA22" s="4" t="inlineStr">
+        <is>
+          <t>R3_FROZEN_2026-09-08</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -1709,6 +2600,61 @@
           <t>HOLD · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
+      <c r="Q23" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN</t>
+        </is>
+      </c>
+      <c r="R23" s="4" t="inlineStr">
+        <is>
+          <t>OBSERVATION</t>
+        </is>
+      </c>
+      <c r="S23" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="T23" s="4" t="inlineStr">
+        <is>
+          <t>NOT_VALIDATED</t>
+        </is>
+      </c>
+      <c r="U23" s="4" t="inlineStr">
+        <is>
+          <t>RESEARCH_ONLY</t>
+        </is>
+      </c>
+      <c r="V23" s="4" t="inlineStr">
+        <is>
+          <t>INSUFFICIENT_SUBSTRATE</t>
+        </is>
+      </c>
+      <c r="W23" s="4" t="inlineStr">
+        <is>
+          <t>NOT_AVAILABLE_AT_ASOF</t>
+        </is>
+      </c>
+      <c r="X23" s="4" t="inlineStr">
+        <is>
+          <t>TOTAL · no validated specialist contributes</t>
+        </is>
+      </c>
+      <c r="Y23" s="4" t="inlineStr">
+        <is>
+          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+        </is>
+      </c>
+      <c r="Z23" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AA23" s="4" t="inlineStr">
+        <is>
+          <t>R3_FROZEN_2026-09-08</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -1777,6 +2723,61 @@
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
+      <c r="Q24" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="R24" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="S24" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="T24" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="U24" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="V24" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="W24" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="X24" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="Y24" s="4" t="inlineStr">
+        <is>
+          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
+        </is>
+      </c>
+      <c r="Z24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -1845,6 +2846,61 @@
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
+      <c r="Q25" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="R25" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="S25" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="T25" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="U25" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="V25" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="W25" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="X25" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="Y25" s="4" t="inlineStr">
+        <is>
+          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
+        </is>
+      </c>
+      <c r="Z25" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA25" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -1913,6 +2969,61 @@
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
+      <c r="Q26" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="R26" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="S26" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="T26" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="U26" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="V26" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="W26" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="X26" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="Y26" s="4" t="inlineStr">
+        <is>
+          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
+        </is>
+      </c>
+      <c r="Z26" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA26" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -1981,6 +3092,61 @@
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
+      <c r="Q27" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="R27" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="S27" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="T27" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="U27" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="V27" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="W27" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="X27" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="Y27" s="4" t="inlineStr">
+        <is>
+          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
+        </is>
+      </c>
+      <c r="Z27" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA27" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -2049,6 +3215,61 @@
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
+      <c r="Q28" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="R28" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="S28" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="T28" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="U28" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="V28" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="W28" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="X28" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="Y28" s="4" t="inlineStr">
+        <is>
+          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
+        </is>
+      </c>
+      <c r="Z28" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA28" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -2117,6 +3338,61 @@
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
+      <c r="Q29" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="R29" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="S29" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="T29" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="U29" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="V29" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="W29" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="X29" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="Y29" s="4" t="inlineStr">
+        <is>
+          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
+        </is>
+      </c>
+      <c r="Z29" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA29" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -2185,6 +3461,61 @@
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
+      <c r="Q30" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="R30" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="S30" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="T30" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="U30" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="V30" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="W30" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="X30" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="Y30" s="4" t="inlineStr">
+        <is>
+          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
+        </is>
+      </c>
+      <c r="Z30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA30" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -2253,95 +3584,198 @@
           <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
+      <c r="Q31" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="R31" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="S31" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="T31" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="U31" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="V31" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="W31" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="X31" s="4" t="inlineStr">
+        <is>
+          <t>NOT_APPLICABLE</t>
+        </is>
+      </c>
+      <c r="Y31" s="4" t="inlineStr">
+        <is>
+          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
+        </is>
+      </c>
+      <c r="Z31" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AA31" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
+          <t>R3 columns are RESEARCH / SHADOW INTELLIGENCE. They describe an R2 candidate and never change one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
+          <t>R3 Decision · TAKE / AVOID / ABSTAIN. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate. ABSTAIN is R3 stating that it does not know · it is not a neutral default and not a placeholder.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
+          <t>R3 probabilities are deliberately absent rather than zero. An unvalidated model reporting 0.5 is indistinguishable, months later, from a validated one reporting 0.5.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+          <t>R3 specialist states · NOT_VALIDATED (branch resolved, no usable model) · INSUFFICIENT_SUBSTRATE (data cannot support the claim) · NOT_AVAILABLE_AT_ASOF (input did not exist on this date) · BLOCKED (no substrate at all) · DESCRIPTIVE_ONLY (real information, not predictive).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+          <t>NOT_APPLICABLE on an R1 row is correct · R3 evaluates R2 candidates only, and R1 is retired advisory.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+          <t>R3 can only ever become actionable through explicit authorisation after out-of-sample and incremental-value evidence. It cannot promote itself.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
+          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
           <t>The 🔎 line answers "why is NEW zero today?" from the lifecycle reconciler · every scored name gets exactly one verdict (reports/context/why_not_current_{market}.json). A zero here is never presented without its reason.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="A5:P5"/>
-    <mergeCell ref="A42:P42"/>
-    <mergeCell ref="A36:P36"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A37:P37"/>
-    <mergeCell ref="A40:P40"/>
-    <mergeCell ref="A6:P6"/>
-    <mergeCell ref="A39:P39"/>
-    <mergeCell ref="A34:P34"/>
-    <mergeCell ref="A35:P35"/>
-    <mergeCell ref="A4:P4"/>
-    <mergeCell ref="A3:P3"/>
-    <mergeCell ref="A38:P38"/>
-    <mergeCell ref="A43:P43"/>
-    <mergeCell ref="A41:P41"/>
-    <mergeCell ref="A2:P2"/>
+  <mergeCells count="22">
+    <mergeCell ref="A6:AA6"/>
+    <mergeCell ref="A41:AA41"/>
+    <mergeCell ref="A46:AA46"/>
+    <mergeCell ref="A37:AA37"/>
+    <mergeCell ref="A3:AA3"/>
+    <mergeCell ref="A2:AA2"/>
+    <mergeCell ref="A42:AA42"/>
+    <mergeCell ref="A47:AA47"/>
+    <mergeCell ref="A5:AA5"/>
+    <mergeCell ref="A35:AA35"/>
+    <mergeCell ref="A4:AA4"/>
+    <mergeCell ref="A43:AA43"/>
+    <mergeCell ref="A38:AA38"/>
+    <mergeCell ref="A44:AA44"/>
+    <mergeCell ref="A34:AA34"/>
+    <mergeCell ref="A40:AA40"/>
+    <mergeCell ref="A48:AA48"/>
+    <mergeCell ref="A39:AA39"/>
+    <mergeCell ref="A45:AA45"/>
+    <mergeCell ref="A36:AA36"/>
+    <mergeCell ref="A49:AA49"/>
+    <mergeCell ref="A1:AA1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -533,21 +533,21 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>🔴 1 position(s) left CURRENT on a STOP BREACH (R1 1 · R2 0) and are recorded in EXIT HISTORY with their loss intact · 0 newly breached today</t>
+          <t>⚠ lifecycle dataset is dated 2026-09-08, not this report's as-of · rerun the pipeline</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=2 · 516 scored · 19 already in CURRENT · biggest blocker: model disagreement (397) · lost to the 15-name ensemble truncation: 2 · lifecycle defects: 1</t>
+          <t>🔎 NEW=2 · 30 scored · 19 already in CURRENT · biggest blocker: model disagreement (25) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>⛔ STALE INPUT · recommendations_v3 STALE (1 day(s) old) · ensemble STALE (1 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 = RESEARCH / SHADOW INTELLIGENCE · DOES NOT CHANGE R2 ACTION · 8 candidate(s) evaluated · every specialist is currently unvalidated, so every decision is ABSTAIN and every probability is withheld rather than guessed</t>
+          <t>⛔ STALE INPUT · recommendations_v3 STALE (1 day(s) old) · ensemble STALE (1 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 = RESEARCH / SHADOW INTELLIGENCE · DOES NOT CHANGE R2 ACTION · 0 candidate(s) evaluated · every specialist is currently unvalidated, so every decision is ABSTAIN and every probability is withheld rather than guessed</t>
         </is>
       </c>
     </row>
@@ -757,57 +757,57 @@
       </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
-          <t>OBSERVATION</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="T8" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="U8" s="4" t="inlineStr">
         <is>
-          <t>RESEARCH_ONLY</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="V8" s="4" t="inlineStr">
         <is>
-          <t>INSUFFICIENT_SUBSTRATE</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>NOT_AVAILABLE_AT_ASOF</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="X8" s="4" t="inlineStr">
         <is>
-          <t>TOTAL · no validated specialist contributes</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="Y8" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+          <t>no R3 snapshot for this ticker on this date</t>
         </is>
       </c>
       <c r="Z8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AA8" s="4" t="inlineStr">
         <is>
-          <t>R3_FROZEN_2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -880,57 +880,57 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
-          <t>OBSERVATION</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="T9" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="U9" s="4" t="inlineStr">
         <is>
-          <t>RESEARCH_ONLY</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="V9" s="4" t="inlineStr">
         <is>
-          <t>INSUFFICIENT_SUBSTRATE</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="W9" s="4" t="inlineStr">
         <is>
-          <t>NOT_AVAILABLE_AT_ASOF</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="X9" s="4" t="inlineStr">
         <is>
-          <t>TOTAL · no validated specialist contributes</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="Y9" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+          <t>no R3 snapshot for this ticker on this date</t>
         </is>
       </c>
       <c r="Z9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AA9" s="4" t="inlineStr">
         <is>
-          <t>R3_FROZEN_2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1003,57 +1003,57 @@
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
-          <t>OBSERVATION</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="T10" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="U10" s="4" t="inlineStr">
         <is>
-          <t>RESEARCH_ONLY</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>INSUFFICIENT_SUBSTRATE</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>NOT_AVAILABLE_AT_ASOF</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="X10" s="4" t="inlineStr">
         <is>
-          <t>TOTAL · no validated specialist contributes</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="Y10" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+          <t>no R3 snapshot for this ticker on this date</t>
         </is>
       </c>
       <c r="Z10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AA10" s="4" t="inlineStr">
         <is>
-          <t>R3_FROZEN_2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1126,57 +1126,57 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
-          <t>OBSERVATION</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="T11" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="U11" s="4" t="inlineStr">
         <is>
-          <t>RESEARCH_ONLY</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="V11" s="4" t="inlineStr">
         <is>
-          <t>INSUFFICIENT_SUBSTRATE</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>NOT_AVAILABLE_AT_ASOF</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="X11" s="4" t="inlineStr">
         <is>
-          <t>TOTAL · no validated specialist contributes</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="Y11" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+          <t>no R3 snapshot for this ticker on this date</t>
         </is>
       </c>
       <c r="Z11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AA11" s="4" t="inlineStr">
         <is>
-          <t>R3_FROZEN_2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -1249,57 +1249,57 @@
       </c>
       <c r="Q12" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
-          <t>OBSERVATION</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="T12" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="U12" s="4" t="inlineStr">
         <is>
-          <t>RESEARCH_ONLY</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="V12" s="4" t="inlineStr">
         <is>
-          <t>INSUFFICIENT_SUBSTRATE</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>NOT_AVAILABLE_AT_ASOF</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="X12" s="4" t="inlineStr">
         <is>
-          <t>TOTAL · no validated specialist contributes</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="Y12" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+          <t>no R3 snapshot for this ticker on this date</t>
         </is>
       </c>
       <c r="Z12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AA12" s="4" t="inlineStr">
         <is>
-          <t>R3_FROZEN_2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2356,57 +2356,57 @@
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>OBSERVATION</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="S21" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="T21" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="U21" s="4" t="inlineStr">
         <is>
-          <t>RESEARCH_ONLY</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="V21" s="4" t="inlineStr">
         <is>
-          <t>INSUFFICIENT_SUBSTRATE</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="W21" s="4" t="inlineStr">
         <is>
-          <t>NOT_AVAILABLE_AT_ASOF</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="X21" s="4" t="inlineStr">
         <is>
-          <t>TOTAL · no validated specialist contributes</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="Y21" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+          <t>no R3 snapshot for this ticker on this date</t>
         </is>
       </c>
       <c r="Z21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AA21" s="4" t="inlineStr">
         <is>
-          <t>R3_FROZEN_2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2479,57 +2479,57 @@
       </c>
       <c r="Q22" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>OBSERVATION</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="T22" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="U22" s="4" t="inlineStr">
         <is>
-          <t>RESEARCH_ONLY</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>INSUFFICIENT_SUBSTRATE</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>NOT_AVAILABLE_AT_ASOF</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="X22" s="4" t="inlineStr">
         <is>
-          <t>TOTAL · no validated specialist contributes</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="Y22" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+          <t>no R3 snapshot for this ticker on this date</t>
         </is>
       </c>
       <c r="Z22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AA22" s="4" t="inlineStr">
         <is>
-          <t>R3_FROZEN_2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -2602,57 +2602,57 @@
       </c>
       <c r="Q23" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
-          <t>OBSERVATION</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="T23" s="4" t="inlineStr">
         <is>
-          <t>NOT_VALIDATED</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="U23" s="4" t="inlineStr">
         <is>
-          <t>RESEARCH_ONLY</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="V23" s="4" t="inlineStr">
         <is>
-          <t>INSUFFICIENT_SUBSTRATE</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>NOT_AVAILABLE_AT_ASOF</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="X23" s="4" t="inlineStr">
         <is>
-          <t>TOTAL · no validated specialist contributes</t>
+          <t>NOT_EVALUATED</t>
         </is>
       </c>
       <c r="Y23" s="4" t="inlineStr">
         <is>
-          <t>ABSTAIN because every specialist is at a non-validated disposition. This is R3 stating that it does not know, which is the honest output of an unvalidated decision layer - not a pl</t>
+          <t>no R3 snapshot for this ticker on this date</t>
         </is>
       </c>
       <c r="Z23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="AA23" s="4" t="inlineStr">
         <is>
-          <t>R3_FROZEN_2026-09-08</t>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA49"/>
+  <dimension ref="A1:Q48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -496,17 +496,7 @@
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="50" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-    <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
-    <col width="22" customWidth="1" min="20" max="20"/>
-    <col width="22" customWidth="1" min="21" max="21"/>
-    <col width="22" customWidth="1" min="22" max="22"/>
-    <col width="22" customWidth="1" min="23" max="23"/>
-    <col width="34" customWidth="1" min="24" max="24"/>
-    <col width="60" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
-    <col width="22" customWidth="1" min="27" max="27"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -547,7 +537,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>⛔ STALE INPUT · recommendations_v3 STALE (1 day(s) old) · ensemble STALE (1 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 = RESEARCH / SHADOW INTELLIGENCE · DOES NOT CHANGE R2 ACTION · 0 candidate(s) evaluated · every specialist is currently unvalidated, so every decision is ABSTAIN and every probability is withheld rather than guessed</t>
+          <t>⛔ STALE INPUT · recommendations_v3 STALE (1 day(s) old) · ensemble STALE (1 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW INTELLIGENCE — RESEARCH ONLY. R3 reviews R2 candidates but does NOT change R2 Action, Confidence, Stop or Position. ABSTAIN means R3 has no validated opinion yet — it is NOT Hold, Buy, Avoid, or a 50/50 probability. A future AVOID is a research annotation and never implies an R2 EXIT. R3 can become actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) evaluated today.</t>
         </is>
       </c>
     </row>
@@ -634,57 +624,7 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>R3 Decision</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr">
-        <is>
-          <t>R3 Evidence</t>
-        </is>
-      </c>
-      <c r="S7" s="3" t="inlineStr">
-        <is>
-          <t>R3 Risk</t>
-        </is>
-      </c>
-      <c r="T7" s="3" t="inlineStr">
-        <is>
-          <t>R3 Fundamental</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>R3 Statistical</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="inlineStr">
-        <is>
-          <t>R3 Temporal</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="inlineStr">
-        <is>
-          <t>R3 Sector</t>
-        </is>
-      </c>
-      <c r="X7" s="3" t="inlineStr">
-        <is>
-          <t>R3 Uncertainty</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>R3 Reason</t>
-        </is>
-      </c>
-      <c r="Z7" s="3" t="inlineStr">
-        <is>
-          <t>R3 As-of</t>
-        </is>
-      </c>
-      <c r="AA7" s="3" t="inlineStr">
-        <is>
-          <t>R3 Model</t>
+          <t>R3 SHADOW</t>
         </is>
       </c>
     </row>
@@ -757,57 +697,7 @@
       </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="R8" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="S8" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="T8" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="U8" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="V8" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="W8" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="X8" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="Y8" s="4" t="inlineStr">
-        <is>
-          <t>no R3 snapshot for this ticker on this date</t>
-        </is>
-      </c>
-      <c r="Z8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA8" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>NOT_EVALUATED · no R3 snapshot for this date</t>
         </is>
       </c>
     </row>
@@ -880,57 +770,7 @@
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="R9" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="S9" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="T9" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="U9" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="V9" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="W9" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="X9" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="Y9" s="4" t="inlineStr">
-        <is>
-          <t>no R3 snapshot for this ticker on this date</t>
-        </is>
-      </c>
-      <c r="Z9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA9" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>NOT_EVALUATED · no R3 snapshot for this date</t>
         </is>
       </c>
     </row>
@@ -1003,57 +843,7 @@
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="R10" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="S10" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="T10" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="U10" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="V10" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="W10" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="X10" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="Y10" s="4" t="inlineStr">
-        <is>
-          <t>no R3 snapshot for this ticker on this date</t>
-        </is>
-      </c>
-      <c r="Z10" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA10" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>NOT_EVALUATED · no R3 snapshot for this date</t>
         </is>
       </c>
     </row>
@@ -1126,57 +916,7 @@
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="R11" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="S11" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="T11" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="U11" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="V11" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="W11" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="X11" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="Y11" s="4" t="inlineStr">
-        <is>
-          <t>no R3 snapshot for this ticker on this date</t>
-        </is>
-      </c>
-      <c r="Z11" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA11" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>NOT_EVALUATED · no R3 snapshot for this date</t>
         </is>
       </c>
     </row>
@@ -1249,57 +989,7 @@
       </c>
       <c r="Q12" s="4" t="inlineStr">
         <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="R12" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="S12" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="T12" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="U12" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="V12" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="W12" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="X12" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="Y12" s="4" t="inlineStr">
-        <is>
-          <t>no R3 snapshot for this ticker on this date</t>
-        </is>
-      </c>
-      <c r="Z12" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA12" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>NOT_EVALUATED · no R3 snapshot for this date</t>
         </is>
       </c>
     </row>
@@ -1372,57 +1062,7 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="R13" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="S13" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="T13" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="U13" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="V13" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="W13" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="X13" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="Y13" s="4" t="inlineStr">
-        <is>
-          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
-        </is>
-      </c>
-      <c r="Z13" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA13" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>N/A · R3 evaluates R2 candidates only</t>
         </is>
       </c>
     </row>
@@ -1495,57 +1135,7 @@
       </c>
       <c r="Q14" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="R14" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="S14" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="T14" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="U14" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="V14" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="W14" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="X14" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="Y14" s="4" t="inlineStr">
-        <is>
-          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
-        </is>
-      </c>
-      <c r="Z14" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA14" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>N/A · R3 evaluates R2 candidates only</t>
         </is>
       </c>
     </row>
@@ -1618,57 +1208,7 @@
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="R15" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="S15" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="T15" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="U15" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="V15" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="W15" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="X15" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="Y15" s="4" t="inlineStr">
-        <is>
-          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
-        </is>
-      </c>
-      <c r="Z15" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA15" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>N/A · R3 evaluates R2 candidates only</t>
         </is>
       </c>
     </row>
@@ -1741,57 +1281,7 @@
       </c>
       <c r="Q16" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="R16" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="S16" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="T16" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="U16" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="V16" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="W16" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="X16" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="Y16" s="4" t="inlineStr">
-        <is>
-          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
-        </is>
-      </c>
-      <c r="Z16" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA16" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>N/A · R3 evaluates R2 candidates only</t>
         </is>
       </c>
     </row>
@@ -1864,57 +1354,7 @@
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="R17" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="S17" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="T17" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="U17" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="V17" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="W17" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="X17" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="Y17" s="4" t="inlineStr">
-        <is>
-          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
-        </is>
-      </c>
-      <c r="Z17" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA17" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>N/A · R3 evaluates R2 candidates only</t>
         </is>
       </c>
     </row>
@@ -1987,57 +1427,7 @@
       </c>
       <c r="Q18" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="R18" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="S18" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="T18" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="U18" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="V18" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="W18" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="X18" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="Y18" s="4" t="inlineStr">
-        <is>
-          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
-        </is>
-      </c>
-      <c r="Z18" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA18" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>N/A · R3 evaluates R2 candidates only</t>
         </is>
       </c>
     </row>
@@ -2110,57 +1500,7 @@
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="R19" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="S19" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="T19" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="U19" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="V19" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="W19" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="X19" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="Y19" s="4" t="inlineStr">
-        <is>
-          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
-        </is>
-      </c>
-      <c r="Z19" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA19" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>N/A · R3 evaluates R2 candidates only</t>
         </is>
       </c>
     </row>
@@ -2233,57 +1573,7 @@
       </c>
       <c r="Q20" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="R20" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="S20" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="T20" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="U20" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="V20" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="W20" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="X20" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="Y20" s="4" t="inlineStr">
-        <is>
-          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
-        </is>
-      </c>
-      <c r="Z20" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA20" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>N/A · R3 evaluates R2 candidates only</t>
         </is>
       </c>
     </row>
@@ -2356,57 +1646,7 @@
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="R21" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="S21" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="T21" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="U21" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="V21" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="W21" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="X21" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="Y21" s="4" t="inlineStr">
-        <is>
-          <t>no R3 snapshot for this ticker on this date</t>
-        </is>
-      </c>
-      <c r="Z21" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA21" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>NOT_EVALUATED · no R3 snapshot for this date</t>
         </is>
       </c>
     </row>
@@ -2479,57 +1719,7 @@
       </c>
       <c r="Q22" s="4" t="inlineStr">
         <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="R22" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="S22" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="T22" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="U22" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="V22" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="W22" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="X22" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="Y22" s="4" t="inlineStr">
-        <is>
-          <t>no R3 snapshot for this ticker on this date</t>
-        </is>
-      </c>
-      <c r="Z22" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA22" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>NOT_EVALUATED · no R3 snapshot for this date</t>
         </is>
       </c>
     </row>
@@ -2602,57 +1792,7 @@
       </c>
       <c r="Q23" s="4" t="inlineStr">
         <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="R23" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="S23" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="T23" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="U23" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="V23" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="W23" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="X23" s="4" t="inlineStr">
-        <is>
-          <t>NOT_EVALUATED</t>
-        </is>
-      </c>
-      <c r="Y23" s="4" t="inlineStr">
-        <is>
-          <t>no R3 snapshot for this ticker on this date</t>
-        </is>
-      </c>
-      <c r="Z23" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA23" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>NOT_EVALUATED · no R3 snapshot for this date</t>
         </is>
       </c>
     </row>
@@ -2725,57 +1865,7 @@
       </c>
       <c r="Q24" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="R24" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="S24" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="T24" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="U24" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="V24" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="W24" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="X24" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="Y24" s="4" t="inlineStr">
-        <is>
-          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
-        </is>
-      </c>
-      <c r="Z24" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA24" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>N/A · R3 evaluates R2 candidates only</t>
         </is>
       </c>
     </row>
@@ -2848,57 +1938,7 @@
       </c>
       <c r="Q25" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="R25" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="S25" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="T25" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="U25" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="V25" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="W25" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="X25" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="Y25" s="4" t="inlineStr">
-        <is>
-          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
-        </is>
-      </c>
-      <c r="Z25" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA25" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>N/A · R3 evaluates R2 candidates only</t>
         </is>
       </c>
     </row>
@@ -2971,57 +2011,7 @@
       </c>
       <c r="Q26" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="R26" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="S26" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="T26" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="U26" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="V26" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="W26" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="X26" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="Y26" s="4" t="inlineStr">
-        <is>
-          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
-        </is>
-      </c>
-      <c r="Z26" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA26" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>N/A · R3 evaluates R2 candidates only</t>
         </is>
       </c>
     </row>
@@ -3094,57 +2084,7 @@
       </c>
       <c r="Q27" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="R27" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="S27" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="T27" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="U27" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="V27" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="W27" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="X27" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="Y27" s="4" t="inlineStr">
-        <is>
-          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
-        </is>
-      </c>
-      <c r="Z27" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA27" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>N/A · R3 evaluates R2 candidates only</t>
         </is>
       </c>
     </row>
@@ -3217,57 +2157,7 @@
       </c>
       <c r="Q28" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="R28" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="S28" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="T28" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="U28" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="V28" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="W28" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="X28" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="Y28" s="4" t="inlineStr">
-        <is>
-          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
-        </is>
-      </c>
-      <c r="Z28" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA28" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>N/A · R3 evaluates R2 candidates only</t>
         </is>
       </c>
     </row>
@@ -3340,57 +2230,7 @@
       </c>
       <c r="Q29" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="R29" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="S29" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="T29" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="U29" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="V29" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="W29" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="X29" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="Y29" s="4" t="inlineStr">
-        <is>
-          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
-        </is>
-      </c>
-      <c r="Z29" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA29" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>N/A · R3 evaluates R2 candidates only</t>
         </is>
       </c>
     </row>
@@ -3463,57 +2303,7 @@
       </c>
       <c r="Q30" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="R30" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="S30" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="T30" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="U30" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="V30" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="W30" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="X30" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="Y30" s="4" t="inlineStr">
-        <is>
-          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
-        </is>
-      </c>
-      <c r="Z30" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA30" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>N/A · R3 evaluates R2 candidates only</t>
         </is>
       </c>
     </row>
@@ -3586,196 +2376,138 @@
       </c>
       <c r="Q31" s="4" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="R31" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="S31" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="T31" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="U31" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="V31" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="W31" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="X31" s="4" t="inlineStr">
-        <is>
-          <t>NOT_APPLICABLE</t>
-        </is>
-      </c>
-      <c r="Y31" s="4" t="inlineStr">
-        <is>
-          <t>R3 evaluates R2 candidates · this row is R1 advisory</t>
-        </is>
-      </c>
-      <c r="Z31" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="AA31" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>N/A · R3 evaluates R2 candidates only</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>R3 columns are RESEARCH / SHADOW INTELLIGENCE. They describe an R2 candidate and never change one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
+          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>R3 Decision · TAKE / AVOID / ABSTAIN. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate. ABSTAIN is R3 stating that it does not know · it is not a neutral default and not a placeholder.</t>
+          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>R3 probabilities are deliberately absent rather than zero. An unvalidated model reporting 0.5 is indistinguishable, months later, from a validated one reporting 0.5.</t>
+          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>R3 specialist states · NOT_VALIDATED (branch resolved, no usable model) · INSUFFICIENT_SUBSTRATE (data cannot support the claim) · NOT_AVAILABLE_AT_ASOF (input did not exist on this date) · BLOCKED (no substrate at all) · DESCRIPTIVE_ONLY (real information, not predictive).</t>
+          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>NOT_APPLICABLE on an R1 row is correct · R3 evaluates R2 candidates only, and R1 is retired advisory.</t>
+          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>R3 can only ever become actionable through explicit authorisation after out-of-sample and incremental-value evidence. It cannot promote itself.</t>
+          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
+          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
+          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
+          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
           <t>The 🔎 line answers "why is NEW zero today?" from the lifecycle reconciler · every scored name gets exactly one verdict (reports/context/why_not_current_{market}.json). A zero here is never presented without its reason.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="A6:AA6"/>
-    <mergeCell ref="A41:AA41"/>
-    <mergeCell ref="A46:AA46"/>
-    <mergeCell ref="A37:AA37"/>
-    <mergeCell ref="A3:AA3"/>
-    <mergeCell ref="A2:AA2"/>
-    <mergeCell ref="A42:AA42"/>
-    <mergeCell ref="A47:AA47"/>
-    <mergeCell ref="A5:AA5"/>
-    <mergeCell ref="A35:AA35"/>
-    <mergeCell ref="A4:AA4"/>
-    <mergeCell ref="A43:AA43"/>
-    <mergeCell ref="A38:AA38"/>
-    <mergeCell ref="A44:AA44"/>
-    <mergeCell ref="A34:AA34"/>
-    <mergeCell ref="A40:AA40"/>
-    <mergeCell ref="A48:AA48"/>
-    <mergeCell ref="A39:AA39"/>
-    <mergeCell ref="A45:AA45"/>
-    <mergeCell ref="A36:AA36"/>
-    <mergeCell ref="A49:AA49"/>
-    <mergeCell ref="A1:AA1"/>
+  <mergeCells count="21">
+    <mergeCell ref="A44:Q44"/>
+    <mergeCell ref="A40:Q40"/>
+    <mergeCell ref="A39:Q39"/>
+    <mergeCell ref="A34:Q34"/>
+    <mergeCell ref="A48:Q48"/>
+    <mergeCell ref="A45:Q45"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A36:Q36"/>
+    <mergeCell ref="A6:Q6"/>
+    <mergeCell ref="A41:Q41"/>
+    <mergeCell ref="A46:Q46"/>
+    <mergeCell ref="A37:Q37"/>
+    <mergeCell ref="A3:Q3"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A42:Q42"/>
+    <mergeCell ref="A47:Q47"/>
+    <mergeCell ref="A5:Q5"/>
+    <mergeCell ref="A35:Q35"/>
+    <mergeCell ref="A4:Q4"/>
+    <mergeCell ref="A43:Q43"/>
+    <mergeCell ref="A38:Q38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q48"/>
+  <dimension ref="A1:Q50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1850,8 +1850,10 @@
       <c r="M24" s="4" t="n">
         <v>-8.619999999999999</v>
       </c>
-      <c r="N24" s="4" t="n">
-        <v>221.57</v>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
@@ -2383,115 +2385,130 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
+          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
+          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
+          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
+          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
+          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
+          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
+          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
+          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
+          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
           <t>The 🔎 line answers "why is NEW zero today?" from the lifecycle reconciler · every scored name gets exactly one verdict (reports/context/why_not_current_{market}.json). A zero here is never presented without its reason.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="23">
     <mergeCell ref="A44:Q44"/>
     <mergeCell ref="A40:Q40"/>
     <mergeCell ref="A39:Q39"/>
     <mergeCell ref="A34:Q34"/>
     <mergeCell ref="A48:Q48"/>
+    <mergeCell ref="A49:Q49"/>
     <mergeCell ref="A45:Q45"/>
     <mergeCell ref="A1:Q1"/>
     <mergeCell ref="A36:Q36"/>
@@ -2500,6 +2517,7 @@
     <mergeCell ref="A46:Q46"/>
     <mergeCell ref="A37:Q37"/>
     <mergeCell ref="A3:Q3"/>
+    <mergeCell ref="A50:Q50"/>
     <mergeCell ref="A2:Q2"/>
     <mergeCell ref="A42:Q42"/>
     <mergeCell ref="A47:Q47"/>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -539,14 +539,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 WHY NEW=0 · 516 scored · 25 already in CURRENT · biggest blocker: model disagreement (408) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 2</t>
+          <t>🔎 WHY NEW=0 · 30 scored · 25 already in CURRENT · biggest blocker: model disagreement (25) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 16 candidate(s) reviewed today.</t>
+          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -103,10 +103,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W55"/>
+  <dimension ref="A1:W54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -518,14 +518,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>29 investable · NEW 0 · ACTIVE+ 18 · ACTIVE 11   ·   R2 16 · MOMENTUM 0 · R1 13 (advisory)   ·   8 row(s) read 0.00%: admitted at the 2026-09-10 close and still marked at it (same-close admission, not a stale price)</t>
+          <t>28 investable · NEW 7 · ACTIVE+ 10 · ACTIVE 11   ·   R2 15 · MOMENTUM 0 · R1 13 (advisory)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>🛡 DOWNSIDE · 29 position(s) with an INTACT stop · if all of them fired today the average outcome is -6.98% from entry, worst single -13.46%</t>
+          <t>🛡 DOWNSIDE · 28 position(s) with an INTACT stop · if all of them fired today the average outcome is -7.07% from entry, worst single -14.95%</t>
         </is>
       </c>
     </row>
@@ -539,7 +539,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 WHY NEW=0 · 516 scored · 25 already in CURRENT · biggest blocker: model disagreement (408) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 2</t>
+          <t>🔎 NEW=7 · 516 scored · 24 already in CURRENT · biggest blocker: model disagreement (405) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 2</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -695,40 +695,38 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-08</t>
+          <t>NEW today</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>382.85</v>
+        <v>135.11</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>390.93</v>
+        <v>135.11</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="K8" s="5" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
+      <c r="K8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>59.1</v>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="N8" s="6" t="n">
-        <v>106733315426.1837</v>
+          <t>Basic Materials</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>20179016711.53197</v>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
@@ -741,7 +739,7 @@
         </is>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>369.8646</v>
+        <v>126.8686</v>
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
@@ -749,22 +747,22 @@
         </is>
       </c>
       <c r="S8" s="4" t="n">
-        <v>5.39</v>
+        <v>6.1</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-3.39</v>
+        <v>-6.1</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>414.08</v>
+        <v>151.59</v>
       </c>
       <c r="V8" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-VLO-20260908-e69cee</t>
+          <t>USA-R2-CF-20260911-ddeaf8</t>
         </is>
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -776,7 +774,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -786,7 +784,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -796,19 +794,19 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-10</t>
+          <t>NEW today</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>135.21</v>
+        <v>243</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>135.21</v>
+        <v>243</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
@@ -823,11 +821,11 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>Basic Materials</t>
-        </is>
-      </c>
-      <c r="N9" s="6" t="n">
-        <v>20179016711.53197</v>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>213353612143.8822</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
@@ -840,7 +838,7 @@
         </is>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>126.9675</v>
+        <v>225.3375</v>
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
@@ -848,22 +846,22 @@
         </is>
       </c>
       <c r="S9" s="4" t="n">
-        <v>6.1</v>
+        <v>7.27</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-6.1</v>
+        <v>-7.27</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>151.69</v>
+        <v>278.33</v>
       </c>
       <c r="V9" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-CF-20260910-8ec428</t>
+          <t>USA-R2-CRM-20260911-92c3e2</t>
         </is>
       </c>
       <c r="W9" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -875,7 +873,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>EIX</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -885,7 +883,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -895,19 +893,19 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-10</t>
+          <t>NEW today</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>243.67</v>
+        <v>56.75</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>243.67</v>
+        <v>56.75</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
@@ -922,11 +920,11 @@
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="N10" s="6" t="n">
-        <v>213353612143.8822</v>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>21847412064.79042</v>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
@@ -939,7 +937,7 @@
         </is>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>226.0075</v>
+        <v>50.4125</v>
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
@@ -947,22 +945,22 @@
         </is>
       </c>
       <c r="S10" s="4" t="n">
-        <v>7.25</v>
+        <v>11.17</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-7.25</v>
+        <v>-11.17</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>278.99</v>
+        <v>69.42</v>
       </c>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-CRM-20260910-c681ff</t>
+          <t>USA-R2-EIX-20260911-899825</t>
         </is>
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -974,7 +972,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>EIX</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -984,7 +982,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -994,19 +992,19 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-10</t>
+          <t>NEW today</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>56.63</v>
+        <v>530.12</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>56.63</v>
+        <v>530.12</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -1021,11 +1019,11 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="N11" s="6" t="n">
-        <v>21847412064.79042</v>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>121227179253.6498</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
@@ -1038,7 +1036,7 @@
         </is>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>50.3118</v>
+        <v>506.135</v>
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
@@ -1046,22 +1044,22 @@
         </is>
       </c>
       <c r="S11" s="4" t="n">
-        <v>11.16</v>
+        <v>4.52</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-11.16</v>
+        <v>-4.52</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>69.27</v>
+        <v>566.1</v>
       </c>
       <c r="V11" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-EIX-20260910-5a23b8</t>
+          <t>USA-R2-LMT-20260911-47e24c</t>
         </is>
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1071,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>NCLH</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1083,7 +1081,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1093,19 +1091,19 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-10</t>
+          <t>NEW today</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>528.67</v>
+        <v>14.57</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>528.67</v>
+        <v>14.57</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
@@ -1116,15 +1114,15 @@
         <v>0</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>59.1</v>
+        <v>59.4</v>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="N12" s="6" t="n">
-        <v>121227179253.6498</v>
+          <t>Consumer Cyclical</t>
+        </is>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>7149900531.60001</v>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
@@ -1133,11 +1131,11 @@
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>Mid</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>504.6906</v>
+        <v>13.7729</v>
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
@@ -1145,22 +1143,22 @@
         </is>
       </c>
       <c r="S12" s="4" t="n">
-        <v>4.54</v>
+        <v>5.47</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-4.54</v>
+        <v>-5.47</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>564.65</v>
+        <v>16.16</v>
       </c>
       <c r="V12" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-LMT-20260910-af96ee</t>
+          <t>USA-R2-NCLH-20260911-4deec4</t>
         </is>
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1170,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>NCLH</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1182,7 +1180,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1192,19 +1190,19 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-10</t>
+          <t>NEW today</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>14.48</v>
+        <v>61.16</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>14.48</v>
+        <v>61.16</v>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
@@ -1215,15 +1213,15 @@
         <v>0</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>59.4</v>
+        <v>59.1</v>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="N13" s="6" t="n">
-        <v>7149900531.60001</v>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>60020554038.7197</v>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
@@ -1232,11 +1230,11 @@
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>Mid</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>13.6829</v>
+        <v>58.3643</v>
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
@@ -1244,22 +1242,22 @@
         </is>
       </c>
       <c r="S13" s="4" t="n">
-        <v>5.5</v>
+        <v>4.57</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-5.5</v>
+        <v>-4.57</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>16.07</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="V13" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-NCLH-20260910-d50523</t>
+          <t>USA-R2-OXY-20260911-840d2e</t>
         </is>
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1269,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>UDR</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1281,7 +1279,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1291,19 +1289,19 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-10</t>
+          <t>NEW today</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>60.92</v>
+        <v>35.14</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>60.92</v>
+        <v>35.14</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
@@ -1318,11 +1316,11 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="N14" s="6" t="n">
-        <v>60020554038.7197</v>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>13480313738.1309</v>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
@@ -1335,7 +1333,7 @@
         </is>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>58.1079</v>
+        <v>33.9629</v>
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
@@ -1343,22 +1341,22 @@
         </is>
       </c>
       <c r="S14" s="4" t="n">
-        <v>4.61</v>
+        <v>3.35</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-4.61</v>
+        <v>-3.35</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>65.13</v>
+        <v>36.91</v>
       </c>
       <c r="V14" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-OXY-20260910-f426ae</t>
+          <t>USA-R2-UDR-20260911-e6df0a</t>
         </is>
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1368,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>TER</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1390,38 +1388,40 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-10</t>
+          <t>Admitted 2026-09-08</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>382.85</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>385.43</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="H15" s="4" t="n">
-        <v>370.31</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>370.31</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="4" t="n">
-        <v>59.1</v>
+      <c r="K15" s="6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="N15" s="6" t="n">
-        <v>55821306891.77267</v>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>106733315426.1837</v>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         </is>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>343.6075</v>
+        <v>364.3357</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1442,22 +1442,22 @@
         </is>
       </c>
       <c r="S15" s="4" t="n">
-        <v>7.21</v>
+        <v>5.47</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-7.21</v>
+        <v>-4.84</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>423.71</v>
+        <v>414.08</v>
       </c>
       <c r="V15" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-TER-20260910-474826</t>
+          <t>USA-R2-VLO-20260908-e69cee</t>
         </is>
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>UDR</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1489,38 +1489,40 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-10</t>
+          <t>Admitted 2026-08-10</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>374.34</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>367.56</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="H16" s="4" t="n">
-        <v>34.94</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>34.94</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="4" t="n">
-        <v>59.1</v>
+      <c r="K16" s="7" t="n">
+        <v>-1.81</v>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="N16" s="6" t="n">
-        <v>13480313738.1309</v>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>77037113169.76082</v>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
@@ -1533,7 +1535,7 @@
         </is>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>33.7579</v>
+        <v>355.6478</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1541,22 +1543,22 @@
         </is>
       </c>
       <c r="S16" s="4" t="n">
-        <v>3.37</v>
+        <v>3.24</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-3.37</v>
+        <v>-4.99</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>36.7</v>
+        <v>400.86</v>
       </c>
       <c r="V16" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-UDR-20260910-18bd12</t>
+          <t>USA-R2-TRV-20260810-9cd25d</t>
         </is>
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1602,7 @@
         <v>126.01</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>123.36</v>
+        <v>123.28</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -1608,7 +1610,7 @@
         </is>
       </c>
       <c r="K17" s="7" t="n">
-        <v>-2.1</v>
+        <v>-2.17</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
@@ -1620,7 +1622,7 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N17" s="6" t="n">
+      <c r="N17" s="5" t="n">
         <v>25692123442.84064</v>
       </c>
       <c r="O17" s="4" t="inlineStr">
@@ -1634,7 +1636,7 @@
         </is>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>116.7014</v>
+        <v>116.62</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1645,7 +1647,7 @@
         <v>5.4</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-7.39</v>
+        <v>-7.45</v>
       </c>
       <c r="U17" s="4" t="n">
         <v>135.86</v>
@@ -1669,7 +1671,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1698,10 +1700,10 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>375.62</v>
+        <v>175.23</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>367.14</v>
+        <v>165.86</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
@@ -1709,7 +1711,7 @@
         </is>
       </c>
       <c r="K18" s="7" t="n">
-        <v>-2.26</v>
+        <v>-5.35</v>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
@@ -1718,11 +1720,11 @@
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="N18" s="6" t="n">
-        <v>77037113169.76082</v>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="N18" s="5" t="n">
+        <v>418890007002.7825</v>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
@@ -1735,7 +1737,7 @@
         </is>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>355.19</v>
+        <v>153.6918</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1743,22 +1745,22 @@
         </is>
       </c>
       <c r="S18" s="4" t="n">
-        <v>3.25</v>
+        <v>7.34</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-5.44</v>
+        <v>-12.29</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>402.23</v>
+        <v>204.13</v>
       </c>
       <c r="V18" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-TRV-20260810-9cd25d</t>
+          <t>USA-R2-PLTR-20260810-f9e975</t>
         </is>
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1770,7 +1772,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1790,19 +1792,19 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-10</t>
+          <t>Admitted 2026-09-08</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>175.23</v>
+        <v>40.26</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>166.2</v>
+        <v>37.38</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
@@ -1810,7 +1812,7 @@
         </is>
       </c>
       <c r="K19" s="7" t="n">
-        <v>-5.16</v>
+        <v>-7.15</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
@@ -1822,8 +1824,8 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N19" s="6" t="n">
-        <v>418890007002.7825</v>
+      <c r="N19" s="5" t="n">
+        <v>25609435171.5677</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
@@ -1836,7 +1838,7 @@
         </is>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>154.0269</v>
+        <v>34.2429</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1844,22 +1846,22 @@
         </is>
       </c>
       <c r="S19" s="4" t="n">
-        <v>7.32</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-12.1</v>
+        <v>-14.95</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>204.13</v>
+        <v>46.92</v>
       </c>
       <c r="V19" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-PLTR-20260810-f9e975</t>
+          <t>USA-R2-SMCI-20260908-c2c66b</t>
         </is>
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1873,12 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1886,24 +1888,24 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-08</t>
+          <t>Admitted 2026-08-14</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>40.26</v>
+        <v>63.83</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>37.94</v>
+        <v>63.75</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
@@ -1911,7 +1913,7 @@
         </is>
       </c>
       <c r="K20" s="7" t="n">
-        <v>-5.77</v>
+        <v>-0.13</v>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
@@ -1920,11 +1922,11 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="N20" s="6" t="n">
-        <v>25609435171.5677</v>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="n">
+        <v>136489737964.495</v>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
@@ -1937,7 +1939,7 @@
         </is>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>34.8397</v>
+        <v>60.0271</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1945,22 +1947,22 @@
         </is>
       </c>
       <c r="S20" s="4" t="n">
-        <v>8.16</v>
+        <v>5.84</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-13.46</v>
+        <v>-5.96</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>46.92</v>
+        <v>69.53</v>
       </c>
       <c r="V20" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-SMCI-20260908-c2c66b</t>
+          <t>USA-R1-BMY-20260814-a3b600</t>
         </is>
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1974,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1992,27 +1994,27 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-14</t>
+          <t>Admitted 2026-09-01</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>63.83</v>
+        <v>275.17</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>64</v>
+        <v>272.2</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="K21" s="5" t="n">
-        <v>0.27</v>
+      <c r="K21" s="7" t="n">
+        <v>-1.08</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
@@ -2021,11 +2023,11 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="N21" s="6" t="n">
-        <v>136489737964.495</v>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="n">
+        <v>53431824008.73483</v>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
@@ -2038,7 +2040,7 @@
         </is>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>60.0271</v>
+        <v>261.9314</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -2046,17 +2048,17 @@
         </is>
       </c>
       <c r="S21" s="4" t="n">
-        <v>6.21</v>
+        <v>3.77</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-5.96</v>
+        <v>-4.81</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>69.53</v>
+        <v>295.03</v>
       </c>
       <c r="V21" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-BMY-20260814-a3b600</t>
+          <t>USA-R1-GRMN-20260901-4c77f2</t>
         </is>
       </c>
       <c r="W21" s="4" t="inlineStr">
@@ -2073,7 +2075,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2093,19 +2095,19 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-01</t>
+          <t>Admitted 2026-08-10</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>275.17</v>
+        <v>505.11</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>272.01</v>
+        <v>492.44</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
@@ -2113,7 +2115,7 @@
         </is>
       </c>
       <c r="K22" s="7" t="n">
-        <v>-1.15</v>
+        <v>-2.51</v>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
@@ -2125,8 +2127,8 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N22" s="6" t="n">
-        <v>53431824008.73483</v>
+      <c r="N22" s="5" t="n">
+        <v>3710222886174.651</v>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
@@ -2139,7 +2141,7 @@
         </is>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>261.9314</v>
+        <v>469.0698</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -2147,17 +2149,17 @@
         </is>
       </c>
       <c r="S22" s="4" t="n">
-        <v>3.7</v>
+        <v>4.75</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-4.81</v>
+        <v>-7.13</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>295.03</v>
+        <v>559.17</v>
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-GRMN-20260901-4c77f2</t>
+          <t>USA-R1-MSFT-20260810-6110fc</t>
         </is>
       </c>
       <c r="W22" s="4" t="inlineStr">
@@ -2174,7 +2176,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -2203,10 +2205,10 @@
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>505.11</v>
+        <v>175.23</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>490.99</v>
+        <v>165.86</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
@@ -2214,7 +2216,7 @@
         </is>
       </c>
       <c r="K23" s="7" t="n">
-        <v>-2.8</v>
+        <v>-5.35</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
@@ -2226,8 +2228,8 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N23" s="6" t="n">
-        <v>3710222886174.651</v>
+      <c r="N23" s="5" t="n">
+        <v>418890007002.7825</v>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
@@ -2240,7 +2242,7 @@
         </is>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>469.0698</v>
+        <v>155.965</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2248,17 +2250,17 @@
         </is>
       </c>
       <c r="S23" s="4" t="n">
-        <v>4.46</v>
+        <v>5.97</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-7.13</v>
+        <v>-10.99</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>559.17</v>
+        <v>204.13</v>
       </c>
       <c r="V23" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-MSFT-20260810-6110fc</t>
+          <t>USA-R1-PLTR-20260810-5c4552</t>
         </is>
       </c>
       <c r="W23" s="4" t="inlineStr">
@@ -2275,7 +2277,7 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -2304,10 +2306,10 @@
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>175.23</v>
+        <v>272.96</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>166.2</v>
+        <v>248.83</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
@@ -2315,7 +2317,7 @@
         </is>
       </c>
       <c r="K24" s="7" t="n">
-        <v>-5.16</v>
+        <v>-8.84</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -2327,8 +2329,8 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N24" s="6" t="n">
-        <v>418890007002.7825</v>
+      <c r="N24" s="5" t="n">
+        <v>105949765544.345</v>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
@@ -2341,7 +2343,7 @@
         </is>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>155.965</v>
+        <v>247.1386</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2349,17 +2351,17 @@
         </is>
       </c>
       <c r="S24" s="4" t="n">
-        <v>6.16</v>
+        <v>0.68</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-10.99</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>204.13</v>
+        <v>311.69</v>
       </c>
       <c r="V24" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-PLTR-20260810-5c4552</t>
+          <t>USA-R1-ADBE-20260810-4ad164</t>
         </is>
       </c>
       <c r="W24" s="4" t="inlineStr">
@@ -2376,22 +2378,22 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -2405,18 +2407,18 @@
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>272.96</v>
+        <v>360.65</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>250.5</v>
+        <v>367.21</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="K25" s="7" t="n">
-        <v>-8.23</v>
+      <c r="K25" s="6" t="n">
+        <v>1.82</v>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
@@ -2425,11 +2427,11 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="N25" s="6" t="n">
-        <v>105949765544.345</v>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="N25" s="5" t="n">
+        <v>700325596737.0536</v>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
@@ -2442,7 +2444,7 @@
         </is>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>247.1386</v>
+        <v>355.6657</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2450,22 +2452,22 @@
         </is>
       </c>
       <c r="S25" s="4" t="n">
-        <v>1.34</v>
+        <v>3.14</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-9.460000000000001</v>
+        <v>-1.38</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>311.69</v>
+        <v>384</v>
       </c>
       <c r="V25" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-ADBE-20260810-4ad164</t>
+          <t>USA-R2-V-20260810-69160d</t>
         </is>
       </c>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>HOLD · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2477,7 +2479,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2497,27 +2499,27 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-10</t>
+          <t>Admitted 2026-08-11</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>360.65</v>
+        <v>63.61</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>366.76</v>
+        <v>63.75</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="K26" s="5" t="n">
-        <v>1.69</v>
+      <c r="K26" s="6" t="n">
+        <v>0.22</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -2526,11 +2528,11 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="N26" s="6" t="n">
-        <v>700325596737.0536</v>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="N26" s="5" t="n">
+        <v>136489737964.495</v>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
@@ -2543,7 +2545,7 @@
         </is>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>355.2186</v>
+        <v>61.0343</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -2551,22 +2553,22 @@
         </is>
       </c>
       <c r="S26" s="4" t="n">
-        <v>3.15</v>
+        <v>4.26</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-1.51</v>
+        <v>-4.05</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>384</v>
+        <v>69.45</v>
       </c>
       <c r="V26" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-V-20260810-69160d</t>
+          <t>USA-R2-BMY-20260811-c99117</t>
         </is>
       </c>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2580,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2607,18 +2609,18 @@
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>63.61</v>
+        <v>89.53</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>64</v>
+        <v>84.51000000000001</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="K27" s="5" t="n">
-        <v>0.62</v>
+      <c r="K27" s="7" t="n">
+        <v>-5.61</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
@@ -2630,8 +2632,8 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N27" s="6" t="n">
-        <v>136489737964.495</v>
+      <c r="N27" s="5" t="n">
+        <v>33166527215.04348</v>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
@@ -2644,7 +2646,7 @@
         </is>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>61.295</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
@@ -2652,17 +2654,17 @@
         </is>
       </c>
       <c r="S27" s="4" t="n">
-        <v>4.23</v>
+        <v>5.72</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-3.64</v>
+        <v>-11</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>69.45</v>
+        <v>99.06</v>
       </c>
       <c r="V27" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-BMY-20260811-c99117</t>
+          <t>USA-R2-DXCM-20260811-b3de8c</t>
         </is>
       </c>
       <c r="W27" s="4" t="inlineStr">
@@ -2679,12 +2681,12 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -2694,32 +2696,32 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-11</t>
+          <t>Admitted 2026-08-14</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>89.53</v>
+        <v>196.21</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>84.36</v>
+        <v>243</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="K28" s="7" t="n">
-        <v>-5.77</v>
+      <c r="K28" s="6" t="n">
+        <v>23.85</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
@@ -2728,11 +2730,11 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="N28" s="6" t="n">
-        <v>33166527215.04348</v>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="N28" s="5" t="n">
+        <v>213353612143.8822</v>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
@@ -2745,7 +2747,7 @@
         </is>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>79.5307</v>
+        <v>179.3029</v>
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
@@ -2753,22 +2755,24 @@
         </is>
       </c>
       <c r="S28" s="4" t="n">
-        <v>5.72</v>
+        <v>26.21</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-11.17</v>
-      </c>
-      <c r="U28" s="4" t="n">
-        <v>99.06</v>
+        <v>-8.619999999999999</v>
+      </c>
+      <c r="U28" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V28" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-DXCM-20260811-b3de8c</t>
+          <t>USA-R1-CRM-20260814-be7c1c</t>
         </is>
       </c>
       <c r="W28" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2784,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2800,27 +2804,27 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-14</t>
+          <t>Admitted 2026-09-01</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>196.21</v>
+        <v>103.51</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>243.67</v>
+        <v>113.33</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="K29" s="5" t="n">
-        <v>24.19</v>
+      <c r="K29" s="6" t="n">
+        <v>9.49</v>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
@@ -2829,11 +2833,11 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="N29" s="6" t="n">
-        <v>213353612143.8822</v>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="N29" s="5" t="n">
+        <v>109799408364.9603</v>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
@@ -2846,7 +2850,7 @@
         </is>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>179.3029</v>
+        <v>91.0157</v>
       </c>
       <c r="R29" s="4" t="inlineStr">
         <is>
@@ -2854,19 +2858,17 @@
         </is>
       </c>
       <c r="S29" s="4" t="n">
-        <v>26.42</v>
+        <v>19.69</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-8.619999999999999</v>
-      </c>
-      <c r="U29" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-12.07</v>
+      </c>
+      <c r="U29" s="4" t="n">
+        <v>122.25</v>
       </c>
       <c r="V29" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-CRM-20260814-be7c1c</t>
+          <t>USA-R1-HOOD-20260901-b8d64b</t>
         </is>
       </c>
       <c r="W29" s="4" t="inlineStr">
@@ -2883,7 +2885,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2912,18 +2914,18 @@
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>103.51</v>
+        <v>361.99</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>114.31</v>
+        <v>385.43</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="K30" s="5" t="n">
-        <v>10.43</v>
+      <c r="K30" s="6" t="n">
+        <v>6.48</v>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
@@ -2932,11 +2934,11 @@
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="N30" s="6" t="n">
-        <v>109799408364.9603</v>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="N30" s="5" t="n">
+        <v>106733315426.1837</v>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
@@ -2949,7 +2951,7 @@
         </is>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>91.0157</v>
+        <v>342.2271</v>
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
@@ -2957,17 +2959,17 @@
         </is>
       </c>
       <c r="S30" s="4" t="n">
-        <v>20.38</v>
+        <v>11.21</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-12.07</v>
+        <v>-5.46</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>122.25</v>
+        <v>391.63</v>
       </c>
       <c r="V30" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-HOOD-20260901-b8d64b</t>
+          <t>USA-R1-VLO-20260901-3c6acd</t>
         </is>
       </c>
       <c r="W30" s="4" t="inlineStr">
@@ -2984,7 +2986,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>SAIC</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -3004,27 +3006,27 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-01</t>
+          <t>Admitted 2026-08-14</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>361.99</v>
+        <v>126.68</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>390.93</v>
+        <v>128.76</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="K31" s="5" t="n">
-        <v>7.99</v>
+      <c r="K31" s="6" t="n">
+        <v>1.64</v>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
@@ -3033,11 +3035,11 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="N31" s="6" t="n">
-        <v>106733315426.1837</v>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="N31" s="5" t="n">
+        <v>5310066989.662829</v>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
@@ -3046,11 +3048,11 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>Mid</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>342.2271</v>
+        <v>119.43</v>
       </c>
       <c r="R31" s="4" t="inlineStr">
         <is>
@@ -3058,17 +3060,17 @@
         </is>
       </c>
       <c r="S31" s="4" t="n">
-        <v>12.46</v>
+        <v>7.25</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-5.46</v>
+        <v>-5.72</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>391.63</v>
+        <v>137.55</v>
       </c>
       <c r="V31" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-VLO-20260901-3c6acd</t>
+          <t>USA-R1-SAIC-20260814-889ae8</t>
         </is>
       </c>
       <c r="W31" s="4" t="inlineStr">
@@ -3085,7 +3087,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -3105,27 +3107,27 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-14</t>
+          <t>Admitted 2026-09-01</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>126.68</v>
+        <v>187.7</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>129.08</v>
+        <v>189.32</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="K32" s="5" t="n">
-        <v>1.89</v>
+      <c r="K32" s="6" t="n">
+        <v>0.86</v>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
@@ -3134,11 +3136,11 @@
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="N32" s="6" t="n">
-        <v>5310066989.662829</v>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="N32" s="5" t="n">
+        <v>24541437631.37434</v>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
@@ -3147,11 +3149,11 @@
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>Mid</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>119.43</v>
+        <v>180.8543</v>
       </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
@@ -3159,17 +3161,17 @@
         </is>
       </c>
       <c r="S32" s="4" t="n">
-        <v>7.48</v>
+        <v>4.47</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-5.72</v>
+        <v>-3.65</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>137.55</v>
+        <v>197.97</v>
       </c>
       <c r="V32" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-SAIC-20260814-889ae8</t>
+          <t>USA-R1-EXPD-20260901-065905</t>
         </is>
       </c>
       <c r="W32" s="4" t="inlineStr">
@@ -3186,7 +3188,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -3215,18 +3217,18 @@
         </is>
       </c>
       <c r="H33" s="4" t="n">
-        <v>187.7</v>
+        <v>161.85</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>189.68</v>
+        <v>158.85</v>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="K33" s="5" t="n">
-        <v>1.05</v>
+      <c r="K33" s="7" t="n">
+        <v>-1.85</v>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
@@ -3235,11 +3237,11 @@
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="N33" s="6" t="n">
-        <v>24541437631.37434</v>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="N33" s="5" t="n">
+        <v>114683252142.2478</v>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
@@ -3252,7 +3254,7 @@
         </is>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>180.8543</v>
+        <v>147.9529</v>
       </c>
       <c r="R33" s="4" t="inlineStr">
         <is>
@@ -3260,17 +3262,17 @@
         </is>
       </c>
       <c r="S33" s="4" t="n">
-        <v>4.65</v>
+        <v>6.86</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-3.65</v>
+        <v>-8.59</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>197.97</v>
+        <v>182.7</v>
       </c>
       <c r="V33" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-EXPD-20260901-065905</t>
+          <t>USA-R1-FTNT-20260901-30d75e</t>
         </is>
       </c>
       <c r="W33" s="4" t="inlineStr">
@@ -3287,7 +3289,7 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>FOX</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -3307,19 +3309,19 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-01</t>
+          <t>Admitted 2026-08-19</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="H34" s="4" t="n">
-        <v>161.85</v>
+        <v>60.09</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>159.19</v>
+        <v>58.06</v>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
@@ -3327,7 +3329,7 @@
         </is>
       </c>
       <c r="K34" s="7" t="n">
-        <v>-1.64</v>
+        <v>-3.38</v>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
@@ -3336,11 +3338,11 @@
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="N34" s="6" t="n">
-        <v>114683252142.2478</v>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="N34" s="5" t="n">
+        <v>24564051543.2472</v>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
@@ -3353,7 +3355,7 @@
         </is>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>147.9529</v>
+        <v>56.6217</v>
       </c>
       <c r="R34" s="4" t="inlineStr">
         <is>
@@ -3361,17 +3363,17 @@
         </is>
       </c>
       <c r="S34" s="4" t="n">
-        <v>7.06</v>
+        <v>2.48</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-8.59</v>
+        <v>-5.78</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>182.7</v>
+        <v>65.3</v>
       </c>
       <c r="V34" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-FTNT-20260901-30d75e</t>
+          <t>USA-R1-FOX-20260819-7b9e84</t>
         </is>
       </c>
       <c r="W34" s="4" t="inlineStr">
@@ -3420,7 +3422,7 @@
         <v>344.5</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>332.71</v>
+        <v>332.6</v>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
@@ -3428,7 +3430,7 @@
         </is>
       </c>
       <c r="K35" s="7" t="n">
-        <v>-3.42</v>
+        <v>-3.45</v>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
@@ -3440,7 +3442,7 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="N35" s="6" t="n">
+      <c r="N35" s="5" t="n">
         <v>4139043588458.335</v>
       </c>
       <c r="O35" s="4" t="inlineStr">
@@ -3462,7 +3464,7 @@
         </is>
       </c>
       <c r="S35" s="4" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="T35" s="4" t="n">
         <v>-6.2</v>
@@ -3481,221 +3483,120 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>FOX</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>Admitted 2026-08-19</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>60.09</v>
-      </c>
-      <c r="I36" s="4" t="n">
-        <v>57.78</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="K36" s="7" t="n">
-        <v>-3.85</v>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
-      </c>
-      <c r="M36" s="4" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="N36" s="6" t="n">
-        <v>24564051543.2472</v>
-      </c>
-      <c r="O36" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="P36" s="4" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-      <c r="Q36" s="4" t="n">
-        <v>56.6217</v>
-      </c>
-      <c r="R36" s="4" t="inlineStr">
-        <is>
-          <t>INTACT</t>
-        </is>
-      </c>
-      <c r="S36" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="T36" s="4" t="n">
-        <v>-5.78</v>
-      </c>
-      <c r="U36" s="4" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="V36" s="4" t="inlineStr">
-        <is>
-          <t>USA-R1-FOX-20260819-7b9e84</t>
-        </is>
-      </c>
-      <c r="W36" s="4" t="inlineStr">
-        <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
+          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
+          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
+          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
+          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
+          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
+          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
+          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
+          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
+          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
+          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
+          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
+          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="8" t="inlineStr">
         <is>
           <t>The 🔎 line answers "why is NEW zero today?" from the lifecycle reconciler · every scored name gets exactly one verdict (reports/context/why_not_current_{market}.json). A zero here is never presented without its reason.</t>
         </is>
@@ -3717,13 +3618,13 @@
     <mergeCell ref="A46:W46"/>
     <mergeCell ref="A50:W50"/>
     <mergeCell ref="A3:W3"/>
-    <mergeCell ref="A55:W55"/>
     <mergeCell ref="A2:W2"/>
     <mergeCell ref="A47:W47"/>
     <mergeCell ref="A42:W42"/>
     <mergeCell ref="A5:W5"/>
     <mergeCell ref="A53:W53"/>
     <mergeCell ref="A4:W4"/>
+    <mergeCell ref="A38:W38"/>
     <mergeCell ref="A52:W52"/>
     <mergeCell ref="A43:W43"/>
   </mergeCells>
@@ -3901,10 +3802,10 @@
         <v>78.03</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>72.61</v>
+        <v>72.56</v>
       </c>
       <c r="J5" s="7" t="n">
-        <v>-6.95</v>
+        <v>-7.01</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>31</v>
@@ -3975,10 +3876,10 @@
         <v>193.17</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>171.35</v>
+        <v>170.62</v>
       </c>
       <c r="J6" s="7" t="n">
-        <v>-11.29</v>
+        <v>-11.67</v>
       </c>
       <c r="K6" s="4" t="n">
         <v>31</v>
@@ -4049,10 +3950,10 @@
         <v>193.17</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>171.35</v>
+        <v>170.62</v>
       </c>
       <c r="J7" s="7" t="n">
-        <v>-11.29</v>
+        <v>-11.67</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>30</v>
@@ -4069,7 +3970,7 @@
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>STOP BREACHED - stop 160.0364 - dynamic_risk_v2 · ENFORCED - MARK, position still open in R2</t>
+          <t>STOP BREACHED - stop 159.3014 - dynamic_risk_v2 · ENFORCED - MARK, position still open in R2</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
@@ -4123,10 +4024,10 @@
         <v>90.22</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>84.36</v>
+        <v>84.51000000000001</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>-6.5</v>
+        <v>-6.33</v>
       </c>
       <c r="K8" s="4" t="n">
         <v>20</v>
@@ -4197,10 +4098,10 @@
         <v>71.41</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>56.63</v>
+        <v>56.75</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>-20.7</v>
+        <v>-20.53</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>25</v>
@@ -5156,10 +5057,10 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>60.91</v>
+        <v>60.63</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>60.91</v>
+        <v>60.63</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>0</v>
@@ -5309,7 +5210,7 @@
       <c r="I24" s="4" t="n">
         <v>77.52</v>
       </c>
-      <c r="J24" s="5" t="n">
+      <c r="J24" s="6" t="n">
         <v>2.88</v>
       </c>
       <c r="K24" s="4" t="n">
@@ -5457,7 +5358,7 @@
       <c r="I26" s="4" t="n">
         <v>101.38</v>
       </c>
-      <c r="J26" s="5" t="n">
+      <c r="J26" s="6" t="n">
         <v>4.27</v>
       </c>
       <c r="K26" s="4" t="n">
@@ -5531,7 +5432,7 @@
       <c r="I27" s="4" t="n">
         <v>153.64</v>
       </c>
-      <c r="J27" s="5" t="n">
+      <c r="J27" s="6" t="n">
         <v>6.67</v>
       </c>
       <c r="K27" s="4" t="n">
@@ -5605,7 +5506,7 @@
       <c r="I28" s="4" t="n">
         <v>83.09999999999999</v>
       </c>
-      <c r="J28" s="5" t="n">
+      <c r="J28" s="6" t="n">
         <v>5.1</v>
       </c>
       <c r="K28" s="4" t="n">
@@ -5827,7 +5728,7 @@
       <c r="I31" s="4" t="n">
         <v>77.68000000000001</v>
       </c>
-      <c r="J31" s="5" t="n">
+      <c r="J31" s="6" t="n">
         <v>0.03</v>
       </c>
       <c r="K31" s="4" t="n">
@@ -6049,7 +5950,7 @@
       <c r="I34" s="4" t="n">
         <v>343.12</v>
       </c>
-      <c r="J34" s="5" t="n">
+      <c r="J34" s="6" t="n">
         <v>0.21</v>
       </c>
       <c r="K34" s="4" t="n">
@@ -6123,7 +6024,7 @@
       <c r="I35" s="4" t="n">
         <v>343.12</v>
       </c>
-      <c r="J35" s="5" t="n">
+      <c r="J35" s="6" t="n">
         <v>0.21</v>
       </c>
       <c r="K35" s="4" t="n">
@@ -6493,7 +6394,7 @@
       <c r="I40" s="4" t="n">
         <v>74.41</v>
       </c>
-      <c r="J40" s="5" t="n">
+      <c r="J40" s="6" t="n">
         <v>2.9</v>
       </c>
       <c r="K40" s="4" t="n">
@@ -6715,7 +6616,7 @@
       <c r="I43" s="4" t="n">
         <v>241.56</v>
       </c>
-      <c r="J43" s="5" t="n">
+      <c r="J43" s="6" t="n">
         <v>7.28</v>
       </c>
       <c r="K43" s="4" t="n">
@@ -6789,7 +6690,7 @@
       <c r="I44" s="4" t="n">
         <v>107.52</v>
       </c>
-      <c r="J44" s="5" t="n">
+      <c r="J44" s="6" t="n">
         <v>1.67</v>
       </c>
       <c r="K44" s="4" t="n">
@@ -6863,7 +6764,7 @@
       <c r="I45" s="4" t="n">
         <v>468.73</v>
       </c>
-      <c r="J45" s="5" t="n">
+      <c r="J45" s="6" t="n">
         <v>7.07</v>
       </c>
       <c r="K45" s="4" t="n">
@@ -6937,7 +6838,7 @@
       <c r="I46" s="4" t="n">
         <v>190.75</v>
       </c>
-      <c r="J46" s="5" t="n">
+      <c r="J46" s="6" t="n">
         <v>5.23</v>
       </c>
       <c r="K46" s="4" t="n">
@@ -7011,7 +6912,7 @@
       <c r="I47" s="4" t="n">
         <v>28.75</v>
       </c>
-      <c r="J47" s="5" t="n">
+      <c r="J47" s="6" t="n">
         <v>6.21</v>
       </c>
       <c r="K47" s="4" t="n">
@@ -7159,7 +7060,7 @@
       <c r="I49" s="4" t="n">
         <v>300.54</v>
       </c>
-      <c r="J49" s="5" t="n">
+      <c r="J49" s="6" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="K49" s="4" t="n">
@@ -7233,7 +7134,7 @@
       <c r="I50" s="4" t="n">
         <v>50.19</v>
       </c>
-      <c r="J50" s="5" t="n">
+      <c r="J50" s="6" t="n">
         <v>6.18</v>
       </c>
       <c r="K50" s="4" t="n">
@@ -7307,7 +7208,7 @@
       <c r="I51" s="4" t="n">
         <v>16.85</v>
       </c>
-      <c r="J51" s="5" t="n">
+      <c r="J51" s="6" t="n">
         <v>4.28</v>
       </c>
       <c r="K51" s="4" t="n">
@@ -7381,7 +7282,7 @@
       <c r="I52" s="4" t="n">
         <v>93.5</v>
       </c>
-      <c r="J52" s="5" t="n">
+      <c r="J52" s="6" t="n">
         <v>7.52</v>
       </c>
       <c r="K52" s="4" t="n">
@@ -7529,7 +7430,7 @@
       <c r="I54" s="4" t="n">
         <v>547.29</v>
       </c>
-      <c r="J54" s="5" t="n">
+      <c r="J54" s="6" t="n">
         <v>3.33</v>
       </c>
       <c r="K54" s="4" t="n">
@@ -7677,7 +7578,7 @@
       <c r="I56" s="4" t="n">
         <v>292.99</v>
       </c>
-      <c r="J56" s="5" t="n">
+      <c r="J56" s="6" t="n">
         <v>2.16</v>
       </c>
       <c r="K56" s="4" t="n">
@@ -7751,7 +7652,7 @@
       <c r="I57" s="4" t="n">
         <v>187.87</v>
       </c>
-      <c r="J57" s="5" t="n">
+      <c r="J57" s="6" t="n">
         <v>3.81</v>
       </c>
       <c r="K57" s="4" t="n">
@@ -7899,7 +7800,7 @@
       <c r="I59" s="4" t="n">
         <v>98.69</v>
       </c>
-      <c r="J59" s="5" t="n">
+      <c r="J59" s="6" t="n">
         <v>0.73</v>
       </c>
       <c r="K59" s="4" t="n">
@@ -7973,7 +7874,7 @@
       <c r="I60" s="4" t="n">
         <v>348.03</v>
       </c>
-      <c r="J60" s="5" t="n">
+      <c r="J60" s="6" t="n">
         <v>7.44</v>
       </c>
       <c r="K60" s="4" t="n">
@@ -8047,7 +7948,7 @@
       <c r="I61" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="J61" s="5" t="n">
+      <c r="J61" s="6" t="n">
         <v>0.08</v>
       </c>
       <c r="K61" s="4" t="n">
@@ -8121,7 +8022,7 @@
       <c r="I62" s="4" t="n">
         <v>244.91</v>
       </c>
-      <c r="J62" s="5" t="n">
+      <c r="J62" s="6" t="n">
         <v>3.52</v>
       </c>
       <c r="K62" s="4" t="n">
@@ -8195,7 +8096,7 @@
       <c r="I63" s="4" t="n">
         <v>383.9</v>
       </c>
-      <c r="J63" s="5" t="n">
+      <c r="J63" s="6" t="n">
         <v>6.45</v>
       </c>
       <c r="K63" s="4" t="n">
@@ -8417,7 +8318,7 @@
       <c r="I66" s="4" t="n">
         <v>105.65</v>
       </c>
-      <c r="J66" s="5" t="n">
+      <c r="J66" s="6" t="n">
         <v>2.78</v>
       </c>
       <c r="K66" s="4" t="n">
@@ -8491,7 +8392,7 @@
       <c r="I67" s="4" t="n">
         <v>309.19</v>
       </c>
-      <c r="J67" s="5" t="n">
+      <c r="J67" s="6" t="n">
         <v>6.06</v>
       </c>
       <c r="K67" s="4" t="n">
@@ -8639,7 +8540,7 @@
       <c r="I69" s="4" t="n">
         <v>543.1900000000001</v>
       </c>
-      <c r="J69" s="5" t="n">
+      <c r="J69" s="6" t="n">
         <v>0.34</v>
       </c>
       <c r="K69" s="4" t="n">
@@ -8713,7 +8614,7 @@
       <c r="I70" s="4" t="n">
         <v>178.48</v>
       </c>
-      <c r="J70" s="5" t="n">
+      <c r="J70" s="6" t="n">
         <v>5.91</v>
       </c>
       <c r="K70" s="4" t="n">
@@ -8787,7 +8688,7 @@
       <c r="I71" s="4" t="n">
         <v>37.93</v>
       </c>
-      <c r="J71" s="5" t="n">
+      <c r="J71" s="6" t="n">
         <v>2.08</v>
       </c>
       <c r="K71" s="4" t="n">
@@ -8935,7 +8836,7 @@
       <c r="I73" s="4" t="n">
         <v>352.65</v>
       </c>
-      <c r="J73" s="5" t="n">
+      <c r="J73" s="6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="K73" s="4" t="n">
@@ -9305,7 +9206,7 @@
       <c r="I78" s="4" t="n">
         <v>56.03</v>
       </c>
-      <c r="J78" s="5" t="n">
+      <c r="J78" s="6" t="n">
         <v>0.21</v>
       </c>
       <c r="K78" s="4" t="n">
@@ -9379,7 +9280,7 @@
       <c r="I79" s="4" t="n">
         <v>345.82</v>
       </c>
-      <c r="J79" s="5" t="n">
+      <c r="J79" s="6" t="n">
         <v>3.91</v>
       </c>
       <c r="K79" s="4" t="n">
@@ -9522,10 +9423,10 @@
         </is>
       </c>
       <c r="H81" s="4" t="n">
-        <v>375.62</v>
+        <v>374.34</v>
       </c>
       <c r="I81" s="4" t="n">
-        <v>371.15</v>
+        <v>369.89</v>
       </c>
       <c r="J81" s="7" t="n">
         <v>-1.19</v>
@@ -9675,7 +9576,7 @@
       <c r="I83" s="4" t="n">
         <v>59.68</v>
       </c>
-      <c r="J83" s="5" t="n">
+      <c r="J83" s="6" t="n">
         <v>2.93</v>
       </c>
       <c r="K83" s="4" t="n">
@@ -9749,7 +9650,7 @@
       <c r="I84" s="4" t="n">
         <v>294.03</v>
       </c>
-      <c r="J84" s="5" t="n">
+      <c r="J84" s="6" t="n">
         <v>10.77</v>
       </c>
       <c r="K84" s="4" t="n">
@@ -9897,7 +9798,7 @@
       <c r="I86" s="4" t="n">
         <v>368.81</v>
       </c>
-      <c r="J86" s="5" t="n">
+      <c r="J86" s="6" t="n">
         <v>1.21</v>
       </c>
       <c r="K86" s="4" t="n">
@@ -9971,7 +9872,7 @@
       <c r="I87" s="4" t="n">
         <v>178.58</v>
       </c>
-      <c r="J87" s="5" t="n">
+      <c r="J87" s="6" t="n">
         <v>0.58</v>
       </c>
       <c r="K87" s="4" t="n">
@@ -10045,7 +9946,7 @@
       <c r="I88" s="4" t="n">
         <v>633.71</v>
       </c>
-      <c r="J88" s="5" t="n">
+      <c r="J88" s="6" t="n">
         <v>4.75</v>
       </c>
       <c r="K88" s="4" t="n">
@@ -10267,7 +10168,7 @@
       <c r="I91" s="4" t="n">
         <v>164.04</v>
       </c>
-      <c r="J91" s="5" t="n">
+      <c r="J91" s="6" t="n">
         <v>8.539999999999999</v>
       </c>
       <c r="K91" s="4" t="n">
@@ -10341,7 +10242,7 @@
       <c r="I92" s="4" t="n">
         <v>164.04</v>
       </c>
-      <c r="J92" s="5" t="n">
+      <c r="J92" s="6" t="n">
         <v>8.539999999999999</v>
       </c>
       <c r="K92" s="4" t="n">
@@ -10711,7 +10612,7 @@
       <c r="I97" s="4" t="n">
         <v>72.38</v>
       </c>
-      <c r="J97" s="5" t="n">
+      <c r="J97" s="6" t="n">
         <v>0.43</v>
       </c>
       <c r="K97" s="4" t="n">
@@ -10933,7 +10834,7 @@
       <c r="I100" s="4" t="n">
         <v>41.61</v>
       </c>
-      <c r="J100" s="5" t="n">
+      <c r="J100" s="6" t="n">
         <v>0.26</v>
       </c>
       <c r="K100" s="4" t="n">
@@ -11007,7 +10908,7 @@
       <c r="I101" s="4" t="n">
         <v>25.87</v>
       </c>
-      <c r="J101" s="5" t="n">
+      <c r="J101" s="6" t="n">
         <v>5.59</v>
       </c>
       <c r="K101" s="4" t="n">
@@ -11229,7 +11130,7 @@
       <c r="I104" s="4" t="n">
         <v>79.78</v>
       </c>
-      <c r="J104" s="5" t="n">
+      <c r="J104" s="6" t="n">
         <v>1.67</v>
       </c>
       <c r="K104" s="4" t="n">
@@ -11451,7 +11352,7 @@
       <c r="I107" s="4" t="n">
         <v>49.56</v>
       </c>
-      <c r="J107" s="5" t="n">
+      <c r="J107" s="6" t="n">
         <v>0.79</v>
       </c>
       <c r="K107" s="4" t="n">
@@ -11525,7 +11426,7 @@
       <c r="I108" s="4" t="n">
         <v>134.45</v>
       </c>
-      <c r="J108" s="5" t="n">
+      <c r="J108" s="6" t="n">
         <v>0.35</v>
       </c>
       <c r="K108" s="4" t="n">
@@ -11599,7 +11500,7 @@
       <c r="I109" s="4" t="n">
         <v>846.37</v>
       </c>
-      <c r="J109" s="5" t="n">
+      <c r="J109" s="6" t="n">
         <v>3.15</v>
       </c>
       <c r="K109" s="4" t="n">
@@ -11673,7 +11574,7 @@
       <c r="I110" s="4" t="n">
         <v>193.62</v>
       </c>
-      <c r="J110" s="5" t="n">
+      <c r="J110" s="6" t="n">
         <v>3.42</v>
       </c>
       <c r="K110" s="4" t="n">
@@ -11969,7 +11870,7 @@
       <c r="I114" s="4" t="n">
         <v>436.49</v>
       </c>
-      <c r="J114" s="5" t="n">
+      <c r="J114" s="6" t="n">
         <v>7.04</v>
       </c>
       <c r="K114" s="4" t="n">
@@ -12117,7 +12018,7 @@
       <c r="I116" s="4" t="n">
         <v>91.53</v>
       </c>
-      <c r="J116" s="5" t="n">
+      <c r="J116" s="6" t="n">
         <v>8.83</v>
       </c>
       <c r="K116" s="4" t="n">
@@ -12339,7 +12240,7 @@
       <c r="I119" s="4" t="n">
         <v>1499.37</v>
       </c>
-      <c r="J119" s="5" t="n">
+      <c r="J119" s="6" t="n">
         <v>17.96</v>
       </c>
       <c r="K119" s="4" t="n">
@@ -12561,7 +12462,7 @@
       <c r="I122" s="4" t="n">
         <v>130.9</v>
       </c>
-      <c r="J122" s="5" t="n">
+      <c r="J122" s="6" t="n">
         <v>12.6</v>
       </c>
       <c r="K122" s="4" t="n">
@@ -12709,7 +12610,7 @@
       <c r="I124" s="4" t="n">
         <v>109.39</v>
       </c>
-      <c r="J124" s="5" t="n">
+      <c r="J124" s="6" t="n">
         <v>1.87</v>
       </c>
       <c r="K124" s="4" t="n">
@@ -12783,7 +12684,7 @@
       <c r="I125" s="4" t="n">
         <v>108.49</v>
       </c>
-      <c r="J125" s="5" t="n">
+      <c r="J125" s="6" t="n">
         <v>2.3</v>
       </c>
       <c r="K125" s="4" t="n">
@@ -12857,7 +12758,7 @@
       <c r="I126" s="4" t="n">
         <v>185.98</v>
       </c>
-      <c r="J126" s="5" t="n">
+      <c r="J126" s="6" t="n">
         <v>2.91</v>
       </c>
       <c r="K126" s="4" t="n">
@@ -12931,7 +12832,7 @@
       <c r="I127" s="4" t="n">
         <v>126.35</v>
       </c>
-      <c r="J127" s="5" t="n">
+      <c r="J127" s="6" t="n">
         <v>9.18</v>
       </c>
       <c r="K127" s="4" t="n">
@@ -13153,7 +13054,7 @@
       <c r="I130" s="4" t="n">
         <v>222.18</v>
       </c>
-      <c r="J130" s="5" t="n">
+      <c r="J130" s="6" t="n">
         <v>3.3</v>
       </c>
       <c r="K130" s="4" t="n">
@@ -13301,7 +13202,7 @@
       <c r="I132" s="4" t="n">
         <v>413.28</v>
       </c>
-      <c r="J132" s="5" t="n">
+      <c r="J132" s="6" t="n">
         <v>3.45</v>
       </c>
       <c r="K132" s="4" t="n">
@@ -13523,7 +13424,7 @@
       <c r="I135" s="4" t="n">
         <v>235.69</v>
       </c>
-      <c r="J135" s="5" t="n">
+      <c r="J135" s="6" t="n">
         <v>5.13</v>
       </c>
       <c r="K135" s="4" t="n">
@@ -13819,7 +13720,7 @@
       <c r="I139" s="4" t="n">
         <v>814.79</v>
       </c>
-      <c r="J139" s="5" t="n">
+      <c r="J139" s="6" t="n">
         <v>2.35</v>
       </c>
       <c r="K139" s="4" t="n">
@@ -13893,7 +13794,7 @@
       <c r="I140" s="4" t="n">
         <v>76.38</v>
       </c>
-      <c r="J140" s="5" t="n">
+      <c r="J140" s="6" t="n">
         <v>0.74</v>
       </c>
       <c r="K140" s="4" t="n">
@@ -14041,7 +13942,7 @@
       <c r="I142" s="4" t="n">
         <v>162.83</v>
       </c>
-      <c r="J142" s="5" t="n">
+      <c r="J142" s="6" t="n">
         <v>0.64</v>
       </c>
       <c r="K142" s="4" t="n">
@@ -14189,7 +14090,7 @@
       <c r="I144" s="4" t="n">
         <v>61.66</v>
       </c>
-      <c r="J144" s="5" t="n">
+      <c r="J144" s="6" t="n">
         <v>4.76</v>
       </c>
       <c r="K144" s="4" t="n">
@@ -14411,7 +14312,7 @@
       <c r="I147" s="4" t="n">
         <v>151.61</v>
       </c>
-      <c r="J147" s="5" t="n">
+      <c r="J147" s="6" t="n">
         <v>0.78</v>
       </c>
       <c r="K147" s="4" t="n">
@@ -14485,7 +14386,7 @@
       <c r="I148" s="4" t="n">
         <v>242.23</v>
       </c>
-      <c r="J148" s="5" t="n">
+      <c r="J148" s="6" t="n">
         <v>8.539999999999999</v>
       </c>
       <c r="K148" s="4" t="n">
@@ -14559,7 +14460,7 @@
       <c r="I149" s="4" t="n">
         <v>10.74</v>
       </c>
-      <c r="J149" s="5" t="n">
+      <c r="J149" s="6" t="n">
         <v>14.5</v>
       </c>
       <c r="K149" s="4" t="n">
@@ -14776,10 +14677,10 @@
         </is>
       </c>
       <c r="H152" s="4" t="n">
-        <v>35.28</v>
+        <v>34.99</v>
       </c>
       <c r="I152" s="4" t="n">
-        <v>35.02</v>
+        <v>34.73</v>
       </c>
       <c r="J152" s="7" t="n">
         <v>-0.74</v>
@@ -15225,7 +15126,7 @@
       <c r="I158" s="4" t="n">
         <v>194.1</v>
       </c>
-      <c r="J158" s="5" t="n">
+      <c r="J158" s="6" t="n">
         <v>4.23</v>
       </c>
       <c r="K158" s="4" t="n">
@@ -15299,7 +15200,7 @@
       <c r="I159" s="4" t="n">
         <v>142.59</v>
       </c>
-      <c r="J159" s="5" t="n">
+      <c r="J159" s="6" t="n">
         <v>2.22</v>
       </c>
       <c r="K159" s="4" t="n">
@@ -15521,7 +15422,7 @@
       <c r="I162" s="4" t="n">
         <v>222.51</v>
       </c>
-      <c r="J162" s="5" t="n">
+      <c r="J162" s="6" t="n">
         <v>4.78</v>
       </c>
       <c r="K162" s="4" t="n">
@@ -15743,7 +15644,7 @@
       <c r="I165" s="4" t="n">
         <v>28.3</v>
       </c>
-      <c r="J165" s="5" t="n">
+      <c r="J165" s="6" t="n">
         <v>6.31</v>
       </c>
       <c r="K165" s="4" t="n">
@@ -15817,7 +15718,7 @@
       <c r="I166" s="4" t="n">
         <v>140.69</v>
       </c>
-      <c r="J166" s="5" t="n">
+      <c r="J166" s="6" t="n">
         <v>2.73</v>
       </c>
       <c r="K166" s="4" t="n">
@@ -15965,7 +15866,7 @@
       <c r="I168" s="4" t="n">
         <v>18.22</v>
       </c>
-      <c r="J168" s="5" t="n">
+      <c r="J168" s="6" t="n">
         <v>5.32</v>
       </c>
       <c r="K168" s="4" t="n">
@@ -16113,7 +16014,7 @@
       <c r="I170" s="4" t="n">
         <v>124.88</v>
       </c>
-      <c r="J170" s="5" t="n">
+      <c r="J170" s="6" t="n">
         <v>2.95</v>
       </c>
       <c r="K170" s="4" t="n">
@@ -16256,10 +16157,10 @@
         </is>
       </c>
       <c r="H172" s="4" t="n">
-        <v>59.06</v>
+        <v>58.79</v>
       </c>
       <c r="I172" s="4" t="n">
-        <v>58.62</v>
+        <v>58.35</v>
       </c>
       <c r="J172" s="7" t="n">
         <v>-0.75</v>
@@ -16483,7 +16384,7 @@
       <c r="I175" s="4" t="n">
         <v>148.87</v>
       </c>
-      <c r="J175" s="5" t="n">
+      <c r="J175" s="6" t="n">
         <v>2.33</v>
       </c>
       <c r="K175" s="4" t="n">
@@ -16631,7 +16532,7 @@
       <c r="I177" s="4" t="n">
         <v>87.89</v>
       </c>
-      <c r="J177" s="5" t="n">
+      <c r="J177" s="6" t="n">
         <v>2.26</v>
       </c>
       <c r="K177" s="4" t="n">
@@ -16705,7 +16606,7 @@
       <c r="I178" s="4" t="n">
         <v>94.90000000000001</v>
       </c>
-      <c r="J178" s="5" t="n">
+      <c r="J178" s="6" t="n">
         <v>3.69</v>
       </c>
       <c r="K178" s="4" t="n">
@@ -16853,7 +16754,7 @@
       <c r="I180" s="4" t="n">
         <v>61.99</v>
       </c>
-      <c r="J180" s="5" t="n">
+      <c r="J180" s="6" t="n">
         <v>0.6</v>
       </c>
       <c r="K180" s="4" t="n">
@@ -17001,7 +16902,7 @@
       <c r="I182" s="4" t="n">
         <v>14.27</v>
       </c>
-      <c r="J182" s="5" t="n">
+      <c r="J182" s="6" t="n">
         <v>0.59</v>
       </c>
       <c r="K182" s="4" t="n">
@@ -17075,7 +16976,7 @@
       <c r="I183" s="4" t="n">
         <v>30.86</v>
       </c>
-      <c r="J183" s="5" t="n">
+      <c r="J183" s="6" t="n">
         <v>8.140000000000001</v>
       </c>
       <c r="K183" s="4" t="n">
@@ -17149,7 +17050,7 @@
       <c r="I184" s="4" t="n">
         <v>35.13</v>
       </c>
-      <c r="J184" s="5" t="n">
+      <c r="J184" s="6" t="n">
         <v>7.87</v>
       </c>
       <c r="K184" s="4" t="n">
@@ -17292,10 +17193,10 @@
         </is>
       </c>
       <c r="H186" s="4" t="n">
-        <v>217.55</v>
+        <v>217.31</v>
       </c>
       <c r="I186" s="4" t="n">
-        <v>209.66</v>
+        <v>209.43</v>
       </c>
       <c r="J186" s="7" t="n">
         <v>-3.63</v>
@@ -17667,7 +17568,7 @@
       <c r="I191" s="4" t="n">
         <v>352.68</v>
       </c>
-      <c r="J191" s="5" t="n">
+      <c r="J191" s="6" t="n">
         <v>5.4</v>
       </c>
       <c r="K191" s="4" t="n">
@@ -18111,7 +18012,7 @@
       <c r="I197" s="4" t="n">
         <v>81.45999999999999</v>
       </c>
-      <c r="J197" s="5" t="n">
+      <c r="J197" s="6" t="n">
         <v>8.92</v>
       </c>
       <c r="K197" s="4" t="n">
@@ -18185,7 +18086,7 @@
       <c r="I198" s="4" t="n">
         <v>131.33</v>
       </c>
-      <c r="J198" s="5" t="n">
+      <c r="J198" s="6" t="n">
         <v>12.28</v>
       </c>
       <c r="K198" s="4" t="n">
@@ -18328,12 +18229,12 @@
         </is>
       </c>
       <c r="H200" s="4" t="n">
-        <v>311.36</v>
+        <v>310.43</v>
       </c>
       <c r="I200" s="4" t="n">
-        <v>334.58</v>
-      </c>
-      <c r="J200" s="5" t="n">
+        <v>333.58</v>
+      </c>
+      <c r="J200" s="6" t="n">
         <v>7.46</v>
       </c>
       <c r="K200" s="4" t="n">
@@ -18407,7 +18308,7 @@
       <c r="I201" s="4" t="n">
         <v>99.47</v>
       </c>
-      <c r="J201" s="5" t="n">
+      <c r="J201" s="6" t="n">
         <v>4.68</v>
       </c>
       <c r="K201" s="4" t="n">
@@ -18555,7 +18456,7 @@
       <c r="I203" s="4" t="n">
         <v>938.4</v>
       </c>
-      <c r="J203" s="5" t="n">
+      <c r="J203" s="6" t="n">
         <v>8.050000000000001</v>
       </c>
       <c r="K203" s="4" t="n">
@@ -18851,7 +18752,7 @@
       <c r="I207" s="4" t="n">
         <v>487.28</v>
       </c>
-      <c r="J207" s="5" t="n">
+      <c r="J207" s="6" t="n">
         <v>4.37</v>
       </c>
       <c r="K207" s="4" t="n">
@@ -18925,7 +18826,7 @@
       <c r="I208" s="4" t="n">
         <v>564.22</v>
       </c>
-      <c r="J208" s="5" t="n">
+      <c r="J208" s="6" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="K208" s="4" t="n">
@@ -19073,7 +18974,7 @@
       <c r="I210" s="4" t="n">
         <v>245.11</v>
       </c>
-      <c r="J210" s="5" t="n">
+      <c r="J210" s="6" t="n">
         <v>15.45</v>
       </c>
       <c r="K210" s="4" t="n">
@@ -19147,7 +19048,7 @@
       <c r="I211" s="4" t="n">
         <v>193.26</v>
       </c>
-      <c r="J211" s="5" t="n">
+      <c r="J211" s="6" t="n">
         <v>1.05</v>
       </c>
       <c r="K211" s="4" t="n">
@@ -19221,7 +19122,7 @@
       <c r="I212" s="4" t="n">
         <v>149.66</v>
       </c>
-      <c r="J212" s="5" t="n">
+      <c r="J212" s="6" t="n">
         <v>147.09</v>
       </c>
       <c r="K212" s="4" t="n">
@@ -19295,7 +19196,7 @@
       <c r="I213" s="4" t="n">
         <v>153.1</v>
       </c>
-      <c r="J213" s="5" t="n">
+      <c r="J213" s="6" t="n">
         <v>17.39</v>
       </c>
       <c r="K213" s="4" t="n">
@@ -19443,7 +19344,7 @@
       <c r="I215" s="4" t="n">
         <v>362.27</v>
       </c>
-      <c r="J215" s="5" t="n">
+      <c r="J215" s="6" t="n">
         <v>7.98</v>
       </c>
       <c r="K215" s="4" t="n">
@@ -19517,7 +19418,7 @@
       <c r="I216" s="4" t="n">
         <v>69.12</v>
       </c>
-      <c r="J216" s="5" t="n">
+      <c r="J216" s="6" t="n">
         <v>6.29</v>
       </c>
       <c r="K216" s="4" t="n">
@@ -19591,7 +19492,7 @@
       <c r="I217" s="4" t="n">
         <v>47.81</v>
       </c>
-      <c r="J217" s="5" t="n">
+      <c r="J217" s="6" t="n">
         <v>5.01</v>
       </c>
       <c r="K217" s="4" t="n">
@@ -19813,7 +19714,7 @@
       <c r="I220" s="4" t="n">
         <v>55.1</v>
       </c>
-      <c r="J220" s="5" t="n">
+      <c r="J220" s="6" t="n">
         <v>4.18</v>
       </c>
       <c r="K220" s="4" t="n">
@@ -20109,7 +20010,7 @@
       <c r="I224" s="4" t="n">
         <v>92.02</v>
       </c>
-      <c r="J224" s="5" t="n">
+      <c r="J224" s="6" t="n">
         <v>1.48</v>
       </c>
       <c r="K224" s="4" t="n">
@@ -20183,7 +20084,7 @@
       <c r="I225" s="4" t="n">
         <v>63.01</v>
       </c>
-      <c r="J225" s="5" t="n">
+      <c r="J225" s="6" t="n">
         <v>1.99</v>
       </c>
       <c r="K225" s="4" t="n">
@@ -20257,7 +20158,7 @@
       <c r="I226" s="4" t="n">
         <v>514.55</v>
       </c>
-      <c r="J226" s="5" t="n">
+      <c r="J226" s="6" t="n">
         <v>8.220000000000001</v>
       </c>
       <c r="K226" s="4" t="n">
@@ -20479,7 +20380,7 @@
       <c r="I229" s="4" t="n">
         <v>358.67</v>
       </c>
-      <c r="J229" s="5" t="n">
+      <c r="J229" s="6" t="n">
         <v>2.84</v>
       </c>
       <c r="K229" s="4" t="n">
@@ -20627,7 +20528,7 @@
       <c r="I231" s="4" t="n">
         <v>598.47</v>
       </c>
-      <c r="J231" s="5" t="n">
+      <c r="J231" s="6" t="n">
         <v>6.6</v>
       </c>
       <c r="K231" s="4" t="n">
@@ -20849,7 +20750,7 @@
       <c r="I234" s="4" t="n">
         <v>46.23</v>
       </c>
-      <c r="J234" s="5" t="n">
+      <c r="J234" s="6" t="n">
         <v>1.12</v>
       </c>
       <c r="K234" s="4" t="n">
@@ -21071,7 +20972,7 @@
       <c r="I237" s="4" t="n">
         <v>312.88</v>
       </c>
-      <c r="J237" s="5" t="n">
+      <c r="J237" s="6" t="n">
         <v>0.47</v>
       </c>
       <c r="K237" s="4" t="n">
@@ -21219,7 +21120,7 @@
       <c r="I239" s="4" t="n">
         <v>68.92</v>
       </c>
-      <c r="J239" s="5" t="n">
+      <c r="J239" s="6" t="n">
         <v>0.5</v>
       </c>
       <c r="K239" s="4" t="n">
@@ -21441,7 +21342,7 @@
       <c r="I242" s="4" t="n">
         <v>939.03</v>
       </c>
-      <c r="J242" s="5" t="n">
+      <c r="J242" s="6" t="n">
         <v>14.43</v>
       </c>
       <c r="K242" s="4" t="n">
@@ -21737,7 +21638,7 @@
       <c r="I246" s="4" t="n">
         <v>335</v>
       </c>
-      <c r="J246" s="5" t="n">
+      <c r="J246" s="6" t="n">
         <v>4.13</v>
       </c>
       <c r="K246" s="4" t="n">
@@ -21811,7 +21712,7 @@
       <c r="I247" s="4" t="n">
         <v>335</v>
       </c>
-      <c r="J247" s="5" t="n">
+      <c r="J247" s="6" t="n">
         <v>4.13</v>
       </c>
       <c r="K247" s="4" t="n">
@@ -22107,7 +22008,7 @@
       <c r="I251" s="4" t="n">
         <v>19.22</v>
       </c>
-      <c r="J251" s="5" t="n">
+      <c r="J251" s="6" t="n">
         <v>2.02</v>
       </c>
       <c r="K251" s="4" t="n">
@@ -22181,7 +22082,7 @@
       <c r="I252" s="4" t="n">
         <v>58.51</v>
       </c>
-      <c r="J252" s="5" t="n">
+      <c r="J252" s="6" t="n">
         <v>4.73</v>
       </c>
       <c r="K252" s="4" t="n">
@@ -22255,7 +22156,7 @@
       <c r="I253" s="4" t="n">
         <v>90.08</v>
       </c>
-      <c r="J253" s="5" t="n">
+      <c r="J253" s="6" t="n">
         <v>3.7</v>
       </c>
       <c r="K253" s="4" t="n">
@@ -22329,7 +22230,7 @@
       <c r="I254" s="4" t="n">
         <v>32.02</v>
       </c>
-      <c r="J254" s="5" t="n">
+      <c r="J254" s="6" t="n">
         <v>1.72</v>
       </c>
       <c r="K254" s="4" t="n">
@@ -22403,7 +22304,7 @@
       <c r="I255" s="4" t="n">
         <v>109.03</v>
       </c>
-      <c r="J255" s="5" t="n">
+      <c r="J255" s="6" t="n">
         <v>1.63</v>
       </c>
       <c r="K255" s="4" t="n">
@@ -22625,7 +22526,7 @@
       <c r="I258" s="4" t="n">
         <v>23.75</v>
       </c>
-      <c r="J258" s="5" t="n">
+      <c r="J258" s="6" t="n">
         <v>0.25</v>
       </c>
       <c r="K258" s="4" t="n">
@@ -22699,7 +22600,7 @@
       <c r="I259" s="4" t="n">
         <v>24.4</v>
       </c>
-      <c r="J259" s="5" t="n">
+      <c r="J259" s="6" t="n">
         <v>0.57</v>
       </c>
       <c r="K259" s="4" t="n">
@@ -22921,7 +22822,7 @@
       <c r="I262" s="4" t="n">
         <v>32.21</v>
       </c>
-      <c r="J262" s="5" t="n">
+      <c r="J262" s="6" t="n">
         <v>10.38</v>
       </c>
       <c r="K262" s="4" t="n">
@@ -23069,7 +22970,7 @@
       <c r="I264" s="4" t="n">
         <v>270</v>
       </c>
-      <c r="J264" s="5" t="n">
+      <c r="J264" s="6" t="n">
         <v>4.44</v>
       </c>
       <c r="K264" s="4" t="n">
@@ -23143,7 +23044,7 @@
       <c r="I265" s="4" t="n">
         <v>171.77</v>
       </c>
-      <c r="J265" s="5" t="n">
+      <c r="J265" s="6" t="n">
         <v>12.21</v>
       </c>
       <c r="K265" s="4" t="n">
@@ -23439,7 +23340,7 @@
       <c r="I269" s="4" t="n">
         <v>151.52</v>
       </c>
-      <c r="J269" s="5" t="n">
+      <c r="J269" s="6" t="n">
         <v>2.89</v>
       </c>
       <c r="K269" s="4" t="n">
@@ -23513,7 +23414,7 @@
       <c r="I270" s="4" t="n">
         <v>32.98</v>
       </c>
-      <c r="J270" s="5" t="n">
+      <c r="J270" s="6" t="n">
         <v>5.87</v>
       </c>
       <c r="K270" s="4" t="n">
@@ -23957,7 +23858,7 @@
       <c r="I276" s="4" t="n">
         <v>261.51</v>
       </c>
-      <c r="J276" s="5" t="n">
+      <c r="J276" s="6" t="n">
         <v>7.25</v>
       </c>
       <c r="K276" s="4" t="n">
@@ -24031,7 +23932,7 @@
       <c r="I277" s="4" t="n">
         <v>41.39</v>
       </c>
-      <c r="J277" s="5" t="n">
+      <c r="J277" s="6" t="n">
         <v>0.15</v>
       </c>
       <c r="K277" s="4" t="n">
@@ -24105,7 +24006,7 @@
       <c r="I278" s="4" t="n">
         <v>29.89</v>
       </c>
-      <c r="J278" s="5" t="n">
+      <c r="J278" s="6" t="n">
         <v>0.34</v>
       </c>
       <c r="K278" s="4" t="n">
@@ -24179,7 +24080,7 @@
       <c r="I279" s="4" t="n">
         <v>345.88</v>
       </c>
-      <c r="J279" s="5" t="n">
+      <c r="J279" s="6" t="n">
         <v>2.81</v>
       </c>
       <c r="K279" s="4" t="n">
@@ -24253,7 +24154,7 @@
       <c r="I280" s="4" t="n">
         <v>128.12</v>
       </c>
-      <c r="J280" s="5" t="n">
+      <c r="J280" s="6" t="n">
         <v>5.82</v>
       </c>
       <c r="K280" s="4" t="n">
@@ -24327,7 +24228,7 @@
       <c r="I281" s="4" t="n">
         <v>87.12</v>
       </c>
-      <c r="J281" s="5" t="n">
+      <c r="J281" s="6" t="n">
         <v>2.49</v>
       </c>
       <c r="K281" s="4" t="n">
@@ -24549,7 +24450,7 @@
       <c r="I284" s="4" t="n">
         <v>161.92</v>
       </c>
-      <c r="J284" s="5" t="n">
+      <c r="J284" s="6" t="n">
         <v>7.05</v>
       </c>
       <c r="K284" s="4" t="n">
@@ -24697,7 +24598,7 @@
       <c r="I286" s="4" t="n">
         <v>96.93000000000001</v>
       </c>
-      <c r="J286" s="5" t="n">
+      <c r="J286" s="6" t="n">
         <v>8.06</v>
       </c>
       <c r="K286" s="4" t="n">
@@ -24845,7 +24746,7 @@
       <c r="I288" s="4" t="n">
         <v>391.06</v>
       </c>
-      <c r="J288" s="5" t="n">
+      <c r="J288" s="6" t="n">
         <v>4.89</v>
       </c>
       <c r="K288" s="4" t="n">
@@ -24993,7 +24894,7 @@
       <c r="I290" s="4" t="n">
         <v>185.35</v>
       </c>
-      <c r="J290" s="5" t="n">
+      <c r="J290" s="6" t="n">
         <v>2.65</v>
       </c>
       <c r="K290" s="4" t="n">
@@ -25067,7 +24968,7 @@
       <c r="I291" s="4" t="n">
         <v>22.43</v>
       </c>
-      <c r="J291" s="5" t="n">
+      <c r="J291" s="6" t="n">
         <v>0.63</v>
       </c>
       <c r="K291" s="4" t="n">
@@ -25141,7 +25042,7 @@
       <c r="I292" s="4" t="n">
         <v>90.38</v>
       </c>
-      <c r="J292" s="5" t="n">
+      <c r="J292" s="6" t="n">
         <v>1.35</v>
       </c>
       <c r="K292" s="4" t="n">
@@ -25289,7 +25190,7 @@
       <c r="I294" s="4" t="n">
         <v>30.23</v>
       </c>
-      <c r="J294" s="5" t="n">
+      <c r="J294" s="6" t="n">
         <v>4.99</v>
       </c>
       <c r="K294" s="4" t="n">
@@ -25363,7 +25264,7 @@
       <c r="I295" s="4" t="n">
         <v>55.23</v>
       </c>
-      <c r="J295" s="5" t="n">
+      <c r="J295" s="6" t="n">
         <v>1.56</v>
       </c>
       <c r="K295" s="4" t="n">
@@ -25437,7 +25338,7 @@
       <c r="I296" s="4" t="n">
         <v>108.54</v>
       </c>
-      <c r="J296" s="5" t="n">
+      <c r="J296" s="6" t="n">
         <v>15</v>
       </c>
       <c r="K296" s="4" t="n">
@@ -25585,7 +25486,7 @@
       <c r="I298" s="4" t="n">
         <v>332.56</v>
       </c>
-      <c r="J298" s="5" t="n">
+      <c r="J298" s="6" t="n">
         <v>5.74</v>
       </c>
       <c r="K298" s="4" t="n">
@@ -25733,7 +25634,7 @@
       <c r="I300" s="4" t="n">
         <v>139.25</v>
       </c>
-      <c r="J300" s="5" t="n">
+      <c r="J300" s="6" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="K300" s="4" t="n">
@@ -25807,7 +25708,7 @@
       <c r="I301" s="4" t="n">
         <v>427.16</v>
       </c>
-      <c r="J301" s="5" t="n">
+      <c r="J301" s="6" t="n">
         <v>3.82</v>
       </c>
       <c r="K301" s="4" t="n">
@@ -26029,7 +25930,7 @@
       <c r="I304" s="4" t="n">
         <v>34.28</v>
       </c>
-      <c r="J304" s="5" t="n">
+      <c r="J304" s="6" t="n">
         <v>1.89</v>
       </c>
       <c r="K304" s="4" t="n">
@@ -26103,7 +26004,7 @@
       <c r="I305" s="4" t="n">
         <v>1335.39</v>
       </c>
-      <c r="J305" s="5" t="n">
+      <c r="J305" s="6" t="n">
         <v>2.57</v>
       </c>
       <c r="K305" s="4" t="n">
@@ -26177,7 +26078,7 @@
       <c r="I306" s="4" t="n">
         <v>1035.39</v>
       </c>
-      <c r="J306" s="5" t="n">
+      <c r="J306" s="6" t="n">
         <v>0.58</v>
       </c>
       <c r="K306" s="4" t="n">
@@ -26325,7 +26226,7 @@
       <c r="I308" s="4" t="n">
         <v>92.95999999999999</v>
       </c>
-      <c r="J308" s="5" t="n">
+      <c r="J308" s="6" t="n">
         <v>8.27</v>
       </c>
       <c r="K308" s="4" t="n">
@@ -26399,7 +26300,7 @@
       <c r="I309" s="4" t="n">
         <v>138.41</v>
       </c>
-      <c r="J309" s="5" t="n">
+      <c r="J309" s="6" t="n">
         <v>3.26</v>
       </c>
       <c r="K309" s="4" t="n">
@@ -26843,7 +26744,7 @@
       <c r="I315" s="4" t="n">
         <v>40.08</v>
       </c>
-      <c r="J315" s="5" t="n">
+      <c r="J315" s="6" t="n">
         <v>5.67</v>
       </c>
       <c r="K315" s="4" t="n">
@@ -26917,7 +26818,7 @@
       <c r="I316" s="4" t="n">
         <v>148.09</v>
       </c>
-      <c r="J316" s="5" t="n">
+      <c r="J316" s="6" t="n">
         <v>9.07</v>
       </c>
       <c r="K316" s="4" t="n">
@@ -27065,7 +26966,7 @@
       <c r="I318" s="4" t="n">
         <v>29.64</v>
       </c>
-      <c r="J318" s="5" t="n">
+      <c r="J318" s="6" t="n">
         <v>2.62</v>
       </c>
       <c r="K318" s="4" t="n">
@@ -27139,7 +27040,7 @@
       <c r="I319" s="4" t="n">
         <v>73.31</v>
       </c>
-      <c r="J319" s="5" t="n">
+      <c r="J319" s="6" t="n">
         <v>0.77</v>
       </c>
       <c r="K319" s="4" t="n">
@@ -27287,7 +27188,7 @@
       <c r="I321" s="4" t="n">
         <v>95.54000000000001</v>
       </c>
-      <c r="J321" s="5" t="n">
+      <c r="J321" s="6" t="n">
         <v>5.29</v>
       </c>
       <c r="K321" s="4" t="n">
@@ -27657,7 +27558,7 @@
       <c r="I326" s="4" t="n">
         <v>117.58</v>
       </c>
-      <c r="J326" s="5" t="n">
+      <c r="J326" s="6" t="n">
         <v>0.72</v>
       </c>
       <c r="K326" s="4" t="n">
@@ -27731,7 +27632,7 @@
       <c r="I327" s="4" t="n">
         <v>69.29000000000001</v>
       </c>
-      <c r="J327" s="5" t="n">
+      <c r="J327" s="6" t="n">
         <v>12.01</v>
       </c>
       <c r="K327" s="4" t="n">
@@ -27805,7 +27706,7 @@
       <c r="I328" s="4" t="n">
         <v>69.29000000000001</v>
       </c>
-      <c r="J328" s="5" t="n">
+      <c r="J328" s="6" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="K328" s="4" t="n">
@@ -28249,7 +28150,7 @@
       <c r="I334" s="4" t="n">
         <v>1133.7</v>
       </c>
-      <c r="J334" s="5" t="n">
+      <c r="J334" s="6" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="K334" s="4" t="n">
@@ -28471,7 +28372,7 @@
       <c r="I337" s="4" t="n">
         <v>335.99</v>
       </c>
-      <c r="J337" s="5" t="n">
+      <c r="J337" s="6" t="n">
         <v>4.21</v>
       </c>
       <c r="K337" s="4" t="n">
@@ -28545,7 +28446,7 @@
       <c r="I338" s="4" t="n">
         <v>294.34</v>
       </c>
-      <c r="J338" s="5" t="n">
+      <c r="J338" s="6" t="n">
         <v>4.42</v>
       </c>
       <c r="K338" s="4" t="n">
@@ -28619,7 +28520,7 @@
       <c r="I339" s="4" t="n">
         <v>79</v>
       </c>
-      <c r="J339" s="5" t="n">
+      <c r="J339" s="6" t="n">
         <v>14.71</v>
       </c>
       <c r="K339" s="4" t="n">
@@ -28989,7 +28890,7 @@
       <c r="I344" s="4" t="n">
         <v>332.96</v>
       </c>
-      <c r="J344" s="5" t="n">
+      <c r="J344" s="6" t="n">
         <v>3.85</v>
       </c>
       <c r="K344" s="4" t="n">
@@ -29063,7 +28964,7 @@
       <c r="I345" s="4" t="n">
         <v>190.18</v>
       </c>
-      <c r="J345" s="5" t="n">
+      <c r="J345" s="6" t="n">
         <v>7.32</v>
       </c>
       <c r="K345" s="4" t="n">
@@ -29359,7 +29260,7 @@
       <c r="I349" s="4" t="n">
         <v>82.23</v>
       </c>
-      <c r="J349" s="5" t="n">
+      <c r="J349" s="6" t="n">
         <v>1.08</v>
       </c>
       <c r="K349" s="4" t="n">
@@ -29433,7 +29334,7 @@
       <c r="I350" s="4" t="n">
         <v>107.23</v>
       </c>
-      <c r="J350" s="5" t="n">
+      <c r="J350" s="6" t="n">
         <v>1.22</v>
       </c>
       <c r="K350" s="4" t="n">
@@ -29581,7 +29482,7 @@
       <c r="I352" s="4" t="n">
         <v>288.17</v>
       </c>
-      <c r="J352" s="5" t="n">
+      <c r="J352" s="6" t="n">
         <v>2.02</v>
       </c>
       <c r="K352" s="4" t="n">
@@ -29655,7 +29556,7 @@
       <c r="I353" s="4" t="n">
         <v>257.27</v>
       </c>
-      <c r="J353" s="5" t="n">
+      <c r="J353" s="6" t="n">
         <v>0.25</v>
       </c>
       <c r="K353" s="4" t="n">
@@ -29729,7 +29630,7 @@
       <c r="I354" s="4" t="n">
         <v>54.79</v>
       </c>
-      <c r="J354" s="5" t="n">
+      <c r="J354" s="6" t="n">
         <v>0.77</v>
       </c>
       <c r="K354" s="4" t="n">
@@ -29877,7 +29778,7 @@
       <c r="I356" s="4" t="n">
         <v>1079.61</v>
       </c>
-      <c r="J356" s="5" t="n">
+      <c r="J356" s="6" t="n">
         <v>5.07</v>
       </c>
       <c r="K356" s="4" t="n">
@@ -29951,7 +29852,7 @@
       <c r="I357" s="4" t="n">
         <v>144.84</v>
       </c>
-      <c r="J357" s="5" t="n">
+      <c r="J357" s="6" t="n">
         <v>1</v>
       </c>
       <c r="K357" s="4" t="n">
@@ -30168,12 +30069,12 @@
         </is>
       </c>
       <c r="H360" s="4" t="n">
-        <v>390.37</v>
+        <v>388.68</v>
       </c>
       <c r="I360" s="4" t="n">
-        <v>402.54</v>
-      </c>
-      <c r="J360" s="5" t="n">
+        <v>400.8</v>
+      </c>
+      <c r="J360" s="6" t="n">
         <v>3.12</v>
       </c>
       <c r="K360" s="4" t="n">
@@ -30247,7 +30148,7 @@
       <c r="I361" s="4" t="n">
         <v>104.7</v>
       </c>
-      <c r="J361" s="5" t="n">
+      <c r="J361" s="6" t="n">
         <v>19.69</v>
       </c>
       <c r="K361" s="4" t="n">
@@ -30321,7 +30222,7 @@
       <c r="I362" s="4" t="n">
         <v>377.73</v>
       </c>
-      <c r="J362" s="5" t="n">
+      <c r="J362" s="6" t="n">
         <v>3.85</v>
       </c>
       <c r="K362" s="4" t="n">
@@ -30395,7 +30296,7 @@
       <c r="I363" s="4" t="n">
         <v>190.01</v>
       </c>
-      <c r="J363" s="5" t="n">
+      <c r="J363" s="6" t="n">
         <v>4.73</v>
       </c>
       <c r="K363" s="4" t="n">
@@ -30469,7 +30370,7 @@
       <c r="I364" s="4" t="n">
         <v>108.05</v>
       </c>
-      <c r="J364" s="5" t="n">
+      <c r="J364" s="6" t="n">
         <v>1.34</v>
       </c>
       <c r="K364" s="4" t="n">
@@ -30543,7 +30444,7 @@
       <c r="I365" s="4" t="n">
         <v>290.6</v>
       </c>
-      <c r="J365" s="5" t="n">
+      <c r="J365" s="6" t="n">
         <v>2.1</v>
       </c>
       <c r="K365" s="4" t="n">
@@ -30765,7 +30666,7 @@
       <c r="I368" s="4" t="n">
         <v>46.83</v>
       </c>
-      <c r="J368" s="5" t="n">
+      <c r="J368" s="6" t="n">
         <v>3.15</v>
       </c>
       <c r="K368" s="4" t="n">
@@ -30839,7 +30740,7 @@
       <c r="I369" s="4" t="n">
         <v>180.05</v>
       </c>
-      <c r="J369" s="5" t="n">
+      <c r="J369" s="6" t="n">
         <v>0.96</v>
       </c>
       <c r="K369" s="4" t="n">
@@ -30987,7 +30888,7 @@
       <c r="I371" s="4" t="n">
         <v>137.71</v>
       </c>
-      <c r="J371" s="5" t="n">
+      <c r="J371" s="6" t="n">
         <v>0.05</v>
       </c>
       <c r="K371" s="4" t="n">
@@ -31357,7 +31258,7 @@
       <c r="I376" s="4" t="n">
         <v>21.58</v>
       </c>
-      <c r="J376" s="5" t="n">
+      <c r="J376" s="6" t="n">
         <v>5.74</v>
       </c>
       <c r="K376" s="4" t="n">
@@ -31431,7 +31332,7 @@
       <c r="I377" s="4" t="n">
         <v>132.18</v>
       </c>
-      <c r="J377" s="5" t="n">
+      <c r="J377" s="6" t="n">
         <v>3.22</v>
       </c>
       <c r="K377" s="4" t="n">
@@ -31505,7 +31406,7 @@
       <c r="I378" s="4" t="n">
         <v>193.43</v>
       </c>
-      <c r="J378" s="5" t="n">
+      <c r="J378" s="6" t="n">
         <v>1.37</v>
       </c>
       <c r="K378" s="4" t="n">
@@ -31579,7 +31480,7 @@
       <c r="I379" s="4" t="n">
         <v>215.36</v>
       </c>
-      <c r="J379" s="5" t="n">
+      <c r="J379" s="6" t="n">
         <v>3.82</v>
       </c>
       <c r="K379" s="4" t="n">
@@ -31727,7 +31628,7 @@
       <c r="I381" s="4" t="n">
         <v>245</v>
       </c>
-      <c r="J381" s="5" t="n">
+      <c r="J381" s="6" t="n">
         <v>3.16</v>
       </c>
       <c r="K381" s="4" t="n">
@@ -31801,7 +31702,7 @@
       <c r="I382" s="4" t="n">
         <v>245</v>
       </c>
-      <c r="J382" s="5" t="n">
+      <c r="J382" s="6" t="n">
         <v>3.16</v>
       </c>
       <c r="K382" s="4" t="n">
@@ -31875,7 +31776,7 @@
       <c r="I383" s="4" t="n">
         <v>122.78</v>
       </c>
-      <c r="J383" s="5" t="n">
+      <c r="J383" s="6" t="n">
         <v>2.26</v>
       </c>
       <c r="K383" s="4" t="n">
@@ -31949,7 +31850,7 @@
       <c r="I384" s="4" t="n">
         <v>463.82</v>
       </c>
-      <c r="J384" s="5" t="n">
+      <c r="J384" s="6" t="n">
         <v>5.18</v>
       </c>
       <c r="K384" s="4" t="n">
@@ -32097,7 +31998,7 @@
       <c r="I386" s="4" t="n">
         <v>634.54</v>
       </c>
-      <c r="J386" s="5" t="n">
+      <c r="J386" s="6" t="n">
         <v>2.68</v>
       </c>
       <c r="K386" s="4" t="n">
@@ -32319,7 +32220,7 @@
       <c r="I389" s="4" t="n">
         <v>236.93</v>
       </c>
-      <c r="J389" s="5" t="n">
+      <c r="J389" s="6" t="n">
         <v>11.76</v>
       </c>
       <c r="K389" s="4" t="n">
@@ -32467,7 +32368,7 @@
       <c r="I391" s="4" t="n">
         <v>200.21</v>
       </c>
-      <c r="J391" s="5" t="n">
+      <c r="J391" s="6" t="n">
         <v>2.69</v>
       </c>
       <c r="K391" s="4" t="n">
@@ -32541,7 +32442,7 @@
       <c r="I392" s="4" t="n">
         <v>94.31999999999999</v>
       </c>
-      <c r="J392" s="5" t="n">
+      <c r="J392" s="6" t="n">
         <v>0.88</v>
       </c>
       <c r="K392" s="4" t="n">
@@ -32615,7 +32516,7 @@
       <c r="I393" s="4" t="n">
         <v>73.95</v>
       </c>
-      <c r="J393" s="5" t="n">
+      <c r="J393" s="6" t="n">
         <v>2.71</v>
       </c>
       <c r="K393" s="4" t="n">
@@ -32689,7 +32590,7 @@
       <c r="I394" s="4" t="n">
         <v>82.7</v>
       </c>
-      <c r="J394" s="5" t="n">
+      <c r="J394" s="6" t="n">
         <v>8.74</v>
       </c>
       <c r="K394" s="4" t="n">
@@ -32763,7 +32664,7 @@
       <c r="I395" s="4" t="n">
         <v>62.09</v>
       </c>
-      <c r="J395" s="5" t="n">
+      <c r="J395" s="6" t="n">
         <v>6.58</v>
       </c>
       <c r="K395" s="4" t="n">
@@ -32837,7 +32738,7 @@
       <c r="I396" s="4" t="n">
         <v>205.78</v>
       </c>
-      <c r="J396" s="5" t="n">
+      <c r="J396" s="6" t="n">
         <v>0.5</v>
       </c>
       <c r="K396" s="4" t="n">
@@ -32911,7 +32812,7 @@
       <c r="I397" s="4" t="n">
         <v>51.62</v>
       </c>
-      <c r="J397" s="5" t="n">
+      <c r="J397" s="6" t="n">
         <v>3.64</v>
       </c>
       <c r="K397" s="4" t="n">
@@ -32985,7 +32886,7 @@
       <c r="I398" s="4" t="n">
         <v>25.61</v>
       </c>
-      <c r="J398" s="5" t="n">
+      <c r="J398" s="6" t="n">
         <v>1.91</v>
       </c>
       <c r="K398" s="4" t="n">
@@ -33059,7 +32960,7 @@
       <c r="I399" s="4" t="n">
         <v>32.14</v>
       </c>
-      <c r="J399" s="5" t="n">
+      <c r="J399" s="6" t="n">
         <v>3.28</v>
       </c>
       <c r="K399" s="4" t="n">
@@ -33281,7 +33182,7 @@
       <c r="I402" s="4" t="n">
         <v>295.1</v>
       </c>
-      <c r="J402" s="5" t="n">
+      <c r="J402" s="6" t="n">
         <v>4.65</v>
       </c>
       <c r="K402" s="4" t="n">
@@ -33429,7 +33330,7 @@
       <c r="I404" s="4" t="n">
         <v>32.67</v>
       </c>
-      <c r="J404" s="5" t="n">
+      <c r="J404" s="6" t="n">
         <v>11.12</v>
       </c>
       <c r="K404" s="4" t="n">
@@ -33503,7 +33404,7 @@
       <c r="I405" s="4" t="n">
         <v>406.93</v>
       </c>
-      <c r="J405" s="5" t="n">
+      <c r="J405" s="6" t="n">
         <v>0.19</v>
       </c>
       <c r="K405" s="4" t="n">
@@ -33577,7 +33478,7 @@
       <c r="I406" s="4" t="n">
         <v>406.93</v>
       </c>
-      <c r="J406" s="5" t="n">
+      <c r="J406" s="6" t="n">
         <v>0.19</v>
       </c>
       <c r="K406" s="4" t="n">
@@ -33651,7 +33552,7 @@
       <c r="I407" s="4" t="n">
         <v>956.12</v>
       </c>
-      <c r="J407" s="5" t="n">
+      <c r="J407" s="6" t="n">
         <v>1.25</v>
       </c>
       <c r="K407" s="4" t="n">
@@ -33799,7 +33700,7 @@
       <c r="I409" s="4" t="n">
         <v>130.61</v>
       </c>
-      <c r="J409" s="5" t="n">
+      <c r="J409" s="6" t="n">
         <v>4.42</v>
       </c>
       <c r="K409" s="4" t="n">
@@ -33947,7 +33848,7 @@
       <c r="I411" s="4" t="n">
         <v>181.78</v>
       </c>
-      <c r="J411" s="5" t="n">
+      <c r="J411" s="6" t="n">
         <v>22.34</v>
       </c>
       <c r="K411" s="4" t="n">
@@ -34243,7 +34144,7 @@
       <c r="I415" s="4" t="n">
         <v>65.47</v>
       </c>
-      <c r="J415" s="5" t="n">
+      <c r="J415" s="6" t="n">
         <v>0.91</v>
       </c>
       <c r="K415" s="4" t="n">
@@ -34465,7 +34366,7 @@
       <c r="I418" s="4" t="n">
         <v>37.34</v>
       </c>
-      <c r="J418" s="5" t="n">
+      <c r="J418" s="6" t="n">
         <v>16.69</v>
       </c>
       <c r="K418" s="4" t="n">
@@ -34539,7 +34440,7 @@
       <c r="I419" s="4" t="n">
         <v>279.67</v>
       </c>
-      <c r="J419" s="5" t="n">
+      <c r="J419" s="6" t="n">
         <v>8.35</v>
       </c>
       <c r="K419" s="4" t="n">
@@ -34613,7 +34514,7 @@
       <c r="I420" s="4" t="n">
         <v>27.2</v>
       </c>
-      <c r="J420" s="5" t="n">
+      <c r="J420" s="6" t="n">
         <v>6.04</v>
       </c>
       <c r="K420" s="4" t="n">
@@ -34835,7 +34736,7 @@
       <c r="I423" s="4" t="n">
         <v>404.03</v>
       </c>
-      <c r="J423" s="5" t="n">
+      <c r="J423" s="6" t="n">
         <v>4.26</v>
       </c>
       <c r="K423" s="4" t="n">
@@ -34909,7 +34810,7 @@
       <c r="I424" s="4" t="n">
         <v>279.32</v>
       </c>
-      <c r="J424" s="5" t="n">
+      <c r="J424" s="6" t="n">
         <v>2.56</v>
       </c>
       <c r="K424" s="4" t="n">
@@ -35057,7 +34958,7 @@
       <c r="I426" s="4" t="n">
         <v>151.08</v>
       </c>
-      <c r="J426" s="5" t="n">
+      <c r="J426" s="6" t="n">
         <v>4.57</v>
       </c>
       <c r="K426" s="4" t="n">
@@ -35131,7 +35032,7 @@
       <c r="I427" s="4" t="n">
         <v>102.86</v>
       </c>
-      <c r="J427" s="5" t="n">
+      <c r="J427" s="6" t="n">
         <v>0.38</v>
       </c>
       <c r="K427" s="4" t="n">
@@ -35279,7 +35180,7 @@
       <c r="I429" s="4" t="n">
         <v>125.7</v>
       </c>
-      <c r="J429" s="5" t="n">
+      <c r="J429" s="6" t="n">
         <v>4.01</v>
       </c>
       <c r="K429" s="4" t="n">
@@ -35353,7 +35254,7 @@
       <c r="I430" s="4" t="n">
         <v>279.52</v>
       </c>
-      <c r="J430" s="5" t="n">
+      <c r="J430" s="6" t="n">
         <v>0.57</v>
       </c>
       <c r="K430" s="4" t="n">
@@ -35427,7 +35328,7 @@
       <c r="I431" s="4" t="n">
         <v>141.46</v>
       </c>
-      <c r="J431" s="5" t="n">
+      <c r="J431" s="6" t="n">
         <v>5</v>
       </c>
       <c r="K431" s="4" t="n">
@@ -35501,7 +35402,7 @@
       <c r="I432" s="4" t="n">
         <v>334.68</v>
       </c>
-      <c r="J432" s="5" t="n">
+      <c r="J432" s="6" t="n">
         <v>2.18</v>
       </c>
       <c r="K432" s="4" t="n">
@@ -35649,7 +35550,7 @@
       <c r="I434" s="4" t="n">
         <v>75.54000000000001</v>
       </c>
-      <c r="J434" s="5" t="n">
+      <c r="J434" s="6" t="n">
         <v>2.58</v>
       </c>
       <c r="K434" s="4" t="n">
@@ -35723,7 +35624,7 @@
       <c r="I435" s="4" t="n">
         <v>150.36</v>
       </c>
-      <c r="J435" s="5" t="n">
+      <c r="J435" s="6" t="n">
         <v>1.97</v>
       </c>
       <c r="K435" s="4" t="n">
@@ -35797,7 +35698,7 @@
       <c r="I436" s="4" t="n">
         <v>311.33</v>
       </c>
-      <c r="J436" s="5" t="n">
+      <c r="J436" s="6" t="n">
         <v>10.42</v>
       </c>
       <c r="K436" s="4" t="n">
@@ -36241,7 +36142,7 @@
       <c r="I442" s="4" t="n">
         <v>70.3</v>
       </c>
-      <c r="J442" s="5" t="n">
+      <c r="J442" s="6" t="n">
         <v>4.16</v>
       </c>
       <c r="K442" s="4" t="n">
@@ -36463,7 +36364,7 @@
       <c r="I445" s="4" t="n">
         <v>72.78</v>
       </c>
-      <c r="J445" s="5" t="n">
+      <c r="J445" s="6" t="n">
         <v>2.11</v>
       </c>
       <c r="K445" s="4" t="n">
@@ -36537,7 +36438,7 @@
       <c r="I446" s="4" t="n">
         <v>180.49</v>
       </c>
-      <c r="J446" s="5" t="n">
+      <c r="J446" s="6" t="n">
         <v>6.37</v>
       </c>
       <c r="K446" s="4" t="n">
@@ -36685,7 +36586,7 @@
       <c r="I448" s="4" t="n">
         <v>163.08</v>
       </c>
-      <c r="J448" s="5" t="n">
+      <c r="J448" s="6" t="n">
         <v>1.72</v>
       </c>
       <c r="K448" s="4" t="n">
@@ -36759,7 +36660,7 @@
       <c r="I449" s="4" t="n">
         <v>1167.22</v>
       </c>
-      <c r="J449" s="5" t="n">
+      <c r="J449" s="6" t="n">
         <v>2.12</v>
       </c>
       <c r="K449" s="4" t="n">
@@ -36981,7 +36882,7 @@
       <c r="I452" s="4" t="n">
         <v>221.07</v>
       </c>
-      <c r="J452" s="5" t="n">
+      <c r="J452" s="6" t="n">
         <v>8.43</v>
       </c>
       <c r="K452" s="4" t="n">
@@ -37055,7 +36956,7 @@
       <c r="I453" s="4" t="n">
         <v>113.25</v>
       </c>
-      <c r="J453" s="5" t="n">
+      <c r="J453" s="6" t="n">
         <v>2.12</v>
       </c>
       <c r="K453" s="4" t="n">
@@ -37129,7 +37030,7 @@
       <c r="I454" s="4" t="n">
         <v>35.01</v>
       </c>
-      <c r="J454" s="5" t="n">
+      <c r="J454" s="6" t="n">
         <v>4.95</v>
       </c>
       <c r="K454" s="4" t="n">
@@ -37203,7 +37104,7 @@
       <c r="I455" s="4" t="n">
         <v>189.09</v>
       </c>
-      <c r="J455" s="5" t="n">
+      <c r="J455" s="6" t="n">
         <v>4.85</v>
       </c>
       <c r="K455" s="4" t="n">
@@ -37277,7 +37178,7 @@
       <c r="I456" s="4" t="n">
         <v>189.09</v>
       </c>
-      <c r="J456" s="5" t="n">
+      <c r="J456" s="6" t="n">
         <v>4.85</v>
       </c>
       <c r="K456" s="4" t="n">
@@ -37351,7 +37252,7 @@
       <c r="I457" s="4" t="n">
         <v>87.44</v>
       </c>
-      <c r="J457" s="5" t="n">
+      <c r="J457" s="6" t="n">
         <v>5</v>
       </c>
       <c r="K457" s="4" t="n">
@@ -37499,7 +37400,7 @@
       <c r="I459" s="4" t="n">
         <v>63.85</v>
       </c>
-      <c r="J459" s="5" t="n">
+      <c r="J459" s="6" t="n">
         <v>1.83</v>
       </c>
       <c r="K459" s="4" t="n">
@@ -37869,7 +37770,7 @@
       <c r="I464" s="4" t="n">
         <v>137.49</v>
       </c>
-      <c r="J464" s="5" t="n">
+      <c r="J464" s="6" t="n">
         <v>1.05</v>
       </c>
       <c r="K464" s="4" t="n">
@@ -37943,7 +37844,7 @@
       <c r="I465" s="4" t="n">
         <v>181.28</v>
       </c>
-      <c r="J465" s="5" t="n">
+      <c r="J465" s="6" t="n">
         <v>1.45</v>
       </c>
       <c r="K465" s="4" t="n">
@@ -38091,7 +37992,7 @@
       <c r="I467" s="4" t="n">
         <v>68.14</v>
       </c>
-      <c r="J467" s="5" t="n">
+      <c r="J467" s="6" t="n">
         <v>4.71</v>
       </c>
       <c r="K467" s="4" t="n">
@@ -38165,7 +38066,7 @@
       <c r="I468" s="4" t="n">
         <v>169.46</v>
       </c>
-      <c r="J468" s="5" t="n">
+      <c r="J468" s="6" t="n">
         <v>0.75</v>
       </c>
       <c r="K468" s="4" t="n">
@@ -38313,7 +38214,7 @@
       <c r="I470" s="4" t="n">
         <v>52.97</v>
       </c>
-      <c r="J470" s="5" t="n">
+      <c r="J470" s="6" t="n">
         <v>10.08</v>
       </c>
       <c r="K470" s="4" t="n">
@@ -38757,7 +38658,7 @@
       <c r="I476" s="4" t="n">
         <v>41.19</v>
       </c>
-      <c r="J476" s="5" t="n">
+      <c r="J476" s="6" t="n">
         <v>0.41</v>
       </c>
       <c r="K476" s="4" t="n">
@@ -38831,7 +38732,7 @@
       <c r="I477" s="4" t="n">
         <v>41.19</v>
       </c>
-      <c r="J477" s="5" t="n">
+      <c r="J477" s="6" t="n">
         <v>0.41</v>
       </c>
       <c r="K477" s="4" t="n">
@@ -39053,7 +38954,7 @@
       <c r="I480" s="4" t="n">
         <v>202.25</v>
       </c>
-      <c r="J480" s="5" t="n">
+      <c r="J480" s="6" t="n">
         <v>2.22</v>
       </c>
       <c r="K480" s="4" t="n">
@@ -39201,7 +39102,7 @@
       <c r="I482" s="4" t="n">
         <v>175.73</v>
       </c>
-      <c r="J482" s="5" t="n">
+      <c r="J482" s="6" t="n">
         <v>3.64</v>
       </c>
       <c r="K482" s="4" t="n">
@@ -39349,7 +39250,7 @@
       <c r="I484" s="4" t="n">
         <v>440.34</v>
       </c>
-      <c r="J484" s="5" t="n">
+      <c r="J484" s="6" t="n">
         <v>6.91</v>
       </c>
       <c r="K484" s="4" t="n">
@@ -39423,7 +39324,7 @@
       <c r="I485" s="4" t="n">
         <v>440.34</v>
       </c>
-      <c r="J485" s="5" t="n">
+      <c r="J485" s="6" t="n">
         <v>6.91</v>
       </c>
       <c r="K485" s="4" t="n">
@@ -39571,7 +39472,7 @@
       <c r="I487" s="4" t="n">
         <v>480.93</v>
       </c>
-      <c r="J487" s="5" t="n">
+      <c r="J487" s="6" t="n">
         <v>1.39</v>
       </c>
       <c r="K487" s="4" t="n">
@@ -40015,7 +39916,7 @@
       <c r="I493" s="4" t="n">
         <v>134.51</v>
       </c>
-      <c r="J493" s="5" t="n">
+      <c r="J493" s="6" t="n">
         <v>3.98</v>
       </c>
       <c r="K493" s="4" t="n">
@@ -40089,7 +39990,7 @@
       <c r="I494" s="4" t="n">
         <v>287.62</v>
       </c>
-      <c r="J494" s="5" t="n">
+      <c r="J494" s="6" t="n">
         <v>2.52</v>
       </c>
       <c r="K494" s="4" t="n">
@@ -40311,7 +40212,7 @@
       <c r="I497" s="4" t="n">
         <v>14.73</v>
       </c>
-      <c r="J497" s="5" t="n">
+      <c r="J497" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="K497" s="4" t="n">
@@ -40528,10 +40429,10 @@
         </is>
       </c>
       <c r="H500" s="4" t="n">
-        <v>7.45</v>
+        <v>7.39</v>
       </c>
       <c r="I500" s="4" t="n">
-        <v>7.44</v>
+        <v>7.38</v>
       </c>
       <c r="J500" s="7" t="n">
         <v>-0.13</v>
@@ -40755,7 +40656,7 @@
       <c r="I503" s="4" t="n">
         <v>281.39</v>
       </c>
-      <c r="J503" s="5" t="n">
+      <c r="J503" s="6" t="n">
         <v>3.8</v>
       </c>
       <c r="K503" s="4" t="n">
@@ -40829,7 +40730,7 @@
       <c r="I504" s="4" t="n">
         <v>80.09</v>
       </c>
-      <c r="J504" s="5" t="n">
+      <c r="J504" s="6" t="n">
         <v>0.17</v>
       </c>
       <c r="K504" s="4" t="n">
@@ -40977,7 +40878,7 @@
       <c r="I506" s="4" t="n">
         <v>181.38</v>
       </c>
-      <c r="J506" s="5" t="n">
+      <c r="J506" s="6" t="n">
         <v>0.87</v>
       </c>
       <c r="K506" s="4" t="n">
@@ -41051,7 +40952,7 @@
       <c r="I507" s="4" t="n">
         <v>100.72</v>
       </c>
-      <c r="J507" s="5" t="n">
+      <c r="J507" s="6" t="n">
         <v>2.5</v>
       </c>
       <c r="K507" s="4" t="n">
@@ -41125,7 +41026,7 @@
       <c r="I508" s="4" t="n">
         <v>114.1</v>
       </c>
-      <c r="J508" s="5" t="n">
+      <c r="J508" s="6" t="n">
         <v>3.99</v>
       </c>
       <c r="K508" s="4" t="n">
@@ -41199,7 +41100,7 @@
       <c r="I509" s="4" t="n">
         <v>188.07</v>
       </c>
-      <c r="J509" s="5" t="n">
+      <c r="J509" s="6" t="n">
         <v>1.67</v>
       </c>
       <c r="K509" s="4" t="n">
@@ -41273,7 +41174,7 @@
       <c r="I510" s="4" t="n">
         <v>262.9</v>
       </c>
-      <c r="J510" s="5" t="n">
+      <c r="J510" s="6" t="n">
         <v>5.12</v>
       </c>
       <c r="K510" s="4" t="n">
@@ -41347,7 +41248,7 @@
       <c r="I511" s="4" t="n">
         <v>313.45</v>
       </c>
-      <c r="J511" s="5" t="n">
+      <c r="J511" s="6" t="n">
         <v>1.68</v>
       </c>
       <c r="K511" s="4" t="n">
@@ -41421,7 +41322,7 @@
       <c r="I512" s="4" t="n">
         <v>155.08</v>
       </c>
-      <c r="J512" s="5" t="n">
+      <c r="J512" s="6" t="n">
         <v>3.74</v>
       </c>
       <c r="K512" s="4" t="n">
@@ -41791,7 +41692,7 @@
       <c r="I517" s="4" t="n">
         <v>344.5</v>
       </c>
-      <c r="J517" s="5" t="n">
+      <c r="J517" s="6" t="n">
         <v>0.27</v>
       </c>
       <c r="K517" s="4" t="n">
@@ -41865,7 +41766,7 @@
       <c r="I518" s="4" t="n">
         <v>60.09</v>
       </c>
-      <c r="J518" s="5" t="n">
+      <c r="J518" s="6" t="n">
         <v>9.130000000000001</v>
       </c>
       <c r="K518" s="4" t="n">
@@ -41939,7 +41840,7 @@
       <c r="I519" s="4" t="n">
         <v>47.25</v>
       </c>
-      <c r="J519" s="5" t="n">
+      <c r="J519" s="6" t="n">
         <v>0.88</v>
       </c>
       <c r="K519" s="4" t="n">
@@ -42235,7 +42136,7 @@
       <c r="I523" s="4" t="n">
         <v>39.84</v>
       </c>
-      <c r="J523" s="5" t="n">
+      <c r="J523" s="6" t="n">
         <v>26.08</v>
       </c>
       <c r="K523" s="4" t="n">
@@ -42309,7 +42210,7 @@
       <c r="I524" s="4" t="n">
         <v>126.68</v>
       </c>
-      <c r="J524" s="5" t="n">
+      <c r="J524" s="6" t="n">
         <v>1.03</v>
       </c>
       <c r="K524" s="4" t="n">
@@ -42378,10 +42279,10 @@
         </is>
       </c>
       <c r="H525" s="4" t="n">
-        <v>23.1</v>
+        <v>22.91</v>
       </c>
       <c r="I525" s="4" t="n">
-        <v>21.61</v>
+        <v>21.43</v>
       </c>
       <c r="J525" s="7" t="n">
         <v>-6.45</v>
@@ -42531,7 +42432,7 @@
       <c r="I527" s="4" t="n">
         <v>71.41</v>
       </c>
-      <c r="J527" s="5" t="n">
+      <c r="J527" s="6" t="n">
         <v>2.17</v>
       </c>
       <c r="K527" s="4" t="n">
@@ -42970,10 +42871,10 @@
         </is>
       </c>
       <c r="H533" s="4" t="n">
-        <v>217.55</v>
+        <v>217.31</v>
       </c>
       <c r="I533" s="4" t="n">
-        <v>217.55</v>
+        <v>217.31</v>
       </c>
       <c r="J533" s="4" t="n">
         <v>0</v>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -539,14 +539,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=7 · 516 scored · 24 already in CURRENT · biggest blocker: model disagreement (405) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 2</t>
+          <t>🔎 NEW=7 · 30 scored · 24 already in CURRENT · biggest blocker: model disagreement (25) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 16 candidate(s) reviewed today.</t>
+          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -2393,7 +2393,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W54"/>
+  <dimension ref="A1:W51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -518,14 +518,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>28 investable · NEW 7 · ACTIVE+ 10 · ACTIVE 11   ·   R2 15 · MOMENTUM 0 · R1 13 (advisory)</t>
+          <t>25 investable · NEW 4 · ACTIVE+ 10 · ACTIVE 11   ·   R2 12 · MOMENTUM 0 · R1 13 (advisory)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>🛡 DOWNSIDE · 28 position(s) with an INTACT stop · if all of them fired today the average outcome is -7.07% from entry, worst single -14.95%</t>
+          <t>🛡 DOWNSIDE · 25 position(s) with an INTACT stop · if all of them fired today the average outcome is -6.99% from entry, worst single -14.95%</t>
         </is>
       </c>
     </row>
@@ -539,7 +539,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=7 · 516 scored · 24 already in CURRENT · biggest blocker: model disagreement (405) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 2</t>
+          <t>🔎 NEW=4 · 516 scored · 22 already in CURRENT · biggest blocker: model disagreement (405) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 2</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>243</v>
+        <v>530.12</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>243</v>
+        <v>530.12</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
@@ -821,11 +821,11 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N9" s="5" t="n">
-        <v>213353612143.8822</v>
+        <v>121227179253.6498</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>225.3375</v>
+        <v>506.135</v>
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
@@ -846,17 +846,17 @@
         </is>
       </c>
       <c r="S9" s="4" t="n">
-        <v>7.27</v>
+        <v>4.52</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-7.27</v>
+        <v>-4.52</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>278.33</v>
+        <v>566.1</v>
       </c>
       <c r="V9" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-CRM-20260911-92c3e2</t>
+          <t>USA-R2-LMT-20260911-47e24c</t>
         </is>
       </c>
       <c r="W9" s="4" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>EIX</t>
+          <t>NCLH</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -902,10 +902,10 @@
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>56.75</v>
+        <v>14.57</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>56.75</v>
+        <v>14.57</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
@@ -916,15 +916,15 @@
         <v>0</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>59.1</v>
+        <v>59.4</v>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Cyclical</t>
         </is>
       </c>
       <c r="N10" s="5" t="n">
-        <v>21847412064.79042</v>
+        <v>7149900531.60001</v>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
@@ -933,11 +933,11 @@
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>Mid</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>50.4125</v>
+        <v>13.7729</v>
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
@@ -945,17 +945,17 @@
         </is>
       </c>
       <c r="S10" s="4" t="n">
-        <v>11.17</v>
+        <v>5.47</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-11.17</v>
+        <v>-5.47</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>69.42</v>
+        <v>16.16</v>
       </c>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-EIX-20260911-899825</t>
+          <t>USA-R2-NCLH-20260911-4deec4</t>
         </is>
       </c>
       <c r="W10" s="4" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>UDR</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>530.12</v>
+        <v>35.14</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>530.12</v>
+        <v>35.14</v>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
@@ -1019,11 +1019,11 @@
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Real Estate</t>
         </is>
       </c>
       <c r="N11" s="5" t="n">
-        <v>121227179253.6498</v>
+        <v>13480313738.1309</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
@@ -1036,7 +1036,7 @@
         </is>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>506.135</v>
+        <v>33.9629</v>
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
@@ -1044,17 +1044,17 @@
         </is>
       </c>
       <c r="S11" s="4" t="n">
-        <v>4.52</v>
+        <v>3.35</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-4.52</v>
+        <v>-3.35</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>566.1</v>
+        <v>36.91</v>
       </c>
       <c r="V11" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-LMT-20260911-47e24c</t>
+          <t>USA-R2-UDR-20260911-e6df0a</t>
         </is>
       </c>
       <c r="W11" s="4" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>NCLH</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1091,51 +1091,53 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-08</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>382.85</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>385.43</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>106733315426.1837</v>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="H12" s="4" t="n">
-        <v>14.57</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>14.57</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="M12" s="4" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>7149900531.60001</v>
-      </c>
-      <c r="O12" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>Mid</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>13.7729</v>
+        <v>364.3357</v>
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
@@ -1146,19 +1148,19 @@
         <v>5.47</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-5.47</v>
+        <v>-4.84</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>16.16</v>
+        <v>414.08</v>
       </c>
       <c r="V12" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-NCLH-20260911-4deec4</t>
+          <t>USA-R2-VLO-20260908-e69cee</t>
         </is>
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1172,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -1180,7 +1182,7 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1190,51 +1192,53 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-08-10</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>374.34</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>367.56</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>-1.81</v>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>77037113169.76082</v>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="H13" s="4" t="n">
-        <v>61.16</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>61.16</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="M13" s="4" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v>60020554038.7197</v>
-      </c>
-      <c r="O13" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>58.3643</v>
+        <v>355.6478</v>
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
@@ -1242,22 +1246,22 @@
         </is>
       </c>
       <c r="S13" s="4" t="n">
-        <v>4.57</v>
+        <v>3.24</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-4.57</v>
+        <v>-4.99</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>65.34999999999999</v>
+        <v>400.86</v>
       </c>
       <c r="V13" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-OXY-20260911-840d2e</t>
+          <t>USA-R2-TRV-20260810-9cd25d</t>
         </is>
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1273,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>UDR</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1279,7 +1283,7 @@
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1289,51 +1293,53 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>126.01</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>123.28</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="n">
+        <v>-2.17</v>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>25692123442.84064</v>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="H14" s="4" t="n">
-        <v>35.14</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>35.14</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="M14" s="4" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v>13480313738.1309</v>
-      </c>
-      <c r="O14" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>33.9629</v>
+        <v>116.62</v>
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
@@ -1341,22 +1347,22 @@
         </is>
       </c>
       <c r="S14" s="4" t="n">
-        <v>3.35</v>
+        <v>5.4</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-3.35</v>
+        <v>-7.45</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>36.91</v>
+        <v>135.86</v>
       </c>
       <c r="V14" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-UDR-20260911-e6df0a</t>
+          <t>USA-R2-INCY-20260909-bb0ff1</t>
         </is>
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1374,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1388,27 +1394,27 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-08</t>
+          <t>Admitted 2026-08-10</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>382.85</v>
+        <v>175.23</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>385.43</v>
+        <v>165.86</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="K15" s="6" t="n">
-        <v>0.67</v>
+      <c r="K15" s="7" t="n">
+        <v>-5.35</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
@@ -1417,11 +1423,11 @@
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N15" s="5" t="n">
-        <v>106733315426.1837</v>
+        <v>418890007002.7825</v>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
@@ -1434,7 +1440,7 @@
         </is>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>364.3357</v>
+        <v>153.6918</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1442,22 +1448,22 @@
         </is>
       </c>
       <c r="S15" s="4" t="n">
-        <v>5.47</v>
+        <v>7.34</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-4.84</v>
+        <v>-12.29</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>414.08</v>
+        <v>204.13</v>
       </c>
       <c r="V15" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-VLO-20260908-e69cee</t>
+          <t>USA-R2-PLTR-20260810-f9e975</t>
         </is>
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1475,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1489,19 +1495,19 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-10</t>
+          <t>Admitted 2026-09-08</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>374.34</v>
+        <v>40.26</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>367.56</v>
+        <v>37.38</v>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
@@ -1509,7 +1515,7 @@
         </is>
       </c>
       <c r="K16" s="7" t="n">
-        <v>-1.81</v>
+        <v>-7.15</v>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
@@ -1518,11 +1524,11 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N16" s="5" t="n">
-        <v>77037113169.76082</v>
+        <v>25609435171.5677</v>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
@@ -1535,7 +1541,7 @@
         </is>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>355.6478</v>
+        <v>34.2429</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1543,22 +1549,22 @@
         </is>
       </c>
       <c r="S16" s="4" t="n">
-        <v>3.24</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-4.99</v>
+        <v>-14.95</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>400.86</v>
+        <v>46.92</v>
       </c>
       <c r="V16" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-TRV-20260810-9cd25d</t>
+          <t>USA-R2-SMCI-20260908-c2c66b</t>
         </is>
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1570,12 +1576,12 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1585,24 +1591,24 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-08-14</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>126.01</v>
+        <v>63.83</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>123.28</v>
+        <v>63.75</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
@@ -1610,7 +1616,7 @@
         </is>
       </c>
       <c r="K17" s="7" t="n">
-        <v>-2.17</v>
+        <v>-0.13</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
@@ -1623,7 +1629,7 @@
         </is>
       </c>
       <c r="N17" s="5" t="n">
-        <v>25692123442.84064</v>
+        <v>136489737964.495</v>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
@@ -1636,7 +1642,7 @@
         </is>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>116.62</v>
+        <v>60.0271</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1644,22 +1650,22 @@
         </is>
       </c>
       <c r="S17" s="4" t="n">
-        <v>5.4</v>
+        <v>5.84</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-7.45</v>
+        <v>-5.96</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>135.86</v>
+        <v>69.53</v>
       </c>
       <c r="V17" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-INCY-20260909-bb0ff1</t>
+          <t>USA-R1-BMY-20260814-a3b600</t>
         </is>
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -1671,12 +1677,12 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1686,24 +1692,24 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-10</t>
+          <t>Admitted 2026-09-01</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>175.23</v>
+        <v>275.17</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>165.86</v>
+        <v>272.2</v>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
@@ -1711,7 +1717,7 @@
         </is>
       </c>
       <c r="K18" s="7" t="n">
-        <v>-5.35</v>
+        <v>-1.08</v>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
@@ -1724,7 +1730,7 @@
         </is>
       </c>
       <c r="N18" s="5" t="n">
-        <v>418890007002.7825</v>
+        <v>53431824008.73483</v>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
@@ -1737,7 +1743,7 @@
         </is>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>153.6918</v>
+        <v>261.9314</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1745,22 +1751,22 @@
         </is>
       </c>
       <c r="S18" s="4" t="n">
-        <v>7.34</v>
+        <v>3.77</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-12.29</v>
+        <v>-4.81</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>204.13</v>
+        <v>295.03</v>
       </c>
       <c r="V18" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-PLTR-20260810-f9e975</t>
+          <t>USA-R1-GRMN-20260901-4c77f2</t>
         </is>
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -1772,12 +1778,12 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1787,24 +1793,24 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-08</t>
+          <t>Admitted 2026-08-10</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>40.26</v>
+        <v>505.11</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>37.38</v>
+        <v>492.44</v>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
@@ -1812,7 +1818,7 @@
         </is>
       </c>
       <c r="K19" s="7" t="n">
-        <v>-7.15</v>
+        <v>-2.51</v>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
@@ -1825,7 +1831,7 @@
         </is>
       </c>
       <c r="N19" s="5" t="n">
-        <v>25609435171.5677</v>
+        <v>3710222886174.651</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
@@ -1838,7 +1844,7 @@
         </is>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>34.2429</v>
+        <v>469.0698</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1846,22 +1852,22 @@
         </is>
       </c>
       <c r="S19" s="4" t="n">
-        <v>8.390000000000001</v>
+        <v>4.75</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-14.95</v>
+        <v>-7.13</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>46.92</v>
+        <v>559.17</v>
       </c>
       <c r="V19" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-SMCI-20260908-c2c66b</t>
+          <t>USA-R1-MSFT-20260810-6110fc</t>
         </is>
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1879,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1893,19 +1899,19 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-14</t>
+          <t>Admitted 2026-08-10</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>63.83</v>
+        <v>175.23</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>63.75</v>
+        <v>165.86</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
@@ -1913,7 +1919,7 @@
         </is>
       </c>
       <c r="K20" s="7" t="n">
-        <v>-0.13</v>
+        <v>-5.35</v>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
@@ -1922,11 +1928,11 @@
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N20" s="5" t="n">
-        <v>136489737964.495</v>
+        <v>418890007002.7825</v>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
@@ -1939,7 +1945,7 @@
         </is>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>60.0271</v>
+        <v>155.965</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1947,17 +1953,17 @@
         </is>
       </c>
       <c r="S20" s="4" t="n">
-        <v>5.84</v>
+        <v>5.97</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-5.96</v>
+        <v>-10.99</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>69.53</v>
+        <v>204.13</v>
       </c>
       <c r="V20" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-BMY-20260814-a3b600</t>
+          <t>USA-R1-PLTR-20260810-5c4552</t>
         </is>
       </c>
       <c r="W20" s="4" t="inlineStr">
@@ -1974,7 +1980,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1994,19 +2000,19 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-01</t>
+          <t>Admitted 2026-08-10</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>275.17</v>
+        <v>272.96</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>272.2</v>
+        <v>248.83</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -2014,7 +2020,7 @@
         </is>
       </c>
       <c r="K21" s="7" t="n">
-        <v>-1.08</v>
+        <v>-8.84</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
@@ -2027,7 +2033,7 @@
         </is>
       </c>
       <c r="N21" s="5" t="n">
-        <v>53431824008.73483</v>
+        <v>105949765544.345</v>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
@@ -2040,7 +2046,7 @@
         </is>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>261.9314</v>
+        <v>247.1386</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -2048,17 +2054,17 @@
         </is>
       </c>
       <c r="S21" s="4" t="n">
-        <v>3.77</v>
+        <v>0.68</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-4.81</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>295.03</v>
+        <v>311.69</v>
       </c>
       <c r="V21" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-GRMN-20260901-4c77f2</t>
+          <t>USA-R1-ADBE-20260810-4ad164</t>
         </is>
       </c>
       <c r="W21" s="4" t="inlineStr">
@@ -2075,22 +2081,22 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -2104,18 +2110,18 @@
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>505.11</v>
+        <v>360.65</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>492.44</v>
+        <v>367.21</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="K22" s="7" t="n">
-        <v>-2.51</v>
+      <c r="K22" s="6" t="n">
+        <v>1.82</v>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
@@ -2124,11 +2130,11 @@
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N22" s="5" t="n">
-        <v>3710222886174.651</v>
+        <v>700325596737.0536</v>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
@@ -2141,7 +2147,7 @@
         </is>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>469.0698</v>
+        <v>355.6657</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -2149,22 +2155,22 @@
         </is>
       </c>
       <c r="S22" s="4" t="n">
-        <v>4.75</v>
+        <v>3.14</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-7.13</v>
+        <v>-1.38</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>559.17</v>
+        <v>384</v>
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-MSFT-20260810-6110fc</t>
+          <t>USA-R2-V-20260810-69160d</t>
         </is>
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>HOLD · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2176,47 +2182,47 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-10</t>
+          <t>Admitted 2026-08-11</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>175.23</v>
+        <v>63.61</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>165.86</v>
+        <v>63.75</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="K23" s="7" t="n">
-        <v>-5.35</v>
+      <c r="K23" s="6" t="n">
+        <v>0.22</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
@@ -2225,11 +2231,11 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N23" s="5" t="n">
-        <v>418890007002.7825</v>
+        <v>136489737964.495</v>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
@@ -2242,7 +2248,7 @@
         </is>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>155.965</v>
+        <v>61.0343</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2250,22 +2256,22 @@
         </is>
       </c>
       <c r="S23" s="4" t="n">
-        <v>5.97</v>
+        <v>4.26</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-10.99</v>
+        <v>-4.05</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>204.13</v>
+        <v>69.45</v>
       </c>
       <c r="V23" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-PLTR-20260810-5c4552</t>
+          <t>USA-R2-BMY-20260811-c99117</t>
         </is>
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>HOLD · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2277,39 +2283,39 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-10</t>
+          <t>Admitted 2026-08-11</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>272.96</v>
+        <v>89.53</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>248.83</v>
+        <v>84.51000000000001</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
@@ -2317,7 +2323,7 @@
         </is>
       </c>
       <c r="K24" s="7" t="n">
-        <v>-8.84</v>
+        <v>-5.61</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -2326,11 +2332,11 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Healthcare</t>
         </is>
       </c>
       <c r="N24" s="5" t="n">
-        <v>105949765544.345</v>
+        <v>33166527215.04348</v>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
@@ -2343,7 +2349,7 @@
         </is>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>247.1386</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2351,22 +2357,22 @@
         </is>
       </c>
       <c r="S24" s="4" t="n">
-        <v>0.68</v>
+        <v>5.72</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-9.460000000000001</v>
+        <v>-11</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>311.69</v>
+        <v>99.06</v>
       </c>
       <c r="V24" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-ADBE-20260810-4ad164</t>
+          <t>USA-R2-DXCM-20260811-b3de8c</t>
         </is>
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+          <t>HOLD · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2378,12 +2384,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -2393,24 +2399,24 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-10</t>
+          <t>Admitted 2026-08-14</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>360.65</v>
+        <v>196.21</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>367.21</v>
+        <v>243</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
@@ -2418,7 +2424,7 @@
         </is>
       </c>
       <c r="K25" s="6" t="n">
-        <v>1.82</v>
+        <v>23.85</v>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
@@ -2427,11 +2433,11 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N25" s="5" t="n">
-        <v>700325596737.0536</v>
+        <v>213353612143.8822</v>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
@@ -2444,7 +2450,7 @@
         </is>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>355.6657</v>
+        <v>179.3029</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2452,22 +2458,24 @@
         </is>
       </c>
       <c r="S25" s="4" t="n">
-        <v>3.14</v>
+        <v>26.21</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-1.38</v>
-      </c>
-      <c r="U25" s="4" t="n">
-        <v>384</v>
+        <v>-8.619999999999999</v>
+      </c>
+      <c r="U25" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V25" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-V-20260810-69160d</t>
+          <t>USA-R1-CRM-20260814-be7c1c</t>
         </is>
       </c>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -2479,12 +2487,12 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -2494,24 +2502,24 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-11</t>
+          <t>Admitted 2026-09-01</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>63.61</v>
+        <v>103.51</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>63.75</v>
+        <v>113.33</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
@@ -2519,7 +2527,7 @@
         </is>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.22</v>
+        <v>9.49</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -2528,11 +2536,11 @@
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Financial Services</t>
         </is>
       </c>
       <c r="N26" s="5" t="n">
-        <v>136489737964.495</v>
+        <v>109799408364.9603</v>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
@@ -2545,7 +2553,7 @@
         </is>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>61.0343</v>
+        <v>91.0157</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -2553,22 +2561,22 @@
         </is>
       </c>
       <c r="S26" s="4" t="n">
-        <v>4.26</v>
+        <v>19.69</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-4.05</v>
+        <v>-12.07</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>69.45</v>
+        <v>122.25</v>
       </c>
       <c r="V26" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-BMY-20260811-c99117</t>
+          <t>USA-R1-HOOD-20260901-b8d64b</t>
         </is>
       </c>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -2580,12 +2588,12 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>DXCM</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -2595,32 +2603,32 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-11</t>
+          <t>Admitted 2026-09-01</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>89.53</v>
+        <v>361.99</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>84.51000000000001</v>
+        <v>385.43</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="K27" s="7" t="n">
-        <v>-5.61</v>
+      <c r="K27" s="6" t="n">
+        <v>6.48</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
@@ -2629,11 +2637,11 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N27" s="5" t="n">
-        <v>33166527215.04348</v>
+        <v>106733315426.1837</v>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
@@ -2646,7 +2654,7 @@
         </is>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>79.68000000000001</v>
+        <v>342.2271</v>
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
@@ -2654,22 +2662,22 @@
         </is>
       </c>
       <c r="S27" s="4" t="n">
-        <v>5.72</v>
+        <v>11.21</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-11</v>
+        <v>-5.46</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>99.06</v>
+        <v>391.63</v>
       </c>
       <c r="V27" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-DXCM-20260811-b3de8c</t>
+          <t>USA-R1-VLO-20260901-3c6acd</t>
         </is>
       </c>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2689,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>SAIC</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2710,10 +2718,10 @@
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>196.21</v>
+        <v>126.68</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>243</v>
+        <v>128.76</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
@@ -2721,7 +2729,7 @@
         </is>
       </c>
       <c r="K28" s="6" t="n">
-        <v>23.85</v>
+        <v>1.64</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
@@ -2734,7 +2742,7 @@
         </is>
       </c>
       <c r="N28" s="5" t="n">
-        <v>213353612143.8822</v>
+        <v>5310066989.662829</v>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
@@ -2743,11 +2751,11 @@
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>Mid</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>179.3029</v>
+        <v>119.43</v>
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
@@ -2755,19 +2763,17 @@
         </is>
       </c>
       <c r="S28" s="4" t="n">
-        <v>26.21</v>
+        <v>7.25</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-8.619999999999999</v>
-      </c>
-      <c r="U28" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>-5.72</v>
+      </c>
+      <c r="U28" s="4" t="n">
+        <v>137.55</v>
       </c>
       <c r="V28" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-CRM-20260814-be7c1c</t>
+          <t>USA-R1-SAIC-20260814-889ae8</t>
         </is>
       </c>
       <c r="W28" s="4" t="inlineStr">
@@ -2784,7 +2790,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2813,10 +2819,10 @@
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>103.51</v>
+        <v>187.7</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>113.33</v>
+        <v>189.32</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
@@ -2824,7 +2830,7 @@
         </is>
       </c>
       <c r="K29" s="6" t="n">
-        <v>9.49</v>
+        <v>0.86</v>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
@@ -2833,11 +2839,11 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="N29" s="5" t="n">
-        <v>109799408364.9603</v>
+        <v>24541437631.37434</v>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
@@ -2850,7 +2856,7 @@
         </is>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>91.0157</v>
+        <v>180.8543</v>
       </c>
       <c r="R29" s="4" t="inlineStr">
         <is>
@@ -2858,17 +2864,17 @@
         </is>
       </c>
       <c r="S29" s="4" t="n">
-        <v>19.69</v>
+        <v>4.47</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-12.07</v>
+        <v>-3.65</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>122.25</v>
+        <v>197.97</v>
       </c>
       <c r="V29" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-HOOD-20260901-b8d64b</t>
+          <t>USA-R1-EXPD-20260901-065905</t>
         </is>
       </c>
       <c r="W29" s="4" t="inlineStr">
@@ -2885,7 +2891,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2914,18 +2920,18 @@
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>361.99</v>
+        <v>161.85</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>385.43</v>
+        <v>158.85</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="K30" s="6" t="n">
-        <v>6.48</v>
+      <c r="K30" s="7" t="n">
+        <v>-1.85</v>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
@@ -2934,11 +2940,11 @@
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N30" s="5" t="n">
-        <v>106733315426.1837</v>
+        <v>114683252142.2478</v>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
@@ -2951,7 +2957,7 @@
         </is>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>342.2271</v>
+        <v>147.9529</v>
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
@@ -2959,17 +2965,17 @@
         </is>
       </c>
       <c r="S30" s="4" t="n">
-        <v>11.21</v>
+        <v>6.86</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-5.46</v>
+        <v>-8.59</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>391.63</v>
+        <v>182.7</v>
       </c>
       <c r="V30" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-VLO-20260901-3c6acd</t>
+          <t>USA-R1-FTNT-20260901-30d75e</t>
         </is>
       </c>
       <c r="W30" s="4" t="inlineStr">
@@ -2986,7 +2992,7 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>FOX</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -3006,27 +3012,27 @@
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-14</t>
+          <t>Admitted 2026-08-19</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="H31" s="4" t="n">
-        <v>126.68</v>
+        <v>60.09</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>128.76</v>
+        <v>58.06</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="K31" s="6" t="n">
-        <v>1.64</v>
+      <c r="K31" s="7" t="n">
+        <v>-3.38</v>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
@@ -3035,11 +3041,11 @@
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="N31" s="5" t="n">
-        <v>5310066989.662829</v>
+        <v>24564051543.2472</v>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
@@ -3048,11 +3054,11 @@
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>Mid</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>119.43</v>
+        <v>56.6217</v>
       </c>
       <c r="R31" s="4" t="inlineStr">
         <is>
@@ -3060,17 +3066,17 @@
         </is>
       </c>
       <c r="S31" s="4" t="n">
-        <v>7.25</v>
+        <v>2.48</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-5.72</v>
+        <v>-5.78</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>137.55</v>
+        <v>65.3</v>
       </c>
       <c r="V31" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-SAIC-20260814-889ae8</t>
+          <t>USA-R1-FOX-20260819-7b9e84</t>
         </is>
       </c>
       <c r="W31" s="4" t="inlineStr">
@@ -3087,7 +3093,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -3107,27 +3113,27 @@
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-01</t>
+          <t>Admitted 2026-08-19</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="H32" s="4" t="n">
-        <v>187.7</v>
+        <v>344.5</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>189.32</v>
+        <v>332.6</v>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="K32" s="6" t="n">
-        <v>0.86</v>
+      <c r="K32" s="7" t="n">
+        <v>-3.45</v>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
@@ -3136,11 +3142,11 @@
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="N32" s="5" t="n">
-        <v>24541437631.37434</v>
+        <v>4139043588458.335</v>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
@@ -3153,7 +3159,7 @@
         </is>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>180.8543</v>
+        <v>323.138</v>
       </c>
       <c r="R32" s="4" t="inlineStr">
         <is>
@@ -3161,17 +3167,17 @@
         </is>
       </c>
       <c r="S32" s="4" t="n">
-        <v>4.47</v>
+        <v>2.84</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-3.65</v>
+        <v>-6.2</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>197.97</v>
+        <v>376.54</v>
       </c>
       <c r="V32" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-EXPD-20260901-065905</t>
+          <t>USA-R1-GOOGL-20260819-1fce1a</t>
         </is>
       </c>
       <c r="W32" s="4" t="inlineStr">
@@ -3180,423 +3186,120 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>FTNT</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>Admitted 2026-09-01</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>161.85</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>158.85</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="K33" s="7" t="n">
-        <v>-1.85</v>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
-      </c>
-      <c r="M33" s="4" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="N33" s="5" t="n">
-        <v>114683252142.2478</v>
-      </c>
-      <c r="O33" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="P33" s="4" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-      <c r="Q33" s="4" t="n">
-        <v>147.9529</v>
-      </c>
-      <c r="R33" s="4" t="inlineStr">
-        <is>
-          <t>INTACT</t>
-        </is>
-      </c>
-      <c r="S33" s="4" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="T33" s="4" t="n">
-        <v>-8.59</v>
-      </c>
-      <c r="U33" s="4" t="n">
-        <v>182.7</v>
-      </c>
-      <c r="V33" s="4" t="inlineStr">
-        <is>
-          <t>USA-R1-FTNT-20260901-30d75e</t>
-        </is>
-      </c>
-      <c r="W33" s="4" t="inlineStr">
-        <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>FOX</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>Admitted 2026-08-19</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>60.09</v>
-      </c>
-      <c r="I34" s="4" t="n">
-        <v>58.06</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="K34" s="7" t="n">
-        <v>-3.38</v>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
-      </c>
-      <c r="M34" s="4" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="N34" s="5" t="n">
-        <v>24564051543.2472</v>
-      </c>
-      <c r="O34" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="P34" s="4" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-      <c r="Q34" s="4" t="n">
-        <v>56.6217</v>
-      </c>
-      <c r="R34" s="4" t="inlineStr">
-        <is>
-          <t>INTACT</t>
-        </is>
-      </c>
-      <c r="S34" s="4" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T34" s="4" t="n">
-        <v>-5.78</v>
-      </c>
-      <c r="U34" s="4" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="V34" s="4" t="inlineStr">
-        <is>
-          <t>USA-R1-FOX-20260819-7b9e84</t>
-        </is>
-      </c>
-      <c r="W34" s="4" t="inlineStr">
-        <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
-        </is>
-      </c>
-    </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>GOOGL</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>Admitted 2026-08-19</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>344.5</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>332.6</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="K35" s="7" t="n">
-        <v>-3.45</v>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
-      </c>
-      <c r="M35" s="4" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="N35" s="5" t="n">
-        <v>4139043588458.335</v>
-      </c>
-      <c r="O35" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="P35" s="4" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-      <c r="Q35" s="4" t="n">
-        <v>323.138</v>
-      </c>
-      <c r="R35" s="4" t="inlineStr">
-        <is>
-          <t>INTACT</t>
-        </is>
-      </c>
-      <c r="S35" s="4" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="T35" s="4" t="n">
-        <v>-6.2</v>
-      </c>
-      <c r="U35" s="4" t="n">
-        <v>376.54</v>
-      </c>
-      <c r="V35" s="4" t="inlineStr">
-        <is>
-          <t>USA-R1-GOOGL-20260819-1fce1a</t>
-        </is>
-      </c>
-      <c r="W35" s="4" t="inlineStr">
-        <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
+          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
+          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
+          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
+          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
+          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
+          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
+          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
+          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
+          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
+          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
+          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
+          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>The 🔎 line answers "why is NEW zero today?" from the lifecycle reconciler · every scored name gets exactly one verdict (reports/context/why_not_current_{market}.json). A zero here is never presented without its reason.</t>
         </is>
@@ -3610,22 +3313,22 @@
     <mergeCell ref="A39:W39"/>
     <mergeCell ref="A49:W49"/>
     <mergeCell ref="A51:W51"/>
+    <mergeCell ref="A36:W36"/>
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="A45:W45"/>
     <mergeCell ref="A6:W6"/>
-    <mergeCell ref="A54:W54"/>
     <mergeCell ref="A41:W41"/>
     <mergeCell ref="A46:W46"/>
+    <mergeCell ref="A37:W37"/>
     <mergeCell ref="A50:W50"/>
     <mergeCell ref="A3:W3"/>
     <mergeCell ref="A2:W2"/>
     <mergeCell ref="A47:W47"/>
     <mergeCell ref="A42:W42"/>
     <mergeCell ref="A5:W5"/>
-    <mergeCell ref="A53:W53"/>
+    <mergeCell ref="A35:W35"/>
     <mergeCell ref="A4:W4"/>
     <mergeCell ref="A38:W38"/>
-    <mergeCell ref="A52:W52"/>
     <mergeCell ref="A43:W43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -539,14 +539,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=4 · 516 scored · 22 already in CURRENT · biggest blocker: model disagreement (405) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 2</t>
+          <t>🔎 NEW=4 · 30 scored · 22 already in CURRENT · biggest blocker: model disagreement (25) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 16 candidate(s) reviewed today.</t>
+          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
